--- a/Protein_final_summaryGO.xlsx
+++ b/Protein_final_summaryGO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:U80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,90 +436,100 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>interaction_count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_compounds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>compounds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>geneid</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pathway_count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n_pathways</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>pathways</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>pathway_compounds</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>total_count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>n_compounds</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>compounds</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>geneid</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>n_pathways</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>pathways</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>pathway_compounds</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>n_go_terms</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>go_ids</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>go_names</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>go_bp_ids</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>go_bp_names</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>go_mf_ids</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>go_mf_names</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>go_cc_ids</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>go_cc_names</t>
         </is>
@@ -528,7 +538,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P20309</t>
+          <t>O15439</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -539,628 +549,676 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>bethanechol;carbachol</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CHRM3</t>
+          <t>ABCC4</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1131</v>
+        <v>10257</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>28</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>GO:0004435;GO:0004930;GO:0005515;GO:0005789;GO:0005886;GO:0006940;GO:0007165;GO:0007186;GO:0007187;GO:0007197;GO:0007207;GO:0007213;GO:0007268;GO:0007399;GO:0009925;GO:0016020;GO:0016323;GO:0016907;GO:0019722;GO:0030425;GO:0036211;GO:0038023;GO:0042166;GO:0045202;GO:0045211;GO:0045987;GO:0046541;GO:0095500</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor activity;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;acetylcholine binding;acetylcholine receptor signaling pathway;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;basal plasma membrane;basolateral plasma membrane;calcium-mediated signaling;chemical synaptic transmission;dendrite;endoplasmic reticulum membrane;membrane;nervous system development;phosphatidylinositol-4,5-bisphosphate phospholipase C activity;phospholipase C-activating G protein-coupled acetylcholine receptor signaling pathway;plasma membrane;positive regulation of smooth muscle contraction;postsynaptic membrane;protein binding;protein modification process;regulation of smooth muscle contraction;saliva secretion;signal transduction;signaling receptor activity;synapse</t>
-        </is>
+      <c r="M2" t="n">
+        <v>39</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GO:0006940;GO:0007165;GO:0007186;GO:0007187;GO:0007197;GO:0007207;GO:0007213;GO:0007268;GO:0007399;GO:0019722;GO:0036211;GO:0045987;GO:0046541;GO:0095500</t>
+          <t>GO:0001409;GO:0002576;GO:0005515;GO:0005524;GO:0005886;GO:0006805;GO:0006855;GO:0008559;GO:0015132;GO:0015143;GO:0015216;GO:0015431;GO:0015432;GO:0015562;GO:0015721;GO:0015732;GO:0015747;GO:0016020;GO:0016323;GO:0016324;GO:0016404;GO:0016887;GO:0022857;GO:0031088;GO:0032310;GO:0034634;GO:0034775;GO:0042626;GO:0042910;GO:0055085;GO:0060271;GO:0070730;GO:0071716;GO:0098591;GO:0140115;GO:0140359;GO:0150104;GO:1903790;GO:1905948</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;acetylcholine receptor signaling pathway;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;calcium-mediated signaling;chemical synaptic transmission;nervous system development;phospholipase C-activating G protein-coupled acetylcholine receptor signaling pathway;positive regulation of smooth muscle contraction;protein modification process;regulation of smooth muscle contraction;saliva secretion;signal transduction</t>
+          <t>15-hydroxyprostaglandin dehydrogenase (NAD+) activity;ABC-type 3',5'-cyclic GMP transmembrane transporter activity;ABC-type bile acid transporter activity;ABC-type glutathione S-conjugate transporter activity;ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled transmembrane transporter activity;apical plasma membrane;basolateral plasma membrane;bile acid and bile salt transport;cAMP transport;cilium assembly;efflux transmembrane transporter activity;export across plasma membrane;external side of apical plasma membrane;glutathione transmembrane transport;glutathione transmembrane transporter activity;guanine nucleotide transmembrane transport;guanine nucleotide transmembrane transporter activity;leukotriene transport;membrane;plasma membrane;platelet degranulation;platelet dense granule membrane;prostaglandin secretion;prostaglandin transmembrane transporter activity;prostaglandin transport;protein binding;purine nucleotide transmembrane transporter activity;transmembrane transport;transmembrane transporter activity;transport across blood-brain barrier;urate transmembrane transporter activity;urate transport;xenobiotic metabolic process;xenobiotic transmembrane transport;xenobiotic transmembrane transporter activity</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>GO:0004435;GO:0004930;GO:0005515;GO:0016907;GO:0038023;GO:0042166</t>
+          <t>GO:0002576;GO:0006805;GO:0006855;GO:0015721;GO:0015732;GO:0015747;GO:0032310;GO:0034775;GO:0055085;GO:0060271;GO:0070730;GO:0071716;GO:0140115;GO:0150104;GO:1903790</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled receptor activity;acetylcholine binding;phosphatidylinositol-4,5-bisphosphate phospholipase C activity;protein binding;signaling receptor activity</t>
+          <t>bile acid and bile salt transport;cAMP transport;cilium assembly;export across plasma membrane;glutathione transmembrane transport;guanine nucleotide transmembrane transport;leukotriene transport;platelet degranulation;prostaglandin secretion;prostaglandin transport;transmembrane transport;transport across blood-brain barrier;urate transport;xenobiotic metabolic process;xenobiotic transmembrane transport</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>GO:0005789;GO:0005886;GO:0009925;GO:0016020;GO:0016323;GO:0030425;GO:0045202;GO:0045211</t>
+          <t>GO:0001409;GO:0005515;GO:0005524;GO:0008559;GO:0015132;GO:0015143;GO:0015216;GO:0015431;GO:0015432;GO:0015562;GO:0016404;GO:0016887;GO:0022857;GO:0034634;GO:0042626;GO:0042910;GO:0140359;GO:1905948</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>basal plasma membrane;basolateral plasma membrane;dendrite;endoplasmic reticulum membrane;membrane;plasma membrane;postsynaptic membrane;synapse</t>
+          <t>15-hydroxyprostaglandin dehydrogenase (NAD+) activity;ABC-type 3',5'-cyclic GMP transmembrane transporter activity;ABC-type bile acid transporter activity;ABC-type glutathione S-conjugate transporter activity;ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled transmembrane transporter activity;efflux transmembrane transporter activity;glutathione transmembrane transporter activity;guanine nucleotide transmembrane transporter activity;prostaglandin transmembrane transporter activity;protein binding;purine nucleotide transmembrane transporter activity;transmembrane transporter activity;urate transmembrane transporter activity;xenobiotic transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0016020;GO:0016323;GO:0016324;GO:0031088;GO:0098591</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>apical plasma membrane;basolateral plasma membrane;external side of apical plasma membrane;membrane;plasma membrane;platelet dense granule membrane</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O14788</t>
+          <t>O94956</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TNFSF11</t>
+          <t>SLCO2B1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8600</v>
+        <v>11309</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>35</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>GO:0000122;GO:0002548;GO:0005102;GO:0005125;GO:0005164;GO:0005515;GO:0005576;GO:0005615;GO:0005737;GO:0005886;GO:0006955;GO:0007154;GO:0007166;GO:0016020;GO:0019221;GO:0019722;GO:0023052;GO:0030316;GO:0032813;GO:0033209;GO:0034112;GO:0042802;GO:0043123;GO:0043410;GO:0045672;GO:0045780;GO:0045944;GO:0048018;GO:0050870;GO:0051466;GO:0070374;GO:0071812;GO:1901224;GO:1902533;GO:2001238</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>calcium-mediated signaling;cell communication;cell surface receptor signaling pathway;cytokine activity;cytokine-mediated signaling pathway;cytoplasm;extracellular region;identical protein binding;immune response;membrane;monocyte chemotaxis;negative regulation of transcription by RNA polymerase II;obsolete extracellular space;osteoclast differentiation;plasma membrane;positive regulation of ERK1 and ERK2 cascade;positive regulation of MAPK cascade;positive regulation of T cell activation;positive regulation of bone resorption;positive regulation of canonical NF-kappaB signal transduction;positive regulation of corticotropin-releasing hormone secretion;positive regulation of extrinsic apoptotic signaling pathway;positive regulation of fever generation by positive regulation of prostaglandin secretion;positive regulation of homotypic cell-cell adhesion;positive regulation of intracellular signal transduction;positive regulation of non-canonical NF-kappaB signal transduction;positive regulation of osteoclast differentiation;positive regulation of transcription by RNA polymerase II;protein binding;receptor ligand activity;signaling;signaling receptor binding;tumor necrosis factor receptor binding;tumor necrosis factor receptor superfamily binding;tumor necrosis factor-mediated signaling pathway</t>
-        </is>
+      <c r="M3" t="n">
+        <v>15</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>GO:0000122;GO:0002548;GO:0006955;GO:0007154;GO:0007166;GO:0019221;GO:0019722;GO:0023052;GO:0030316;GO:0033209;GO:0034112;GO:0043123;GO:0043410;GO:0045672;GO:0045780;GO:0045944;GO:0050870;GO:0051466;GO:0070374;GO:0071812;GO:1901224;GO:1902533;GO:2001238</t>
+          <t>GO:0005515;GO:0005886;GO:0006805;GO:0009925;GO:0015132;GO:0015291;GO:0015732;GO:0016020;GO:0016323;GO:0016324;GO:0022857;GO:0042167;GO:0043252;GO:0055085;GO:0150104</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>calcium-mediated signaling;cell communication;cell surface receptor signaling pathway;cytokine-mediated signaling pathway;immune response;monocyte chemotaxis;negative regulation of transcription by RNA polymerase II;osteoclast differentiation;positive regulation of ERK1 and ERK2 cascade;positive regulation of MAPK cascade;positive regulation of T cell activation;positive regulation of bone resorption;positive regulation of canonical NF-kappaB signal transduction;positive regulation of corticotropin-releasing hormone secretion;positive regulation of extrinsic apoptotic signaling pathway;positive regulation of fever generation by positive regulation of prostaglandin secretion;positive regulation of homotypic cell-cell adhesion;positive regulation of intracellular signal transduction;positive regulation of non-canonical NF-kappaB signal transduction;positive regulation of osteoclast differentiation;positive regulation of transcription by RNA polymerase II;signaling;tumor necrosis factor-mediated signaling pathway</t>
+          <t>apical plasma membrane;basal plasma membrane;basolateral plasma membrane;heme catabolic process;membrane;plasma membrane;prostaglandin transmembrane transporter activity;prostaglandin transport;protein binding;secondary active transmembrane transporter activity;sodium-independent organic anion transport;transmembrane transport;transmembrane transporter activity;transport across blood-brain barrier;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>GO:0005102;GO:0005125;GO:0005164;GO:0005515;GO:0032813;GO:0042802;GO:0048018</t>
+          <t>GO:0006805;GO:0015732;GO:0042167;GO:0043252;GO:0055085;GO:0150104</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>cytokine activity;identical protein binding;protein binding;receptor ligand activity;signaling receptor binding;tumor necrosis factor receptor binding;tumor necrosis factor receptor superfamily binding</t>
+          <t>heme catabolic process;prostaglandin transport;sodium-independent organic anion transport;transmembrane transport;transport across blood-brain barrier;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>GO:0005576;GO:0005615;GO:0005737;GO:0005886;GO:0016020</t>
+          <t>GO:0005515;GO:0015132;GO:0015291;GO:0022857</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>cytoplasm;extracellular region;membrane;obsolete extracellular space;plasma membrane</t>
+          <t>prostaglandin transmembrane transporter activity;protein binding;secondary active transmembrane transporter activity;transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0009925;GO:0016020;GO:0016323;GO:0016324</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>apical plasma membrane;basal plasma membrane;basolateral plasma membrane;membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O95644</t>
+          <t>O95342</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NFATC1</t>
+          <t>ABCB11</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4772</v>
+        <v>8647</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>28</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>GO:0000785;GO:0000978;GO:0000981;GO:0001228;GO:0003180;GO:0003184;GO:0003677;GO:0003700;GO:0005515;GO:0005528;GO:0005634;GO:0005654;GO:0005667;GO:0005737;GO:0005829;GO:0006355;GO:0016604;GO:0030178;GO:0030346;GO:0033173;GO:0035556;GO:0045893;GO:0045944;GO:0048273;GO:0050728;GO:0061629;GO:1905064;GO:1990837</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;FK506 binding;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;aortic valve morphogenesis;calcineurin-NFAT signaling cascade;chromatin;cytoplasm;cytosol;intracellular signal transduction;mitogen-activated protein kinase p38 binding;negative regulation of Wnt signaling pathway;negative regulation of inflammatory response;negative regulation of vascular associated smooth muscle cell differentiation;nuclear body;nucleoplasm;nucleus;positive regulation of DNA-templated transcription;positive regulation of transcription by RNA polymerase II;protein binding;protein phosphatase 2B binding;pulmonary valve morphogenesis;regulation of DNA-templated transcription;sequence-specific double-stranded DNA binding;transcription regulator complex</t>
-        </is>
+      <c r="M4" t="n">
+        <v>35</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>GO:0003180;GO:0003184;GO:0006355;GO:0030178;GO:0033173;GO:0035556;GO:0045893;GO:0045944;GO:0050728;GO:1905064</t>
+          <t>GO:0005515;GO:0005524;GO:0005768;GO:0005886;GO:0006631;GO:0006699;GO:0006805;GO:0006855;GO:0008206;GO:0008559;GO:0009986;GO:0015125;GO:0015126;GO:0015432;GO:0015721;GO:0015722;GO:0016020;GO:0016323;GO:0016324;GO:0016567;GO:0016887;GO:0031998;GO:0042632;GO:0045177;GO:0046581;GO:0046618;GO:0046691;GO:0055037;GO:0055038;GO:0055085;GO:0055088;GO:0055091;GO:0070062;GO:0120189;GO:0140359</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>aortic valve morphogenesis;calcineurin-NFAT signaling cascade;intracellular signal transduction;negative regulation of Wnt signaling pathway;negative regulation of inflammatory response;negative regulation of vascular associated smooth muscle cell differentiation;positive regulation of DNA-templated transcription;positive regulation of transcription by RNA polymerase II;pulmonary valve morphogenesis;regulation of DNA-templated transcription</t>
+          <t>ABC-type bile acid transporter activity;ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;apical part of cell;apical plasma membrane;basolateral plasma membrane;bile acid and bile salt transport;bile acid biosynthetic process;bile acid metabolic process;bile acid transmembrane transporter activity;canalicular bile acid transmembrane transporter activity;canalicular bile acid transport;cell surface;cholesterol homeostasis;endosome;extracellular exosome;fatty acid metabolic process;intercellular canaliculus;intracellular canaliculus;lipid homeostasis;membrane;phospholipid homeostasis;plasma membrane;positive regulation of bile acid secretion;protein binding;protein ubiquitination;recycling endosome;recycling endosome membrane;regulation of fatty acid beta-oxidation;transmembrane transport;xenobiotic export from cell;xenobiotic metabolic process;xenobiotic transmembrane transport</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>GO:0000978;GO:0000981;GO:0001228;GO:0003677;GO:0003700;GO:0005515;GO:0005528;GO:0030346;GO:0048273;GO:0061629;GO:1990837</t>
+          <t>GO:0006631;GO:0006699;GO:0006805;GO:0006855;GO:0008206;GO:0015721;GO:0015722;GO:0016567;GO:0031998;GO:0042632;GO:0046618;GO:0055085;GO:0055088;GO:0055091;GO:0120189</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;FK506 binding;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;mitogen-activated protein kinase p38 binding;protein binding;protein phosphatase 2B binding;sequence-specific double-stranded DNA binding</t>
+          <t>bile acid and bile salt transport;bile acid biosynthetic process;bile acid metabolic process;canalicular bile acid transport;cholesterol homeostasis;fatty acid metabolic process;lipid homeostasis;phospholipid homeostasis;positive regulation of bile acid secretion;protein ubiquitination;regulation of fatty acid beta-oxidation;transmembrane transport;xenobiotic export from cell;xenobiotic metabolic process;xenobiotic transmembrane transport</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>GO:0000785;GO:0005634;GO:0005654;GO:0005667;GO:0005737;GO:0005829;GO:0016604</t>
+          <t>GO:0005515;GO:0005524;GO:0008559;GO:0015125;GO:0015126;GO:0015432;GO:0016887;GO:0140359</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>chromatin;cytoplasm;cytosol;nuclear body;nucleoplasm;nucleus;transcription regulator complex</t>
+          <t>ABC-type bile acid transporter activity;ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;bile acid transmembrane transporter activity;canalicular bile acid transmembrane transporter activity;protein binding</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>GO:0005768;GO:0005886;GO:0009986;GO:0016020;GO:0016323;GO:0016324;GO:0045177;GO:0046581;GO:0046691;GO:0055037;GO:0055038;GO:0070062</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>apical part of cell;apical plasma membrane;basolateral plasma membrane;cell surface;endosome;extracellular exosome;intercellular canaliculus;intracellular canaliculus;membrane;plasma membrane;recycling endosome;recycling endosome membrane</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P00338</t>
+          <t>P02768</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LDHA</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3939</v>
+        <v>213</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>19</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>GO:0003824;GO:0004457;GO:0004459;GO:0005515;GO:0005634;GO:0005737;GO:0005739;GO:0005829;GO:0006089;GO:0006096;GO:0016020;GO:0016491;GO:0016616;GO:0019752;GO:0035686;GO:0042802;GO:0042867;GO:0045296;GO:0070062</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>L-lactate dehydrogenase (NAD+) activity;cadherin binding;carboxylic acid metabolic process;catalytic activity;cytoplasm;cytosol;extracellular exosome;glycolytic process;identical protein binding;lactate dehydrogenase activity;lactate metabolic process;membrane;mitochondrion;nucleus;oxidoreductase activity;oxidoreductase activity, acting on the CH-OH group of donors, NAD or NADP as acceptor;protein binding;pyruvate catabolic process;sperm fibrous sheath</t>
-        </is>
+      <c r="M5" t="n">
+        <v>31</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>GO:0006089;GO:0006096;GO:0019752;GO:0042867</t>
+          <t>GO:0003677;GO:0005504;GO:0005507;GO:0005515;GO:0005576;GO:0005634;GO:0005737;GO:0005788;GO:0006783;GO:0009267;GO:0015643;GO:0015723;GO:0016209;GO:0019825;GO:0020037;GO:0030170;GO:0031093;GO:0031667;GO:0032991;GO:0034599;GO:0042167;GO:0042802;GO:0051087;GO:0051902;GO:0070062;GO:0072562;GO:0072732;GO:0098869;GO:0140104;GO:0140272;GO:1903981</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>carboxylic acid metabolic process;glycolytic process;lactate metabolic process;pyruvate catabolic process</t>
+          <t>DNA binding;antioxidant activity;bilirubin transport;blood microparticle;cellular oxidant detoxification;cellular response to calcium ion starvation;cellular response to oxidative stress;cellular response to starvation;copper ion binding;cytoplasm;endoplasmic reticulum lumen;enterobactin binding;exogenous protein binding;extracellular exosome;extracellular region;fatty acid binding;heme binding;heme biosynthetic process;heme catabolic process;identical protein binding;molecular carrier activity;negative regulation of mitochondrial depolarization;nucleus;oxygen binding;platelet alpha granule lumen;protein binding;protein-containing complex;protein-folding chaperone binding;pyridoxal phosphate binding;response to nutrient levels;toxic substance binding</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>GO:0003824;GO:0004457;GO:0004459;GO:0005515;GO:0016491;GO:0016616;GO:0042802;GO:0045296</t>
+          <t>GO:0006783;GO:0009267;GO:0015723;GO:0031667;GO:0034599;GO:0042167;GO:0051902;GO:0072732;GO:0098869</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>L-lactate dehydrogenase (NAD+) activity;cadherin binding;catalytic activity;identical protein binding;lactate dehydrogenase activity;oxidoreductase activity;oxidoreductase activity, acting on the CH-OH group of donors, NAD or NADP as acceptor;protein binding</t>
+          <t>bilirubin transport;cellular oxidant detoxification;cellular response to calcium ion starvation;cellular response to oxidative stress;cellular response to starvation;heme biosynthetic process;heme catabolic process;negative regulation of mitochondrial depolarization;response to nutrient levels</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>GO:0005634;GO:0005737;GO:0005739;GO:0005829;GO:0016020;GO:0035686;GO:0070062</t>
+          <t>GO:0003677;GO:0005504;GO:0005507;GO:0005515;GO:0015643;GO:0016209;GO:0019825;GO:0020037;GO:0030170;GO:0042802;GO:0051087;GO:0140104;GO:0140272;GO:1903981</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>cytoplasm;cytosol;extracellular exosome;membrane;mitochondrion;nucleus;sperm fibrous sheath</t>
+          <t>DNA binding;antioxidant activity;copper ion binding;enterobactin binding;exogenous protein binding;fatty acid binding;heme binding;identical protein binding;molecular carrier activity;oxygen binding;protein binding;protein-folding chaperone binding;pyridoxal phosphate binding;toxic substance binding</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>GO:0005576;GO:0005634;GO:0005737;GO:0005788;GO:0031093;GO:0032991;GO:0070062;GO:0072562</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>blood microparticle;cytoplasm;endoplasmic reticulum lumen;extracellular exosome;extracellular region;nucleus;platelet alpha granule lumen;protein-containing complex</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P01100</t>
+          <t>P46721</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FOS</t>
+          <t>SLCO1A2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2353</v>
+        <v>6579</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>73</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>GO:0000785;GO:0000976;GO:0000978;GO:0000979;GO:0000981;GO:0001221;GO:0001228;GO:0001661;GO:0003407;GO:0003677;GO:0003682;GO:0003690;GO:0003700;GO:0005515;GO:0005634;GO:0005654;GO:0005667;GO:0005737;GO:0005783;GO:0005829;GO:0006355;GO:0006357;GO:0006366;GO:0006954;GO:0007179;GO:0007565;GO:0009410;GO:0009416;GO:0009612;GO:0009629;GO:0009636;GO:0014823;GO:0014856;GO:0016363;GO:0021987;GO:0030182;GO:0032496;GO:0032570;GO:0032868;GO:0032870;GO:0032993;GO:0034097;GO:0034224;GO:0034614;GO:0035902;GO:0035976;GO:0042802;GO:0043565;GO:0044877;GO:0045471;GO:0045893;GO:0045944;GO:0048545;GO:0051412;GO:0051450;GO:0051591;GO:0060395;GO:0061629;GO:0070412;GO:0071356;GO:0071364;GO:0071374;GO:0071456;GO:0071560;GO:0072375;GO:0140467;GO:1902895;GO:1903131;GO:1904321;GO:1904628;GO:1990646;GO:1990837;GO:1990841</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;R-SMAD binding;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II core promoter sequence-specific DNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;SMAD protein signal transduction;cellular response to epidermal growth factor stimulus;cellular response to hormone stimulus;cellular response to hypoxia;cellular response to parathyroid hormone stimulus;cellular response to phorbol 13-acetate 12-myristate;cellular response to prolactin;cellular response to reactive oxygen species;cellular response to transforming growth factor beta stimulus;cellular response to tumor necrosis factor;cellular response to zinc ion starvation;cerebral cortex development;chromatin;chromatin binding;conditioned taste aversion;cytoplasm;cytosol;double-stranded DNA binding;endoplasmic reticulum;female pregnancy;identical protein binding;inflammatory response;integrated stress response signaling;medium-term memory;mononuclear cell differentiation;myoblast proliferation;neural retina development;neuron differentiation;nuclear matrix;nucleoplasm;nucleus;positive regulation of DNA-templated transcription;positive regulation of miRNA transcription;positive regulation of transcription by RNA polymerase II;promoter-specific chromatin binding;protein binding;protein-DNA complex;protein-containing complex binding;regulation of DNA-templated transcription;regulation of transcription by RNA polymerase II;response to activity;response to cAMP;response to corticosterone;response to cytokine;response to ethanol;response to forskolin;response to gravity;response to immobilization stress;response to insulin;response to light stimulus;response to lipopolysaccharide;response to mechanical stimulus;response to progesterone;response to steroid hormone;response to toxic substance;response to xenobiotic stimulus;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;skeletal muscle cell proliferation;transcription by RNA polymerase II;transcription cis-regulatory region binding;transcription coregulator binding;transcription factor AP-1 complex;transcription regulator complex;transforming growth factor beta receptor signaling pathway</t>
-        </is>
+      <c r="M6" t="n">
+        <v>13</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>GO:0001661;GO:0003407;GO:0006355;GO:0006357;GO:0006366;GO:0006954;GO:0007179;GO:0007565;GO:0009410;GO:0009416;GO:0009612;GO:0009629;GO:0009636;GO:0014823;GO:0014856;GO:0021987;GO:0030182;GO:0032496;GO:0032570;GO:0032868;GO:0032870;GO:0034097;GO:0034224;GO:0034614;GO:0035902;GO:0045471;GO:0045893;GO:0045944;GO:0048545;GO:0051412;GO:0051450;GO:0051591;GO:0060395;GO:0071356;GO:0071364;GO:0071374;GO:0071456;GO:0071560;GO:0072375;GO:0140467;GO:1902895;GO:1903131;GO:1904321;GO:1904628;GO:1990646</t>
+          <t>GO:0005515;GO:0005886;GO:0006805;GO:0009925;GO:0015125;GO:0015291;GO:0015721;GO:0016020;GO:0016323;GO:0016324;GO:0022857;GO:0043252;GO:0055085</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>SMAD protein signal transduction;cellular response to epidermal growth factor stimulus;cellular response to hormone stimulus;cellular response to hypoxia;cellular response to parathyroid hormone stimulus;cellular response to phorbol 13-acetate 12-myristate;cellular response to prolactin;cellular response to reactive oxygen species;cellular response to transforming growth factor beta stimulus;cellular response to tumor necrosis factor;cellular response to zinc ion starvation;cerebral cortex development;conditioned taste aversion;female pregnancy;inflammatory response;integrated stress response signaling;medium-term memory;mononuclear cell differentiation;myoblast proliferation;neural retina development;neuron differentiation;positive regulation of DNA-templated transcription;positive regulation of miRNA transcription;positive regulation of transcription by RNA polymerase II;regulation of DNA-templated transcription;regulation of transcription by RNA polymerase II;response to activity;response to cAMP;response to corticosterone;response to cytokine;response to ethanol;response to forskolin;response to gravity;response to immobilization stress;response to insulin;response to light stimulus;response to lipopolysaccharide;response to mechanical stimulus;response to progesterone;response to steroid hormone;response to toxic substance;response to xenobiotic stimulus;skeletal muscle cell proliferation;transcription by RNA polymerase II;transforming growth factor beta receptor signaling pathway</t>
+          <t>apical plasma membrane;basal plasma membrane;basolateral plasma membrane;bile acid and bile salt transport;bile acid transmembrane transporter activity;membrane;plasma membrane;protein binding;secondary active transmembrane transporter activity;sodium-independent organic anion transport;transmembrane transport;transmembrane transporter activity;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>GO:0000976;GO:0000978;GO:0000979;GO:0000981;GO:0001221;GO:0001228;GO:0003677;GO:0003682;GO:0003690;GO:0003700;GO:0005515;GO:0042802;GO:0043565;GO:0044877;GO:0061629;GO:0070412;GO:1990837;GO:1990841</t>
+          <t>GO:0006805;GO:0015721;GO:0043252;GO:0055085</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;R-SMAD binding;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II core promoter sequence-specific DNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;chromatin binding;double-stranded DNA binding;identical protein binding;promoter-specific chromatin binding;protein binding;protein-containing complex binding;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;transcription cis-regulatory region binding;transcription coregulator binding</t>
+          <t>bile acid and bile salt transport;sodium-independent organic anion transport;transmembrane transport;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>GO:0000785;GO:0005634;GO:0005654;GO:0005667;GO:0005737;GO:0005783;GO:0005829;GO:0016363;GO:0032993;GO:0035976</t>
+          <t>GO:0005515;GO:0015125;GO:0015291;GO:0022857</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>chromatin;cytoplasm;cytosol;endoplasmic reticulum;nuclear matrix;nucleoplasm;nucleus;protein-DNA complex;transcription factor AP-1 complex;transcription regulator complex</t>
+          <t>bile acid transmembrane transporter activity;protein binding;secondary active transmembrane transporter activity;transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0009925;GO:0016020;GO:0016323;GO:0016324</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>apical plasma membrane;basal plasma membrane;basolateral plasma membrane;membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P01137</t>
+          <t>P51639</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TGFB1</t>
+          <t>HMGCR</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7040</v>
+        <v>25675</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>178</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>GO:0001570;GO:0001657;GO:0001666;GO:0001763;GO:0001837;GO:0001843;GO:0002040;GO:0002062;GO:0002244;GO:0002248;GO:0002460;GO:0002859;GO:0003179;GO:0003180;GO:0005114;GO:0005125;GO:0005160;GO:0005515;GO:0005576;GO:0005615;GO:0005634;GO:0005737;GO:0005796;GO:0005886;GO:0005902;GO:0006611;GO:0006754;GO:0006796;GO:0007179;GO:0007406;GO:0007435;GO:0007507;GO:0007565;GO:0008083;GO:0008284;GO:0008285;GO:0009410;GO:0009611;GO:0009749;GO:0009986;GO:0010332;GO:0010575;GO:0010628;GO:0010629;GO:0010716;GO:0010718;GO:0010742;GO:0010763;GO:0010936;GO:0014003;GO:0014008;GO:0016202;GO:0019899;GO:0021915;GO:0030141;GO:0030154;GO:0030214;GO:0030308;GO:0030334;GO:0030335;GO:0030424;GO:0031012;GO:0031093;GO:0031100;GO:0031293;GO:0031334;GO:0031536;GO:0032355;GO:0032570;GO:0032667;GO:0032700;GO:0032740;GO:0032755;GO:0032760;GO:0032801;GO:0032930;GO:0032967;GO:0033280;GO:0034125;GO:0034616;GO:0034713;GO:0034714;GO:0035902;GO:0036120;GO:0036446;GO:0042127;GO:0042306;GO:0042307;GO:0042475;GO:0042552;GO:0042802;GO:0043025;GO:0043065;GO:0043117;GO:0043123;GO:0043410;GO:0043536;GO:0043537;GO:0043539;GO:0044877;GO:0045066;GO:0045216;GO:0045471;GO:0045591;GO:0045596;GO:0045597;GO:0045599;GO:0045662;GO:0045742;GO:0045786;GO:0045892;GO:0045893;GO:0045944;GO:0048298;GO:0048535;GO:0048565;GO:0048642;GO:0048661;GO:0048839;GO:0050679;GO:0050680;GO:0050714;GO:0050729;GO:0050765;GO:0050832;GO:0050921;GO:0051130;GO:0051240;GO:0051247;GO:0051280;GO:0051897;GO:0055010;GO:0060312;GO:0060325;GO:0060364;GO:0060391;GO:0070168;GO:0070374;GO:0070723;GO:0071260;GO:0071333;GO:0071363;GO:0071404;GO:0071456;GO:0071479;GO:0071549;GO:0071560;GO:0071677;GO:0071895;GO:0072562;GO:0085029;GO:0090190;GO:0090263;GO:0097191;GO:0097421;GO:0098586;GO:0099126;GO:0141091;GO:1900126;GO:1900182;GO:1901203;GO:1902074;GO:1902462;GO:1902893;GO:1902894;GO:1902895;GO:1903077;GO:1904018;GO:1904894;GO:1905005;GO:1905641;GO:1990314;GO:1990402;GO:2000048;GO:2000343;GO:2000353;GO:2000636;GO:2000727</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ATP biosynthetic process;Golgi lumen;adaptive immune response based on somatic recombination of immune receptors built from immunoglobulin superfamily domains;animal organ regeneration;aortic valve morphogenesis;axon;blood microparticle;cell differentiation;cell surface;cell-cell junction organization;cellular response to acetaldehyde;cellular response to dexamethasone stimulus;cellular response to glucose stimulus;cellular response to growth factor stimulus;cellular response to hypoxia;cellular response to insulin-like growth factor stimulus;cellular response to ionizing radiation;cellular response to low-density lipoprotein particle stimulus;cellular response to mechanical stimulus;cellular response to platelet-derived growth factor stimulus;cellular response to transforming growth factor beta stimulus;cellular response to virus;chondrocyte differentiation;connective tissue replacement involved in inflammatory response wound healing;cytokine activity;cytoplasm;defense response to fungus;digestive tract development;embryonic liver development;enzyme binding;epithelial to mesenchymal transition;extracellular matrix;extracellular matrix assembly;extracellular region;extrinsic apoptotic signaling pathway;face morphogenesis;female pregnancy;frontal suture morphogenesis;growth factor activity;heart development;heart valve morphogenesis;hematopoietic progenitor cell differentiation;hyaluronan catabolic process;identical protein binding;inner ear development;liver regeneration;lymph node development;macrophage derived foam cell differentiation;membrane protein intracellular domain proteolysis;microvillus;morphogenesis of a branching structure;myelination;myofibroblast differentiation;negative regulation of DNA-templated transcription;negative regulation of MyD88-dependent toll-like receptor signaling pathway;negative regulation of biomineral tissue development;negative regulation of blood vessel endothelial cell migration;negative regulation of cell cycle;negative regulation of cell differentiation;negative regulation of cell growth;negative regulation of cell population proliferation;negative regulation of cell-cell adhesion mediated by cadherin;negative regulation of epithelial cell proliferation;negative regulation of extracellular matrix disassembly;negative regulation of fat cell differentiation;negative regulation of gene expression;negative regulation of hyaluronan biosynthetic process;negative regulation of interleukin-17 production;negative regulation of macrophage cytokine production;negative regulation of miRNA transcription;negative regulation of myoblast differentiation;negative regulation of natural killer cell mediated cytotoxicity directed against tumor cell target;negative regulation of neuroblast proliferation;negative regulation of phagocytosis;negative regulation of protein localization to plasma membrane;negative regulation of release of sequestered calcium ion into cytosol;negative regulation of skeletal muscle tissue development;neural tube closure;neural tube development;neuronal cell body;nucleus;obsolete extracellular space;odontoblast differentiation;odontogenesis of dentin-containing tooth;oligodendrocyte development;phosphate-containing compound metabolic process;plasma membrane;platelet alpha granule lumen;positive regulation of DNA-templated transcription;positive regulation of ERK1 and ERK2 cascade;positive regulation of MAPK cascade;positive regulation of SMAD protein signal transduction;positive regulation of apoptotic process;positive regulation of blood vessel endothelial cell migration;positive regulation of branching involved in ureteric bud morphogenesis;positive regulation of canonical NF-kappaB signal transduction;positive regulation of canonical Wnt signaling pathway;positive regulation of cardiac muscle cell differentiation;positive regulation of cell differentiation;positive regulation of cell migration;positive regulation of cell population proliferation;positive regulation of cellular component organization;positive regulation of chemokine (C-X-C motif) ligand 2 production;positive regulation of chemotaxis;positive regulation of collagen biosynthetic process;positive regulation of endothelial cell apoptotic process;positive regulation of epidermal growth factor receptor signaling pathway;positive regulation of epithelial cell proliferation;positive regulation of epithelial to mesenchymal transition;positive regulation of exit from mitosis;positive regulation of extracellular matrix assembly;positive regulation of fibroblast migration;positive regulation of gene expression;positive regulation of inflammatory response;positive regulation of interleukin-17 production;positive regulation of interleukin-6 production;positive regulation of isotype switching to IgA isotypes;positive regulation of mesenchymal stem cell proliferation;positive regulation of miRNA transcription;positive regulation of microglia differentiation;positive regulation of mononuclear cell migration;positive regulation of multicellular organismal process;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of primary miRNA processing;positive regulation of protein import into nucleus;positive regulation of protein localization to nucleus;positive regulation of protein metabolic process;positive regulation of protein secretion;positive regulation of protein-containing complex assembly;positive regulation of receptor signaling pathway via STAT;positive regulation of regulatory T cell differentiation;positive regulation of smooth muscle cell proliferation;positive regulation of superoxide anion generation;positive regulation of transcription by RNA polymerase II;positive regulation of tumor necrosis factor production;positive regulation of vascular endothelial growth factor production;positive regulation of vascular permeability;positive regulation of vasculature development;protein binding;protein export from nucleus;protein serine/threonine kinase activator activity;protein-containing complex binding;receptor catabolic process;regulation of blood vessel remodeling;regulation of cell migration;regulation of cell population proliferation;regulation of epithelial to mesenchymal transition involved in endocardial cushion formation;regulation of interleukin-23 production;regulation of miRNA transcription;regulation of protein import into nucleus;regulation of striated muscle tissue development;regulatory T cell differentiation;response to cholesterol;response to estradiol;response to ethanol;response to gamma radiation;response to glucose;response to hypoxia;response to immobilization stress;response to laminar fluid shear stress;response to progesterone;response to salt;response to vitamin D;response to wounding;response to xenobiotic stimulus;salivary gland morphogenesis;secretory granule;sprouting angiogenesis;transforming growth factor beta complex;transforming growth factor beta receptor binding;transforming growth factor beta receptor signaling pathway;transforming growth factor beta receptor superfamily signaling pathway;type I transforming growth factor beta receptor binding;type II transforming growth factor beta receptor binding;type III transforming growth factor beta receptor binding;ureteric bud development;vasculogenesis;ventricular cardiac muscle tissue morphogenesis</t>
-        </is>
+      <c r="M7" t="n">
+        <v>31</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GO:0001570;GO:0001657;GO:0001666;GO:0001763;GO:0001837;GO:0001843;GO:0002040;GO:0002062;GO:0002244;GO:0002248;GO:0002460;GO:0002859;GO:0003179;GO:0003180;GO:0006611;GO:0006754;GO:0006796;GO:0007179;GO:0007406;GO:0007435;GO:0007507;GO:0007565;GO:0008284;GO:0008285;GO:0009410;GO:0009611;GO:0009749;GO:0010332;GO:0010575;GO:0010628;GO:0010629;GO:0010716;GO:0010718;GO:0010742;GO:0010763;GO:0010936;GO:0014003;GO:0014008;GO:0016202;GO:0021915;GO:0030154;GO:0030214;GO:0030308;GO:0030334;GO:0030335;GO:0031100;GO:0031293;GO:0031334;GO:0031536;GO:0032355;GO:0032570;GO:0032667;GO:0032700;GO:0032740;GO:0032755;GO:0032760;GO:0032801;GO:0032930;GO:0032967;GO:0033280;GO:0034125;GO:0034616;GO:0035902;GO:0036120;GO:0036446;GO:0042127;GO:0042306;GO:0042307;GO:0042475;GO:0042552;GO:0043065;GO:0043117;GO:0043123;GO:0043410;GO:0043536;GO:0043537;GO:0045066;GO:0045216;GO:0045471;GO:0045591;GO:0045596;GO:0045597;GO:0045599;GO:0045662;GO:0045742;GO:0045786;GO:0045892;GO:0045893;GO:0045944;GO:0048298;GO:0048535;GO:0048565;GO:0048642;GO:0048661;GO:0048839;GO:0050679;GO:0050680;GO:0050714;GO:0050729;GO:0050765;GO:0050832;GO:0050921;GO:0051130;GO:0051240;GO:0051247;GO:0051280;GO:0051897;GO:0055010;GO:0060312;GO:0060325;GO:0060364;GO:0060391;GO:0070168;GO:0070374;GO:0070723;GO:0071260;GO:0071333;GO:0071363;GO:0071404;GO:0071456;GO:0071479;GO:0071549;GO:0071560;GO:0071677;GO:0071895;GO:0085029;GO:0090190;GO:0090263;GO:0097191;GO:0097421;GO:0098586;GO:0141091;GO:1900126;GO:1900182;GO:1901203;GO:1902074;GO:1902462;GO:1902893;GO:1902894;GO:1902895;GO:1903077;GO:1904018;GO:1904894;GO:1905005;GO:1905641;GO:1990314;GO:1990402;GO:2000048;GO:2000343;GO:2000353;GO:2000636;GO:2000727</t>
+          <t>GO:0004420;GO:0005778;GO:0005783;GO:0005789;GO:0006743;GO:0007584;GO:0008284;GO:0008299;GO:0010664;GO:0010666;GO:0015936;GO:0016126;GO:0016616;GO:0031667;GO:0032874;GO:0042632;GO:0042802;GO:0043066;GO:0045445;GO:0045471;GO:0045907;GO:0048643;GO:0048661;GO:0050661;GO:0050709;GO:0051721;GO:0061179;GO:0070328;GO:0070372;GO:0070374;GO:0070723</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ATP biosynthetic process;adaptive immune response based on somatic recombination of immune receptors built from immunoglobulin superfamily domains;animal organ regeneration;aortic valve morphogenesis;cell differentiation;cell-cell junction organization;cellular response to acetaldehyde;cellular response to dexamethasone stimulus;cellular response to glucose stimulus;cellular response to growth factor stimulus;cellular response to hypoxia;cellular response to insulin-like growth factor stimulus;cellular response to ionizing radiation;cellular response to low-density lipoprotein particle stimulus;cellular response to mechanical stimulus;cellular response to platelet-derived growth factor stimulus;cellular response to transforming growth factor beta stimulus;cellular response to virus;chondrocyte differentiation;connective tissue replacement involved in inflammatory response wound healing;defense response to fungus;digestive tract development;embryonic liver development;epithelial to mesenchymal transition;extracellular matrix assembly;extrinsic apoptotic signaling pathway;face morphogenesis;female pregnancy;frontal suture morphogenesis;heart development;heart valve morphogenesis;hematopoietic progenitor cell differentiation;hyaluronan catabolic process;inner ear development;liver regeneration;lymph node development;macrophage derived foam cell differentiation;membrane protein intracellular domain proteolysis;morphogenesis of a branching structure;myelination;myofibroblast differentiation;negative regulation of DNA-templated transcription;negative regulation of MyD88-dependent toll-like receptor signaling pathway;negative regulation of biomineral tissue development;negative regulation of blood vessel endothelial cell migration;negative regulation of cell cycle;negative regulation of cell differentiation;negative regulation of cell growth;negative regulation of cell population proliferation;negative regulation of cell-cell adhesion mediated by cadherin;negative regulation of epithelial cell proliferation;negative regulation of extracellular matrix disassembly;negative regulation of fat cell differentiation;negative regulation of gene expression;negative regulation of hyaluronan biosynthetic process;negative regulation of interleukin-17 production;negative regulation of macrophage cytokine production;negative regulation of miRNA transcription;negative regulation of myoblast differentiation;negative regulation of natural killer cell mediated cytotoxicity directed against tumor cell target;negative regulation of neuroblast proliferation;negative regulation of phagocytosis;negative regulation of protein localization to plasma membrane;negative regulation of release of sequestered calcium ion into cytosol;negative regulation of skeletal muscle tissue development;neural tube closure;neural tube development;odontoblast differentiation;odontogenesis of dentin-containing tooth;oligodendrocyte development;phosphate-containing compound metabolic process;positive regulation of DNA-templated transcription;positive regulation of ERK1 and ERK2 cascade;positive regulation of MAPK cascade;positive regulation of SMAD protein signal transduction;positive regulation of apoptotic process;positive regulation of blood vessel endothelial cell migration;positive regulation of branching involved in ureteric bud morphogenesis;positive regulation of canonical NF-kappaB signal transduction;positive regulation of canonical Wnt signaling pathway;positive regulation of cardiac muscle cell differentiation;positive regulation of cell differentiation;positive regulation of cell migration;positive regulation of cell population proliferation;positive regulation of cellular component organization;positive regulation of chemokine (C-X-C motif) ligand 2 production;positive regulation of chemotaxis;positive regulation of collagen biosynthetic process;positive regulation of endothelial cell apoptotic process;positive regulation of epidermal growth factor receptor signaling pathway;positive regulation of epithelial cell proliferation;positive regulation of epithelial to mesenchymal transition;positive regulation of exit from mitosis;positive regulation of extracellular matrix assembly;positive regulation of fibroblast migration;positive regulation of gene expression;positive regulation of inflammatory response;positive regulation of interleukin-17 production;positive regulation of interleukin-6 production;positive regulation of isotype switching to IgA isotypes;positive regulation of mesenchymal stem cell proliferation;positive regulation of miRNA transcription;positive regulation of microglia differentiation;positive regulation of mononuclear cell migration;positive regulation of multicellular organismal process;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of primary miRNA processing;positive regulation of protein import into nucleus;positive regulation of protein localization to nucleus;positive regulation of protein metabolic process;positive regulation of protein secretion;positive regulation of protein-containing complex assembly;positive regulation of receptor signaling pathway via STAT;positive regulation of regulatory T cell differentiation;positive regulation of smooth muscle cell proliferation;positive regulation of superoxide anion generation;positive regulation of transcription by RNA polymerase II;positive regulation of tumor necrosis factor production;positive regulation of vascular endothelial growth factor production;positive regulation of vascular permeability;positive regulation of vasculature development;protein export from nucleus;receptor catabolic process;regulation of blood vessel remodeling;regulation of cell migration;regulation of cell population proliferation;regulation of epithelial to mesenchymal transition involved in endocardial cushion formation;regulation of interleukin-23 production;regulation of miRNA transcription;regulation of protein import into nucleus;regulation of striated muscle tissue development;regulatory T cell differentiation;response to cholesterol;response to estradiol;response to ethanol;response to gamma radiation;response to glucose;response to hypoxia;response to immobilization stress;response to laminar fluid shear stress;response to progesterone;response to salt;response to vitamin D;response to wounding;response to xenobiotic stimulus;salivary gland morphogenesis;sprouting angiogenesis;transforming growth factor beta receptor signaling pathway;transforming growth factor beta receptor superfamily signaling pathway;ureteric bud development;vasculogenesis;ventricular cardiac muscle tissue morphogenesis</t>
+          <t>NADP binding;cholesterol homeostasis;coenzyme A metabolic process;endoplasmic reticulum;endoplasmic reticulum membrane;hydroxymethylglutaryl-CoA reductase (NADPH) activity;identical protein binding;isoprenoid biosynthetic process;myoblast differentiation;negative regulation of apoptotic process;negative regulation of insulin secretion involved in cellular response to glucose stimulus;negative regulation of protein secretion;negative regulation of striated muscle cell apoptotic process;oxidoreductase activity, acting on the CH-OH group of donors, NAD or NADP as acceptor;peroxisomal membrane;positive regulation of ERK1 and ERK2 cascade;positive regulation of cardiac muscle cell apoptotic process;positive regulation of cell population proliferation;positive regulation of skeletal muscle tissue development;positive regulation of smooth muscle cell proliferation;positive regulation of stress-activated MAPK cascade;positive regulation of vasoconstriction;protein phosphatase 2A binding;regulation of ERK1 and ERK2 cascade;response to cholesterol;response to ethanol;response to nutrient;response to nutrient levels;sterol biosynthetic process;triglyceride homeostasis;ubiquinone metabolic process</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>GO:0005114;GO:0005125;GO:0005160;GO:0005515;GO:0008083;GO:0019899;GO:0034713;GO:0034714;GO:0042802;GO:0043539;GO:0044877</t>
+          <t>GO:0006743;GO:0007584;GO:0008284;GO:0008299;GO:0010664;GO:0010666;GO:0015936;GO:0016126;GO:0031667;GO:0032874;GO:0042632;GO:0043066;GO:0045445;GO:0045471;GO:0045907;GO:0048643;GO:0048661;GO:0050709;GO:0061179;GO:0070328;GO:0070372;GO:0070374;GO:0070723</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>cytokine activity;enzyme binding;growth factor activity;identical protein binding;protein binding;protein serine/threonine kinase activator activity;protein-containing complex binding;transforming growth factor beta receptor binding;type I transforming growth factor beta receptor binding;type II transforming growth factor beta receptor binding;type III transforming growth factor beta receptor binding</t>
+          <t>cholesterol homeostasis;coenzyme A metabolic process;isoprenoid biosynthetic process;myoblast differentiation;negative regulation of apoptotic process;negative regulation of insulin secretion involved in cellular response to glucose stimulus;negative regulation of protein secretion;negative regulation of striated muscle cell apoptotic process;positive regulation of ERK1 and ERK2 cascade;positive regulation of cardiac muscle cell apoptotic process;positive regulation of cell population proliferation;positive regulation of skeletal muscle tissue development;positive regulation of smooth muscle cell proliferation;positive regulation of stress-activated MAPK cascade;positive regulation of vasoconstriction;regulation of ERK1 and ERK2 cascade;response to cholesterol;response to ethanol;response to nutrient;response to nutrient levels;sterol biosynthetic process;triglyceride homeostasis;ubiquinone metabolic process</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>GO:0005576;GO:0005615;GO:0005634;GO:0005737;GO:0005796;GO:0005886;GO:0005902;GO:0009986;GO:0030141;GO:0030424;GO:0031012;GO:0031093;GO:0043025;GO:0072562;GO:0099126</t>
+          <t>GO:0004420;GO:0016616;GO:0042802;GO:0050661;GO:0051721</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Golgi lumen;axon;blood microparticle;cell surface;cytoplasm;extracellular matrix;extracellular region;microvillus;neuronal cell body;nucleus;obsolete extracellular space;plasma membrane;platelet alpha granule lumen;secretory granule;transforming growth factor beta complex</t>
+          <t>NADP binding;hydroxymethylglutaryl-CoA reductase (NADPH) activity;identical protein binding;oxidoreductase activity, acting on the CH-OH group of donors, NAD or NADP as acceptor;protein phosphatase 2A binding</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>GO:0005778;GO:0005783;GO:0005789</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum;endoplasmic reticulum membrane;peroxisomal membrane</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P01375</t>
+          <t>Q9UNQ0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TNF</t>
+          <t>ABCG2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7124</v>
+        <v>9429</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>184</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>GO:0000122;GO:0000976;GO:0001666;GO:0001774;GO:0001819;GO:0001891;GO:0001937;GO:0001975;GO:0002020;GO:0002037;GO:0002281;GO:0002439;GO:0002639;GO:0002700;GO:0002719;GO:0003009;GO:0003085;GO:0005125;GO:0005164;GO:0005515;GO:0005576;GO:0005615;GO:0005886;GO:0006325;GO:0006954;GO:0006955;GO:0007259;GO:0007623;GO:0008285;GO:0008625;GO:0009410;GO:0009612;GO:0009615;GO:0009617;GO:0009651;GO:0009750;GO:0009897;GO:0009986;GO:0010459;GO:0010573;GO:0010628;GO:0010629;GO:0010744;GO:0010888;GO:0014823;GO:0016020;GO:0019722;GO:0031334;GO:0031349;GO:0031622;GO:0031642;GO:0031663;GO:0031667;GO:0032496;GO:0032715;GO:0032722;GO:0032724;GO:0032731;GO:0032741;GO:0032755;GO:0032757;GO:0033209;GO:0034116;GO:0034138;GO:0035900;GO:0036005;GO:0042127;GO:0042311;GO:0042802;GO:0043025;GO:0043065;GO:0043066;GO:0043068;GO:0043122;GO:0043123;GO:0043243;GO:0043410;GO:0043525;GO:0043537;GO:0045071;GO:0045087;GO:0045121;GO:0045429;GO:0045471;GO:0045598;GO:0045599;GO:0045668;GO:0045672;GO:0045732;GO:0045760;GO:0045785;GO:0045840;GO:0045892;GO:0045893;GO:0045930;GO:0045944;GO:0046325;GO:0046330;GO:0046677;GO:0048018;GO:0048143;GO:0048566;GO:0048661;GO:0050678;GO:0050729;GO:0050768;GO:0050793;GO:0050796;GO:0050804;GO:0050806;GO:0050807;GO:0050890;GO:0050901;GO:0050966;GO:0050995;GO:0051044;GO:0051046;GO:0051222;GO:0051239;GO:0051384;GO:0051798;GO:0051897;GO:0051966;GO:0055037;GO:0060252;GO:0060557;GO:0061044;GO:0061048;GO:0070374;GO:0070886;GO:0071219;GO:0071222;GO:0071300;GO:0071316;GO:0071346;GO:0071479;GO:0071677;GO:0071803;GO:0072577;GO:0072659;GO:0090324;GO:0090594;GO:0097191;GO:0097237;GO:0097421;GO:0097527;GO:0120190;GO:0140072;GO:0140374;GO:0140460;GO:0150078;GO:0150129;GO:1900017;GO:1900222;GO:1901224;GO:1901647;GO:1902004;GO:1902065;GO:1902565;GO:1902894;GO:1902895;GO:1903078;GO:1903140;GO:1903347;GO:1903829;GO:1904638;GO:1904646;GO:1904707;GO:1904880;GO:1904996;GO:1904999;GO:1905235;GO:1905242;GO:1990268;GO:2000010;GO:2000334;GO:2000343;GO:2000347;GO:2000351;GO:2000377;GO:2000573;GO:2001234;GO:2001238;GO:2001240</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>antiviral innate immune response;astrocyte activation;calcium-mediated signaling;cell surface;cell surface receptor signaling pathway via JAK-STAT;cellular response to amyloid-beta;cellular response to ionizing radiation;cellular response to lipopolysaccharide;cellular response to molecule of bacterial origin;cellular response to nicotine;cellular response to retinoic acid;cellular response to toxic substance;cellular response to type II interferon;chromatin organization;chronic inflammatory response to antigenic stimulus;circadian rhythm;cognition;cytokine activity;detection of mechanical stimulus involved in sensory perception of pain;embryonic digestive tract development;endothelial cell apoptotic process;external side of plasma membrane;extracellular region;extrinsic apoptotic signaling pathway;extrinsic apoptotic signaling pathway via death domain receptors;histone H3K9ac reader activity;identical protein binding;immune response;inflammatory response;inflammatory response to wounding;innate immune response;leukocyte tethering or rolling;lipopolysaccharide-mediated signaling pathway;liver regeneration;macrophage activation involved in immune response;membrane;membrane raft;microglial cell activation;modulation of chemical synaptic transmission;necroptotic signaling pathway;negative regulation of D-glucose import across plasma membrane;negative regulation of DNA-templated transcription;negative regulation of L-glutamate import across plasma membrane;negative regulation of amyloid-beta clearance;negative regulation of apoptotic process;negative regulation of apoptotic signaling pathway;negative regulation of bicellular tight junction assembly;negative regulation of bile acid secretion;negative regulation of blood vessel endothelial cell migration;negative regulation of branching involved in lung morphogenesis;negative regulation of cell population proliferation;negative regulation of cytokine production involved in immune response;negative regulation of endothelial cell proliferation;negative regulation of extrinsic apoptotic signaling pathway in absence of ligand;negative regulation of fat cell differentiation;negative regulation of gene expression;negative regulation of heart rate;negative regulation of interleukin-6 production;negative regulation of lipid catabolic process;negative regulation of lipid storage;negative regulation of miRNA transcription;negative regulation of mitotic cell cycle;negative regulation of myelination;negative regulation of neurogenesis;negative regulation of osteoblast differentiation;negative regulation of oxidative phosphorylation;negative regulation of systemic arterial blood pressure;negative regulation of transcription by RNA polymerase II;negative regulation of vascular wound healing;negative regulation of viral genome replication;neuronal cell body;obsolete extracellular space;phagocytic cup;plasma membrane;positive regulation of DNA biosynthetic process;positive regulation of DNA-templated transcription;positive regulation of ERK1 and ERK2 cascade;positive regulation of JNK cascade;positive regulation of MAPK cascade;positive regulation of action potential;positive regulation of amyloid-beta formation;positive regulation of apoptotic process;positive regulation of blood microparticle formation;positive regulation of calcineurin-NFAT signaling cascade;positive regulation of canonical NF-kappaB signal transduction;positive regulation of cell adhesion;positive regulation of chemokine (C-X-C motif) ligand 2 production;positive regulation of chemokine production;positive regulation of cytokine production;positive regulation of cytokine production involved in inflammatory response;positive regulation of defense response;positive regulation of extrinsic apoptotic signaling pathway;positive regulation of fever generation;positive regulation of fractalkine production;positive regulation of gene expression;positive regulation of glial cell proliferation;positive regulation of hair follicle development;positive regulation of hepatocyte proliferation;positive regulation of heterotypic cell-cell adhesion;positive regulation of immunoglobulin production;positive regulation of inflammatory response;positive regulation of interleukin-1 beta production;positive regulation of interleukin-18 production;positive regulation of interleukin-33 production;positive regulation of interleukin-6 production;positive regulation of interleukin-8 production;positive regulation of leukocyte adhesion to arterial endothelial cell;positive regulation of leukocyte adhesion to vascular endothelial cell;positive regulation of macrophage derived foam cell differentiation;positive regulation of membrane protein ectodomain proteolysis;positive regulation of miRNA transcription;positive regulation of mitotic nuclear division;positive regulation of mononuclear cell migration;positive regulation of neuroinflammatory response;positive regulation of neuron apoptotic process;positive regulation of neutrophil activation;positive regulation of nitric oxide biosynthetic process;positive regulation of non-canonical NF-kappaB signal transduction;positive regulation of osteoclast differentiation;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of podosome assembly;positive regulation of programmed cell death;positive regulation of protein catabolic process;positive regulation of protein localization;positive regulation of protein localization to cell surface;positive regulation of protein localization to plasma membrane;positive regulation of protein transport;positive regulation of protein-containing complex assembly;positive regulation of protein-containing complex disassembly;positive regulation of smooth muscle cell proliferation;positive regulation of synaptic transmission;positive regulation of synoviocyte proliferation;positive regulation of transcription by RNA polymerase II;positive regulation of vascular associated smooth muscle cell proliferation;positive regulation of vitamin D biosynthetic process;protease binding;protein binding;protein localization to plasma membrane;receptor ligand activity;recycling endosome;regulation of canonical NF-kappaB signal transduction;regulation of cell population proliferation;regulation of developmental process;regulation of endothelial cell apoptotic process;regulation of epithelial cell proliferation;regulation of establishment of endothelial barrier;regulation of fat cell differentiation;regulation of insulin secretion;regulation of multicellular organismal process;regulation of production of molecular mediator of immune response;regulation of reactive oxygen species metabolic process;regulation of secretion;regulation of synapse organization;regulation of synaptic transmission, glutamatergic;response to 3,3',5-triiodo-L-thyronine;response to Gram-negative bacterium;response to L-glutamate;response to activity;response to amphetamine;response to antibiotic;response to bacterium;response to ethanol;response to fructose;response to glucocorticoid;response to gold nanoparticle;response to hydrogen sulfide;response to hypoxia;response to isolation stress;response to lipopolysaccharide;response to macrophage colony-stimulating factor;response to mechanical stimulus;response to nutrient levels;response to quercetin;response to resveratrol;response to salt stress;response to virus;response to xenobiotic stimulus;skeletal muscle contraction;toll-like receptor 3 signaling pathway;transcription cis-regulatory region binding;tumor necrosis factor receptor binding;tumor necrosis factor-mediated signaling pathway;vascular endothelial growth factor production;vasodilation</t>
-        </is>
+      <c r="M8" t="n">
+        <v>39</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>GO:0000122;GO:0001666;GO:0001774;GO:0001819;GO:0001937;GO:0001975;GO:0002037;GO:0002281;GO:0002439;GO:0002639;GO:0002700;GO:0002719;GO:0003009;GO:0003085;GO:0006325;GO:0006954;GO:0006955;GO:0007259;GO:0007623;GO:0008285;GO:0008625;GO:0009410;GO:0009612;GO:0009615;GO:0009617;GO:0009651;GO:0009750;GO:0010459;GO:0010573;GO:0010628;GO:0010629;GO:0010744;GO:0010888;GO:0014823;GO:0019722;GO:0031334;GO:0031349;GO:0031622;GO:0031642;GO:0031663;GO:0031667;GO:0032496;GO:0032715;GO:0032722;GO:0032724;GO:0032731;GO:0032741;GO:0032755;GO:0032757;GO:0033209;GO:0034116;GO:0034138;GO:0035900;GO:0036005;GO:0042127;GO:0042311;GO:0043065;GO:0043066;GO:0043068;GO:0043122;GO:0043123;GO:0043243;GO:0043410;GO:0043525;GO:0043537;GO:0045071;GO:0045087;GO:0045429;GO:0045471;GO:0045598;GO:0045599;GO:0045668;GO:0045672;GO:0045732;GO:0045760;GO:0045785;GO:0045840;GO:0045892;GO:0045893;GO:0045930;GO:0045944;GO:0046325;GO:0046330;GO:0046677;GO:0048143;GO:0048566;GO:0048661;GO:0050678;GO:0050729;GO:0050768;GO:0050793;GO:0050796;GO:0050804;GO:0050806;GO:0050807;GO:0050890;GO:0050901;GO:0050966;GO:0050995;GO:0051044;GO:0051046;GO:0051222;GO:0051239;GO:0051384;GO:0051798;GO:0051897;GO:0051966;GO:0060252;GO:0060557;GO:0061044;GO:0061048;GO:0070374;GO:0070886;GO:0071219;GO:0071222;GO:0071300;GO:0071316;GO:0071346;GO:0071479;GO:0071677;GO:0071803;GO:0072577;GO:0072659;GO:0090324;GO:0090594;GO:0097191;GO:0097237;GO:0097421;GO:0097527;GO:0120190;GO:0140374;GO:0140460;GO:0150078;GO:0150129;GO:1900017;GO:1900222;GO:1901224;GO:1901647;GO:1902004;GO:1902065;GO:1902565;GO:1902894;GO:1902895;GO:1903078;GO:1903140;GO:1903347;GO:1903829;GO:1904638;GO:1904646;GO:1904707;GO:1904880;GO:1904996;GO:1904999;GO:1905235;GO:1905242;GO:1990268;GO:2000010;GO:2000334;GO:2000343;GO:2000347;GO:2000351;GO:2000377;GO:2000573;GO:2001234;GO:2001238;GO:2001240</t>
+          <t>GO:0005515;GO:0005524;GO:0005886;GO:0006869;GO:0008559;GO:0015143;GO:0015225;GO:0015562;GO:0015747;GO:0015878;GO:0016020;GO:0016324;GO:0016887;GO:0022857;GO:0030148;GO:0031526;GO:0031966;GO:0032217;GO:0032218;GO:0042626;GO:0042802;GO:0042803;GO:0042908;GO:0042910;GO:0045121;GO:0046415;GO:0046983;GO:0055085;GO:0070633;GO:0097744;GO:0098591;GO:0098754;GO:0140115;GO:0140359;GO:0150104;GO:0160244;GO:1990748;GO:1990961;GO:1990962</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>antiviral innate immune response;astrocyte activation;calcium-mediated signaling;cell surface receptor signaling pathway via JAK-STAT;cellular response to amyloid-beta;cellular response to ionizing radiation;cellular response to lipopolysaccharide;cellular response to molecule of bacterial origin;cellular response to nicotine;cellular response to retinoic acid;cellular response to toxic substance;cellular response to type II interferon;chromatin organization;chronic inflammatory response to antigenic stimulus;circadian rhythm;cognition;detection of mechanical stimulus involved in sensory perception of pain;embryonic digestive tract development;endothelial cell apoptotic process;extrinsic apoptotic signaling pathway;extrinsic apoptotic signaling pathway via death domain receptors;immune response;inflammatory response;inflammatory response to wounding;innate immune response;leukocyte tethering or rolling;lipopolysaccharide-mediated signaling pathway;liver regeneration;macrophage activation involved in immune response;microglial cell activation;modulation of chemical synaptic transmission;necroptotic signaling pathway;negative regulation of D-glucose import across plasma membrane;negative regulation of DNA-templated transcription;negative regulation of L-glutamate import across plasma membrane;negative regulation of amyloid-beta clearance;negative regulation of apoptotic process;negative regulation of apoptotic signaling pathway;negative regulation of bicellular tight junction assembly;negative regulation of bile acid secretion;negative regulation of blood vessel endothelial cell migration;negative regulation of branching involved in lung morphogenesis;negative regulation of cell population proliferation;negative regulation of cytokine production involved in immune response;negative regulation of endothelial cell proliferation;negative regulation of extrinsic apoptotic signaling pathway in absence of ligand;negative regulation of fat cell differentiation;negative regulation of gene expression;negative regulation of heart rate;negative regulation of interleukin-6 production;negative regulation of lipid catabolic process;negative regulation of lipid storage;negative regulation of miRNA transcription;negative regulation of mitotic cell cycle;negative regulation of myelination;negative regulation of neurogenesis;negative regulation of osteoblast differentiation;negative regulation of oxidative phosphorylation;negative regulation of systemic arterial blood pressure;negative regulation of transcription by RNA polymerase II;negative regulation of vascular wound healing;negative regulation of viral genome replication;positive regulation of DNA biosynthetic process;positive regulation of DNA-templated transcription;positive regulation of ERK1 and ERK2 cascade;positive regulation of JNK cascade;positive regulation of MAPK cascade;positive regulation of action potential;positive regulation of amyloid-beta formation;positive regulation of apoptotic process;positive regulation of blood microparticle formation;positive regulation of calcineurin-NFAT signaling cascade;positive regulation of canonical NF-kappaB signal transduction;positive regulation of cell adhesion;positive regulation of chemokine (C-X-C motif) ligand 2 production;positive regulation of chemokine production;positive regulation of cytokine production;positive regulation of cytokine production involved in inflammatory response;positive regulation of defense response;positive regulation of extrinsic apoptotic signaling pathway;positive regulation of fever generation;positive regulation of fractalkine production;positive regulation of gene expression;positive regulation of glial cell proliferation;positive regulation of hair follicle development;positive regulation of hepatocyte proliferation;positive regulation of heterotypic cell-cell adhesion;positive regulation of immunoglobulin production;positive regulation of inflammatory response;positive regulation of interleukin-1 beta production;positive regulation of interleukin-18 production;positive regulation of interleukin-33 production;positive regulation of interleukin-6 production;positive regulation of interleukin-8 production;positive regulation of leukocyte adhesion to arterial endothelial cell;positive regulation of leukocyte adhesion to vascular endothelial cell;positive regulation of macrophage derived foam cell differentiation;positive regulation of membrane protein ectodomain proteolysis;positive regulation of miRNA transcription;positive regulation of mitotic nuclear division;positive regulation of mononuclear cell migration;positive regulation of neuroinflammatory response;positive regulation of neuron apoptotic process;positive regulation of neutrophil activation;positive regulation of nitric oxide biosynthetic process;positive regulation of non-canonical NF-kappaB signal transduction;positive regulation of osteoclast differentiation;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of podosome assembly;positive regulation of programmed cell death;positive regulation of protein catabolic process;positive regulation of protein localization;positive regulation of protein localization to cell surface;positive regulation of protein localization to plasma membrane;positive regulation of protein transport;positive regulation of protein-containing complex assembly;positive regulation of protein-containing complex disassembly;positive regulation of smooth muscle cell proliferation;positive regulation of synaptic transmission;positive regulation of synoviocyte proliferation;positive regulation of transcription by RNA polymerase II;positive regulation of vascular associated smooth muscle cell proliferation;positive regulation of vitamin D biosynthetic process;protein localization to plasma membrane;regulation of canonical NF-kappaB signal transduction;regulation of cell population proliferation;regulation of developmental process;regulation of endothelial cell apoptotic process;regulation of epithelial cell proliferation;regulation of establishment of endothelial barrier;regulation of fat cell differentiation;regulation of insulin secretion;regulation of multicellular organismal process;regulation of production of molecular mediator of immune response;regulation of reactive oxygen species metabolic process;regulation of secretion;regulation of synapse organization;regulation of synaptic transmission, glutamatergic;response to 3,3',5-triiodo-L-thyronine;response to Gram-negative bacterium;response to L-glutamate;response to activity;response to amphetamine;response to antibiotic;response to bacterium;response to ethanol;response to fructose;response to glucocorticoid;response to gold nanoparticle;response to hydrogen sulfide;response to hypoxia;response to isolation stress;response to lipopolysaccharide;response to macrophage colony-stimulating factor;response to mechanical stimulus;response to nutrient levels;response to quercetin;response to resveratrol;response to salt stress;response to virus;response to xenobiotic stimulus;skeletal muscle contraction;toll-like receptor 3 signaling pathway;tumor necrosis factor-mediated signaling pathway;vascular endothelial growth factor production;vasodilation</t>
+          <t>ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled transmembrane transporter activity;apical plasma membrane;biotin transmembrane transporter activity;biotin transport;brush border membrane;cellular detoxification;detoxification;efflux transmembrane transporter activity;export across plasma membrane;external side of apical plasma membrane;identical protein binding;lipid transport;membrane;membrane raft;mitochondrial membrane;plasma membrane;protein binding;protein dimerization activity;protein homodimerization activity;renal urate salt excretion;riboflavin transmembrane transporter activity;riboflavin transport;sphingolipid biosynthetic process;sulfite export across plasma membrane;transepithelial transport;transmembrane transport;transmembrane transporter activity;transport across blood-brain barrier;urate metabolic process;urate transmembrane transporter activity;urate transport;xenobiotic detoxification by transmembrane export across the plasma membrane;xenobiotic transmembrane transporter activity;xenobiotic transport;xenobiotic transport across blood-brain barrier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>GO:0000976;GO:0002020;GO:0005125;GO:0005164;GO:0005515;GO:0042802;GO:0048018;GO:0140072</t>
+          <t>GO:0006869;GO:0015747;GO:0015878;GO:0030148;GO:0032218;GO:0042908;GO:0046415;GO:0055085;GO:0070633;GO:0097744;GO:0098754;GO:0140115;GO:0150104;GO:0160244;GO:1990748;GO:1990961;GO:1990962</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>cytokine activity;histone H3K9ac reader activity;identical protein binding;protease binding;protein binding;receptor ligand activity;transcription cis-regulatory region binding;tumor necrosis factor receptor binding</t>
+          <t>biotin transport;cellular detoxification;detoxification;export across plasma membrane;lipid transport;renal urate salt excretion;riboflavin transport;sphingolipid biosynthetic process;sulfite export across plasma membrane;transepithelial transport;transmembrane transport;transport across blood-brain barrier;urate metabolic process;urate transport;xenobiotic detoxification by transmembrane export across the plasma membrane;xenobiotic transport;xenobiotic transport across blood-brain barrier</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>GO:0001891;GO:0005576;GO:0005615;GO:0005886;GO:0009897;GO:0009986;GO:0016020;GO:0043025;GO:0045121;GO:0055037</t>
+          <t>GO:0005515;GO:0005524;GO:0008559;GO:0015143;GO:0015225;GO:0015562;GO:0016887;GO:0022857;GO:0032217;GO:0042626;GO:0042802;GO:0042803;GO:0042910;GO:0046983;GO:0140359</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>cell surface;external side of plasma membrane;extracellular region;membrane;membrane raft;neuronal cell body;obsolete extracellular space;phagocytic cup;plasma membrane;recycling endosome</t>
+          <t>ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled transmembrane transporter activity;biotin transmembrane transporter activity;efflux transmembrane transporter activity;identical protein binding;protein binding;protein dimerization activity;protein homodimerization activity;riboflavin transmembrane transporter activity;transmembrane transporter activity;urate transmembrane transporter activity;xenobiotic transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0016020;GO:0016324;GO:0031526;GO:0031966;GO:0045121;GO:0098591</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>apical plasma membrane;brush border membrane;external side of apical plasma membrane;membrane;membrane raft;mitochondrial membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P01584</t>
+          <t>Q9Y6L6</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IL1B</t>
+          <t>SLCO1B1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3553</v>
+        <v>10599</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>94</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>GO:0001819;GO:0002711;GO:0005125;GO:0005149;GO:0005178;GO:0005515;GO:0005576;GO:0005615;GO:0005764;GO:0005829;GO:0006915;GO:0006954;GO:0006955;GO:0007165;GO:0007267;GO:0007566;GO:0008284;GO:0008285;GO:0010573;GO:0010575;GO:0010628;GO:0010641;GO:0010718;GO:0010744;GO:0010829;GO:0014805;GO:0019221;GO:0019904;GO:0030141;GO:0030213;GO:0030335;GO:0030949;GO:0031394;GO:0031622;GO:0031982;GO:0032308;GO:0032496;GO:0032725;GO:0032729;GO:0032743;GO:0032755;GO:0032757;GO:0033092;GO:0034116;GO:0042102;GO:0043122;GO:0043123;GO:0043409;GO:0043410;GO:0045429;GO:0045766;GO:0045833;GO:0045840;GO:0045893;GO:0045917;GO:0046330;GO:0046627;GO:0046827;GO:0048018;GO:0050691;GO:0050729;GO:0050767;GO:0050768;GO:0050796;GO:0050805;GO:0050830;GO:0050995;GO:0050996;GO:0050999;GO:0051044;GO:0051897;GO:0060252;GO:0060355;GO:0070164;GO:0070372;GO:0070374;GO:0070487;GO:0070498;GO:0070555;GO:0071222;GO:0071260;GO:0071466;GO:0071639;GO:0097398;GO:0150078;GO:1900745;GO:1901224;GO:1902680;GO:1903140;GO:1903530;GO:1903597;GO:1905075;GO:2000556;GO:2001240</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>apoptotic process;cell-cell signaling;cellular response to interleukin-17;cellular response to lipopolysaccharide;cellular response to mechanical stimulus;cellular response to xenobiotic stimulus;cytokine activity;cytokine-mediated signaling pathway;cytosol;defense response to Gram-positive bacterium;embryo implantation;extracellular region;hyaluronan biosynthetic process;immune response;inflammatory response;integrin binding;interleukin-1 receptor binding;interleukin-1-mediated signaling pathway;lysosome;monocyte aggregation;negative regulation of D-glucose transmembrane transport;negative regulation of MAPK cascade;negative regulation of adiponectin secretion;negative regulation of cell population proliferation;negative regulation of extrinsic apoptotic signaling pathway in absence of ligand;negative regulation of gap junction assembly;negative regulation of insulin receptor signaling pathway;negative regulation of lipid catabolic process;negative regulation of lipid metabolic process;negative regulation of neurogenesis;negative regulation of synaptic transmission;obsolete extracellular space;positive regulation of DNA-templated transcription;positive regulation of ERK1 and ERK2 cascade;positive regulation of JNK cascade;positive regulation of MAPK cascade;positive regulation of RNA biosynthetic process;positive regulation of T cell mediated immunity;positive regulation of T cell proliferation;positive regulation of T-helper 1 cell cytokine production;positive regulation of angiogenesis;positive regulation of canonical NF-kappaB signal transduction;positive regulation of cell adhesion molecule production;positive regulation of cell migration;positive regulation of cell population proliferation;positive regulation of complement activation;positive regulation of cytokine production;positive regulation of epithelial to mesenchymal transition;positive regulation of fever generation;positive regulation of gene expression;positive regulation of glial cell proliferation;positive regulation of granulocyte macrophage colony-stimulating factor production;positive regulation of heterotypic cell-cell adhesion;positive regulation of immature T cell proliferation in thymus;positive regulation of inflammatory response;positive regulation of interleukin-2 production;positive regulation of interleukin-6 production;positive regulation of interleukin-8 production;positive regulation of lipid catabolic process;positive regulation of macrophage derived foam cell differentiation;positive regulation of membrane protein ectodomain proteolysis;positive regulation of mitotic nuclear division;positive regulation of monocyte chemotactic protein-1 production;positive regulation of neuroinflammatory response;positive regulation of nitric oxide biosynthetic process;positive regulation of non-canonical NF-kappaB signal transduction;positive regulation of p38MAPK cascade;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of platelet-derived growth factor receptor signaling pathway;positive regulation of prostaglandin biosynthetic process;positive regulation of prostaglandin secretion;positive regulation of protein export from nucleus;positive regulation of tight junction disassembly;positive regulation of type II interferon production;positive regulation of vascular endothelial growth factor production;positive regulation of vascular endothelial growth factor receptor signaling pathway;protein binding;protein domain specific binding;receptor ligand activity;regulation of ERK1 and ERK2 cascade;regulation of canonical NF-kappaB signal transduction;regulation of defense response to virus by host;regulation of establishment of endothelial barrier;regulation of insulin secretion;regulation of neurogenesis;regulation of nitric-oxide synthase activity;regulation of secretion by cell;response to interleukin-1;response to lipopolysaccharide;secretory granule;signal transduction;smooth muscle adaptation;vascular endothelial growth factor production;vesicle</t>
-        </is>
+      <c r="M9" t="n">
+        <v>17</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>GO:0001819;GO:0002711;GO:0006915;GO:0006954;GO:0006955;GO:0007165;GO:0007267;GO:0007566;GO:0008284;GO:0008285;GO:0010573;GO:0010575;GO:0010628;GO:0010641;GO:0010718;GO:0010744;GO:0010829;GO:0014805;GO:0019221;GO:0030213;GO:0030335;GO:0030949;GO:0031394;GO:0031622;GO:0032308;GO:0032496;GO:0032725;GO:0032729;GO:0032743;GO:0032755;GO:0032757;GO:0033092;GO:0034116;GO:0042102;GO:0043122;GO:0043123;GO:0043409;GO:0043410;GO:0045429;GO:0045766;GO:0045833;GO:0045840;GO:0045893;GO:0045917;GO:0046330;GO:0046627;GO:0046827;GO:0050691;GO:0050729;GO:0050767;GO:0050768;GO:0050796;GO:0050805;GO:0050830;GO:0050995;GO:0050996;GO:0050999;GO:0051044;GO:0051897;GO:0060252;GO:0060355;GO:0070164;GO:0070372;GO:0070374;GO:0070487;GO:0070498;GO:0070555;GO:0071222;GO:0071260;GO:0071466;GO:0071639;GO:0097398;GO:0150078;GO:1900745;GO:1901224;GO:1902680;GO:1903140;GO:1903530;GO:1903597;GO:1905075;GO:2000556;GO:2001240</t>
+          <t>GO:0005515;GO:0005886;GO:0006805;GO:0009925;GO:0015125;GO:0015132;GO:0015291;GO:0015349;GO:0015721;GO:0015732;GO:0016020;GO:0016323;GO:0022857;GO:0042167;GO:0043252;GO:0055085;GO:0070327</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>apoptotic process;cell-cell signaling;cellular response to interleukin-17;cellular response to lipopolysaccharide;cellular response to mechanical stimulus;cellular response to xenobiotic stimulus;cytokine-mediated signaling pathway;defense response to Gram-positive bacterium;embryo implantation;hyaluronan biosynthetic process;immune response;inflammatory response;interleukin-1-mediated signaling pathway;monocyte aggregation;negative regulation of D-glucose transmembrane transport;negative regulation of MAPK cascade;negative regulation of adiponectin secretion;negative regulation of cell population proliferation;negative regulation of extrinsic apoptotic signaling pathway in absence of ligand;negative regulation of gap junction assembly;negative regulation of insulin receptor signaling pathway;negative regulation of lipid catabolic process;negative regulation of lipid metabolic process;negative regulation of neurogenesis;negative regulation of synaptic transmission;positive regulation of DNA-templated transcription;positive regulation of ERK1 and ERK2 cascade;positive regulation of JNK cascade;positive regulation of MAPK cascade;positive regulation of RNA biosynthetic process;positive regulation of T cell mediated immunity;positive regulation of T cell proliferation;positive regulation of T-helper 1 cell cytokine production;positive regulation of angiogenesis;positive regulation of canonical NF-kappaB signal transduction;positive regulation of cell adhesion molecule production;positive regulation of cell migration;positive regulation of cell population proliferation;positive regulation of complement activation;positive regulation of cytokine production;positive regulation of epithelial to mesenchymal transition;positive regulation of fever generation;positive regulation of gene expression;positive regulation of glial cell proliferation;positive regulation of granulocyte macrophage colony-stimulating factor production;positive regulation of heterotypic cell-cell adhesion;positive regulation of immature T cell proliferation in thymus;positive regulation of inflammatory response;positive regulation of interleukin-2 production;positive regulation of interleukin-6 production;positive regulation of interleukin-8 production;positive regulation of lipid catabolic process;positive regulation of macrophage derived foam cell differentiation;positive regulation of membrane protein ectodomain proteolysis;positive regulation of mitotic nuclear division;positive regulation of monocyte chemotactic protein-1 production;positive regulation of neuroinflammatory response;positive regulation of nitric oxide biosynthetic process;positive regulation of non-canonical NF-kappaB signal transduction;positive regulation of p38MAPK cascade;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of platelet-derived growth factor receptor signaling pathway;positive regulation of prostaglandin biosynthetic process;positive regulation of prostaglandin secretion;positive regulation of protein export from nucleus;positive regulation of tight junction disassembly;positive regulation of type II interferon production;positive regulation of vascular endothelial growth factor production;positive regulation of vascular endothelial growth factor receptor signaling pathway;regulation of ERK1 and ERK2 cascade;regulation of canonical NF-kappaB signal transduction;regulation of defense response to virus by host;regulation of establishment of endothelial barrier;regulation of insulin secretion;regulation of neurogenesis;regulation of nitric-oxide synthase activity;regulation of secretion by cell;response to interleukin-1;response to lipopolysaccharide;signal transduction;smooth muscle adaptation;vascular endothelial growth factor production</t>
+          <t>basal plasma membrane;basolateral plasma membrane;bile acid and bile salt transport;bile acid transmembrane transporter activity;heme catabolic process;membrane;plasma membrane;prostaglandin transmembrane transporter activity;prostaglandin transport;protein binding;secondary active transmembrane transporter activity;sodium-independent organic anion transport;thyroid hormone transmembrane transporter activity;thyroid hormone transport;transmembrane transport;transmembrane transporter activity;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>GO:0005125;GO:0005149;GO:0005178;GO:0005515;GO:0019904;GO:0048018</t>
+          <t>GO:0006805;GO:0015721;GO:0015732;GO:0042167;GO:0043252;GO:0055085;GO:0070327</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>cytokine activity;integrin binding;interleukin-1 receptor binding;protein binding;protein domain specific binding;receptor ligand activity</t>
+          <t>bile acid and bile salt transport;heme catabolic process;prostaglandin transport;sodium-independent organic anion transport;thyroid hormone transport;transmembrane transport;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>GO:0005576;GO:0005615;GO:0005764;GO:0005829;GO:0030141;GO:0031982</t>
+          <t>GO:0005515;GO:0015125;GO:0015132;GO:0015291;GO:0015349;GO:0022857</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>cytosol;extracellular region;lysosome;obsolete extracellular space;secretory granule;vesicle</t>
+          <t>bile acid transmembrane transporter activity;prostaglandin transmembrane transporter activity;protein binding;secondary active transmembrane transporter activity;thyroid hormone transmembrane transporter activity;transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0009925;GO:0016020;GO:0016323</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>basal plasma membrane;basolateral plasma membrane;membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P05019</t>
+          <t>O15440</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1171,75 +1229,81 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IGF1</t>
+          <t>ABCC5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3479</v>
+        <v>10057</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>89</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>GO:0001501;GO:0001649;GO:0001775;GO:0001837;GO:0005158;GO:0005159;GO:0005178;GO:0005179;GO:0005515;GO:0005576;GO:0005615;GO:0007165;GO:0007265;GO:0007517;GO:0007623;GO:0008083;GO:0008283;GO:0008284;GO:0008286;GO:0009408;GO:0009441;GO:0010468;GO:0010560;GO:0010613;GO:0010628;GO:0010629;GO:0014834;GO:0014896;GO:0014904;GO:0014911;GO:0016942;GO:0030141;GO:0030166;GO:0030335;GO:0031093;GO:0031643;GO:0032148;GO:0032691;GO:0032720;GO:0034392;GO:0035630;GO:0035867;GO:0042060;GO:0042104;GO:0042567;GO:0043066;GO:0043388;GO:0043410;GO:0043415;GO:0043568;GO:0045445;GO:0045669;GO:0045725;GO:0045821;GO:0045840;GO:0045893;GO:0045944;GO:0046326;GO:0046579;GO:0048009;GO:0048018;GO:0048146;GO:0048661;GO:0050679;GO:0050714;GO:0050821;GO:0051450;GO:0051897;GO:0060283;GO:0060396;GO:0061051;GO:0070374;GO:0070382;GO:0070886;GO:0090201;GO:0097696;GO:0098794;GO:0098978;GO:0099013;GO:0099170;GO:0150079;GO:1902430;GO:1904075;GO:1904646;GO:1904707;GO:1905460;GO:2000679;GO:2001234;GO:2001237</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Ras protein signal transduction;activation of protein kinase B activity;alphav-beta3 integrin-IGF-1-IGF1R complex;bone mineralization involved in bone maturation;cell activation;cell population proliferation;cell surface receptor signaling pathway via STAT;cellular response to amyloid-beta;circadian rhythm;epithelial to mesenchymal transition;exocytic vesicle;extracellular region;glutamatergic synapse;glycolate metabolic process;growth factor activity;growth hormone receptor signaling pathway;hormone activity;insulin receptor binding;insulin receptor signaling pathway;insulin-like growth factor binding protein complex;insulin-like growth factor receptor binding;insulin-like growth factor receptor signaling pathway;insulin-like growth factor ternary complex;integrin binding;muscle hypertrophy;muscle organ development;myoblast differentiation;myoblast proliferation;myotube cell development;negative regulation of amyloid-beta formation;negative regulation of apoptotic process;negative regulation of apoptotic signaling pathway;negative regulation of extrinsic apoptotic signaling pathway;negative regulation of gene expression;negative regulation of interleukin-1 beta production;negative regulation of neuroinflammatory response;negative regulation of oocyte development;negative regulation of release of cytochrome c from mitochondria;negative regulation of smooth muscle cell apoptotic process;negative regulation of tumor necrosis factor production;negative regulation of vascular associated smooth muscle cell apoptotic process;neuronal dense core vesicle lumen;obsolete extracellular space;osteoblast differentiation;platelet alpha granule lumen;positive regulation of D-glucose import across plasma membrane;positive regulation of DNA binding;positive regulation of DNA-templated transcription;positive regulation of ERK1 and ERK2 cascade;positive regulation of MAPK cascade;positive regulation of Ras protein signal transduction;positive regulation of activated T cell proliferation;positive regulation of calcineurin-NFAT signaling cascade;positive regulation of cardiac muscle hypertrophy;positive regulation of cell growth involved in cardiac muscle cell development;positive regulation of cell migration;positive regulation of cell population proliferation;positive regulation of epithelial cell proliferation;positive regulation of fibroblast proliferation;positive regulation of gene expression;positive regulation of glycogen biosynthetic process;positive regulation of glycolytic process;positive regulation of glycoprotein biosynthetic process;positive regulation of insulin-like growth factor receptor signaling pathway;positive regulation of mitotic nuclear division;positive regulation of myelination;positive regulation of osteoblast differentiation;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of protein secretion;positive regulation of skeletal muscle tissue regeneration;positive regulation of smooth muscle cell migration;positive regulation of smooth muscle cell proliferation;positive regulation of transcription by RNA polymerase II;positive regulation of transcription regulatory region DNA binding;positive regulation of trophectodermal cell proliferation;positive regulation of vascular associated smooth muscle cell proliferation;postsynapse;postsynaptic modulation of chemical synaptic transmission;protein binding;protein stabilization;proteoglycan biosynthetic process;receptor ligand activity;regulation of gene expression;response to heat;secretory granule;signal transduction;skeletal muscle satellite cell maintenance involved in skeletal muscle regeneration;skeletal system development;wound healing</t>
-        </is>
+      <c r="M10" t="n">
+        <v>34</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GO:0001501;GO:0001649;GO:0001775;GO:0001837;GO:0007165;GO:0007265;GO:0007517;GO:0007623;GO:0008283;GO:0008284;GO:0008286;GO:0009408;GO:0009441;GO:0010468;GO:0010560;GO:0010613;GO:0010628;GO:0010629;GO:0014834;GO:0014896;GO:0014904;GO:0014911;GO:0030166;GO:0030335;GO:0031643;GO:0032148;GO:0032691;GO:0032720;GO:0034392;GO:0035630;GO:0042060;GO:0042104;GO:0043066;GO:0043388;GO:0043410;GO:0043415;GO:0043568;GO:0045445;GO:0045669;GO:0045725;GO:0045821;GO:0045840;GO:0045893;GO:0045944;GO:0046326;GO:0046579;GO:0048009;GO:0048146;GO:0048661;GO:0050679;GO:0050714;GO:0050821;GO:0051450;GO:0051897;GO:0060283;GO:0060396;GO:0061051;GO:0070374;GO:0070886;GO:0090201;GO:0097696;GO:0099170;GO:0150079;GO:1902430;GO:1904075;GO:1904646;GO:1904707;GO:1905460;GO:2000679;GO:2001234;GO:2001237</t>
+          <t>GO:0005524;GO:0005796;GO:0005886;GO:0006805;GO:0006855;GO:0008559;GO:0010008;GO:0015216;GO:0015232;GO:0015562;GO:0015865;GO:0016020;GO:0016323;GO:0016324;GO:0016887;GO:0022857;GO:0030213;GO:0034634;GO:0034775;GO:0035351;GO:0042626;GO:0042908;GO:0042910;GO:0055085;GO:0070730;GO:0070731;GO:0098838;GO:0140115;GO:0140359;GO:0150104;GO:1901264;GO:1903790;GO:1905948;GO:1990961</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Ras protein signal transduction;activation of protein kinase B activity;bone mineralization involved in bone maturation;cell activation;cell population proliferation;cell surface receptor signaling pathway via STAT;cellular response to amyloid-beta;circadian rhythm;epithelial to mesenchymal transition;glycolate metabolic process;growth hormone receptor signaling pathway;insulin receptor signaling pathway;insulin-like growth factor receptor signaling pathway;muscle hypertrophy;muscle organ development;myoblast differentiation;myoblast proliferation;myotube cell development;negative regulation of amyloid-beta formation;negative regulation of apoptotic process;negative regulation of apoptotic signaling pathway;negative regulation of extrinsic apoptotic signaling pathway;negative regulation of gene expression;negative regulation of interleukin-1 beta production;negative regulation of neuroinflammatory response;negative regulation of oocyte development;negative regulation of release of cytochrome c from mitochondria;negative regulation of smooth muscle cell apoptotic process;negative regulation of tumor necrosis factor production;negative regulation of vascular associated smooth muscle cell apoptotic process;osteoblast differentiation;positive regulation of D-glucose import across plasma membrane;positive regulation of DNA binding;positive regulation of DNA-templated transcription;positive regulation of ERK1 and ERK2 cascade;positive regulation of MAPK cascade;positive regulation of Ras protein signal transduction;positive regulation of activated T cell proliferation;positive regulation of calcineurin-NFAT signaling cascade;positive regulation of cardiac muscle hypertrophy;positive regulation of cell growth involved in cardiac muscle cell development;positive regulation of cell migration;positive regulation of cell population proliferation;positive regulation of epithelial cell proliferation;positive regulation of fibroblast proliferation;positive regulation of gene expression;positive regulation of glycogen biosynthetic process;positive regulation of glycolytic process;positive regulation of glycoprotein biosynthetic process;positive regulation of insulin-like growth factor receptor signaling pathway;positive regulation of mitotic nuclear division;positive regulation of myelination;positive regulation of osteoblast differentiation;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of protein secretion;positive regulation of skeletal muscle tissue regeneration;positive regulation of smooth muscle cell migration;positive regulation of smooth muscle cell proliferation;positive regulation of transcription by RNA polymerase II;positive regulation of transcription regulatory region DNA binding;positive regulation of trophectodermal cell proliferation;positive regulation of vascular associated smooth muscle cell proliferation;postsynaptic modulation of chemical synaptic transmission;protein stabilization;proteoglycan biosynthetic process;regulation of gene expression;response to heat;signal transduction;skeletal muscle satellite cell maintenance involved in skeletal muscle regeneration;skeletal system development;wound healing</t>
+          <t>ABC-type 3',5'-cyclic GMP transmembrane transporter activity;ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled transmembrane transporter activity;Golgi lumen;apical plasma membrane;basolateral plasma membrane;cAMP transport;cGMP transport;carbohydrate derivative transport;efflux transmembrane transporter activity;endosome membrane;export across plasma membrane;folate transmembrane transport;glutathione transmembrane transport;glutathione transmembrane transporter activity;guanine nucleotide transmembrane transport;heme transmembrane transport;heme transmembrane transporter activity;hyaluronan biosynthetic process;membrane;plasma membrane;purine nucleotide transmembrane transporter activity;purine nucleotide transport;transmembrane transport;transmembrane transporter activity;transport across blood-brain barrier;xenobiotic detoxification by transmembrane export across the plasma membrane;xenobiotic metabolic process;xenobiotic transmembrane transport;xenobiotic transmembrane transporter activity;xenobiotic transport</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>GO:0005158;GO:0005159;GO:0005178;GO:0005179;GO:0005515;GO:0008083;GO:0048018</t>
+          <t>GO:0006805;GO:0006855;GO:0015865;GO:0030213;GO:0034775;GO:0035351;GO:0042908;GO:0055085;GO:0070730;GO:0070731;GO:0098838;GO:0140115;GO:0150104;GO:1901264;GO:1903790;GO:1990961</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>growth factor activity;hormone activity;insulin receptor binding;insulin-like growth factor receptor binding;integrin binding;protein binding;receptor ligand activity</t>
+          <t>cAMP transport;cGMP transport;carbohydrate derivative transport;export across plasma membrane;folate transmembrane transport;glutathione transmembrane transport;guanine nucleotide transmembrane transport;heme transmembrane transport;hyaluronan biosynthetic process;purine nucleotide transport;transmembrane transport;transport across blood-brain barrier;xenobiotic detoxification by transmembrane export across the plasma membrane;xenobiotic metabolic process;xenobiotic transmembrane transport;xenobiotic transport</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>GO:0005576;GO:0005615;GO:0016942;GO:0030141;GO:0031093;GO:0035867;GO:0042567;GO:0070382;GO:0098794;GO:0098978;GO:0099013</t>
+          <t>GO:0005524;GO:0008559;GO:0015216;GO:0015232;GO:0015562;GO:0016887;GO:0022857;GO:0034634;GO:0042626;GO:0042910;GO:0140359;GO:1905948</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>alphav-beta3 integrin-IGF-1-IGF1R complex;exocytic vesicle;extracellular region;glutamatergic synapse;insulin-like growth factor binding protein complex;insulin-like growth factor ternary complex;neuronal dense core vesicle lumen;obsolete extracellular space;platelet alpha granule lumen;postsynapse;secretory granule</t>
+          <t>ABC-type 3',5'-cyclic GMP transmembrane transporter activity;ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled transmembrane transporter activity;efflux transmembrane transporter activity;glutathione transmembrane transporter activity;heme transmembrane transporter activity;purine nucleotide transmembrane transporter activity;transmembrane transporter activity;xenobiotic transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>GO:0005796;GO:0005886;GO:0010008;GO:0016020;GO:0016323;GO:0016324</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Golgi lumen;apical plasma membrane;basolateral plasma membrane;endosome membrane;membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P05107</t>
+          <t>O43924</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1250,75 +1314,81 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ITGB2</t>
+          <t>PDE6D</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3689</v>
+        <v>5147</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>66</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>GO:0001540;GO:0001774;GO:0001851;GO:0002523;GO:0004895;GO:0005178;GO:0005515;GO:0005886;GO:0005925;GO:0006898;GO:0006909;GO:0006911;GO:0006915;GO:0006954;GO:0007155;GO:0007158;GO:0007159;GO:0007160;GO:0007229;GO:0007267;GO:0008305;GO:0008360;GO:0009897;GO:0009986;GO:0016020;GO:0019901;GO:0030369;GO:0030593;GO:0031072;GO:0031623;GO:0032930;GO:0033627;GO:0033631;GO:0034113;GO:0034687;GO:0034688;GO:0034689;GO:0034690;GO:0035579;GO:0035987;GO:0038024;GO:0043113;GO:0043235;GO:0043315;GO:0043542;GO:0044853;GO:0044877;GO:0045121;GO:0045123;GO:0045429;GO:0045766;GO:0045963;GO:0048646;GO:0050730;GO:0050839;GO:0061756;GO:0070062;GO:0070821;GO:0071404;GO:0090314;GO:0097242;GO:0098609;GO:0101003;GO:1903561;GO:1904996;GO:1990266</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ICAM-3 receptor activity;amyloid-beta binding;amyloid-beta clearance;anatomical structure formation involved in morphogenesis;apoptotic process;cargo receptor activity;cell adhesion;cell adhesion mediated by integrin;cell adhesion molecule binding;cell adhesion receptor activity;cell surface;cell-cell adhesion;cell-cell adhesion mediated by integrin;cell-cell signaling;cell-matrix adhesion;cellular extravasation;cellular response to low-density lipoprotein particle stimulus;complement component C3b binding;endodermal cell differentiation;endothelial cell migration;external side of plasma membrane;extracellular exosome;extracellular vesicle;ficolin-1-rich granule membrane;focal adhesion;heat shock protein binding;heterotypic cell-cell adhesion;inflammatory response;integrin alphaD-beta2 complex;integrin alphaL-beta2 complex;integrin alphaM-beta2 complex;integrin alphaX-beta2 complex;integrin binding;integrin complex;integrin-mediated signaling pathway;leukocyte adhesion to vascular endothelial cell;leukocyte cell-cell adhesion;leukocyte migration involved in inflammatory response;membrane;membrane raft;microglial cell activation;negative regulation of dopamine metabolic process;neuron cell-cell adhesion;neutrophil chemotaxis;neutrophil migration;phagocytosis;phagocytosis, engulfment;plasma membrane;plasma membrane raft;positive regulation of angiogenesis;positive regulation of leukocyte adhesion to vascular endothelial cell;positive regulation of neutrophil degranulation;positive regulation of nitric oxide biosynthetic process;positive regulation of protein targeting to membrane;positive regulation of superoxide anion generation;protein binding;protein kinase binding;protein-containing complex binding;receptor clustering;receptor internalization;receptor-mediated endocytosis;regulation of cell shape;regulation of peptidyl-tyrosine phosphorylation;signaling receptor complex;specific granule membrane;tertiary granule membrane</t>
-        </is>
+      <c r="M11" t="n">
+        <v>10</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>GO:0001774;GO:0002523;GO:0006898;GO:0006909;GO:0006911;GO:0006915;GO:0006954;GO:0007155;GO:0007158;GO:0007159;GO:0007160;GO:0007229;GO:0007267;GO:0008360;GO:0030593;GO:0031623;GO:0032930;GO:0033627;GO:0033631;GO:0034113;GO:0035987;GO:0043113;GO:0043315;GO:0043542;GO:0045123;GO:0045429;GO:0045766;GO:0045963;GO:0048646;GO:0050730;GO:0061756;GO:0071404;GO:0090314;GO:0097242;GO:0098609;GO:1904996;GO:1990266</t>
+          <t>GO:0005095;GO:0005515;GO:0005737;GO:0005829;GO:0005929;GO:0007601;GO:0030659;GO:0031267;GO:0031410;GO:0050953</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>amyloid-beta clearance;anatomical structure formation involved in morphogenesis;apoptotic process;cell adhesion;cell adhesion mediated by integrin;cell-cell adhesion;cell-cell adhesion mediated by integrin;cell-cell signaling;cell-matrix adhesion;cellular extravasation;cellular response to low-density lipoprotein particle stimulus;endodermal cell differentiation;endothelial cell migration;heterotypic cell-cell adhesion;inflammatory response;integrin-mediated signaling pathway;leukocyte adhesion to vascular endothelial cell;leukocyte cell-cell adhesion;leukocyte migration involved in inflammatory response;microglial cell activation;negative regulation of dopamine metabolic process;neuron cell-cell adhesion;neutrophil chemotaxis;neutrophil migration;phagocytosis;phagocytosis, engulfment;positive regulation of angiogenesis;positive regulation of leukocyte adhesion to vascular endothelial cell;positive regulation of neutrophil degranulation;positive regulation of nitric oxide biosynthetic process;positive regulation of protein targeting to membrane;positive regulation of superoxide anion generation;receptor clustering;receptor internalization;receptor-mediated endocytosis;regulation of cell shape;regulation of peptidyl-tyrosine phosphorylation</t>
+          <t>GTPase inhibitor activity;cilium;cytoplasm;cytoplasmic vesicle;cytoplasmic vesicle membrane;cytosol;protein binding;sensory perception of light stimulus;small GTPase binding;visual perception</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>GO:0001540;GO:0001851;GO:0004895;GO:0005178;GO:0005515;GO:0019901;GO:0030369;GO:0031072;GO:0038024;GO:0044877;GO:0050839</t>
+          <t>GO:0007601;GO:0050953</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ICAM-3 receptor activity;amyloid-beta binding;cargo receptor activity;cell adhesion molecule binding;cell adhesion receptor activity;complement component C3b binding;heat shock protein binding;integrin binding;protein binding;protein kinase binding;protein-containing complex binding</t>
+          <t>sensory perception of light stimulus;visual perception</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>GO:0005886;GO:0005925;GO:0008305;GO:0009897;GO:0009986;GO:0016020;GO:0034687;GO:0034688;GO:0034689;GO:0034690;GO:0035579;GO:0043235;GO:0044853;GO:0045121;GO:0070062;GO:0070821;GO:0101003;GO:1903561</t>
+          <t>GO:0005095;GO:0005515;GO:0031267</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>cell surface;external side of plasma membrane;extracellular exosome;extracellular vesicle;ficolin-1-rich granule membrane;focal adhesion;integrin alphaD-beta2 complex;integrin alphaL-beta2 complex;integrin alphaM-beta2 complex;integrin alphaX-beta2 complex;integrin complex;membrane;membrane raft;plasma membrane;plasma membrane raft;signaling receptor complex;specific granule membrane;tertiary granule membrane</t>
+          <t>GTPase inhibitor activity;protein binding;small GTPase binding</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005829;GO:0005929;GO:0030659;GO:0031410</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>cilium;cytoplasm;cytoplasmic vesicle;cytoplasmic vesicle membrane;cytosol</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P05231</t>
+          <t>O75626</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1329,75 +1399,81 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IL6</t>
+          <t>PRDM1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3569</v>
+        <v>639</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>107</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>GO:0001781;GO:0001960;GO:0002314;GO:0002384;GO:0002446;GO:0002548;GO:0002639;GO:0002675;GO:0002690;GO:0005125;GO:0005138;GO:0005515;GO:0005576;GO:0005615;GO:0005788;GO:0005886;GO:0005896;GO:0006953;GO:0006954;GO:0006955;GO:0006959;GO:0007259;GO:0008083;GO:0008284;GO:0008285;GO:0010573;GO:0010574;GO:0010575;GO:0010628;GO:0010718;GO:0010888;GO:0014823;GO:0019221;GO:0030154;GO:0030168;GO:0031018;GO:0031175;GO:0032494;GO:0032682;GO:0032722;GO:0032731;GO:0032733;GO:0032740;GO:0032745;GO:0032755;GO:0032757;GO:0032760;GO:0032966;GO:0033138;GO:0035425;GO:0035633;GO:0038001;GO:0042102;GO:0042593;GO:0042802;GO:0043065;GO:0043066;GO:0043410;GO:0045599;GO:0045669;GO:0045727;GO:0045765;GO:0045779;GO:0045893;GO:0045944;GO:0046427;GO:0048661;GO:0050731;GO:0050768;GO:0050796;GO:0050829;GO:0050830;GO:0050871;GO:0051223;GO:0051251;GO:0051384;GO:0051607;GO:0060252;GO:0061470;GO:0061888;GO:0070050;GO:0070091;GO:0070092;GO:0070102;GO:0070301;GO:0070345;GO:0071222;GO:0072540;GO:0072574;GO:0090091;GO:0090594;GO:0097421;GO:0097696;GO:0098586;GO:0150077;GO:0150078;GO:1900017;GO:1901731;GO:1902512;GO:1902895;GO:1903978;GO:1904894;GO:1904996;GO:2000553;GO:2000635;GO:2000660;GO:2000676</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>T follicular helper cell differentiation;T-helper 17 cell lineage commitment;acute-phase response;autocrine signaling;cell differentiation;cell surface receptor signaling pathway via JAK-STAT;cell surface receptor signaling pathway via STAT;cellular response to hydrogen peroxide;cellular response to lipopolysaccharide;cellular response to virus;cytokine activity;cytokine-mediated signaling pathway;defense response to Gram-negative bacterium;defense response to Gram-positive bacterium;defense response to virus;endocrine pancreas development;endoplasmic reticulum lumen;extracellular region;germinal center B cell differentiation;glucagon secretion;glucose homeostasis;growth factor activity;hepatic immune response;hepatocyte proliferation;humoral immune response;identical protein binding;immune response;inflammatory response;inflammatory response to wounding;interleukin-6 receptor binding;interleukin-6 receptor complex;interleukin-6-mediated signaling pathway;liver regeneration;maintenance of blood-brain barrier;monocyte chemotaxis;negative regulation of apoptotic process;negative regulation of bone resorption;negative regulation of cell population proliferation;negative regulation of chemokine production;negative regulation of collagen biosynthetic process;negative regulation of cytokine-mediated signaling pathway;negative regulation of fat cell differentiation;negative regulation of fat cell proliferation;negative regulation of interleukin-1-mediated signaling pathway;negative regulation of lipid storage;negative regulation of neurogenesis;negative regulation of primary miRNA processing;neuron cellular homeostasis;neuron projection development;neutrophil apoptotic process;neutrophil mediated immunity;obsolete extracellular space;paracrine signaling;plasma membrane;platelet activation;positive regulation of B cell activation;positive regulation of DNA-templated transcription;positive regulation of MAPK cascade;positive regulation of T cell proliferation;positive regulation of T-helper 2 cell cytokine production;positive regulation of acute inflammatory response;positive regulation of apoptotic DNA fragmentation;positive regulation of apoptotic process;positive regulation of cell population proliferation;positive regulation of chemokine production;positive regulation of cytokine production involved in inflammatory response;positive regulation of epithelial to mesenchymal transition;positive regulation of extracellular matrix disassembly;positive regulation of gene expression;positive regulation of glial cell proliferation;positive regulation of immunoglobulin production;positive regulation of interleukin-1 beta production;positive regulation of interleukin-10 production;positive regulation of interleukin-17 production;positive regulation of interleukin-21 production;positive regulation of interleukin-6 production;positive regulation of interleukin-8 production;positive regulation of leukocyte adhesion to vascular endothelial cell;positive regulation of leukocyte chemotaxis;positive regulation of lymphocyte activation;positive regulation of miRNA transcription;positive regulation of neuroinflammatory response;positive regulation of osteoblast differentiation;positive regulation of peptidyl-serine phosphorylation;positive regulation of peptidyl-tyrosine phosphorylation;positive regulation of platelet aggregation;positive regulation of receptor signaling pathway via JAK-STAT;positive regulation of receptor signaling pathway via STAT;positive regulation of smooth muscle cell proliferation;positive regulation of transcription by RNA polymerase II;positive regulation of translation;positive regulation of tumor necrosis factor production;positive regulation of type B pancreatic cell apoptotic process;positive regulation of vascular endothelial growth factor production;protein binding;regulation of angiogenesis;regulation of astrocyte activation;regulation of glucagon secretion;regulation of insulin secretion;regulation of microglial cell activation;regulation of neuroinflammatory response;regulation of protein transport;regulation of vascular endothelial growth factor production;response to activity;response to glucocorticoid;response to peptidoglycan;vascular endothelial growth factor production</t>
-        </is>
+      <c r="M12" t="n">
+        <v>20</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GO:0001781;GO:0001960;GO:0002314;GO:0002384;GO:0002446;GO:0002548;GO:0002639;GO:0002675;GO:0002690;GO:0006953;GO:0006954;GO:0006955;GO:0006959;GO:0007259;GO:0008284;GO:0008285;GO:0010573;GO:0010574;GO:0010575;GO:0010628;GO:0010718;GO:0010888;GO:0014823;GO:0019221;GO:0030154;GO:0030168;GO:0031018;GO:0031175;GO:0032494;GO:0032682;GO:0032722;GO:0032731;GO:0032733;GO:0032740;GO:0032745;GO:0032755;GO:0032757;GO:0032760;GO:0032966;GO:0033138;GO:0035425;GO:0035633;GO:0038001;GO:0042102;GO:0042593;GO:0043065;GO:0043066;GO:0043410;GO:0045599;GO:0045669;GO:0045727;GO:0045765;GO:0045779;GO:0045893;GO:0045944;GO:0046427;GO:0048661;GO:0050731;GO:0050768;GO:0050796;GO:0050829;GO:0050830;GO:0050871;GO:0051223;GO:0051251;GO:0051384;GO:0051607;GO:0060252;GO:0061470;GO:0061888;GO:0070050;GO:0070091;GO:0070092;GO:0070102;GO:0070301;GO:0070345;GO:0071222;GO:0072540;GO:0072574;GO:0090091;GO:0090594;GO:0097421;GO:0097696;GO:0098586;GO:0150077;GO:0150078;GO:1900017;GO:1901731;GO:1902512;GO:1902895;GO:1903978;GO:1904894;GO:1904996;GO:2000553;GO:2000635;GO:2000660;GO:2000676</t>
+          <t>GO:0000122;GO:0000976;GO:0000978;GO:0001227;GO:0003700;GO:0005515;GO:0005634;GO:0005654;GO:0005730;GO:0005737;GO:0006357;GO:0010467;GO:0032823;GO:0033082;GO:0045165;GO:0048869;GO:0051136;GO:1990226;GO:1990837;GO:1990841</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>T follicular helper cell differentiation;T-helper 17 cell lineage commitment;acute-phase response;autocrine signaling;cell differentiation;cell surface receptor signaling pathway via JAK-STAT;cell surface receptor signaling pathway via STAT;cellular response to hydrogen peroxide;cellular response to lipopolysaccharide;cellular response to virus;cytokine-mediated signaling pathway;defense response to Gram-negative bacterium;defense response to Gram-positive bacterium;defense response to virus;endocrine pancreas development;germinal center B cell differentiation;glucagon secretion;glucose homeostasis;hepatic immune response;hepatocyte proliferation;humoral immune response;immune response;inflammatory response;inflammatory response to wounding;interleukin-6-mediated signaling pathway;liver regeneration;maintenance of blood-brain barrier;monocyte chemotaxis;negative regulation of apoptotic process;negative regulation of bone resorption;negative regulation of cell population proliferation;negative regulation of chemokine production;negative regulation of collagen biosynthetic process;negative regulation of cytokine-mediated signaling pathway;negative regulation of fat cell differentiation;negative regulation of fat cell proliferation;negative regulation of interleukin-1-mediated signaling pathway;negative regulation of lipid storage;negative regulation of neurogenesis;negative regulation of primary miRNA processing;neuron cellular homeostasis;neuron projection development;neutrophil apoptotic process;neutrophil mediated immunity;paracrine signaling;platelet activation;positive regulation of B cell activation;positive regulation of DNA-templated transcription;positive regulation of MAPK cascade;positive regulation of T cell proliferation;positive regulation of T-helper 2 cell cytokine production;positive regulation of acute inflammatory response;positive regulation of apoptotic DNA fragmentation;positive regulation of apoptotic process;positive regulation of cell population proliferation;positive regulation of chemokine production;positive regulation of cytokine production involved in inflammatory response;positive regulation of epithelial to mesenchymal transition;positive regulation of extracellular matrix disassembly;positive regulation of gene expression;positive regulation of glial cell proliferation;positive regulation of immunoglobulin production;positive regulation of interleukin-1 beta production;positive regulation of interleukin-10 production;positive regulation of interleukin-17 production;positive regulation of interleukin-21 production;positive regulation of interleukin-6 production;positive regulation of interleukin-8 production;positive regulation of leukocyte adhesion to vascular endothelial cell;positive regulation of leukocyte chemotaxis;positive regulation of lymphocyte activation;positive regulation of miRNA transcription;positive regulation of neuroinflammatory response;positive regulation of osteoblast differentiation;positive regulation of peptidyl-serine phosphorylation;positive regulation of peptidyl-tyrosine phosphorylation;positive regulation of platelet aggregation;positive regulation of receptor signaling pathway via JAK-STAT;positive regulation of receptor signaling pathway via STAT;positive regulation of smooth muscle cell proliferation;positive regulation of transcription by RNA polymerase II;positive regulation of translation;positive regulation of tumor necrosis factor production;positive regulation of type B pancreatic cell apoptotic process;positive regulation of vascular endothelial growth factor production;regulation of angiogenesis;regulation of astrocyte activation;regulation of glucagon secretion;regulation of insulin secretion;regulation of microglial cell activation;regulation of neuroinflammatory response;regulation of protein transport;regulation of vascular endothelial growth factor production;response to activity;response to glucocorticoid;response to peptidoglycan;vascular endothelial growth factor production</t>
+          <t>DNA-binding transcription factor activity;DNA-binding transcription repressor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;cell fate commitment;cellular developmental process;cytoplasm;gene expression;histone methyltransferase binding;negative regulation of transcription by RNA polymerase II;nucleolus;nucleoplasm;nucleus;promoter-specific chromatin binding;protein binding;regulation of NK T cell differentiation;regulation of extrathymic T cell differentiation;regulation of natural killer cell differentiation;regulation of transcription by RNA polymerase II;sequence-specific double-stranded DNA binding;transcription cis-regulatory region binding</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>GO:0005125;GO:0005138;GO:0005515;GO:0008083;GO:0042802</t>
+          <t>GO:0000122;GO:0006357;GO:0010467;GO:0032823;GO:0033082;GO:0045165;GO:0048869;GO:0051136</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>cytokine activity;growth factor activity;identical protein binding;interleukin-6 receptor binding;protein binding</t>
+          <t>cell fate commitment;cellular developmental process;gene expression;negative regulation of transcription by RNA polymerase II;regulation of NK T cell differentiation;regulation of extrathymic T cell differentiation;regulation of natural killer cell differentiation;regulation of transcription by RNA polymerase II</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>GO:0005576;GO:0005615;GO:0005788;GO:0005886;GO:0005896</t>
+          <t>GO:0000976;GO:0000978;GO:0001227;GO:0003700;GO:0005515;GO:1990226;GO:1990837;GO:1990841</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>endoplasmic reticulum lumen;extracellular region;interleukin-6 receptor complex;obsolete extracellular space;plasma membrane</t>
+          <t>DNA-binding transcription factor activity;DNA-binding transcription repressor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;histone methyltransferase binding;promoter-specific chromatin binding;protein binding;sequence-specific double-stranded DNA binding;transcription cis-regulatory region binding</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>GO:0005634;GO:0005654;GO:0005730;GO:0005737</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>cytoplasm;nucleolus;nucleoplasm;nucleus</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P06401</t>
+          <t>O95477</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1408,75 +1484,81 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>ABCA1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5241</v>
+        <v>19</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>36</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>GO:0000785;GO:0000978;GO:0000981;GO:0001223;GO:0001228;GO:0003677;GO:0003700;GO:0003707;GO:0004879;GO:0005496;GO:0005515;GO:0005634;GO:0005654;GO:0005737;GO:0005741;GO:0005829;GO:0005886;GO:0006355;GO:0006357;GO:0007165;GO:0007267;GO:0008270;GO:0010628;GO:0010629;GO:0019899;GO:0030518;GO:0034056;GO:0042326;GO:0042802;GO:0043401;GO:0043565;GO:0045944;GO:0050847;GO:0051117;GO:0051457;GO:1990837</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ATPase binding;DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;cell-cell signaling;chromatin;cytoplasm;cytosol;enzyme binding;estrogen response element binding;identical protein binding;maintenance of protein location in nucleus;mitochondrial outer membrane;negative regulation of gene expression;negative regulation of phosphorylation;nuclear receptor activity;nuclear receptor-mediated steroid hormone signaling pathway;nuclear steroid receptor activity;nucleoplasm;nucleus;plasma membrane;positive regulation of gene expression;positive regulation of transcription by RNA polymerase II;progesterone receptor signaling pathway;protein binding;regulation of DNA-templated transcription;regulation of transcription by RNA polymerase II;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;signal transduction;steroid binding;steroid hormone receptor signaling pathway;transcription coactivator binding;zinc ion binding</t>
-        </is>
+      <c r="M13" t="n">
+        <v>78</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>GO:0006355;GO:0006357;GO:0007165;GO:0007267;GO:0010628;GO:0010629;GO:0030518;GO:0042326;GO:0043401;GO:0045944;GO:0050847;GO:0051457</t>
+          <t>GO:0005102;GO:0005515;GO:0005524;GO:0005768;GO:0005789;GO:0005794;GO:0005886;GO:0007040;GO:0007186;GO:0007189;GO:0007584;GO:0008035;GO:0008203;GO:0008320;GO:0009306;GO:0009410;GO:0009897;GO:0009986;GO:0010745;GO:0010875;GO:0010887;GO:0015485;GO:0015850;GO:0015914;GO:0016020;GO:0016197;GO:0016323;GO:0016887;GO:0019905;GO:0023061;GO:0030139;GO:0030301;GO:0031210;GO:0031267;GO:0031667;GO:0032367;GO:0032489;GO:0033344;GO:0033552;GO:0033700;GO:0034185;GO:0034186;GO:0034188;GO:0034380;GO:0034616;GO:0038027;GO:0042158;GO:0042626;GO:0042632;GO:0043691;GO:0045121;GO:0045332;GO:0045335;GO:0046623;GO:0048471;GO:0051117;GO:0055085;GO:0055091;GO:0060155;GO:0071222;GO:0071300;GO:0071345;GO:0071397;GO:0071404;GO:0071466;GO:0071806;GO:0090107;GO:0090108;GO:0090554;GO:0090556;GO:0097708;GO:0099039;GO:0120014;GO:0120020;GO:0140115;GO:0140326;GO:0140328;GO:0140359</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>cell-cell signaling;maintenance of protein location in nucleus;negative regulation of gene expression;negative regulation of phosphorylation;nuclear receptor-mediated steroid hormone signaling pathway;positive regulation of gene expression;positive regulation of transcription by RNA polymerase II;progesterone receptor signaling pathway;regulation of DNA-templated transcription;regulation of transcription by RNA polymerase II;signal transduction;steroid hormone receptor signaling pathway</t>
+          <t>ABC-type transporter activity;ATP binding;ATP hydrolysis activity;ATPase binding;ATPase-coupled intramembrane lipid carrier activity;ATPase-coupled transmembrane transporter activity;G protein-coupled receptor signaling pathway;Golgi apparatus;adenylate cyclase-activating G protein-coupled receptor signaling pathway;apolipoprotein A-I binding;apolipoprotein A-I receptor activity;apolipoprotein A-I-mediated signaling pathway;apolipoprotein binding;basolateral plasma membrane;cell surface;cellular response to cholesterol;cellular response to cytokine stimulus;cellular response to lipopolysaccharide;cellular response to low-density lipoprotein particle stimulus;cellular response to retinoic acid;cellular response to xenobiotic stimulus;cholesterol binding;cholesterol efflux;cholesterol homeostasis;cholesterol metabolic process;cholesterol transfer activity;cholesterol transport;endocytic vesicle;endoplasmic reticulum membrane;endosomal transport;endosome;export across plasma membrane;external side of plasma membrane;floppase activity;high-density lipoprotein particle assembly;high-density lipoprotein particle binding;intracellular cholesterol transport;intracellular vesicle;lipoprotein biosynthetic process;lysosome organization;membrane;membrane raft;negative regulation of cholesterol storage;negative regulation of macrophage derived foam cell differentiation;organic hydroxy compound transport;perinuclear region of cytoplasm;phagocytic vesicle;phosphatidylcholine binding;phosphatidylcholine floppase activity;phosphatidylserine floppase activity;phospholipid efflux;phospholipid homeostasis;phospholipid transfer activity;phospholipid translocation;phospholipid transport;plasma membrane;platelet dense granule organization;positive regulation of cholesterol efflux;positive regulation of high-density lipoprotein particle assembly;protein binding;protein secretion;protein transmembrane transport;regulation of Cdc42 protein signal transduction;regulation of high-density lipoprotein particle assembly;response to laminar fluid shear stress;response to nutrient;response to nutrient levels;response to vitamin B3;response to xenobiotic stimulus;reverse cholesterol transport;signal release;signaling receptor binding;small GTPase binding;sphingolipid floppase activity;sphingolipid translocation;syntaxin binding;transmembrane protein transporter activity;transmembrane transport</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>GO:0000978;GO:0000981;GO:0001223;GO:0001228;GO:0003677;GO:0003700;GO:0003707;GO:0004879;GO:0005496;GO:0005515;GO:0008270;GO:0019899;GO:0034056;GO:0042802;GO:0043565;GO:0051117;GO:1990837</t>
+          <t>GO:0007040;GO:0007186;GO:0007189;GO:0007584;GO:0008203;GO:0009306;GO:0009410;GO:0010745;GO:0010875;GO:0010887;GO:0015850;GO:0015914;GO:0016197;GO:0023061;GO:0030301;GO:0031667;GO:0032367;GO:0032489;GO:0033344;GO:0033552;GO:0033700;GO:0034380;GO:0034616;GO:0038027;GO:0042158;GO:0042632;GO:0043691;GO:0045332;GO:0055085;GO:0055091;GO:0060155;GO:0071222;GO:0071300;GO:0071345;GO:0071397;GO:0071404;GO:0071466;GO:0071806;GO:0090107;GO:0090108;GO:0099039;GO:0140115</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ATPase binding;DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;enzyme binding;estrogen response element binding;identical protein binding;nuclear receptor activity;nuclear steroid receptor activity;protein binding;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;steroid binding;transcription coactivator binding;zinc ion binding</t>
+          <t>G protein-coupled receptor signaling pathway;adenylate cyclase-activating G protein-coupled receptor signaling pathway;apolipoprotein A-I-mediated signaling pathway;cellular response to cholesterol;cellular response to cytokine stimulus;cellular response to lipopolysaccharide;cellular response to low-density lipoprotein particle stimulus;cellular response to retinoic acid;cellular response to xenobiotic stimulus;cholesterol efflux;cholesterol homeostasis;cholesterol metabolic process;cholesterol transport;endosomal transport;export across plasma membrane;high-density lipoprotein particle assembly;intracellular cholesterol transport;lipoprotein biosynthetic process;lysosome organization;negative regulation of cholesterol storage;negative regulation of macrophage derived foam cell differentiation;organic hydroxy compound transport;phospholipid efflux;phospholipid homeostasis;phospholipid translocation;phospholipid transport;platelet dense granule organization;positive regulation of cholesterol efflux;positive regulation of high-density lipoprotein particle assembly;protein secretion;protein transmembrane transport;regulation of Cdc42 protein signal transduction;regulation of high-density lipoprotein particle assembly;response to laminar fluid shear stress;response to nutrient;response to nutrient levels;response to vitamin B3;response to xenobiotic stimulus;reverse cholesterol transport;signal release;sphingolipid translocation;transmembrane transport</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>GO:0000785;GO:0005634;GO:0005654;GO:0005737;GO:0005741;GO:0005829;GO:0005886</t>
+          <t>GO:0005102;GO:0005515;GO:0005524;GO:0008035;GO:0008320;GO:0015485;GO:0016887;GO:0019905;GO:0031210;GO:0031267;GO:0034185;GO:0034186;GO:0034188;GO:0042626;GO:0046623;GO:0051117;GO:0090554;GO:0090556;GO:0120014;GO:0120020;GO:0140326;GO:0140328;GO:0140359</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>chromatin;cytoplasm;cytosol;mitochondrial outer membrane;nucleoplasm;nucleus;plasma membrane</t>
+          <t>ABC-type transporter activity;ATP binding;ATP hydrolysis activity;ATPase binding;ATPase-coupled intramembrane lipid carrier activity;ATPase-coupled transmembrane transporter activity;apolipoprotein A-I binding;apolipoprotein A-I receptor activity;apolipoprotein binding;cholesterol binding;cholesterol transfer activity;floppase activity;high-density lipoprotein particle binding;phosphatidylcholine binding;phosphatidylcholine floppase activity;phosphatidylserine floppase activity;phospholipid transfer activity;protein binding;signaling receptor binding;small GTPase binding;sphingolipid floppase activity;syntaxin binding;transmembrane protein transporter activity</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>GO:0005768;GO:0005789;GO:0005794;GO:0005886;GO:0009897;GO:0009986;GO:0016020;GO:0016323;GO:0030139;GO:0045121;GO:0045335;GO:0048471;GO:0097708</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Golgi apparatus;basolateral plasma membrane;cell surface;endocytic vesicle;endoplasmic reticulum membrane;endosome;external side of plasma membrane;intracellular vesicle;membrane;membrane raft;perinuclear region of cytoplasm;phagocytic vesicle;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P07339</t>
+          <t>P01130</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1487,75 +1569,81 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CTSD</t>
+          <t>LDLR</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1509</v>
+        <v>3949</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>31</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>GO:0004175;GO:0004190;GO:0004197;GO:0005515;GO:0005576;GO:0005615;GO:0005737;GO:0005764;GO:0005765;GO:0005829;GO:0006508;GO:0008233;GO:0010008;GO:0016787;GO:0019886;GO:0031012;GO:0031904;GO:0035580;GO:0038020;GO:0042159;GO:0042470;GO:0043065;GO:0043202;GO:0045121;GO:0070001;GO:0070062;GO:0070201;GO:0097194;GO:1901143;GO:1904724;GO:1904813</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>antigen processing and presentation of exogenous peptide antigen via MHC class II;aspartic-type endopeptidase activity;aspartic-type peptidase activity;cysteine-type endopeptidase activity;cytoplasm;cytosol;endopeptidase activity;endosome lumen;endosome membrane;execution phase of apoptosis;extracellular exosome;extracellular matrix;extracellular region;ficolin-1-rich granule lumen;hydrolase activity;insulin catabolic process;insulin receptor recycling;lipoprotein catabolic process;lysosomal lumen;lysosomal membrane;lysosome;melanosome;membrane raft;obsolete extracellular space;peptidase activity;positive regulation of apoptotic process;protein binding;proteolysis;regulation of establishment of protein localization;specific granule lumen;tertiary granule lumen</t>
-        </is>
+      <c r="M14" t="n">
+        <v>66</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>GO:0006508;GO:0019886;GO:0038020;GO:0042159;GO:0043065;GO:0070201;GO:0097194;GO:1901143</t>
+          <t>GO:0001523;GO:0001540;GO:0001920;GO:0002020;GO:0005041;GO:0005509;GO:0005515;GO:0005764;GO:0005768;GO:0005769;GO:0005770;GO:0005794;GO:0005886;GO:0005905;GO:0006629;GO:0006897;GO:0006898;GO:0006909;GO:0007616;GO:0009897;GO:0009986;GO:0010008;GO:0010628;GO:0010629;GO:0010867;GO:0010899;GO:0010989;GO:0015914;GO:0016020;GO:0016323;GO:0030169;GO:0030229;GO:0030299;GO:0030301;GO:0030669;GO:0032050;GO:0034381;GO:0034383;GO:0034384;GO:0036020;GO:0036477;GO:0042632;GO:0042802;GO:0043235;GO:0045177;GO:0048844;GO:0050729;GO:0051241;GO:0051246;GO:0051248;GO:0060090;GO:0061771;GO:0061889;GO:0070508;GO:0071398;GO:0071404;GO:0071813;GO:0090118;GO:0090181;GO:0097242;GO:0097443;GO:0150094;GO:1903979;GO:1905167;GO:1905907;GO:1990666</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>antigen processing and presentation of exogenous peptide antigen via MHC class II;execution phase of apoptosis;insulin catabolic process;insulin receptor recycling;lipoprotein catabolic process;positive regulation of apoptotic process;proteolysis;regulation of establishment of protein localization</t>
+          <t>Golgi apparatus;PCSK9-LDLR complex;amyloid-beta binding;amyloid-beta clearance;amyloid-beta clearance by cellular catabolic process;apical part of cell;artery morphogenesis;basolateral plasma membrane;calcium ion binding;cell surface;cellular response to fatty acid;cellular response to low-density lipoprotein particle stimulus;cholesterol homeostasis;cholesterol import;cholesterol transport;clathrin heavy chain binding;clathrin-coated endocytic vesicle membrane;clathrin-coated pit;early endosome;endocytosis;endolysosome membrane;endosome;endosome membrane;external side of plasma membrane;high-density lipoprotein particle clearance;identical protein binding;intestinal cholesterol absorption;late endosome;lipid metabolic process;lipoprotein particle binding;long-term memory;low-density lipoprotein particle binding;low-density lipoprotein particle clearance;low-density lipoprotein particle receptor activity;lysosome;membrane;molecular adaptor activity;negative regulation of amyloid fibril formation;negative regulation of astrocyte activation;negative regulation of gene expression;negative regulation of low-density lipoprotein particle clearance;negative regulation of microglial cell activation;negative regulation of multicellular organismal process;negative regulation of protein metabolic process;negative regulation of receptor recycling;phagocytosis;phospholipid transport;plasma lipoprotein particle clearance;plasma membrane;positive regulation of gene expression;positive regulation of inflammatory response;positive regulation of lysosomal protein catabolic process;positive regulation of triglyceride biosynthetic process;protease binding;protein binding;receptor-mediated endocytosis;receptor-mediated endocytosis involved in cholesterol transport;regulation of cholesterol metabolic process;regulation of phosphatidylcholine catabolic process;regulation of protein metabolic process;response to caloric restriction;retinoid metabolic process;signaling receptor complex;somatodendritic compartment;sorting endosome;very-low-density lipoprotein particle receptor activity</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>GO:0004175;GO:0004190;GO:0004197;GO:0005515;GO:0008233;GO:0016787;GO:0070001</t>
+          <t>GO:0001523;GO:0001920;GO:0006629;GO:0006897;GO:0006898;GO:0006909;GO:0007616;GO:0010628;GO:0010629;GO:0010867;GO:0010899;GO:0010989;GO:0015914;GO:0030299;GO:0030301;GO:0034381;GO:0034383;GO:0034384;GO:0042632;GO:0048844;GO:0050729;GO:0051241;GO:0051246;GO:0051248;GO:0061771;GO:0061889;GO:0070508;GO:0071398;GO:0071404;GO:0090118;GO:0090181;GO:0097242;GO:0150094;GO:1903979;GO:1905167;GO:1905907</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>aspartic-type endopeptidase activity;aspartic-type peptidase activity;cysteine-type endopeptidase activity;endopeptidase activity;hydrolase activity;peptidase activity;protein binding</t>
+          <t>amyloid-beta clearance;amyloid-beta clearance by cellular catabolic process;artery morphogenesis;cellular response to fatty acid;cellular response to low-density lipoprotein particle stimulus;cholesterol homeostasis;cholesterol import;cholesterol transport;endocytosis;high-density lipoprotein particle clearance;intestinal cholesterol absorption;lipid metabolic process;long-term memory;low-density lipoprotein particle clearance;negative regulation of amyloid fibril formation;negative regulation of astrocyte activation;negative regulation of gene expression;negative regulation of low-density lipoprotein particle clearance;negative regulation of microglial cell activation;negative regulation of multicellular organismal process;negative regulation of protein metabolic process;negative regulation of receptor recycling;phagocytosis;phospholipid transport;plasma lipoprotein particle clearance;positive regulation of gene expression;positive regulation of inflammatory response;positive regulation of lysosomal protein catabolic process;positive regulation of triglyceride biosynthetic process;receptor-mediated endocytosis;receptor-mediated endocytosis involved in cholesterol transport;regulation of cholesterol metabolic process;regulation of phosphatidylcholine catabolic process;regulation of protein metabolic process;response to caloric restriction;retinoid metabolic process</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>GO:0005576;GO:0005615;GO:0005737;GO:0005764;GO:0005765;GO:0005829;GO:0010008;GO:0031012;GO:0031904;GO:0035580;GO:0042470;GO:0043202;GO:0045121;GO:0070062;GO:1904724;GO:1904813</t>
+          <t>GO:0001540;GO:0002020;GO:0005041;GO:0005509;GO:0005515;GO:0030169;GO:0030229;GO:0032050;GO:0042802;GO:0060090;GO:0071813</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>cytoplasm;cytosol;endosome lumen;endosome membrane;extracellular exosome;extracellular matrix;extracellular region;ficolin-1-rich granule lumen;lysosomal lumen;lysosomal membrane;lysosome;melanosome;membrane raft;obsolete extracellular space;specific granule lumen;tertiary granule lumen</t>
+          <t>amyloid-beta binding;calcium ion binding;clathrin heavy chain binding;identical protein binding;lipoprotein particle binding;low-density lipoprotein particle binding;low-density lipoprotein particle receptor activity;molecular adaptor activity;protease binding;protein binding;very-low-density lipoprotein particle receptor activity</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>GO:0005764;GO:0005768;GO:0005769;GO:0005770;GO:0005794;GO:0005886;GO:0005905;GO:0009897;GO:0009986;GO:0010008;GO:0016020;GO:0016323;GO:0030669;GO:0036020;GO:0036477;GO:0043235;GO:0045177;GO:0097443;GO:1990666</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Golgi apparatus;PCSK9-LDLR complex;apical part of cell;basolateral plasma membrane;cell surface;clathrin-coated endocytic vesicle membrane;clathrin-coated pit;early endosome;endolysosome membrane;endosome;endosome membrane;external side of plasma membrane;late endosome;lysosome;membrane;plasma membrane;signaling receptor complex;somatodendritic compartment;sorting endosome</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P07858</t>
+          <t>P01911</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1566,75 +1654,81 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CTSB</t>
+          <t>HLA-DRB1</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1508</v>
+        <v>3123</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>26</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>GO:0004175;GO:0004197;GO:0005515;GO:0005518;GO:0005576;GO:0005615;GO:0005764;GO:0006508;GO:0006590;GO:0008233;GO:0008234;GO:0009897;GO:0016324;GO:0030163;GO:0030574;GO:0030855;GO:0031012;GO:0036021;GO:0042470;GO:0042981;GO:0043394;GO:0046718;GO:0048471;GO:0070062;GO:0097067;GO:1904813</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>apical plasma membrane;cellular response to thyroid hormone stimulus;collagen binding;collagen catabolic process;cysteine-type endopeptidase activity;cysteine-type peptidase activity;endolysosome lumen;endopeptidase activity;epithelial cell differentiation;external side of plasma membrane;extracellular exosome;extracellular matrix;extracellular region;ficolin-1-rich granule lumen;lysosome;melanosome;obsolete extracellular space;peptidase activity;perinuclear region of cytoplasm;protein binding;protein catabolic process;proteoglycan binding;proteolysis;regulation of apoptotic process;symbiont entry into host cell;thyroid hormone generation</t>
-        </is>
+      <c r="M15" t="n">
+        <v>58</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>GO:0006508;GO:0006590;GO:0030163;GO:0030574;GO:0030855;GO:0042981;GO:0046718;GO:0097067</t>
+          <t>GO:0000139;GO:0001772;GO:0001916;GO:0002437;GO:0002469;GO:0002491;GO:0002503;GO:0002842;GO:0002862;GO:0005200;GO:0005515;GO:0005576;GO:0005765;GO:0005789;GO:0005882;GO:0005886;GO:0006955;GO:0006959;GO:0007010;GO:0007165;GO:0008544;GO:0009897;GO:0009986;GO:0012507;GO:0016020;GO:0016045;GO:0019882;GO:0019886;GO:0023026;GO:0030225;GO:0030247;GO:0030658;GO:0030666;GO:0030669;GO:0031902;GO:0032588;GO:0032653;GO:0032673;GO:0032689;GO:0032831;GO:0035774;GO:0042088;GO:0042130;GO:0042605;GO:0042608;GO:0042609;GO:0042613;GO:0043382;GO:0045622;GO:0045657;GO:0050778;GO:0050852;GO:0050870;GO:0051262;GO:0070062;GO:0098553;GO:0120281;GO:2000516</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>cellular response to thyroid hormone stimulus;collagen catabolic process;epithelial cell differentiation;protein catabolic process;proteolysis;regulation of apoptotic process;symbiont entry into host cell;thyroid hormone generation</t>
+          <t>CD4 receptor binding;ER to Golgi transport vesicle membrane;Golgi membrane;MHC class II protein complex;MHC class II protein complex binding;T cell receptor binding;T cell receptor signaling pathway;T-helper 1 type immune response;antigen processing and presentation;antigen processing and presentation of endogenous peptide antigen via MHC class II;antigen processing and presentation of exogenous peptide antigen via MHC class II;autolysosome membrane;cell surface;clathrin-coated endocytic vesicle membrane;cytoskeleton organization;detection of bacterium;endocytic vesicle membrane;endoplasmic reticulum membrane;epidermis development;external side of plasma membrane;extracellular exosome;extracellular region;humoral immune response;immune response;immunological synapse;inflammatory response to antigenic stimulus;intermediate filament;late endosome membrane;lumenal side of endoplasmic reticulum membrane;lysosomal membrane;macrophage differentiation;membrane;myeloid dendritic cell antigen processing and presentation;negative regulation of T cell proliferation;negative regulation of inflammatory response to antigenic stimulus;negative regulation of type II interferon production;peptide antigen assembly with MHC class II protein complex;peptide antigen binding;plasma membrane;polysaccharide binding;positive regulation of CD4-positive, CD25-positive, alpha-beta regulatory T cell differentiation;positive regulation of CD4-positive, alpha-beta T cell activation;positive regulation of T cell activation;positive regulation of T cell mediated cytotoxicity;positive regulation of T cell mediated immune response to tumor cell;positive regulation of immune response;positive regulation of insulin secretion involved in cellular response to glucose stimulus;positive regulation of memory T cell differentiation;positive regulation of monocyte differentiation;protein binding;protein tetramerization;regulation of T-helper cell differentiation;regulation of interleukin-10 production;regulation of interleukin-4 production;signal transduction;structural constituent of cytoskeleton;trans-Golgi network membrane;transport vesicle membrane</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>GO:0004175;GO:0004197;GO:0005515;GO:0005518;GO:0008233;GO:0008234;GO:0043394</t>
+          <t>GO:0001916;GO:0002437;GO:0002469;GO:0002491;GO:0002503;GO:0002842;GO:0002862;GO:0006955;GO:0006959;GO:0007010;GO:0007165;GO:0008544;GO:0016045;GO:0019882;GO:0019886;GO:0030225;GO:0032653;GO:0032673;GO:0032689;GO:0032831;GO:0035774;GO:0042088;GO:0042130;GO:0043382;GO:0045622;GO:0045657;GO:0050778;GO:0050852;GO:0050870;GO:0051262;GO:2000516</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>collagen binding;cysteine-type endopeptidase activity;cysteine-type peptidase activity;endopeptidase activity;peptidase activity;protein binding;proteoglycan binding</t>
+          <t>T cell receptor signaling pathway;T-helper 1 type immune response;antigen processing and presentation;antigen processing and presentation of endogenous peptide antigen via MHC class II;antigen processing and presentation of exogenous peptide antigen via MHC class II;cytoskeleton organization;detection of bacterium;epidermis development;humoral immune response;immune response;inflammatory response to antigenic stimulus;macrophage differentiation;myeloid dendritic cell antigen processing and presentation;negative regulation of T cell proliferation;negative regulation of inflammatory response to antigenic stimulus;negative regulation of type II interferon production;peptide antigen assembly with MHC class II protein complex;positive regulation of CD4-positive, CD25-positive, alpha-beta regulatory T cell differentiation;positive regulation of CD4-positive, alpha-beta T cell activation;positive regulation of T cell activation;positive regulation of T cell mediated cytotoxicity;positive regulation of T cell mediated immune response to tumor cell;positive regulation of immune response;positive regulation of insulin secretion involved in cellular response to glucose stimulus;positive regulation of memory T cell differentiation;positive regulation of monocyte differentiation;protein tetramerization;regulation of T-helper cell differentiation;regulation of interleukin-10 production;regulation of interleukin-4 production;signal transduction</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>GO:0005576;GO:0005615;GO:0005764;GO:0009897;GO:0016324;GO:0031012;GO:0036021;GO:0042470;GO:0048471;GO:0070062;GO:1904813</t>
+          <t>GO:0005200;GO:0005515;GO:0023026;GO:0030247;GO:0042605;GO:0042608;GO:0042609</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>apical plasma membrane;endolysosome lumen;external side of plasma membrane;extracellular exosome;extracellular matrix;extracellular region;ficolin-1-rich granule lumen;lysosome;melanosome;obsolete extracellular space;perinuclear region of cytoplasm</t>
+          <t>CD4 receptor binding;MHC class II protein complex binding;T cell receptor binding;peptide antigen binding;polysaccharide binding;protein binding;structural constituent of cytoskeleton</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>GO:0000139;GO:0001772;GO:0005576;GO:0005765;GO:0005789;GO:0005882;GO:0005886;GO:0009897;GO:0009986;GO:0012507;GO:0016020;GO:0030658;GO:0030666;GO:0030669;GO:0031902;GO:0032588;GO:0042613;GO:0070062;GO:0098553;GO:0120281</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>ER to Golgi transport vesicle membrane;Golgi membrane;MHC class II protein complex;autolysosome membrane;cell surface;clathrin-coated endocytic vesicle membrane;endocytic vesicle membrane;endoplasmic reticulum membrane;external side of plasma membrane;extracellular exosome;extracellular region;immunological synapse;intermediate filament;late endosome membrane;lumenal side of endoplasmic reticulum membrane;lysosomal membrane;membrane;plasma membrane;trans-Golgi network membrane;transport vesicle membrane</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P08172</t>
+          <t>P02741</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1645,75 +1739,81 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>bethanechol</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CHRM2</t>
+          <t>CRP</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1129</v>
+        <v>1401</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>25</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>GO:0004930;GO:0005515;GO:0005886;GO:0006940;GO:0007186;GO:0007187;GO:0007188;GO:0007193;GO:0007197;GO:0007207;GO:0007213;GO:0007268;GO:0007399;GO:0008016;GO:0009615;GO:0016020;GO:0016907;GO:0030425;GO:0030669;GO:0045202;GO:0045211;GO:0098793;GO:0098981;GO:0099171;GO:1990763</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor activity;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;adenylate cyclase-inhibiting G protein-coupled receptor signaling pathway;adenylate cyclase-modulating G protein-coupled receptor signaling pathway;arrestin family protein binding;chemical synaptic transmission;cholinergic synapse;clathrin-coated endocytic vesicle membrane;dendrite;membrane;nervous system development;phospholipase C-activating G protein-coupled acetylcholine receptor signaling pathway;plasma membrane;postsynaptic membrane;presynapse;presynaptic modulation of chemical synaptic transmission;protein binding;regulation of heart contraction;regulation of smooth muscle contraction;response to virus;synapse</t>
-        </is>
+      <c r="M16" t="n">
+        <v>21</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>GO:0006940;GO:0007186;GO:0007187;GO:0007188;GO:0007193;GO:0007197;GO:0007207;GO:0007213;GO:0007268;GO:0007399;GO:0008016;GO:0009615;GO:0099171</t>
+          <t>GO:0001849;GO:0005509;GO:0005515;GO:0005576;GO:0006953;GO:0006954;GO:0008228;GO:0010628;GO:0010745;GO:0010888;GO:0030169;GO:0032677;GO:0032930;GO:0032945;GO:0033265;GO:0042310;GO:0042802;GO:0045087;GO:0046790;GO:0050750;GO:0050830</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;adenylate cyclase-inhibiting G protein-coupled receptor signaling pathway;adenylate cyclase-modulating G protein-coupled receptor signaling pathway;chemical synaptic transmission;nervous system development;phospholipase C-activating G protein-coupled acetylcholine receptor signaling pathway;presynaptic modulation of chemical synaptic transmission;regulation of heart contraction;regulation of smooth muscle contraction;response to virus</t>
+          <t>acute-phase response;calcium ion binding;choline binding;complement component C1q complex binding;defense response to Gram-positive bacterium;extracellular region;identical protein binding;inflammatory response;innate immune response;low-density lipoprotein particle binding;low-density lipoprotein particle receptor binding;negative regulation of lipid storage;negative regulation of macrophage derived foam cell differentiation;negative regulation of mononuclear cell proliferation;opsonization;positive regulation of gene expression;positive regulation of superoxide anion generation;protein binding;regulation of interleukin-8 production;vasoconstriction;virion binding</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>GO:0004930;GO:0005515;GO:0016907;GO:1990763</t>
+          <t>GO:0006953;GO:0006954;GO:0008228;GO:0010628;GO:0010745;GO:0010888;GO:0032677;GO:0032930;GO:0032945;GO:0042310;GO:0045087;GO:0050830</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled receptor activity;arrestin family protein binding;protein binding</t>
+          <t>acute-phase response;defense response to Gram-positive bacterium;inflammatory response;innate immune response;negative regulation of lipid storage;negative regulation of macrophage derived foam cell differentiation;negative regulation of mononuclear cell proliferation;opsonization;positive regulation of gene expression;positive regulation of superoxide anion generation;regulation of interleukin-8 production;vasoconstriction</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>GO:0005886;GO:0016020;GO:0030425;GO:0030669;GO:0045202;GO:0045211;GO:0098793;GO:0098981</t>
+          <t>GO:0001849;GO:0005509;GO:0005515;GO:0030169;GO:0033265;GO:0042802;GO:0046790;GO:0050750</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>cholinergic synapse;clathrin-coated endocytic vesicle membrane;dendrite;membrane;plasma membrane;postsynaptic membrane;presynapse;synapse</t>
+          <t>calcium ion binding;choline binding;complement component C1q complex binding;identical protein binding;low-density lipoprotein particle binding;low-density lipoprotein particle receptor binding;protein binding;virion binding</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>GO:0005576</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>extracellular region</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P08173</t>
+          <t>P08183</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1724,75 +1824,81 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>bethanechol</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CHRM4</t>
+          <t>ABCB1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1132</v>
+        <v>5243</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>16</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>GO:0004930;GO:0005515;GO:0005886;GO:0007165;GO:0007166;GO:0007186;GO:0007187;GO:0007197;GO:0007213;GO:0007268;GO:0016020;GO:0016907;GO:0030425;GO:0040012;GO:0045202;GO:0045211</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor activity;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;cell surface receptor signaling pathway;chemical synaptic transmission;dendrite;membrane;plasma membrane;postsynaptic membrane;protein binding;regulation of locomotion;signal transduction;synapse</t>
-        </is>
+      <c r="M17" t="n">
+        <v>39</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>GO:0007165;GO:0007166;GO:0007186;GO:0007187;GO:0007197;GO:0007213;GO:0007268;GO:0040012</t>
+          <t>GO:0000086;GO:0005515;GO:0005524;GO:0005737;GO:0005886;GO:0006805;GO:0008559;GO:0009410;GO:0009986;GO:0015562;GO:0016020;GO:0016324;GO:0016887;GO:0022857;GO:0031625;GO:0042626;GO:0042910;GO:0045332;GO:0046865;GO:0046943;GO:0055085;GO:0070062;GO:0070633;GO:0072089;GO:0090554;GO:0090555;GO:0098591;GO:0099038;GO:0099040;GO:0140115;GO:0140326;GO:0140328;GO:0140341;GO:0140359;GO:0150104;GO:1905039;GO:1990961;GO:1990962;GO:2001225</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;cell surface receptor signaling pathway;chemical synaptic transmission;regulation of locomotion;signal transduction</t>
+          <t>ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled intramembrane lipid carrier activity;ATPase-coupled transmembrane transporter activity;G2/M transition of mitotic cell cycle;apical plasma membrane;carboxylic acid transmembrane transport;carboxylic acid transmembrane transporter activity;cell surface;ceramide floppase activity;ceramide translocation;cytoplasm;efflux transmembrane transporter activity;export across plasma membrane;external side of apical plasma membrane;extracellular exosome;floppase activity;membrane;phosphatidylcholine floppase activity;phosphatidylethanolamine flippase activity;phosphatidylethanolamine floppase activity;phospholipid translocation;plasma membrane;protein binding;regulation of chloride transport;response to xenobiotic stimulus;stem cell proliferation;terpenoid transport;transepithelial transport;transmembrane transport;transmembrane transporter activity;transport across blood-brain barrier;ubiquitin protein ligase binding;xenobiotic detoxification by transmembrane export across the plasma membrane;xenobiotic metabolic process;xenobiotic transmembrane transporter activity;xenobiotic transport across blood-brain barrier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>GO:0004930;GO:0005515;GO:0016907</t>
+          <t>GO:0000086;GO:0006805;GO:0009410;GO:0045332;GO:0046865;GO:0055085;GO:0070633;GO:0072089;GO:0099040;GO:0140115;GO:0150104;GO:1905039;GO:1990961;GO:1990962;GO:2001225</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled receptor activity;protein binding</t>
+          <t>G2/M transition of mitotic cell cycle;carboxylic acid transmembrane transport;ceramide translocation;export across plasma membrane;phospholipid translocation;regulation of chloride transport;response to xenobiotic stimulus;stem cell proliferation;terpenoid transport;transepithelial transport;transmembrane transport;transport across blood-brain barrier;xenobiotic detoxification by transmembrane export across the plasma membrane;xenobiotic metabolic process;xenobiotic transport across blood-brain barrier</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>GO:0005886;GO:0016020;GO:0030425;GO:0045202;GO:0045211</t>
+          <t>GO:0005515;GO:0005524;GO:0008559;GO:0015562;GO:0016887;GO:0022857;GO:0031625;GO:0042626;GO:0042910;GO:0046943;GO:0090554;GO:0090555;GO:0099038;GO:0140326;GO:0140328;GO:0140341;GO:0140359</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>dendrite;membrane;plasma membrane;postsynaptic membrane;synapse</t>
+          <t>ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled intramembrane lipid carrier activity;ATPase-coupled transmembrane transporter activity;carboxylic acid transmembrane transporter activity;ceramide floppase activity;efflux transmembrane transporter activity;floppase activity;phosphatidylcholine floppase activity;phosphatidylethanolamine flippase activity;phosphatidylethanolamine floppase activity;protein binding;transmembrane transporter activity;ubiquitin protein ligase binding;xenobiotic transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005886;GO:0009986;GO:0016020;GO:0016324;GO:0070062;GO:0098591</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>apical plasma membrane;cell surface;cytoplasm;external side of apical plasma membrane;extracellular exosome;membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P08482</t>
+          <t>P08519</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1803,75 +1909,81 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>bethanechol</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CHRM1</t>
+          <t>LPA</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>25229</v>
+        <v>4018</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>29</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>GO:0004930;GO:0005886;GO:0007186;GO:0007187;GO:0007197;GO:0007213;GO:0007268;GO:0007274;GO:0007603;GO:0009649;GO:0016020;GO:0016907;GO:0030425;GO:0032279;GO:0040012;GO:0042734;GO:0043270;GO:0043679;GO:0045202;GO:0045211;GO:0046541;GO:0050890;GO:0060078;GO:0090316;GO:0098685;GO:0098839;GO:0098978;GO:0098981;GO:0099170</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor activity;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;Schaffer collateral - CA1 synapse;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;asymmetric synapse;axon terminus;chemical synaptic transmission;cholinergic synapse;cognition;dendrite;entrainment of circadian clock;glutamatergic synapse;membrane;neuromuscular synaptic transmission;phototransduction, visible light;plasma membrane;positive regulation of intracellular protein transport;positive regulation of monoatomic ion transport;postsynaptic density membrane;postsynaptic membrane;postsynaptic modulation of chemical synaptic transmission;presynaptic membrane;regulation of locomotion;regulation of postsynaptic membrane potential;saliva secretion;synapse</t>
-        </is>
+      <c r="M18" t="n">
+        <v>11</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>GO:0007186;GO:0007187;GO:0007197;GO:0007213;GO:0007268;GO:0007274;GO:0007603;GO:0009649;GO:0040012;GO:0043270;GO:0046541;GO:0050890;GO:0060078;GO:0090316;GO:0099170</t>
+          <t>GO:0001968;GO:0004252;GO:0004866;GO:0005515;GO:0005576;GO:0006508;GO:0006629;GO:0008015;GO:0008201;GO:0034185;GO:0034358</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;chemical synaptic transmission;cognition;entrainment of circadian clock;neuromuscular synaptic transmission;phototransduction, visible light;positive regulation of intracellular protein transport;positive regulation of monoatomic ion transport;postsynaptic modulation of chemical synaptic transmission;regulation of locomotion;regulation of postsynaptic membrane potential;saliva secretion</t>
+          <t>apolipoprotein binding;blood circulation;endopeptidase inhibitor activity;extracellular region;fibronectin binding;heparin binding;lipid metabolic process;plasma lipoprotein particle;protein binding;proteolysis;serine-type endopeptidase activity</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>GO:0004930;GO:0016907</t>
+          <t>GO:0006508;GO:0006629;GO:0008015</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled receptor activity</t>
+          <t>blood circulation;lipid metabolic process;proteolysis</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>GO:0005886;GO:0016020;GO:0030425;GO:0032279;GO:0042734;GO:0043679;GO:0045202;GO:0045211;GO:0098685;GO:0098839;GO:0098978;GO:0098981</t>
+          <t>GO:0001968;GO:0004252;GO:0004866;GO:0005515;GO:0008201;GO:0034185</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Schaffer collateral - CA1 synapse;asymmetric synapse;axon terminus;cholinergic synapse;dendrite;glutamatergic synapse;membrane;plasma membrane;postsynaptic density membrane;postsynaptic membrane;presynaptic membrane;synapse</t>
+          <t>apolipoprotein binding;endopeptidase inhibitor activity;fibronectin binding;heparin binding;protein binding;serine-type endopeptidase activity</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>GO:0005576;GO:0034358</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>extracellular region;plasma lipoprotein particle</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P08912</t>
+          <t>P10635</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1882,75 +1994,81 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>bethanechol</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CHRM5</t>
+          <t>CYP2D6</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1133</v>
+        <v>1565</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>17</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>GO:0001696;GO:0004435;GO:0004930;GO:0005515;GO:0005886;GO:0007186;GO:0007187;GO:0007197;GO:0007213;GO:0007268;GO:0016020;GO:0016907;GO:0030425;GO:0045202;GO:0045211;GO:0060304;GO:0095500</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor activity;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;acetylcholine receptor signaling pathway;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;chemical synaptic transmission;dendrite;gastric acid secretion;membrane;phosphatidylinositol-4,5-bisphosphate phospholipase C activity;plasma membrane;postsynaptic membrane;protein binding;regulation of phosphatidylinositol dephosphorylation;synapse</t>
-        </is>
+      <c r="M19" t="n">
+        <v>32</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>GO:0001696;GO:0007186;GO:0007187;GO:0007197;GO:0007213;GO:0007268;GO:0060304;GO:0095500</t>
+          <t>GO:0004497;GO:0005506;GO:0005737;GO:0005739;GO:0005783;GO:0005789;GO:0006631;GO:0006805;GO:0008202;GO:0008203;GO:0008210;GO:0008404;GO:0008405;GO:0009804;GO:0009820;GO:0009822;GO:0016098;GO:0016491;GO:0016705;GO:0016712;GO:0019369;GO:0020037;GO:0033076;GO:0042178;GO:0042572;GO:0042759;GO:0062187;GO:0062188;GO:0062189;GO:0070989;GO:0090350;GO:0106302</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;acetylcholine receptor signaling pathway;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;chemical synaptic transmission;gastric acid secretion;regulation of phosphatidylinositol dephosphorylation</t>
+          <t>alkaloid catabolic process;alkaloid metabolic process;anandamide 11,12 epoxidase activity;anandamide 14,15 epoxidase activity;anandamide 8,9 epoxidase activity;arachidonate 11,12-epoxygenase activity;arachidonate 14,15-epoxygenase activity;arachidonate 8,9-epoxygenase activity;arachidonate metabolic process;cholesterol metabolic process;coumarin metabolic process;cytoplasm;endoplasmic reticulum;endoplasmic reticulum membrane;estrogen metabolic process;fatty acid metabolic process;heme binding;iron ion binding;isoquinoline alkaloid metabolic process;long-chain fatty acid biosynthetic process;mitochondrion;monooxygenase activity;monoterpenoid metabolic process;negative regulation of organofluorine metabolic process;oxidative demethylation;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;retinol metabolic process;steroid metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>GO:0004435;GO:0004930;GO:0005515;GO:0016907</t>
+          <t>GO:0006631;GO:0006805;GO:0008202;GO:0008203;GO:0008210;GO:0009804;GO:0009820;GO:0009822;GO:0016098;GO:0019369;GO:0033076;GO:0042178;GO:0042572;GO:0042759;GO:0070989;GO:0090350</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled receptor activity;phosphatidylinositol-4,5-bisphosphate phospholipase C activity;protein binding</t>
+          <t>alkaloid catabolic process;alkaloid metabolic process;arachidonate metabolic process;cholesterol metabolic process;coumarin metabolic process;estrogen metabolic process;fatty acid metabolic process;isoquinoline alkaloid metabolic process;long-chain fatty acid biosynthetic process;monoterpenoid metabolic process;negative regulation of organofluorine metabolic process;oxidative demethylation;retinol metabolic process;steroid metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>GO:0005886;GO:0016020;GO:0030425;GO:0045202;GO:0045211</t>
+          <t>GO:0004497;GO:0005506;GO:0008404;GO:0008405;GO:0016491;GO:0016705;GO:0016712;GO:0020037;GO:0062187;GO:0062188;GO:0062189;GO:0106302</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>dendrite;membrane;plasma membrane;postsynaptic membrane;synapse</t>
+          <t>anandamide 11,12 epoxidase activity;anandamide 14,15 epoxidase activity;anandamide 8,9 epoxidase activity;arachidonate 11,12-epoxygenase activity;arachidonate 14,15-epoxygenase activity;arachidonate 8,9-epoxygenase activity;heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005739;GO:0005783;GO:0005789</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>cytoplasm;endoplasmic reticulum;endoplasmic reticulum membrane;mitochondrion</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P09601</t>
+          <t>P11597</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1961,75 +2079,81 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HMOX1</t>
+          <t>CETP</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3162</v>
+        <v>1071</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>45</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>GO:0001525;GO:0001935;GO:0002246;GO:0002686;GO:0004392;GO:0005198;GO:0005515;GO:0005615;GO:0005634;GO:0005654;GO:0005741;GO:0005783;GO:0005789;GO:0005829;GO:0005886;GO:0006357;GO:0006788;GO:0006879;GO:0006979;GO:0014806;GO:0016020;GO:0019899;GO:0020037;GO:0032722;GO:0034101;GO:0034383;GO:0034605;GO:0035094;GO:0035556;GO:0042167;GO:0042542;GO:0042802;GO:0042803;GO:0043123;GO:0045765;GO:0045766;GO:0048471;GO:0048661;GO:0048662;GO:0060586;GO:0090050;GO:0110076;GO:1900016;GO:1902042;GO:1903589</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>angiogenesis;cellular response to heat;cytosol;endoplasmic reticulum;endoplasmic reticulum membrane;endothelial cell proliferation;enzyme binding;erythrocyte homeostasis;heme binding;heme catabolic process;heme oxidation;heme oxygenase (decyclizing) activity;identical protein binding;intracellular iron ion homeostasis;intracellular signal transduction;low-density lipoprotein particle clearance;membrane;mitochondrial outer membrane;multicellular organismal-level iron ion homeostasis;negative regulation of cytokine production involved in inflammatory response;negative regulation of extrinsic apoptotic signaling pathway via death domain receptors;negative regulation of ferroptosis;negative regulation of leukocyte migration;negative regulation of smooth muscle cell proliferation;nucleoplasm;nucleus;obsolete extracellular space;perinuclear region of cytoplasm;plasma membrane;positive regulation of angiogenesis;positive regulation of blood vessel endothelial cell proliferation involved in sprouting angiogenesis;positive regulation of canonical NF-kappaB signal transduction;positive regulation of cell migration involved in sprouting angiogenesis;positive regulation of chemokine production;positive regulation of smooth muscle cell proliferation;protein binding;protein homodimerization activity;regulation of angiogenesis;regulation of transcription by RNA polymerase II;response to hydrogen peroxide;response to nicotine;response to oxidative stress;smooth muscle hyperplasia;structural molecule activity;wound healing involved in inflammatory response</t>
-        </is>
+      <c r="M20" t="n">
+        <v>29</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>GO:0001525;GO:0001935;GO:0002246;GO:0002686;GO:0006357;GO:0006788;GO:0006879;GO:0006979;GO:0014806;GO:0032722;GO:0034101;GO:0034383;GO:0034605;GO:0035094;GO:0035556;GO:0042167;GO:0042542;GO:0043123;GO:0045765;GO:0045766;GO:0048661;GO:0048662;GO:0060586;GO:0090050;GO:0110076;GO:1900016;GO:1902042;GO:1903589</t>
+          <t>GO:0005576;GO:0006641;GO:0006869;GO:0008203;GO:0008289;GO:0010745;GO:0010874;GO:0015485;GO:0015914;GO:0017129;GO:0030301;GO:0031210;GO:0031982;GO:0032376;GO:0034197;GO:0034364;GO:0034372;GO:0034374;GO:0034375;GO:0042632;GO:0043691;GO:0046470;GO:0055088;GO:0055091;GO:0070062;GO:0070328;GO:0120014;GO:0120020;GO:2001140</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>angiogenesis;cellular response to heat;endothelial cell proliferation;erythrocyte homeostasis;heme catabolic process;heme oxidation;intracellular iron ion homeostasis;intracellular signal transduction;low-density lipoprotein particle clearance;multicellular organismal-level iron ion homeostasis;negative regulation of cytokine production involved in inflammatory response;negative regulation of extrinsic apoptotic signaling pathway via death domain receptors;negative regulation of ferroptosis;negative regulation of leukocyte migration;negative regulation of smooth muscle cell proliferation;positive regulation of angiogenesis;positive regulation of blood vessel endothelial cell proliferation involved in sprouting angiogenesis;positive regulation of canonical NF-kappaB signal transduction;positive regulation of cell migration involved in sprouting angiogenesis;positive regulation of chemokine production;positive regulation of smooth muscle cell proliferation;regulation of angiogenesis;regulation of transcription by RNA polymerase II;response to hydrogen peroxide;response to nicotine;response to oxidative stress;smooth muscle hyperplasia;wound healing involved in inflammatory response</t>
+          <t>cholesterol binding;cholesterol homeostasis;cholesterol metabolic process;cholesterol transfer activity;cholesterol transport;extracellular exosome;extracellular region;high-density lipoprotein particle;high-density lipoprotein particle remodeling;lipid binding;lipid homeostasis;lipid transport;low-density lipoprotein particle remodeling;negative regulation of macrophage derived foam cell differentiation;phosphatidylcholine binding;phosphatidylcholine metabolic process;phospholipid homeostasis;phospholipid transfer activity;phospholipid transport;positive regulation of cholesterol transport;positive regulation of phospholipid transport;regulation of cholesterol efflux;reverse cholesterol transport;triglyceride binding;triglyceride homeostasis;triglyceride metabolic process;triglyceride transport;very-low-density lipoprotein particle remodeling;vesicle</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>GO:0004392;GO:0005198;GO:0005515;GO:0019899;GO:0020037;GO:0042802;GO:0042803</t>
+          <t>GO:0006641;GO:0006869;GO:0008203;GO:0010745;GO:0010874;GO:0015914;GO:0030301;GO:0032376;GO:0034197;GO:0034372;GO:0034374;GO:0034375;GO:0042632;GO:0043691;GO:0046470;GO:0055088;GO:0055091;GO:0070328;GO:2001140</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>enzyme binding;heme binding;heme oxygenase (decyclizing) activity;identical protein binding;protein binding;protein homodimerization activity;structural molecule activity</t>
+          <t>cholesterol homeostasis;cholesterol metabolic process;cholesterol transport;high-density lipoprotein particle remodeling;lipid homeostasis;lipid transport;low-density lipoprotein particle remodeling;negative regulation of macrophage derived foam cell differentiation;phosphatidylcholine metabolic process;phospholipid homeostasis;phospholipid transport;positive regulation of cholesterol transport;positive regulation of phospholipid transport;regulation of cholesterol efflux;reverse cholesterol transport;triglyceride homeostasis;triglyceride metabolic process;triglyceride transport;very-low-density lipoprotein particle remodeling</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>GO:0005615;GO:0005634;GO:0005654;GO:0005741;GO:0005783;GO:0005789;GO:0005829;GO:0005886;GO:0016020;GO:0048471</t>
+          <t>GO:0008289;GO:0015485;GO:0017129;GO:0031210;GO:0120014;GO:0120020</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>cytosol;endoplasmic reticulum;endoplasmic reticulum membrane;membrane;mitochondrial outer membrane;nucleoplasm;nucleus;obsolete extracellular space;perinuclear region of cytoplasm;plasma membrane</t>
+          <t>cholesterol binding;cholesterol transfer activity;lipid binding;phosphatidylcholine binding;phospholipid transfer activity;triglyceride binding</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>GO:0005576;GO:0031982;GO:0034364;GO:0070062</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>extracellular exosome;extracellular region;high-density lipoprotein particle;vesicle</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P11137</t>
+          <t>P19793</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2040,75 +2164,81 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MAP2</t>
+          <t>RXRA</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4133</v>
+        <v>6256</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>48</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>GO:0000226;GO:0002162;GO:0005198;GO:0005515;GO:0005737;GO:0005829;GO:0005856;GO:0005875;GO:0008017;GO:0014069;GO:0015630;GO:0015631;GO:0016358;GO:0021954;GO:0030424;GO:0030425;GO:0030517;GO:0031113;GO:0031115;GO:0031175;GO:0032839;GO:0032880;GO:0034399;GO:0043005;GO:0043025;GO:0043194;GO:0043198;GO:0043203;GO:0044294;GO:0044297;GO:0044304;GO:0044307;GO:0048156;GO:0048813;GO:0060632;GO:0097440;GO:0097441;GO:0097442;GO:0140778;GO:0150001;GO:0150002;GO:0150014;GO:1901953;GO:1902513;GO:1902737;GO:1903744;GO:1990635;GO:1990769</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>CA3 pyramidal cell dendrite;apical dendrite;apical distal dendrite;axon;axon hillock;axon initial segment;basal dendrite;cell body;central nervous system neuron development;cytoplasm;cytoskeleton;cytosol;dendrite;dendrite cytoplasm;dendrite development;dendrite morphogenesis;dendritic branch;dendritic filopodium;dendritic growth cone;dendritic shaft;distal dendrite;dystroglycan binding;main axon;microtubule associated complex;microtubule binding;microtubule cytoskeleton;microtubule cytoskeleton organization;microtubule stabilizing activity;negative regulation of axon extension;negative regulation of microtubule polymerization;neuron projection;neuron projection development;neuronal cell body;nuclear periphery;positive regulation of anterograde dense core granule transport;positive regulation of anterograde synaptic vesicle transport;postsynaptic density;primary dendrite;protein binding;proximal dendrite;proximal neuron projection;regulation of microtubule polymerization;regulation of microtubule-based movement;regulation of organelle transport along microtubule;regulation of protein localization;structural molecule activity;tau protein binding;tubulin binding</t>
-        </is>
+      <c r="M21" t="n">
+        <v>59</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>GO:0000226;GO:0016358;GO:0021954;GO:0030517;GO:0031113;GO:0031115;GO:0031175;GO:0032880;GO:0048813;GO:0060632;GO:1901953;GO:1902513;GO:1903744</t>
+          <t>GO:0000122;GO:0000785;GO:0000976;GO:0000977;GO:0000978;GO:0000981;GO:0001162;GO:0001221;GO:0001223;GO:0001972;GO:0002157;GO:0003677;GO:0003690;GO:0003700;GO:0003707;GO:0003712;GO:0004879;GO:0005515;GO:0005634;GO:0005654;GO:0005737;GO:0005739;GO:0005829;GO:0006355;GO:0007399;GO:0008270;GO:0009755;GO:0010467;GO:0010875;GO:0015721;GO:0019216;GO:0019899;GO:0030154;GO:0030224;GO:0030501;GO:0030518;GO:0031490;GO:0032526;GO:0035357;GO:0042277;GO:0042789;GO:0042802;GO:0042809;GO:0043235;GO:0043565;GO:0044323;GO:0045834;GO:0045893;GO:0045944;GO:0048384;GO:0048469;GO:0050692;GO:0050693;GO:0070564;GO:0070644;GO:0071404;GO:0090575;GO:0140077;GO:1990837</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>central nervous system neuron development;dendrite development;dendrite morphogenesis;microtubule cytoskeleton organization;negative regulation of axon extension;negative regulation of microtubule polymerization;neuron projection development;positive regulation of anterograde dense core granule transport;positive regulation of anterograde synaptic vesicle transport;regulation of microtubule polymerization;regulation of microtubule-based movement;regulation of organelle transport along microtubule;regulation of protein localization</t>
+          <t>DNA binding;DNA binding domain binding;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;LBD domain binding;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II intronic transcription regulatory region sequence-specific DNA binding;RNA polymerase II transcription regulator complex;RNA polymerase II transcription regulatory region sequence-specific DNA binding;bile acid and bile salt transport;cell differentiation;cell maturation;cellular response to low-density lipoprotein particle stimulus;chromatin;chromatin DNA binding;cytoplasm;cytosol;double-stranded DNA binding;enzyme binding;gene expression;hormone-mediated signaling pathway;identical protein binding;mRNA transcription by RNA polymerase II;mitochondrion;monocyte differentiation;negative regulation of transcription by RNA polymerase II;nervous system development;nuclear receptor activity;nuclear receptor-mediated steroid hormone signaling pathway;nuclear steroid receptor activity;nuclear vitamin D receptor binding;nucleoplasm;nucleus;peptide binding;peroxisome proliferator activated receptor signaling pathway;positive regulation of DNA-templated transcription;positive regulation of bone mineralization;positive regulation of cholesterol efflux;positive regulation of lipid metabolic process;positive regulation of lipoprotein transport;positive regulation of thyroid hormone receptor signaling pathway;positive regulation of transcription by RNA polymerase II;positive regulation of vitamin D receptor signaling pathway;protein binding;regulation of DNA-templated transcription;regulation of lipid metabolic process;response to retinoic acid;retinoic acid binding;retinoic acid receptor signaling pathway;retinoic acid-responsive element binding;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;signaling receptor complex;transcription cis-regulatory region binding;transcription coactivator binding;transcription coregulator activity;transcription coregulator binding;vitamin D response element binding;zinc ion binding</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>GO:0002162;GO:0005198;GO:0005515;GO:0008017;GO:0015631;GO:0048156;GO:0140778</t>
+          <t>GO:0000122;GO:0002157;GO:0006355;GO:0007399;GO:0009755;GO:0010467;GO:0010875;GO:0015721;GO:0019216;GO:0030154;GO:0030224;GO:0030501;GO:0030518;GO:0032526;GO:0035357;GO:0042789;GO:0045834;GO:0045893;GO:0045944;GO:0048384;GO:0048469;GO:0070564;GO:0071404;GO:0140077</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>dystroglycan binding;microtubule binding;microtubule stabilizing activity;protein binding;structural molecule activity;tau protein binding;tubulin binding</t>
+          <t>bile acid and bile salt transport;cell differentiation;cell maturation;cellular response to low-density lipoprotein particle stimulus;gene expression;hormone-mediated signaling pathway;mRNA transcription by RNA polymerase II;monocyte differentiation;negative regulation of transcription by RNA polymerase II;nervous system development;nuclear receptor-mediated steroid hormone signaling pathway;peroxisome proliferator activated receptor signaling pathway;positive regulation of DNA-templated transcription;positive regulation of bone mineralization;positive regulation of cholesterol efflux;positive regulation of lipid metabolic process;positive regulation of lipoprotein transport;positive regulation of thyroid hormone receptor signaling pathway;positive regulation of transcription by RNA polymerase II;positive regulation of vitamin D receptor signaling pathway;regulation of DNA-templated transcription;regulation of lipid metabolic process;response to retinoic acid;retinoic acid receptor signaling pathway</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>GO:0005737;GO:0005829;GO:0005856;GO:0005875;GO:0014069;GO:0015630;GO:0030424;GO:0030425;GO:0032839;GO:0034399;GO:0043005;GO:0043025;GO:0043194;GO:0043198;GO:0043203;GO:0044294;GO:0044297;GO:0044304;GO:0044307;GO:0097440;GO:0097441;GO:0097442;GO:0150001;GO:0150002;GO:0150014;GO:1902737;GO:1990635;GO:1990769</t>
+          <t>GO:0000976;GO:0000977;GO:0000978;GO:0000981;GO:0001162;GO:0001221;GO:0001223;GO:0001972;GO:0003677;GO:0003690;GO:0003700;GO:0003707;GO:0003712;GO:0004879;GO:0005515;GO:0008270;GO:0019899;GO:0031490;GO:0042277;GO:0042802;GO:0042809;GO:0043565;GO:0044323;GO:0050692;GO:0050693;GO:0070644;GO:1990837</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CA3 pyramidal cell dendrite;apical dendrite;apical distal dendrite;axon;axon hillock;axon initial segment;basal dendrite;cell body;cytoplasm;cytoskeleton;cytosol;dendrite;dendrite cytoplasm;dendritic branch;dendritic filopodium;dendritic growth cone;dendritic shaft;distal dendrite;main axon;microtubule associated complex;microtubule cytoskeleton;neuron projection;neuronal cell body;nuclear periphery;postsynaptic density;primary dendrite;proximal dendrite;proximal neuron projection</t>
+          <t>DNA binding;DNA binding domain binding;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;LBD domain binding;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II intronic transcription regulatory region sequence-specific DNA binding;RNA polymerase II transcription regulatory region sequence-specific DNA binding;chromatin DNA binding;double-stranded DNA binding;enzyme binding;identical protein binding;nuclear receptor activity;nuclear steroid receptor activity;nuclear vitamin D receptor binding;peptide binding;protein binding;retinoic acid binding;retinoic acid-responsive element binding;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;transcription cis-regulatory region binding;transcription coactivator binding;transcription coregulator activity;transcription coregulator binding;vitamin D response element binding;zinc ion binding</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>GO:0000785;GO:0005634;GO:0005654;GO:0005737;GO:0005739;GO:0005829;GO:0043235;GO:0090575</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>RNA polymerase II transcription regulator complex;chromatin;cytoplasm;cytosol;mitochondrion;nucleoplasm;nucleus;signaling receptor complex</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P11215</t>
+          <t>P20701</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2119,75 +2249,81 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ITGAM</t>
+          <t>ITGAL</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>47</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>GO:0001540;GO:0001774;GO:0001851;GO:0001975;GO:0002430;GO:0002931;GO:0004895;GO:0005178;GO:0005515;GO:0005615;GO:0005886;GO:0006898;GO:0006911;GO:0007155;GO:0007160;GO:0007229;GO:0008305;GO:0009612;GO:0009897;GO:0009986;GO:0010668;GO:0030900;GO:0031072;GO:0032355;GO:0032930;GO:0033631;GO:0034113;GO:0034688;GO:0035579;GO:0038023;GO:0038024;GO:0043315;GO:0044853;GO:0044877;GO:0045121;GO:0045963;GO:0061756;GO:0070062;GO:0070821;GO:0090314;GO:0097242;GO:0098609;GO:0140459;GO:0150062;GO:0150064;GO:1904151;GO:1904643</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>amyloid-beta binding;amyloid-beta clearance;cargo receptor activity;cell adhesion;cell adhesion receptor activity;cell surface;cell-cell adhesion;cell-cell adhesion mediated by integrin;cell-matrix adhesion;complement component C3b binding;complement receptor mediated signaling pathway;complement-mediated synapse pruning;ectodermal cell differentiation;external side of plasma membrane;extracellular exosome;forebrain development;heat shock protein binding;heterotypic cell-cell adhesion;integrin alphaM-beta2 complex;integrin binding;integrin complex;integrin-mediated signaling pathway;leukocyte adhesion to vascular endothelial cell;membrane raft;microglial cell activation;negative regulation of dopamine metabolic process;obsolete extracellular space;phagocytosis, engulfment;plasma membrane;plasma membrane raft;positive regulation of microglial cell mediated cytotoxicity;positive regulation of neutrophil degranulation;positive regulation of protein targeting to membrane;positive regulation of superoxide anion generation;protein binding;protein-containing complex binding;receptor-mediated endocytosis;response to Gram-positive bacterium;response to amphetamine;response to curcumin;response to estradiol;response to ischemia;response to mechanical stimulus;signaling receptor activity;specific granule membrane;tertiary granule membrane;vertebrate eye-specific patterning</t>
-        </is>
+      <c r="M22" t="n">
+        <v>33</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GO:0001774;GO:0001975;GO:0002430;GO:0002931;GO:0006898;GO:0006911;GO:0007155;GO:0007160;GO:0007229;GO:0009612;GO:0010668;GO:0030900;GO:0032355;GO:0032930;GO:0033631;GO:0034113;GO:0043315;GO:0045963;GO:0061756;GO:0090314;GO:0097242;GO:0098609;GO:0140459;GO:0150062;GO:0150064;GO:1904151;GO:1904643</t>
+          <t>GO:0001772;GO:0002291;GO:0004895;GO:0005515;GO:0005886;GO:0005911;GO:0006954;GO:0007155;GO:0007157;GO:0007158;GO:0007159;GO:0007160;GO:0007165;GO:0007229;GO:0008305;GO:0009897;GO:0009986;GO:0016020;GO:0030369;GO:0030667;GO:0033627;GO:0033631;GO:0034687;GO:0035579;GO:0035683;GO:0038023;GO:0042110;GO:0043113;GO:0044877;GO:0045121;GO:0050839;GO:0070062;GO:0098609</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>amyloid-beta clearance;cell adhesion;cell-cell adhesion;cell-cell adhesion mediated by integrin;cell-matrix adhesion;complement receptor mediated signaling pathway;complement-mediated synapse pruning;ectodermal cell differentiation;forebrain development;heterotypic cell-cell adhesion;integrin-mediated signaling pathway;leukocyte adhesion to vascular endothelial cell;microglial cell activation;negative regulation of dopamine metabolic process;phagocytosis, engulfment;positive regulation of microglial cell mediated cytotoxicity;positive regulation of neutrophil degranulation;positive regulation of protein targeting to membrane;positive regulation of superoxide anion generation;receptor-mediated endocytosis;response to Gram-positive bacterium;response to amphetamine;response to curcumin;response to estradiol;response to ischemia;response to mechanical stimulus;vertebrate eye-specific patterning</t>
+          <t>ICAM-3 receptor activity;T cell activation;T cell activation via T cell receptor contact with antigen bound to MHC molecule on antigen presenting cell;cell adhesion;cell adhesion mediated by integrin;cell adhesion molecule binding;cell adhesion receptor activity;cell surface;cell-cell adhesion;cell-cell adhesion mediated by integrin;cell-cell junction;cell-matrix adhesion;external side of plasma membrane;extracellular exosome;heterophilic cell-cell adhesion;immunological synapse;inflammatory response;integrin alphaL-beta2 complex;integrin complex;integrin-mediated signaling pathway;leukocyte cell-cell adhesion;membrane;membrane raft;memory T cell extravasation;neuron cell-cell adhesion;plasma membrane;protein binding;protein-containing complex binding;receptor clustering;secretory granule membrane;signal transduction;signaling receptor activity;specific granule membrane</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>GO:0001540;GO:0001851;GO:0004895;GO:0005178;GO:0005515;GO:0031072;GO:0038023;GO:0038024;GO:0044877</t>
+          <t>GO:0002291;GO:0006954;GO:0007155;GO:0007157;GO:0007158;GO:0007159;GO:0007160;GO:0007165;GO:0007229;GO:0033627;GO:0033631;GO:0035683;GO:0042110;GO:0043113;GO:0098609</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>amyloid-beta binding;cargo receptor activity;cell adhesion receptor activity;complement component C3b binding;heat shock protein binding;integrin binding;protein binding;protein-containing complex binding;signaling receptor activity</t>
+          <t>T cell activation;T cell activation via T cell receptor contact with antigen bound to MHC molecule on antigen presenting cell;cell adhesion;cell adhesion mediated by integrin;cell-cell adhesion;cell-cell adhesion mediated by integrin;cell-matrix adhesion;heterophilic cell-cell adhesion;inflammatory response;integrin-mediated signaling pathway;leukocyte cell-cell adhesion;memory T cell extravasation;neuron cell-cell adhesion;receptor clustering;signal transduction</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>GO:0005615;GO:0005886;GO:0008305;GO:0009897;GO:0009986;GO:0034688;GO:0035579;GO:0044853;GO:0045121;GO:0070062;GO:0070821</t>
+          <t>GO:0004895;GO:0005515;GO:0030369;GO:0038023;GO:0044877;GO:0050839</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>cell surface;external side of plasma membrane;extracellular exosome;integrin alphaM-beta2 complex;integrin complex;membrane raft;obsolete extracellular space;plasma membrane;plasma membrane raft;specific granule membrane;tertiary granule membrane</t>
+          <t>ICAM-3 receptor activity;cell adhesion molecule binding;cell adhesion receptor activity;protein binding;protein-containing complex binding;signaling receptor activity</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>GO:0001772;GO:0005886;GO:0005911;GO:0008305;GO:0009897;GO:0009986;GO:0016020;GO:0030667;GO:0034687;GO:0035579;GO:0045121;GO:0070062</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>cell surface;cell-cell junction;external side of plasma membrane;extracellular exosome;immunological synapse;integrin alphaL-beta2 complex;integrin complex;membrane;membrane raft;plasma membrane;secretory granule membrane;specific granule membrane</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P11229</t>
+          <t>P20813</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2198,75 +2334,81 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>bethanechol</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CHRM1</t>
+          <t>CYP2B6</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1128</v>
+        <v>1555</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>35</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>GO:0004435;GO:0004930;GO:0005515;GO:0005886;GO:0007165;GO:0007186;GO:0007187;GO:0007197;GO:0007200;GO:0007207;GO:0007213;GO:0007268;GO:0007274;GO:0007399;GO:0016020;GO:0016907;GO:0030425;GO:0032279;GO:0040012;GO:0042734;GO:0043270;GO:0043679;GO:0045202;GO:0045211;GO:0046541;GO:0050890;GO:0060078;GO:0060251;GO:0090316;GO:0095500;GO:0098685;GO:0098839;GO:0098978;GO:0098981;GO:0099170</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor activity;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;Schaffer collateral - CA1 synapse;acetylcholine receptor signaling pathway;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;asymmetric synapse;axon terminus;chemical synaptic transmission;cholinergic synapse;cognition;dendrite;glutamatergic synapse;membrane;nervous system development;neuromuscular synaptic transmission;phosphatidylinositol-4,5-bisphosphate phospholipase C activity;phospholipase C-activating G protein-coupled acetylcholine receptor signaling pathway;phospholipase C-activating G protein-coupled receptor signaling pathway;plasma membrane;positive regulation of intracellular protein transport;positive regulation of monoatomic ion transport;postsynaptic density membrane;postsynaptic membrane;postsynaptic modulation of chemical synaptic transmission;presynaptic membrane;protein binding;regulation of glial cell proliferation;regulation of locomotion;regulation of postsynaptic membrane potential;saliva secretion;signal transduction;synapse</t>
-        </is>
+      <c r="M23" t="n">
+        <v>19</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>GO:0007165;GO:0007186;GO:0007187;GO:0007197;GO:0007200;GO:0007207;GO:0007213;GO:0007268;GO:0007274;GO:0007399;GO:0040012;GO:0043270;GO:0046541;GO:0050890;GO:0060078;GO:0060251;GO:0090316;GO:0095500;GO:0099170</t>
+          <t>GO:0004497;GO:0005506;GO:0005737;GO:0005789;GO:0006805;GO:0008202;GO:0008390;GO:0008392;GO:0016705;GO:0016712;GO:0019373;GO:0020037;GO:0042178;GO:0042180;GO:0062184;GO:0062187;GO:0062188;GO:0062189;GO:0101021</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor signaling pathway;G protein-coupled receptor signaling pathway;G protein-coupled receptor signaling pathway, coupled to cyclic nucleotide second messenger;acetylcholine receptor signaling pathway;adenylate cyclase-inhibiting G protein-coupled acetylcholine receptor signaling pathway;chemical synaptic transmission;cognition;nervous system development;neuromuscular synaptic transmission;phospholipase C-activating G protein-coupled acetylcholine receptor signaling pathway;phospholipase C-activating G protein-coupled receptor signaling pathway;positive regulation of intracellular protein transport;positive regulation of monoatomic ion transport;postsynaptic modulation of chemical synaptic transmission;regulation of glial cell proliferation;regulation of locomotion;regulation of postsynaptic membrane potential;saliva secretion;signal transduction</t>
+          <t>anandamide 11,12 epoxidase activity;anandamide 14,15 epoxidase activity;anandamide 8,9 epoxidase activity;arachidonate epoxygenase activity;cytoplasm;endoplasmic reticulum membrane;epoxygenase P450 pathway;estrogen 2-hydroxylase activity;heme binding;iron ion binding;ketone metabolic process;monooxygenase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;steroid metabolic process;testosterone 16-alpha-hydroxylase activity;testosterone 16-beta-hydroxylase activity;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>GO:0004435;GO:0004930;GO:0005515;GO:0016907</t>
+          <t>GO:0006805;GO:0008202;GO:0019373;GO:0042178;GO:0042180</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>G protein-coupled acetylcholine receptor activity;G protein-coupled receptor activity;phosphatidylinositol-4,5-bisphosphate phospholipase C activity;protein binding</t>
+          <t>epoxygenase P450 pathway;ketone metabolic process;steroid metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>GO:0005886;GO:0016020;GO:0030425;GO:0032279;GO:0042734;GO:0043679;GO:0045202;GO:0045211;GO:0098685;GO:0098839;GO:0098978;GO:0098981</t>
+          <t>GO:0004497;GO:0005506;GO:0008390;GO:0008392;GO:0016705;GO:0016712;GO:0020037;GO:0062184;GO:0062187;GO:0062188;GO:0062189;GO:0101021</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Schaffer collateral - CA1 synapse;asymmetric synapse;axon terminus;cholinergic synapse;dendrite;glutamatergic synapse;membrane;plasma membrane;postsynaptic density membrane;postsynaptic membrane;presynaptic membrane;synapse</t>
+          <t>anandamide 11,12 epoxidase activity;anandamide 14,15 epoxidase activity;anandamide 8,9 epoxidase activity;arachidonate epoxygenase activity;estrogen 2-hydroxylase activity;heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;testosterone 16-alpha-hydroxylase activity;testosterone 16-beta-hydroxylase activity</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005789</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>cytoplasm;endoplasmic reticulum membrane</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P11279</t>
+          <t>P20823</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2277,75 +2419,81 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LAMP1</t>
+          <t>HNF1A</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3916</v>
+        <v>6927</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>39</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>GO:0000421;GO:0005515;GO:0005737;GO:0005764;GO:0005765;GO:0005768;GO:0005770;GO:0005771;GO:0005829;GO:0005886;GO:0007042;GO:0008021;GO:0008200;GO:0009897;GO:0009986;GO:0010008;GO:0016020;GO:0019899;GO:0019904;GO:0031902;GO:0031982;GO:0035577;GO:0042383;GO:0042470;GO:0043323;GO:0044194;GO:0044754;GO:0045335;GO:0045954;GO:0048471;GO:0050821;GO:0061474;GO:0070062;GO:0072594;GO:0090160;GO:0101003;GO:0101004;GO:0140507;GO:1902513</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Golgi to lysosome transport;autolysosome;autophagosome membrane;azurophil granule membrane;cell surface;cytolytic granule;cytolytic granule membrane;cytoplasm;cytosol;endosome;endosome membrane;enzyme binding;establishment of protein localization to organelle;external side of plasma membrane;extracellular exosome;ficolin-1-rich granule membrane;granzyme-mediated programmed cell death signaling pathway;ion channel inhibitor activity;late endosome;late endosome membrane;lysosomal lumen acidification;lysosomal membrane;lysosome;melanosome;membrane;multivesicular body;perinuclear region of cytoplasm;phagocytic vesicle;phagolysosome membrane;plasma membrane;positive regulation of natural killer cell degranulation;positive regulation of natural killer cell mediated cytotoxicity;protein binding;protein domain specific binding;protein stabilization;regulation of organelle transport along microtubule;sarcolemma;synaptic vesicle;vesicle</t>
-        </is>
+      <c r="M24" t="n">
+        <v>46</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GO:0007042;GO:0043323;GO:0045954;GO:0050821;GO:0072594;GO:0090160;GO:0140507;GO:1902513</t>
+          <t>GO:0000122;GO:0000785;GO:0000976;GO:0000978;GO:0000981;GO:0001221;GO:0001223;GO:0001228;GO:0001750;GO:0001889;GO:0003677;GO:0003682;GO:0003690;GO:0003700;GO:0005515;GO:0005634;GO:0005667;GO:0005737;GO:0006357;GO:0006366;GO:0010628;GO:0010918;GO:0030073;GO:0030262;GO:0031016;GO:0032024;GO:0032991;GO:0035565;GO:0035623;GO:0042593;GO:0042802;GO:0043066;GO:0043565;GO:0045120;GO:0045893;GO:0045944;GO:0046983;GO:0051897;GO:0060261;GO:0071233;GO:0071333;GO:0072752;GO:0098708;GO:1902031;GO:1903799;GO:2001171</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Golgi to lysosome transport;establishment of protein localization to organelle;granzyme-mediated programmed cell death signaling pathway;lysosomal lumen acidification;positive regulation of natural killer cell degranulation;positive regulation of natural killer cell mediated cytotoxicity;protein stabilization;regulation of organelle transport along microtubule</t>
+          <t>D-glucose import across plasma membrane;DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;apoptotic nuclear changes;cellular response to L-leucine;cellular response to glucose stimulus;cellular response to rapamycin;chromatin;chromatin binding;cytoplasm;double-stranded DNA binding;glucose homeostasis;identical protein binding;insulin secretion;liver development;negative regulation of apoptotic process;negative regulation of miRNA processing;negative regulation of transcription by RNA polymerase II;nucleus;pancreas development;photoreceptor outer segment;positive regulation of ATP biosynthetic process;positive regulation of DNA-templated transcription;positive regulation of gene expression;positive regulation of insulin secretion;positive regulation of mitochondrial membrane potential;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of transcription by RNA polymerase II;positive regulation of transcription initiation by RNA polymerase II;pronucleus;protein binding;protein dimerization activity;protein-containing complex;regulation of NADP metabolic process;regulation of pronephros size;regulation of transcription by RNA polymerase II;renal D-glucose absorption;sequence-specific DNA binding;transcription by RNA polymerase II;transcription cis-regulatory region binding;transcription coactivator binding;transcription coregulator binding;transcription regulator complex</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>GO:0005515;GO:0008200;GO:0019899;GO:0019904</t>
+          <t>GO:0000122;GO:0001889;GO:0006357;GO:0006366;GO:0010628;GO:0010918;GO:0030073;GO:0030262;GO:0031016;GO:0032024;GO:0035565;GO:0035623;GO:0042593;GO:0043066;GO:0045893;GO:0045944;GO:0051897;GO:0060261;GO:0071233;GO:0071333;GO:0072752;GO:0098708;GO:1902031;GO:1903799;GO:2001171</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>enzyme binding;ion channel inhibitor activity;protein binding;protein domain specific binding</t>
+          <t>D-glucose import across plasma membrane;apoptotic nuclear changes;cellular response to L-leucine;cellular response to glucose stimulus;cellular response to rapamycin;glucose homeostasis;insulin secretion;liver development;negative regulation of apoptotic process;negative regulation of miRNA processing;negative regulation of transcription by RNA polymerase II;pancreas development;positive regulation of ATP biosynthetic process;positive regulation of DNA-templated transcription;positive regulation of gene expression;positive regulation of insulin secretion;positive regulation of mitochondrial membrane potential;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of transcription by RNA polymerase II;positive regulation of transcription initiation by RNA polymerase II;regulation of NADP metabolic process;regulation of pronephros size;regulation of transcription by RNA polymerase II;renal D-glucose absorption;transcription by RNA polymerase II</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>GO:0000421;GO:0005737;GO:0005764;GO:0005765;GO:0005768;GO:0005770;GO:0005771;GO:0005829;GO:0005886;GO:0008021;GO:0009897;GO:0009986;GO:0010008;GO:0016020;GO:0031902;GO:0031982;GO:0035577;GO:0042383;GO:0042470;GO:0044194;GO:0044754;GO:0045335;GO:0048471;GO:0061474;GO:0070062;GO:0101003;GO:0101004</t>
+          <t>GO:0000976;GO:0000978;GO:0000981;GO:0001221;GO:0001223;GO:0001228;GO:0003677;GO:0003682;GO:0003690;GO:0003700;GO:0005515;GO:0042802;GO:0043565;GO:0046983</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>autolysosome;autophagosome membrane;azurophil granule membrane;cell surface;cytolytic granule;cytolytic granule membrane;cytoplasm;cytosol;endosome;endosome membrane;external side of plasma membrane;extracellular exosome;ficolin-1-rich granule membrane;late endosome;late endosome membrane;lysosomal membrane;lysosome;melanosome;membrane;multivesicular body;perinuclear region of cytoplasm;phagocytic vesicle;phagolysosome membrane;plasma membrane;sarcolemma;synaptic vesicle;vesicle</t>
+          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;chromatin binding;double-stranded DNA binding;identical protein binding;protein binding;protein dimerization activity;sequence-specific DNA binding;transcription cis-regulatory region binding;transcription coactivator binding;transcription coregulator binding</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>GO:0000785;GO:0001750;GO:0005634;GO:0005667;GO:0005737;GO:0032991;GO:0045120</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>chromatin;cytoplasm;nucleus;photoreceptor outer segment;pronucleus;protein-containing complex;transcription regulator complex</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P12643</t>
+          <t>P24462</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2356,75 +2504,81 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BMP2</t>
+          <t>CYP3A7</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>650</v>
+        <v>1551</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>108</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>GO:0000122;GO:0001501;GO:0001649;GO:0001658;GO:0001666;GO:0001701;GO:0001837;GO:0001934;GO:0002062;GO:0002573;GO:0003007;GO:0003129;GO:0003133;GO:0003176;GO:0003181;GO:0003203;GO:0003210;GO:0003272;GO:0003331;GO:0005102;GO:0005125;GO:0005515;GO:0005576;GO:0005615;GO:0005886;GO:0006355;GO:0006879;GO:0006954;GO:0007219;GO:0007267;GO:0007507;GO:0008083;GO:0008284;GO:0008285;GO:0009887;GO:0009986;GO:0010467;GO:0010628;GO:0010629;GO:0010718;GO:0010894;GO:0010922;GO:0019211;GO:0021537;GO:0021978;GO:0022408;GO:0030177;GO:0030282;GO:0030316;GO:0030335;GO:0030501;GO:0030509;GO:0030512;GO:0032348;GO:0032991;GO:0033690;GO:0035051;GO:0035054;GO:0035360;GO:0039706;GO:0042475;GO:0042482;GO:0043065;GO:0043410;GO:0043569;GO:0045165;GO:0045597;GO:0045599;GO:0045600;GO:0045666;GO:0045778;GO:0045786;GO:0045892;GO:0045893;GO:0045944;GO:0048018;GO:0048662;GO:0048711;GO:0048762;GO:0048839;GO:0051042;GO:0055007;GO:0055008;GO:0060039;GO:0060128;GO:0060129;GO:0060317;GO:0060348;GO:0060391;GO:0060426;GO:0060485;GO:0060537;GO:0061036;GO:0070374;GO:0070700;GO:0070724;GO:0071773;GO:0072138;GO:0090090;GO:1900159;GO:1900745;GO:1901331;GO:1902895;GO:1905072;GO:1905222;GO:2000065;GO:2000725;GO:2000726</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>BMP receptor binding;BMP receptor complex;BMP signaling pathway;Notch signaling pathway;animal organ morphogenesis;aortic valve development;atrioventricular canal morphogenesis;atrioventricular valve morphogenesis;bone development;bone mineralization;branching involved in ureteric bud morphogenesis;cardiac atrium formation;cardiac epithelial to mesenchymal transition;cardiac jelly development;cardiac muscle cell differentiation;cardiac muscle tissue morphogenesis;cardiocyte differentiation;cell fate commitment;cell surface;cell-cell signaling;cellular response to BMP stimulus;chondrocyte differentiation;co-receptor binding;corticotropin hormone secreting cell differentiation;cytokine activity;embryonic heart tube anterior/posterior pattern specification;endocardial cushion formation;endocardial cushion morphogenesis;endodermal-mesodermal cell signaling;epithelial to mesenchymal transition;extracellular region;gene expression;growth factor activity;heart development;heart induction;heart morphogenesis;in utero embryonic development;inflammatory response;inner ear development;intracellular iron ion homeostasis;lung vasculature development;mesenchymal cell differentiation;mesenchymal cell proliferation involved in ureteric bud development;mesenchyme development;muscle tissue development;myeloid leukocyte differentiation;negative regulation of DNA-templated transcription;negative regulation of aldosterone biosynthetic process;negative regulation of calcium-independent cell-cell adhesion;negative regulation of canonical Wnt signaling pathway;negative regulation of cardiac muscle cell differentiation;negative regulation of cell cycle;negative regulation of cell population proliferation;negative regulation of cell-cell adhesion;negative regulation of cortisol biosynthetic process;negative regulation of fat cell differentiation;negative regulation of gene expression;negative regulation of insulin-like growth factor receptor signaling pathway;negative regulation of smooth muscle cell proliferation;negative regulation of steroid biosynthetic process;negative regulation of transcription by RNA polymerase II;negative regulation of transforming growth factor beta receptor signaling pathway;obsolete extracellular space;odontogenesis of dentin-containing tooth;osteoblast differentiation;osteoclast differentiation;pericardium development;phosphatase activator activity;plasma membrane;positive regulation of DNA-templated transcription;positive regulation of ERK1 and ERK2 cascade;positive regulation of MAPK cascade;positive regulation of SMAD protein signal transduction;positive regulation of Wnt signaling pathway;positive regulation of apoptotic process;positive regulation of astrocyte differentiation;positive regulation of bone mineralization;positive regulation of bone mineralization involved in bone maturation;positive regulation of cartilage development;positive regulation of cell differentiation;positive regulation of cell migration;positive regulation of cell population proliferation;positive regulation of epithelial to mesenchymal transition;positive regulation of extracellular matrix constituent secretion;positive regulation of fat cell differentiation;positive regulation of gene expression;positive regulation of miRNA transcription;positive regulation of neuron differentiation;positive regulation of odontoblast differentiation;positive regulation of odontogenesis;positive regulation of ossification;positive regulation of osteoblast proliferation;positive regulation of p38MAPK cascade;positive regulation of peroxisome proliferator activated receptor signaling pathway;positive regulation of phosphatase activity;positive regulation of protein phosphorylation;positive regulation of transcription by RNA polymerase II;protein binding;protein-containing complex;receptor ligand activity;regulation of DNA-templated transcription;regulation of cardiac muscle cell differentiation;response to hypoxia;signaling receptor binding;skeletal system development;telencephalon development;telencephalon regionalization;thyroid-stimulating hormone-secreting cell differentiation</t>
-        </is>
+      <c r="M25" t="n">
+        <v>20</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GO:0000122;GO:0001501;GO:0001649;GO:0001658;GO:0001666;GO:0001701;GO:0001837;GO:0001934;GO:0002062;GO:0002573;GO:0003007;GO:0003129;GO:0003133;GO:0003176;GO:0003181;GO:0003203;GO:0003210;GO:0003272;GO:0003331;GO:0006355;GO:0006879;GO:0006954;GO:0007219;GO:0007267;GO:0007507;GO:0008284;GO:0008285;GO:0009887;GO:0010467;GO:0010628;GO:0010629;GO:0010718;GO:0010894;GO:0010922;GO:0021537;GO:0021978;GO:0022408;GO:0030177;GO:0030282;GO:0030316;GO:0030335;GO:0030501;GO:0030509;GO:0030512;GO:0032348;GO:0033690;GO:0035051;GO:0035054;GO:0035360;GO:0042475;GO:0042482;GO:0043065;GO:0043410;GO:0043569;GO:0045165;GO:0045597;GO:0045599;GO:0045600;GO:0045666;GO:0045778;GO:0045786;GO:0045892;GO:0045893;GO:0045944;GO:0048662;GO:0048711;GO:0048762;GO:0048839;GO:0051042;GO:0055007;GO:0055008;GO:0060039;GO:0060128;GO:0060129;GO:0060317;GO:0060348;GO:0060391;GO:0060426;GO:0060485;GO:0060537;GO:0061036;GO:0070374;GO:0071773;GO:0072138;GO:0090090;GO:1900159;GO:1900745;GO:1901331;GO:1902895;GO:1905072;GO:1905222;GO:2000065;GO:2000725;GO:2000726</t>
+          <t>GO:0002933;GO:0004497;GO:0005506;GO:0005789;GO:0006805;GO:0008202;GO:0008210;GO:0008395;GO:0008401;GO:0016705;GO:0016712;GO:0019825;GO:0020037;GO:0042572;GO:0042573;GO:0050649;GO:0062183;GO:0070989;GO:0101020;GO:0101021</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>BMP signaling pathway;Notch signaling pathway;animal organ morphogenesis;aortic valve development;atrioventricular canal morphogenesis;atrioventricular valve morphogenesis;bone development;bone mineralization;branching involved in ureteric bud morphogenesis;cardiac atrium formation;cardiac epithelial to mesenchymal transition;cardiac jelly development;cardiac muscle cell differentiation;cardiac muscle tissue morphogenesis;cardiocyte differentiation;cell fate commitment;cell-cell signaling;cellular response to BMP stimulus;chondrocyte differentiation;corticotropin hormone secreting cell differentiation;embryonic heart tube anterior/posterior pattern specification;endocardial cushion formation;endocardial cushion morphogenesis;endodermal-mesodermal cell signaling;epithelial to mesenchymal transition;gene expression;heart development;heart induction;heart morphogenesis;in utero embryonic development;inflammatory response;inner ear development;intracellular iron ion homeostasis;lung vasculature development;mesenchymal cell differentiation;mesenchymal cell proliferation involved in ureteric bud development;mesenchyme development;muscle tissue development;myeloid leukocyte differentiation;negative regulation of DNA-templated transcription;negative regulation of aldosterone biosynthetic process;negative regulation of calcium-independent cell-cell adhesion;negative regulation of canonical Wnt signaling pathway;negative regulation of cardiac muscle cell differentiation;negative regulation of cell cycle;negative regulation of cell population proliferation;negative regulation of cell-cell adhesion;negative regulation of cortisol biosynthetic process;negative regulation of fat cell differentiation;negative regulation of gene expression;negative regulation of insulin-like growth factor receptor signaling pathway;negative regulation of smooth muscle cell proliferation;negative regulation of steroid biosynthetic process;negative regulation of transcription by RNA polymerase II;negative regulation of transforming growth factor beta receptor signaling pathway;odontogenesis of dentin-containing tooth;osteoblast differentiation;osteoclast differentiation;pericardium development;positive regulation of DNA-templated transcription;positive regulation of ERK1 and ERK2 cascade;positive regulation of MAPK cascade;positive regulation of SMAD protein signal transduction;positive regulation of Wnt signaling pathway;positive regulation of apoptotic process;positive regulation of astrocyte differentiation;positive regulation of bone mineralization;positive regulation of bone mineralization involved in bone maturation;positive regulation of cartilage development;positive regulation of cell differentiation;positive regulation of cell migration;positive regulation of cell population proliferation;positive regulation of epithelial to mesenchymal transition;positive regulation of extracellular matrix constituent secretion;positive regulation of fat cell differentiation;positive regulation of gene expression;positive regulation of miRNA transcription;positive regulation of neuron differentiation;positive regulation of odontoblast differentiation;positive regulation of odontogenesis;positive regulation of ossification;positive regulation of osteoblast proliferation;positive regulation of p38MAPK cascade;positive regulation of peroxisome proliferator activated receptor signaling pathway;positive regulation of phosphatase activity;positive regulation of protein phosphorylation;positive regulation of transcription by RNA polymerase II;regulation of DNA-templated transcription;regulation of cardiac muscle cell differentiation;response to hypoxia;skeletal system development;telencephalon development;telencephalon regionalization;thyroid-stimulating hormone-secreting cell differentiation</t>
+          <t>all-trans retinoic acid 18-hydroxylase activity;endoplasmic reticulum membrane;estrogen 16-alpha-hydroxylase activity;estrogen 2-hydroxylase activity;estrogen metabolic process;heme binding;iron ion binding;lipid hydroxylation;monooxygenase activity;oxidative demethylation;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;oxygen binding;retinoic acid 4-hydroxylase activity;retinoic acid metabolic process;retinol metabolic process;steroid hydroxylase activity;steroid metabolic process;testosterone 6-beta-hydroxylase activity;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>GO:0005102;GO:0005125;GO:0005515;GO:0008083;GO:0019211;GO:0039706;GO:0048018;GO:0070700</t>
+          <t>GO:0002933;GO:0006805;GO:0008202;GO:0008210;GO:0042572;GO:0042573;GO:0070989</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>BMP receptor binding;co-receptor binding;cytokine activity;growth factor activity;phosphatase activator activity;protein binding;receptor ligand activity;signaling receptor binding</t>
+          <t>estrogen metabolic process;lipid hydroxylation;oxidative demethylation;retinoic acid metabolic process;retinol metabolic process;steroid metabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>GO:0005576;GO:0005615;GO:0005886;GO:0009986;GO:0032991;GO:0070724</t>
+          <t>GO:0004497;GO:0005506;GO:0008395;GO:0008401;GO:0016705;GO:0016712;GO:0019825;GO:0020037;GO:0050649;GO:0062183;GO:0101020;GO:0101021</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>BMP receptor complex;cell surface;extracellular region;obsolete extracellular space;plasma membrane;protein-containing complex</t>
+          <t>all-trans retinoic acid 18-hydroxylase activity;estrogen 16-alpha-hydroxylase activity;estrogen 2-hydroxylase activity;heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;oxygen binding;retinoic acid 4-hydroxylase activity;steroid hydroxylase activity;testosterone 6-beta-hydroxylase activity</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>GO:0005789</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum membrane</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P15382</t>
+          <t>P27487</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2435,75 +2589,81 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KCNE1</t>
+          <t>DPP4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3753</v>
+        <v>1803</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>39</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>GO:0005249;GO:0005251;GO:0005515;GO:0005764;GO:0005886;GO:0006811;GO:0006813;GO:0007605;GO:0008076;GO:0009986;GO:0015459;GO:0016020;GO:0016324;GO:0021750;GO:0030018;GO:0031433;GO:0033363;GO:0042391;GO:0043266;GO:0044325;GO:0045121;GO:0060307;GO:0071320;GO:0071805;GO:0086002;GO:0086003;GO:0086005;GO:0086008;GO:0086009;GO:0086011;GO:0086013;GO:0086091;GO:0090315;GO:0097623;GO:0098915;GO:1901379;GO:1901381;GO:1902260;GO:1902282</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Z disc;apical plasma membrane;cardiac muscle cell action potential involved in contraction;cardiac muscle cell contraction;cell surface;cellular response to cAMP;delayed rectifier potassium channel activity;lysosome;membrane;membrane raft;membrane repolarization;membrane repolarization during action potential;membrane repolarization during cardiac muscle cell action potential;membrane repolarization during ventricular cardiac muscle cell action potential;monoatomic ion transport;negative regulation of delayed rectifier potassium channel activity;negative regulation of protein targeting to membrane;plasma membrane;positive regulation of potassium ion transmembrane transport;potassium channel regulator activity;potassium ion export across plasma membrane;potassium ion transmembrane transport;potassium ion transport;protein binding;regulation of heart rate by cardiac conduction;regulation of membrane potential;regulation of potassium ion transmembrane transport;regulation of potassium ion transport;regulation of ventricular cardiac muscle cell membrane repolarization;secretory granule organization;sensory perception of sound;telethonin binding;transmembrane transporter binding;ventricular cardiac muscle cell action potential;vestibular nucleus development;voltage-gated potassium channel activity;voltage-gated potassium channel activity involved in cardiac muscle cell action potential repolarization;voltage-gated potassium channel activity involved in ventricular cardiac muscle cell action potential repolarization;voltage-gated potassium channel complex</t>
-        </is>
+      <c r="M26" t="n">
+        <v>41</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>GO:0006811;GO:0006813;GO:0007605;GO:0021750;GO:0033363;GO:0042391;GO:0043266;GO:0060307;GO:0071320;GO:0071805;GO:0086002;GO:0086003;GO:0086005;GO:0086009;GO:0086011;GO:0086013;GO:0086091;GO:0090315;GO:0097623;GO:0098915;GO:1901379;GO:1901381;GO:1902260</t>
+          <t>GO:0001618;GO:0001666;GO:0002020;GO:0004252;GO:0005102;GO:0005515;GO:0005576;GO:0005765;GO:0005886;GO:0005925;GO:0006508;GO:0008236;GO:0008239;GO:0008240;GO:0008284;GO:0009986;GO:0010716;GO:0016020;GO:0016324;GO:0016486;GO:0019065;GO:0030027;GO:0030139;GO:0031258;GO:0031295;GO:0033632;GO:0042110;GO:0042802;GO:0042803;GO:0043542;GO:0045121;GO:0045499;GO:0046581;GO:0046718;GO:0046813;GO:0050919;GO:0061025;GO:0070062;GO:0070161;GO:0090024;GO:0120116</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>cardiac muscle cell action potential involved in contraction;cardiac muscle cell contraction;cellular response to cAMP;membrane repolarization;membrane repolarization during action potential;membrane repolarization during cardiac muscle cell action potential;membrane repolarization during ventricular cardiac muscle cell action potential;monoatomic ion transport;negative regulation of delayed rectifier potassium channel activity;negative regulation of protein targeting to membrane;positive regulation of potassium ion transmembrane transport;potassium ion export across plasma membrane;potassium ion transmembrane transport;potassium ion transport;regulation of heart rate by cardiac conduction;regulation of membrane potential;regulation of potassium ion transmembrane transport;regulation of potassium ion transport;regulation of ventricular cardiac muscle cell membrane repolarization;secretory granule organization;sensory perception of sound;ventricular cardiac muscle cell action potential;vestibular nucleus development</t>
+          <t>T cell activation;T cell costimulation;anchoring junction;apical plasma membrane;cell surface;chemorepellent activity;dipeptidyl-peptidase activity;endocytic vesicle;endothelial cell migration;extracellular exosome;extracellular region;focal adhesion;glucagon processing;identical protein binding;intercellular canaliculus;lamellipodium;lamellipodium membrane;lysosomal membrane;membrane;membrane fusion;membrane raft;negative chemotaxis;negative regulation of extracellular matrix disassembly;negative regulation of neutrophil chemotaxis;peptide hormone processing;plasma membrane;positive regulation of cell population proliferation;protease binding;protein binding;protein homodimerization activity;proteolysis;receptor-mediated endocytosis of virus by host cell;receptor-mediated virion attachment to host cell;regulation of cell-cell adhesion mediated by integrin;response to hypoxia;serine-type endopeptidase activity;serine-type peptidase activity;signaling receptor binding;symbiont entry into host cell;tripeptidyl-peptidase activity;virus receptor activity</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>GO:0005249;GO:0005251;GO:0005515;GO:0015459;GO:0031433;GO:0044325;GO:0086008;GO:1902282</t>
+          <t>GO:0001666;GO:0006508;GO:0008284;GO:0010716;GO:0016486;GO:0019065;GO:0031295;GO:0033632;GO:0042110;GO:0043542;GO:0046718;GO:0046813;GO:0050919;GO:0061025;GO:0090024;GO:0120116</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>delayed rectifier potassium channel activity;potassium channel regulator activity;protein binding;telethonin binding;transmembrane transporter binding;voltage-gated potassium channel activity;voltage-gated potassium channel activity involved in cardiac muscle cell action potential repolarization;voltage-gated potassium channel activity involved in ventricular cardiac muscle cell action potential repolarization</t>
+          <t>T cell activation;T cell costimulation;endothelial cell migration;glucagon processing;membrane fusion;negative chemotaxis;negative regulation of extracellular matrix disassembly;negative regulation of neutrophil chemotaxis;peptide hormone processing;positive regulation of cell population proliferation;proteolysis;receptor-mediated endocytosis of virus by host cell;receptor-mediated virion attachment to host cell;regulation of cell-cell adhesion mediated by integrin;response to hypoxia;symbiont entry into host cell</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>GO:0005764;GO:0005886;GO:0008076;GO:0009986;GO:0016020;GO:0016324;GO:0030018;GO:0045121</t>
+          <t>GO:0001618;GO:0002020;GO:0004252;GO:0005102;GO:0005515;GO:0008236;GO:0008239;GO:0008240;GO:0042802;GO:0042803;GO:0045499</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Z disc;apical plasma membrane;cell surface;lysosome;membrane;membrane raft;plasma membrane;voltage-gated potassium channel complex</t>
+          <t>chemorepellent activity;dipeptidyl-peptidase activity;identical protein binding;protease binding;protein binding;protein homodimerization activity;serine-type endopeptidase activity;serine-type peptidase activity;signaling receptor binding;tripeptidyl-peptidase activity;virus receptor activity</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>GO:0005576;GO:0005765;GO:0005886;GO:0005925;GO:0009986;GO:0016020;GO:0016324;GO:0030027;GO:0030139;GO:0031258;GO:0045121;GO:0046581;GO:0070062;GO:0070161</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>anchoring junction;apical plasma membrane;cell surface;endocytic vesicle;extracellular exosome;extracellular region;focal adhesion;intercellular canaliculus;lamellipodium;lamellipodium membrane;lysosomal membrane;membrane;membrane raft;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P19484</t>
+          <t>P29474</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2514,75 +2674,81 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TFEB</t>
+          <t>NOS3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7942</v>
+        <v>4846</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K27" t="n">
-        <v>31</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>GO:0000785;GO:0000976;GO:0000978;GO:0000981;GO:0001228;GO:0001892;GO:0003677;GO:0003700;GO:0005515;GO:0005634;GO:0005667;GO:0005737;GO:0005765;GO:0005829;GO:0006355;GO:0006357;GO:0006959;GO:0007040;GO:0009267;GO:0010508;GO:0019899;GO:0032418;GO:0034198;GO:0045893;GO:0045944;GO:0046982;GO:0046983;GO:0050829;GO:0140367;GO:1905671;GO:1990837</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;antibacterial innate immune response;cellular response to amino acid starvation;cellular response to starvation;chromatin;cytoplasm;cytosol;defense response to Gram-negative bacterium;embryonic placenta development;enzyme binding;humoral immune response;lysosomal membrane;lysosome localization;lysosome organization;nucleus;positive regulation of DNA-templated transcription;positive regulation of autophagy;positive regulation of transcription by RNA polymerase II;protein binding;protein dimerization activity;protein heterodimerization activity;regulation of DNA-templated transcription;regulation of lysosome organization;regulation of transcription by RNA polymerase II;sequence-specific double-stranded DNA binding;transcription cis-regulatory region binding;transcription regulator complex</t>
-        </is>
+      <c r="M27" t="n">
+        <v>58</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GO:0001892;GO:0006355;GO:0006357;GO:0006959;GO:0007040;GO:0009267;GO:0010508;GO:0032418;GO:0034198;GO:0045893;GO:0045944;GO:0050829;GO:0140367;GO:1905671</t>
+          <t>GO:0000139;GO:0001974;GO:0003100;GO:0003180;GO:0003184;GO:0003203;GO:0003785;GO:0004517;GO:0005515;GO:0005516;GO:0005634;GO:0005737;GO:0005794;GO:0005829;GO:0005856;GO:0005886;GO:0005901;GO:0006527;GO:0006809;GO:0007005;GO:0008015;GO:0008217;GO:0008285;GO:0009408;GO:0009725;GO:0010181;GO:0010544;GO:0010628;GO:0014740;GO:0014806;GO:0016175;GO:0016491;GO:0019430;GO:0020037;GO:0030666;GO:0031644;GO:0032496;GO:0034405;GO:0034617;GO:0034618;GO:0042311;GO:0043536;GO:0043542;GO:0045454;GO:0045747;GO:0045766;GO:0045776;GO:0046146;GO:0046209;GO:0046870;GO:0048873;GO:0050660;GO:0050661;GO:0060412;GO:0070168;GO:0097110;GO:0097746;GO:1902042</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>antibacterial innate immune response;cellular response to amino acid starvation;cellular response to starvation;defense response to Gram-negative bacterium;embryonic placenta development;humoral immune response;lysosome localization;lysosome organization;positive regulation of DNA-templated transcription;positive regulation of autophagy;positive regulation of transcription by RNA polymerase II;regulation of DNA-templated transcription;regulation of lysosome organization;regulation of transcription by RNA polymerase II</t>
+          <t>FMN binding;Golgi apparatus;Golgi membrane;L-arginine catabolic process;NADP binding;actin monomer binding;aortic valve morphogenesis;arginine binding;blood circulation;blood vessel diameter maintenance;blood vessel remodeling;cadmium ion binding;calmodulin binding;caveola;cell redox homeostasis;cytoplasm;cytoskeleton;cytosol;endocardial cushion morphogenesis;endocytic vesicle membrane;endothelial cell migration;flavin adenine dinucleotide binding;heme binding;homeostasis of number of cells within a tissue;mitochondrion organization;negative regulation of biomineral tissue development;negative regulation of blood pressure;negative regulation of cell population proliferation;negative regulation of extrinsic apoptotic signaling pathway via death domain receptors;negative regulation of muscle hyperplasia;negative regulation of platelet activation;nitric oxide biosynthetic process;nitric oxide metabolic process;nitric-oxide synthase activity;nucleus;oxidoreductase activity;plasma membrane;positive regulation of Notch signaling pathway;positive regulation of angiogenesis;positive regulation of blood vessel endothelial cell migration;positive regulation of gene expression;protein binding;pulmonary valve morphogenesis;regulation of blood pressure;regulation of nervous system process;regulation of systemic arterial blood pressure by endothelin;removal of superoxide radicals;response to fluid shear stress;response to heat;response to hormone;response to lipopolysaccharide;scaffold protein binding;smooth muscle hyperplasia;superoxide-generating NAD(P)H oxidase activity;tetrahydrobiopterin binding;tetrahydrobiopterin metabolic process;vasodilation;ventricular septum morphogenesis</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>GO:0000976;GO:0000978;GO:0000981;GO:0001228;GO:0003677;GO:0003700;GO:0005515;GO:0019899;GO:0046982;GO:0046983;GO:1990837</t>
+          <t>GO:0001974;GO:0003100;GO:0003180;GO:0003184;GO:0003203;GO:0006527;GO:0006809;GO:0007005;GO:0008015;GO:0008217;GO:0008285;GO:0009408;GO:0009725;GO:0010544;GO:0010628;GO:0014740;GO:0014806;GO:0019430;GO:0031644;GO:0032496;GO:0034405;GO:0042311;GO:0043536;GO:0043542;GO:0045454;GO:0045747;GO:0045766;GO:0045776;GO:0046146;GO:0046209;GO:0048873;GO:0060412;GO:0070168;GO:0097746;GO:1902042</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;enzyme binding;protein binding;protein dimerization activity;protein heterodimerization activity;sequence-specific double-stranded DNA binding;transcription cis-regulatory region binding</t>
+          <t>L-arginine catabolic process;aortic valve morphogenesis;blood circulation;blood vessel diameter maintenance;blood vessel remodeling;cell redox homeostasis;endocardial cushion morphogenesis;endothelial cell migration;homeostasis of number of cells within a tissue;mitochondrion organization;negative regulation of biomineral tissue development;negative regulation of blood pressure;negative regulation of cell population proliferation;negative regulation of extrinsic apoptotic signaling pathway via death domain receptors;negative regulation of muscle hyperplasia;negative regulation of platelet activation;nitric oxide biosynthetic process;nitric oxide metabolic process;positive regulation of Notch signaling pathway;positive regulation of angiogenesis;positive regulation of blood vessel endothelial cell migration;positive regulation of gene expression;pulmonary valve morphogenesis;regulation of blood pressure;regulation of nervous system process;regulation of systemic arterial blood pressure by endothelin;removal of superoxide radicals;response to fluid shear stress;response to heat;response to hormone;response to lipopolysaccharide;smooth muscle hyperplasia;tetrahydrobiopterin metabolic process;vasodilation;ventricular septum morphogenesis</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>GO:0000785;GO:0005634;GO:0005667;GO:0005737;GO:0005765;GO:0005829</t>
+          <t>GO:0003785;GO:0004517;GO:0005515;GO:0005516;GO:0010181;GO:0016175;GO:0016491;GO:0020037;GO:0034617;GO:0034618;GO:0046870;GO:0050660;GO:0050661;GO:0097110</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>chromatin;cytoplasm;cytosol;lysosomal membrane;nucleus;transcription regulator complex</t>
+          <t>FMN binding;NADP binding;actin monomer binding;arginine binding;cadmium ion binding;calmodulin binding;flavin adenine dinucleotide binding;heme binding;nitric-oxide synthase activity;oxidoreductase activity;protein binding;scaffold protein binding;superoxide-generating NAD(P)H oxidase activity;tetrahydrobiopterin binding</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>GO:0000139;GO:0005634;GO:0005737;GO:0005794;GO:0005829;GO:0005856;GO:0005886;GO:0005901;GO:0030666</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Golgi apparatus;Golgi membrane;caveola;cytoplasm;cytoskeleton;cytosol;endocytic vesicle membrane;nucleus;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P21281</t>
+          <t>P31513</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2593,75 +2759,81 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ATP6V1B2</t>
+          <t>FMO3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>526</v>
+        <v>2328</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>23</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>GO:0000221;GO:0001726;GO:0005515;GO:0005524;GO:0005737;GO:0005765;GO:0005829;GO:0005886;GO:0005902;GO:0007035;GO:0015078;GO:0016241;GO:0016324;GO:0030665;GO:0030672;GO:0033180;GO:0042470;GO:0046034;GO:0046961;GO:0070062;GO:0097401;GO:0098850;GO:1902600</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>ATP binding;ATP metabolic process;apical plasma membrane;clathrin-coated vesicle membrane;cytoplasm;cytosol;extracellular exosome;extrinsic component of synaptic vesicle membrane;lysosomal membrane;melanosome;microvillus;plasma membrane;protein binding;proton transmembrane transport;proton transmembrane transporter activity;proton-transporting ATPase activity, rotational mechanism;proton-transporting V-type ATPase, V1 domain;regulation of macroautophagy;ruffle;synaptic vesicle lumen acidification;synaptic vesicle membrane;vacuolar acidification;vacuolar proton-transporting V-type ATPase, V1 domain</t>
-        </is>
+      <c r="M28" t="n">
+        <v>10</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>GO:0007035;GO:0016241;GO:0046034;GO:0097401;GO:1902600</t>
+          <t>GO:0004499;GO:0005515;GO:0005789;GO:0016709;GO:0034899;GO:0042412;GO:0047638;GO:0047822;GO:0050660;GO:0050661</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>ATP metabolic process;proton transmembrane transport;regulation of macroautophagy;synaptic vesicle lumen acidification;vacuolar acidification</t>
+          <t>N,N-dimethylaniline monooxygenase activity;NADP binding;albendazole monooxygenase activity;endoplasmic reticulum membrane;flavin adenine dinucleotide binding;hypotaurine monooxygenase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, NAD(P)H as one donor, and incorporation of one atom of oxygen;protein binding;taurine biosynthetic process;trimethylamine monooxygenase activity</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>GO:0005515;GO:0005524;GO:0015078;GO:0046961</t>
+          <t>GO:0042412</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>ATP binding;protein binding;proton transmembrane transporter activity;proton-transporting ATPase activity, rotational mechanism</t>
+          <t>taurine biosynthetic process</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>GO:0000221;GO:0001726;GO:0005737;GO:0005765;GO:0005829;GO:0005886;GO:0005902;GO:0016324;GO:0030665;GO:0030672;GO:0033180;GO:0042470;GO:0070062;GO:0098850</t>
+          <t>GO:0004499;GO:0005515;GO:0016709;GO:0034899;GO:0047638;GO:0047822;GO:0050660;GO:0050661</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>apical plasma membrane;clathrin-coated vesicle membrane;cytoplasm;cytosol;extracellular exosome;extrinsic component of synaptic vesicle membrane;lysosomal membrane;melanosome;microvillus;plasma membrane;proton-transporting V-type ATPase, V1 domain;ruffle;synaptic vesicle membrane;vacuolar proton-transporting V-type ATPase, V1 domain</t>
+          <t>N,N-dimethylaniline monooxygenase activity;NADP binding;albendazole monooxygenase activity;flavin adenine dinucleotide binding;hypotaurine monooxygenase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, NAD(P)H as one donor, and incorporation of one atom of oxygen;protein binding;trimethylamine monooxygenase activity</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>GO:0005789</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum membrane</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P22760</t>
+          <t>P33527</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2672,75 +2844,81 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>bethanechol</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AADAC</t>
+          <t>ABCC1</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>4363</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>12</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>GO:0003824;GO:0004806;GO:0005515;GO:0005789;GO:0006805;GO:0010898;GO:0016020;GO:0016298;GO:0016787;GO:0017171;GO:0019213;GO:0052689</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>carboxylic ester hydrolase activity;catalytic activity;deacetylase activity;endoplasmic reticulum membrane;hydrolase activity;lipase activity;membrane;positive regulation of triglyceride catabolic process;protein binding;serine hydrolase activity;triacylglycerol lipase activity;xenobiotic metabolic process</t>
-        </is>
+      <c r="M29" t="n">
+        <v>45</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>GO:0006805;GO:0010898</t>
+          <t>GO:0005524;GO:0005886;GO:0006691;GO:0006805;GO:0006869;GO:0008559;GO:0009410;GO:0009925;GO:0015420;GO:0015431;GO:0015562;GO:0015889;GO:0016020;GO:0016323;GO:0016324;GO:0016328;GO:0016887;GO:0022857;GO:0030054;GO:0030148;GO:0034040;GO:0034599;GO:0034634;GO:0034775;GO:0042167;GO:0042626;GO:0042908;GO:0042910;GO:0045332;GO:0046942;GO:0046943;GO:0050729;GO:0055085;GO:0060326;GO:0070062;GO:0070633;GO:0070729;GO:0071716;GO:0099039;GO:0140115;GO:0140359;GO:0150104;GO:1904646;GO:1905039;GO:1990962</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>positive regulation of triglyceride catabolic process;xenobiotic metabolic process</t>
+          <t>ABC-type glutathione S-conjugate transporter activity;ABC-type transporter activity;ABC-type vitamin B12 transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled lipid transmembrane transporter activity;ATPase-coupled transmembrane transporter activity;apical plasma membrane;basal plasma membrane;basolateral plasma membrane;carboxylic acid transmembrane transport;carboxylic acid transmembrane transporter activity;carboxylic acid transport;cell chemotaxis;cell junction;cellular response to amyloid-beta;cellular response to oxidative stress;cobalamin transport;cyclic nucleotide transport;efflux transmembrane transporter activity;export across plasma membrane;extracellular exosome;glutathione transmembrane transport;glutathione transmembrane transporter activity;heme catabolic process;lateral plasma membrane;leukotriene metabolic process;leukotriene transport;lipid transport;membrane;phospholipid translocation;plasma membrane;positive regulation of inflammatory response;response to xenobiotic stimulus;sphingolipid biosynthetic process;sphingolipid translocation;transepithelial transport;transmembrane transport;transmembrane transporter activity;transport across blood-brain barrier;xenobiotic metabolic process;xenobiotic transmembrane transporter activity;xenobiotic transport;xenobiotic transport across blood-brain barrier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>GO:0003824;GO:0004806;GO:0005515;GO:0016298;GO:0016787;GO:0017171;GO:0019213;GO:0052689</t>
+          <t>GO:0006691;GO:0006805;GO:0006869;GO:0009410;GO:0015889;GO:0030148;GO:0034599;GO:0034775;GO:0042167;GO:0042908;GO:0045332;GO:0046942;GO:0050729;GO:0055085;GO:0060326;GO:0070633;GO:0070729;GO:0071716;GO:0099039;GO:0140115;GO:0150104;GO:1904646;GO:1905039;GO:1990962</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>carboxylic ester hydrolase activity;catalytic activity;deacetylase activity;hydrolase activity;lipase activity;protein binding;serine hydrolase activity;triacylglycerol lipase activity</t>
+          <t>carboxylic acid transmembrane transport;carboxylic acid transport;cell chemotaxis;cellular response to amyloid-beta;cellular response to oxidative stress;cobalamin transport;cyclic nucleotide transport;export across plasma membrane;glutathione transmembrane transport;heme catabolic process;leukotriene metabolic process;leukotriene transport;lipid transport;phospholipid translocation;positive regulation of inflammatory response;response to xenobiotic stimulus;sphingolipid biosynthetic process;sphingolipid translocation;transepithelial transport;transmembrane transport;transport across blood-brain barrier;xenobiotic metabolic process;xenobiotic transport;xenobiotic transport across blood-brain barrier</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>GO:0005789;GO:0016020</t>
+          <t>GO:0005524;GO:0008559;GO:0015420;GO:0015431;GO:0015562;GO:0016887;GO:0022857;GO:0034040;GO:0034634;GO:0042626;GO:0042910;GO:0046943;GO:0140359</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>endoplasmic reticulum membrane;membrane</t>
+          <t>ABC-type glutathione S-conjugate transporter activity;ABC-type transporter activity;ABC-type vitamin B12 transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled lipid transmembrane transporter activity;ATPase-coupled transmembrane transporter activity;carboxylic acid transmembrane transporter activity;efflux transmembrane transporter activity;glutathione transmembrane transporter activity;transmembrane transporter activity;xenobiotic transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0009925;GO:0016020;GO:0016323;GO:0016324;GO:0016328;GO:0030054;GO:0070062</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>apical plasma membrane;basal plasma membrane;basolateral plasma membrane;cell junction;extracellular exosome;lateral plasma membrane;membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P29466</t>
+          <t>P35869</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2751,75 +2929,81 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CASP1</t>
+          <t>AHR</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>834</v>
+        <v>196</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>50</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>GO:0002221;GO:0004175;GO:0004197;GO:0005515;GO:0005730;GO:0005737;GO:0005829;GO:0005874;GO:0005886;GO:0006508;GO:0006915;GO:0006954;GO:0007165;GO:0007231;GO:0008234;GO:0008656;GO:0016485;GO:0016540;GO:0019899;GO:0019900;GO:0019955;GO:0032496;GO:0032731;GO:0032741;GO:0032991;GO:0042742;GO:0042802;GO:0042981;GO:0043065;GO:0043123;GO:0046456;GO:0050700;GO:0050727;GO:0050729;GO:0051604;GO:0051607;GO:0070269;GO:0071222;GO:0071260;GO:0071346;GO:0072557;GO:0072558;GO:0072559;GO:0097169;GO:0097179;GO:0140447;GO:0140448;GO:0140970;GO:1900227;GO:1903265</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>AIM2 inflammasome complex;AIM2 inflammasome complex assembly;CARD domain binding;IPAF inflammasome complex;NLRP1 inflammasome complex;NLRP3 inflammasome complex;apoptotic process;cellular response to lipopolysaccharide;cellular response to mechanical stimulus;cellular response to type II interferon;cysteine-type endopeptidase activator activity involved in apoptotic process;cysteine-type endopeptidase activity;cysteine-type peptidase activity;cytokine binding;cytokine precursor processing;cytoplasm;cytosol;defense response to bacterium;defense response to virus;endopeptidase activity;enzyme binding;icosanoid biosynthetic process;identical protein binding;inflammatory response;kinase binding;microtubule;nucleolus;osmosensory signaling pathway;pattern recognition receptor signaling pathway;plasma membrane;positive regulation of NLRP3 inflammasome complex assembly;positive regulation of apoptotic process;positive regulation of canonical NF-kappaB signal transduction;positive regulation of inflammatory response;positive regulation of interleukin-1 beta production;positive regulation of interleukin-18 production;positive regulation of tumor necrosis factor-mediated signaling pathway;protease inhibitor complex;protein autoprocessing;protein binding;protein maturation;protein processing;protein-containing complex;proteolysis;pyroptotic inflammatory response;regulation of apoptotic process;regulation of inflammatory response;response to lipopolysaccharide;signal transduction;signaling receptor ligand precursor processing</t>
-        </is>
+      <c r="M30" t="n">
+        <v>49</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>GO:0002221;GO:0006508;GO:0006915;GO:0006954;GO:0007165;GO:0007231;GO:0016485;GO:0016540;GO:0032496;GO:0032731;GO:0032741;GO:0042742;GO:0042981;GO:0043065;GO:0043123;GO:0046456;GO:0050727;GO:0050729;GO:0051604;GO:0051607;GO:0070269;GO:0071222;GO:0071260;GO:0071346;GO:0140447;GO:0140448;GO:0140970;GO:1900227;GO:1903265</t>
+          <t>GO:0000785;GO:0000976;GO:0000981;GO:0000987;GO:0001094;GO:0001223;GO:0001568;GO:0002819;GO:0002841;GO:0003677;GO:0003700;GO:0004879;GO:0005515;GO:0005634;GO:0005654;GO:0005667;GO:0005737;GO:0005829;GO:0006355;GO:0006357;GO:0006805;GO:0006915;GO:0009410;GO:0009636;GO:0010468;GO:0017025;GO:0030522;GO:0030888;GO:0032922;GO:0032991;GO:0034751;GO:0034752;GO:0034753;GO:0042803;GO:0045892;GO:0045893;GO:0045944;GO:0046982;GO:0046983;GO:0050728;GO:0051239;GO:0051879;GO:0061629;GO:0070888;GO:0071219;GO:0071320;GO:1904322;GO:1904613;GO:1990837</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>AIM2 inflammasome complex assembly;apoptotic process;cellular response to lipopolysaccharide;cellular response to mechanical stimulus;cellular response to type II interferon;cytokine precursor processing;defense response to bacterium;defense response to virus;icosanoid biosynthetic process;inflammatory response;osmosensory signaling pathway;pattern recognition receptor signaling pathway;positive regulation of NLRP3 inflammasome complex assembly;positive regulation of apoptotic process;positive regulation of canonical NF-kappaB signal transduction;positive regulation of inflammatory response;positive regulation of interleukin-1 beta production;positive regulation of interleukin-18 production;positive regulation of tumor necrosis factor-mediated signaling pathway;protein autoprocessing;protein maturation;protein processing;proteolysis;pyroptotic inflammatory response;regulation of apoptotic process;regulation of inflammatory response;response to lipopolysaccharide;signal transduction;signaling receptor ligand precursor processing</t>
+          <t>DNA binding;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;E-box binding;Hsp90 protein binding;RNA polymerase II-specific DNA-binding transcription factor binding;TBP-class protein binding;TFIID-class transcription factor complex binding;apoptotic process;aryl hydrocarbon receptor complex;blood vessel development;cellular response to 2,3,7,8-tetrachlorodibenzodioxine;cellular response to cAMP;cellular response to forskolin;cellular response to molecule of bacterial origin;chromatin;circadian regulation of gene expression;cis-regulatory region sequence-specific DNA binding;cytoplasm;cytosol;cytosolic aryl hydrocarbon receptor complex;intracellular receptor signaling pathway;negative regulation of DNA-templated transcription;negative regulation of T cell mediated immune response to tumor cell;negative regulation of inflammatory response;nuclear aryl hydrocarbon receptor complex;nuclear receptor activity;nucleoplasm;nucleus;positive regulation of DNA-templated transcription;positive regulation of transcription by RNA polymerase II;protein binding;protein dimerization activity;protein heterodimerization activity;protein homodimerization activity;protein-containing complex;regulation of B cell proliferation;regulation of DNA-templated transcription;regulation of adaptive immune response;regulation of gene expression;regulation of multicellular organismal process;regulation of transcription by RNA polymerase II;response to toxic substance;response to xenobiotic stimulus;sequence-specific double-stranded DNA binding;transcription cis-regulatory region binding;transcription coactivator binding;transcription regulator complex;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>GO:0004175;GO:0004197;GO:0005515;GO:0008234;GO:0008656;GO:0019899;GO:0019900;GO:0019955;GO:0042802;GO:0050700</t>
+          <t>GO:0001568;GO:0002819;GO:0002841;GO:0006355;GO:0006357;GO:0006805;GO:0006915;GO:0009410;GO:0009636;GO:0010468;GO:0030522;GO:0030888;GO:0032922;GO:0045892;GO:0045893;GO:0045944;GO:0050728;GO:0051239;GO:0071219;GO:0071320;GO:1904322;GO:1904613</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>CARD domain binding;cysteine-type endopeptidase activator activity involved in apoptotic process;cysteine-type endopeptidase activity;cysteine-type peptidase activity;cytokine binding;endopeptidase activity;enzyme binding;identical protein binding;kinase binding;protein binding</t>
+          <t>apoptotic process;blood vessel development;cellular response to 2,3,7,8-tetrachlorodibenzodioxine;cellular response to cAMP;cellular response to forskolin;cellular response to molecule of bacterial origin;circadian regulation of gene expression;intracellular receptor signaling pathway;negative regulation of DNA-templated transcription;negative regulation of T cell mediated immune response to tumor cell;negative regulation of inflammatory response;positive regulation of DNA-templated transcription;positive regulation of transcription by RNA polymerase II;regulation of B cell proliferation;regulation of DNA-templated transcription;regulation of adaptive immune response;regulation of gene expression;regulation of multicellular organismal process;regulation of transcription by RNA polymerase II;response to toxic substance;response to xenobiotic stimulus;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>GO:0005730;GO:0005737;GO:0005829;GO:0005874;GO:0005886;GO:0032991;GO:0072557;GO:0072558;GO:0072559;GO:0097169;GO:0097179</t>
+          <t>GO:0000976;GO:0000981;GO:0000987;GO:0001094;GO:0001223;GO:0003677;GO:0003700;GO:0004879;GO:0005515;GO:0017025;GO:0042803;GO:0046982;GO:0046983;GO:0051879;GO:0061629;GO:0070888;GO:1990837</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>AIM2 inflammasome complex;IPAF inflammasome complex;NLRP1 inflammasome complex;NLRP3 inflammasome complex;cytoplasm;cytosol;microtubule;nucleolus;plasma membrane;protease inhibitor complex;protein-containing complex</t>
+          <t>DNA binding;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;E-box binding;Hsp90 protein binding;RNA polymerase II-specific DNA-binding transcription factor binding;TBP-class protein binding;TFIID-class transcription factor complex binding;cis-regulatory region sequence-specific DNA binding;nuclear receptor activity;protein binding;protein dimerization activity;protein heterodimerization activity;protein homodimerization activity;sequence-specific double-stranded DNA binding;transcription cis-regulatory region binding;transcription coactivator binding</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>GO:0000785;GO:0005634;GO:0005654;GO:0005667;GO:0005737;GO:0005829;GO:0032991;GO:0034751;GO:0034752;GO:0034753</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>aryl hydrocarbon receptor complex;chromatin;cytoplasm;cytosol;cytosolic aryl hydrocarbon receptor complex;nuclear aryl hydrocarbon receptor complex;nucleoplasm;nucleus;protein-containing complex;transcription regulator complex</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P31749</t>
+          <t>P41235</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2830,75 +3014,81 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AKT1</t>
+          <t>HNF4A</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>207</v>
+        <v>3172</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>141</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>GO:0001649;GO:0001938;GO:0002042;GO:0002430;GO:0003376;GO:0004672;GO:0004674;GO:0004712;GO:0005515;GO:0005516;GO:0005524;GO:0005547;GO:0005634;GO:0005654;GO:0005737;GO:0005739;GO:0005758;GO:0005819;GO:0005829;GO:0005886;GO:0005911;GO:0005938;GO:0005979;GO:0006468;GO:0006809;GO:0006924;GO:0006979;GO:0007165;GO:0007173;GO:0007186;GO:0008283;GO:0008286;GO:0009408;GO:0009725;GO:0010507;GO:0010595;GO:0010628;GO:0010629;GO:0010748;GO:0010761;GO:0010907;GO:0010975;GO:0016020;GO:0016242;GO:0016301;GO:0018105;GO:0018107;GO:0019221;GO:0019899;GO:0019900;GO:0019901;GO:0030027;GO:0030154;GO:0030235;GO:0030291;GO:0030307;GO:0030334;GO:0030335;GO:0031295;GO:0031397;GO:0031929;GO:0031982;GO:0031999;GO:0032079;GO:0032436;GO:0032869;GO:0032991;GO:0033138;GO:0033554;GO:0034405;GO:0035556;GO:0035655;GO:0036064;GO:0042307;GO:0042802;GO:0042803;GO:0042981;GO:0043066;GO:0043276;GO:0043325;GO:0043488;GO:0043491;GO:0043536;GO:0045429;GO:0045600;GO:0045725;GO:0045746;GO:0045861;GO:0045944;GO:0046209;GO:0046326;GO:0046889;GO:0048009;GO:0048266;GO:0048661;GO:0051247;GO:0051897;GO:0060079;GO:0060416;GO:0060644;GO:0070141;GO:0070585;GO:0070848;GO:0071364;GO:0071889;GO:0072656;GO:0072752;GO:0090201;GO:0097700;GO:0098794;GO:0098978;GO:0099104;GO:0099175;GO:0106310;GO:0110002;GO:0140052;GO:0150033;GO:0160049;GO:0160213;GO:1900087;GO:1900182;GO:1901796;GO:1902018;GO:1902176;GO:1903038;GO:1903078;GO:1903318;GO:1903384;GO:1903898;GO:1904263;GO:1904515;GO:1904841;GO:1905552;GO:1905786;GO:1990090;GO:1990418;GO:2000010;GO:2000074;GO:2000402;GO:2001240;GO:2001243</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>14-3-3 protein binding;ATP binding;G protein-coupled receptor signaling pathway;T cell costimulation;TOR signaling;TORC2 complex binding;activation-induced cell death of T cells;anoikis;behavioral response to pain;beta-arrestin-dependent dopamine receptor signaling pathway;calmodulin binding;cell cortex;cell differentiation;cell migration involved in sprouting angiogenesis;cell population proliferation;cell-cell junction;cellular response to epidermal growth factor stimulus;cellular response to insulin stimulus;cellular response to nerve growth factor stimulus;cellular response to oxidised low-density lipoprotein particle stimulus;cellular response to rapamycin;cellular response to stress;ciliary basal body;complement receptor mediated signaling pathway;cytokine-mediated signaling pathway;cytoplasm;cytosol;enzyme binding;epidermal growth factor receptor signaling pathway;excitatory postsynaptic potential;fibroblast migration;glutamatergic synapse;identical protein binding;insulin receptor signaling pathway;insulin-like growth factor receptor signaling pathway;interleukin-18-mediated signaling pathway;intracellular signal transduction;kinase activity;kinase binding;lamellipodium;maintenance of protein location in mitochondrion;mammary gland epithelial cell differentiation;membrane;mitochondrial intermembrane space;mitochondrion;negative regulation of Notch signaling pathway;negative regulation of PERK-mediated unfolded protein response;negative regulation of apoptotic process;negative regulation of autophagy;negative regulation of cGAS/STING signaling pathway;negative regulation of cilium assembly;negative regulation of extrinsic apoptotic signaling pathway in absence of ligand;negative regulation of fatty acid beta-oxidation;negative regulation of gene expression;negative regulation of hydrogen peroxide-induced neuron intrinsic apoptotic signaling pathway;negative regulation of intrinsic apoptotic signaling pathway;negative regulation of leukocyte cell-cell adhesion;negative regulation of long-chain fatty acid import across plasma membrane;negative regulation of lymphocyte migration;negative regulation of macroautophagy;negative regulation of oxidative stress-induced intrinsic apoptotic signaling pathway;negative regulation of protein localization to lysosome;negative regulation of protein maturation;negative regulation of protein ubiquitination;negative regulation of proteolysis;negative regulation of release of cytochrome c from mitochondria;nitric oxide biosynthetic process;nitric oxide metabolic process;nitric-oxide synthase regulator activity;nucleoplasm;nucleus;osteoblast differentiation;peptidyl-serine phosphorylation;peptidyl-threonine phosphorylation;phosphatidylinositol 3-kinase/protein kinase B signal transduction;phosphatidylinositol-3,4,5-trisphosphate binding;phosphatidylinositol-3,4-bisphosphate binding;plasma membrane;positive regulation of D-glucose import across plasma membrane;positive regulation of G1/S transition of mitotic cell cycle;positive regulation of TORC1 signaling;positive regulation of TORC2 signaling;positive regulation of anaphase-promoting complex-dependent catabolic process;positive regulation of blood vessel endothelial cell migration;positive regulation of cell growth;positive regulation of cell migration;positive regulation of endodeoxyribonuclease activity;positive regulation of endothelial cell migration;positive regulation of endothelial cell proliferation;positive regulation of fat cell differentiation;positive regulation of gene expression;positive regulation of glucose metabolic process;positive regulation of glycogen biosynthetic process;positive regulation of lipid biosynthetic process;positive regulation of nitric oxide biosynthetic process;positive regulation of peptidyl-serine phosphorylation;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of proteasomal ubiquitin-dependent protein catabolic process;positive regulation of protein import into nucleus;positive regulation of protein localization to cell surface;positive regulation of protein localization to endoplasmic reticulum;positive regulation of protein localization to nucleus;positive regulation of protein localization to plasma membrane;positive regulation of protein metabolic process;positive regulation of smooth muscle cell proliferation;positive regulation of transcription by RNA polymerase II;postsynapse;potassium channel activator activity;protein binding;protein homodimerization activity;protein kinase activity;protein kinase binding;protein localization to mitochondrion;protein phosphorylation;protein serine kinase activity;protein serine/threonine kinase activity;protein serine/threonine kinase inhibitor activity;protein serine/threonine/tyrosine kinase activity;protein-containing complex;regulation of apoptotic process;regulation of cell migration;regulation of glycogen biosynthetic process;regulation of mRNA stability;regulation of neuron projection development;regulation of postsynapse organization;regulation of signal transduction by p53 class mediator;regulation of tRNA methylation;regulation of type B pancreatic cell development;response to UV-A;response to fluid shear stress;response to growth factor;response to growth hormone;response to heat;response to hormone;response to insulin-like growth factor stimulus;response to oxidative stress;signal transduction;sphingosine-1-phosphate receptor signaling pathway;spindle;vascular endothelial cell response to laminar fluid shear stress;vesicle</t>
-        </is>
+      <c r="M31" t="n">
+        <v>41</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>GO:0001649;GO:0001938;GO:0002042;GO:0002430;GO:0003376;GO:0005979;GO:0006468;GO:0006809;GO:0006924;GO:0006979;GO:0007165;GO:0007173;GO:0007186;GO:0008283;GO:0008286;GO:0009408;GO:0009725;GO:0010507;GO:0010595;GO:0010628;GO:0010629;GO:0010748;GO:0010761;GO:0010907;GO:0010975;GO:0016242;GO:0018105;GO:0018107;GO:0019221;GO:0030154;GO:0030307;GO:0030334;GO:0030335;GO:0031295;GO:0031397;GO:0031929;GO:0031999;GO:0032079;GO:0032436;GO:0032869;GO:0033138;GO:0033554;GO:0034405;GO:0035556;GO:0035655;GO:0042307;GO:0042981;GO:0043066;GO:0043276;GO:0043488;GO:0043491;GO:0043536;GO:0045429;GO:0045600;GO:0045725;GO:0045746;GO:0045861;GO:0045944;GO:0046209;GO:0046326;GO:0046889;GO:0048009;GO:0048266;GO:0048661;GO:0051247;GO:0051897;GO:0060079;GO:0060416;GO:0060644;GO:0070141;GO:0070585;GO:0070848;GO:0071364;GO:0072656;GO:0072752;GO:0090201;GO:0097700;GO:0099175;GO:0110002;GO:0140052;GO:0150033;GO:0160049;GO:0160213;GO:1900087;GO:1900182;GO:1901796;GO:1902018;GO:1902176;GO:1903038;GO:1903078;GO:1903318;GO:1903384;GO:1903898;GO:1904263;GO:1904515;GO:1905552;GO:1905786;GO:1990090;GO:1990418;GO:2000010;GO:2000074;GO:2000402;GO:2001240;GO:2001243</t>
+          <t>GO:0000785;GO:0000976;GO:0000978;GO:0000981;GO:0001228;GO:0003677;GO:0003682;GO:0003700;GO:0004879;GO:0005102;GO:0005504;GO:0005515;GO:0005634;GO:0005654;GO:0005737;GO:0006355;GO:0006357;GO:0006805;GO:0007596;GO:0008270;GO:0008285;GO:0009749;GO:0019216;GO:0030154;GO:0030308;GO:0030522;GO:0042593;GO:0042632;GO:0042752;GO:0042803;GO:0043565;GO:0045892;GO:0045893;GO:0045944;GO:0050796;GO:0055088;GO:0055091;GO:0061629;GO:0070328;GO:1903268;GO:1990837</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>G protein-coupled receptor signaling pathway;T cell costimulation;TOR signaling;activation-induced cell death of T cells;anoikis;behavioral response to pain;beta-arrestin-dependent dopamine receptor signaling pathway;cell differentiation;cell migration involved in sprouting angiogenesis;cell population proliferation;cellular response to epidermal growth factor stimulus;cellular response to insulin stimulus;cellular response to nerve growth factor stimulus;cellular response to oxidised low-density lipoprotein particle stimulus;cellular response to rapamycin;cellular response to stress;complement receptor mediated signaling pathway;cytokine-mediated signaling pathway;epidermal growth factor receptor signaling pathway;excitatory postsynaptic potential;fibroblast migration;insulin receptor signaling pathway;insulin-like growth factor receptor signaling pathway;interleukin-18-mediated signaling pathway;intracellular signal transduction;maintenance of protein location in mitochondrion;mammary gland epithelial cell differentiation;negative regulation of Notch signaling pathway;negative regulation of PERK-mediated unfolded protein response;negative regulation of apoptotic process;negative regulation of autophagy;negative regulation of cGAS/STING signaling pathway;negative regulation of cilium assembly;negative regulation of extrinsic apoptotic signaling pathway in absence of ligand;negative regulation of fatty acid beta-oxidation;negative regulation of gene expression;negative regulation of hydrogen peroxide-induced neuron intrinsic apoptotic signaling pathway;negative regulation of intrinsic apoptotic signaling pathway;negative regulation of leukocyte cell-cell adhesion;negative regulation of long-chain fatty acid import across plasma membrane;negative regulation of lymphocyte migration;negative regulation of macroautophagy;negative regulation of oxidative stress-induced intrinsic apoptotic signaling pathway;negative regulation of protein localization to lysosome;negative regulation of protein maturation;negative regulation of protein ubiquitination;negative regulation of proteolysis;negative regulation of release of cytochrome c from mitochondria;nitric oxide biosynthetic process;nitric oxide metabolic process;osteoblast differentiation;peptidyl-serine phosphorylation;peptidyl-threonine phosphorylation;phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of D-glucose import across plasma membrane;positive regulation of G1/S transition of mitotic cell cycle;positive regulation of TORC1 signaling;positive regulation of TORC2 signaling;positive regulation of anaphase-promoting complex-dependent catabolic process;positive regulation of blood vessel endothelial cell migration;positive regulation of cell growth;positive regulation of cell migration;positive regulation of endodeoxyribonuclease activity;positive regulation of endothelial cell migration;positive regulation of endothelial cell proliferation;positive regulation of fat cell differentiation;positive regulation of gene expression;positive regulation of glucose metabolic process;positive regulation of glycogen biosynthetic process;positive regulation of lipid biosynthetic process;positive regulation of nitric oxide biosynthetic process;positive regulation of peptidyl-serine phosphorylation;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of proteasomal ubiquitin-dependent protein catabolic process;positive regulation of protein import into nucleus;positive regulation of protein localization to cell surface;positive regulation of protein localization to endoplasmic reticulum;positive regulation of protein localization to nucleus;positive regulation of protein localization to plasma membrane;positive regulation of protein metabolic process;positive regulation of smooth muscle cell proliferation;positive regulation of transcription by RNA polymerase II;protein localization to mitochondrion;protein phosphorylation;regulation of apoptotic process;regulation of cell migration;regulation of glycogen biosynthetic process;regulation of mRNA stability;regulation of neuron projection development;regulation of postsynapse organization;regulation of signal transduction by p53 class mediator;regulation of tRNA methylation;regulation of type B pancreatic cell development;response to UV-A;response to fluid shear stress;response to growth factor;response to growth hormone;response to heat;response to hormone;response to insulin-like growth factor stimulus;response to oxidative stress;signal transduction;sphingosine-1-phosphate receptor signaling pathway;vascular endothelial cell response to laminar fluid shear stress</t>
+          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;blood coagulation;cell differentiation;cholesterol homeostasis;chromatin;chromatin binding;cytoplasm;fatty acid binding;glucose homeostasis;intracellular receptor signaling pathway;lipid homeostasis;negative regulation of DNA-templated transcription;negative regulation of cell growth;negative regulation of cell population proliferation;nuclear receptor activity;nucleoplasm;nucleus;phospholipid homeostasis;positive regulation of DNA-templated transcription;positive regulation of ornithine catabolic process;positive regulation of transcription by RNA polymerase II;protein binding;protein homodimerization activity;regulation of DNA-templated transcription;regulation of circadian rhythm;regulation of insulin secretion;regulation of lipid metabolic process;regulation of transcription by RNA polymerase II;response to glucose;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;signaling receptor binding;transcription cis-regulatory region binding;triglyceride homeostasis;xenobiotic metabolic process;zinc ion binding</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>GO:0004672;GO:0004674;GO:0004712;GO:0005515;GO:0005516;GO:0005524;GO:0005547;GO:0016301;GO:0019899;GO:0019900;GO:0019901;GO:0030235;GO:0030291;GO:0042802;GO:0042803;GO:0043325;GO:0071889;GO:0099104;GO:0106310;GO:1904841</t>
+          <t>GO:0006355;GO:0006357;GO:0006805;GO:0007596;GO:0008285;GO:0009749;GO:0019216;GO:0030154;GO:0030308;GO:0030522;GO:0042593;GO:0042632;GO:0042752;GO:0045892;GO:0045893;GO:0045944;GO:0050796;GO:0055088;GO:0055091;GO:0070328;GO:1903268</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>14-3-3 protein binding;ATP binding;TORC2 complex binding;calmodulin binding;enzyme binding;identical protein binding;kinase activity;kinase binding;nitric-oxide synthase regulator activity;phosphatidylinositol-3,4,5-trisphosphate binding;phosphatidylinositol-3,4-bisphosphate binding;potassium channel activator activity;protein binding;protein homodimerization activity;protein kinase activity;protein kinase binding;protein serine kinase activity;protein serine/threonine kinase activity;protein serine/threonine kinase inhibitor activity;protein serine/threonine/tyrosine kinase activity</t>
+          <t>blood coagulation;cell differentiation;cholesterol homeostasis;glucose homeostasis;intracellular receptor signaling pathway;lipid homeostasis;negative regulation of DNA-templated transcription;negative regulation of cell growth;negative regulation of cell population proliferation;phospholipid homeostasis;positive regulation of DNA-templated transcription;positive regulation of ornithine catabolic process;positive regulation of transcription by RNA polymerase II;regulation of DNA-templated transcription;regulation of circadian rhythm;regulation of insulin secretion;regulation of lipid metabolic process;regulation of transcription by RNA polymerase II;response to glucose;triglyceride homeostasis;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>GO:0005634;GO:0005654;GO:0005737;GO:0005739;GO:0005758;GO:0005819;GO:0005829;GO:0005886;GO:0005911;GO:0005938;GO:0016020;GO:0030027;GO:0031982;GO:0032991;GO:0036064;GO:0098794;GO:0098978</t>
+          <t>GO:0000976;GO:0000978;GO:0000981;GO:0001228;GO:0003677;GO:0003682;GO:0003700;GO:0004879;GO:0005102;GO:0005504;GO:0005515;GO:0008270;GO:0042803;GO:0043565;GO:0061629;GO:1990837</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>cell cortex;cell-cell junction;ciliary basal body;cytoplasm;cytosol;glutamatergic synapse;lamellipodium;membrane;mitochondrial intermembrane space;mitochondrion;nucleoplasm;nucleus;plasma membrane;postsynapse;protein-containing complex;spindle;vesicle</t>
+          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;chromatin binding;fatty acid binding;nuclear receptor activity;protein binding;protein homodimerization activity;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;signaling receptor binding;transcription cis-regulatory region binding;zinc ion binding</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>GO:0000785;GO:0005634;GO:0005654;GO:0005737</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>chromatin;cytoplasm;nucleoplasm;nucleus</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>P38606</t>
+          <t>P55318</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2909,75 +3099,81 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ATP6V1A</t>
+          <t>FOXA3</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>523</v>
+        <v>3171</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>41</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>GO:0000139;GO:0000221;GO:0005515;GO:0005524;GO:0005737;GO:0005764;GO:0005765;GO:0005774;GO:0005829;GO:0005886;GO:0005902;GO:0006879;GO:0007035;GO:0007042;GO:0010008;GO:0015078;GO:0016020;GO:0016241;GO:0016324;GO:0016469;GO:0016887;GO:0030133;GO:0030141;GO:0030665;GO:0033176;GO:0033180;GO:0036295;GO:0042592;GO:0046034;GO:0046611;GO:0046961;GO:0048388;GO:0051452;GO:0061795;GO:0070062;GO:0071230;GO:0097401;GO:0098850;GO:0160124;GO:1902600;GO:1904263</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>ATP binding;ATP hydrolysis activity;ATP metabolic process;Golgi lumen acidification;Golgi membrane;apical plasma membrane;cellular response to amino acid stimulus;cellular response to increased oxygen levels;clathrin-coated vesicle membrane;cytoplasm;cytosol;endosomal lumen acidification;endosome membrane;extracellular exosome;extrinsic component of synaptic vesicle membrane;guanyl nucleotide exchange factor activator activity;homeostatic process;intracellular iron ion homeostasis;intracellular pH reduction;lysosomal lumen acidification;lysosomal membrane;lysosomal proton-transporting V-type ATPase complex;lysosome;membrane;microvillus;plasma membrane;positive regulation of TORC1 signaling;protein binding;proton transmembrane transport;proton transmembrane transporter activity;proton-transporting ATPase activity, rotational mechanism;proton-transporting V-type ATPase complex;proton-transporting V-type ATPase, V1 domain;proton-transporting two-sector ATPase complex;regulation of macroautophagy;secretory granule;synaptic vesicle lumen acidification;transport vesicle;vacuolar acidification;vacuolar membrane;vacuolar proton-transporting V-type ATPase, V1 domain</t>
-        </is>
+      <c r="M32" t="n">
+        <v>19</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GO:0006879;GO:0007035;GO:0007042;GO:0016241;GO:0036295;GO:0042592;GO:0046034;GO:0048388;GO:0051452;GO:0061795;GO:0071230;GO:0097401;GO:1902600;GO:1904263</t>
+          <t>GO:0000785;GO:0000976;GO:0000978;GO:0000981;GO:0001678;GO:0003677;GO:0003700;GO:0005515;GO:0005634;GO:0005654;GO:0006355;GO:0006357;GO:0007283;GO:0009653;GO:0019904;GO:0030154;GO:0043565;GO:0045944;GO:1990837</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>ATP metabolic process;Golgi lumen acidification;cellular response to amino acid stimulus;cellular response to increased oxygen levels;endosomal lumen acidification;homeostatic process;intracellular iron ion homeostasis;intracellular pH reduction;lysosomal lumen acidification;positive regulation of TORC1 signaling;proton transmembrane transport;regulation of macroautophagy;synaptic vesicle lumen acidification;vacuolar acidification</t>
+          <t>DNA binding;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;anatomical structure morphogenesis;cell differentiation;chromatin;intracellular glucose homeostasis;nucleoplasm;nucleus;positive regulation of transcription by RNA polymerase II;protein binding;protein domain specific binding;regulation of DNA-templated transcription;regulation of transcription by RNA polymerase II;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;spermatogenesis;transcription cis-regulatory region binding</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>GO:0005515;GO:0005524;GO:0015078;GO:0016887;GO:0046961;GO:0160124</t>
+          <t>GO:0001678;GO:0006355;GO:0006357;GO:0007283;GO:0009653;GO:0030154;GO:0045944</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>ATP binding;ATP hydrolysis activity;guanyl nucleotide exchange factor activator activity;protein binding;proton transmembrane transporter activity;proton-transporting ATPase activity, rotational mechanism</t>
+          <t>anatomical structure morphogenesis;cell differentiation;intracellular glucose homeostasis;positive regulation of transcription by RNA polymerase II;regulation of DNA-templated transcription;regulation of transcription by RNA polymerase II;spermatogenesis</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>GO:0000139;GO:0000221;GO:0005737;GO:0005764;GO:0005765;GO:0005774;GO:0005829;GO:0005886;GO:0005902;GO:0010008;GO:0016020;GO:0016324;GO:0016469;GO:0030133;GO:0030141;GO:0030665;GO:0033176;GO:0033180;GO:0046611;GO:0070062;GO:0098850</t>
+          <t>GO:0000976;GO:0000978;GO:0000981;GO:0003677;GO:0003700;GO:0005515;GO:0019904;GO:0043565;GO:1990837</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Golgi membrane;apical plasma membrane;clathrin-coated vesicle membrane;cytoplasm;cytosol;endosome membrane;extracellular exosome;extrinsic component of synaptic vesicle membrane;lysosomal membrane;lysosomal proton-transporting V-type ATPase complex;lysosome;membrane;microvillus;plasma membrane;proton-transporting V-type ATPase complex;proton-transporting V-type ATPase, V1 domain;proton-transporting two-sector ATPase complex;secretory granule;transport vesicle;vacuolar membrane;vacuolar proton-transporting V-type ATPase, V1 domain</t>
+          <t>DNA binding;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;protein binding;protein domain specific binding;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;transcription cis-regulatory region binding</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>GO:0000785;GO:0005634;GO:0005654</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>chromatin;nucleoplasm;nucleus</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P42574</t>
+          <t>Q12770</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2988,75 +3184,81 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CASP3</t>
+          <t>SCAP</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>836</v>
+        <v>22937</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>72</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>GO:0001554;GO:0001666;GO:0001818;GO:0002020;GO:0004175;GO:0004190;GO:0004197;GO:0004861;GO:0005123;GO:0005515;GO:0005634;GO:0005654;GO:0005737;GO:0005829;GO:0006508;GO:0006915;GO:0007413;GO:0007611;GO:0008047;GO:0008233;GO:0008234;GO:0008627;GO:0009410;GO:0009749;GO:0010038;GO:0010165;GO:0014069;GO:0016005;GO:0016241;GO:0016485;GO:0021766;GO:0030163;GO:0030182;GO:0030216;GO:0030218;GO:0030220;GO:0031264;GO:0031647;GO:0032025;GO:0032355;GO:0032496;GO:0032880;GO:0034349;GO:0034612;GO:0035094;GO:0035556;GO:0036269;GO:0042542;GO:0043025;GO:0043065;GO:0043200;GO:0043523;GO:0043525;GO:0044877;GO:0045471;GO:0048011;GO:0051146;GO:0051384;GO:0051604;GO:0070269;GO:0071887;GO:0072347;GO:0072734;GO:0097190;GO:0097193;GO:0097194;GO:0098693;GO:0098883;GO:0098978;GO:0140639;GO:1902004;GO:1990418</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>apoptotic process;apoptotic signaling pathway;aspartic-type endopeptidase activity;axonal fasciculation;cellular response to staurosporine;cyclin-dependent protein serine/threonine kinase inhibitor activity;cysteine-type endopeptidase activity;cysteine-type peptidase activity;cytoplasm;cytosol;death receptor binding;death-inducing signaling complex;endopeptidase activity;enzyme activator activity;erythrocyte differentiation;execution phase of apoptosis;glial cell apoptotic process;glutamatergic synapse;hippocampus development;intracellular signal transduction;intrinsic apoptotic signaling pathway;intrinsic apoptotic signaling pathway in response to osmotic stress;keratinocyte differentiation;learning or memory;leukocyte apoptotic process;luteolysis;negative regulation of cytokine production;neuron differentiation;neuronal cell body;neurotrophin TRK receptor signaling pathway;nucleoplasm;nucleus;peptidase activity;phospholipase A2 activator activity;platelet formation;positive regulation of amyloid-beta formation;positive regulation of apoptotic process;positive regulation of neuron apoptotic process;positive regulation of pyroptotic inflammatory response;postsynaptic density;protease binding;protein binding;protein catabolic process;protein maturation;protein processing;protein-containing complex binding;proteolysis;pyroptotic inflammatory response;regulation of macroautophagy;regulation of neuron apoptotic process;regulation of protein localization;regulation of protein stability;regulation of synaptic vesicle cycle;response to X-ray;response to amino acid;response to anesthetic;response to cobalt ion;response to estradiol;response to ethanol;response to glucocorticoid;response to glucose;response to hydrogen peroxide;response to hypoxia;response to insulin-like growth factor stimulus;response to lipopolysaccharide;response to metal ion;response to nicotine;response to tumor necrosis factor;response to xenobiotic stimulus;striated muscle cell differentiation;swimming behavior;synapse pruning</t>
-        </is>
+      <c r="M33" t="n">
+        <v>19</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GO:0001554;GO:0001666;GO:0001818;GO:0006508;GO:0006915;GO:0007413;GO:0007611;GO:0008627;GO:0009410;GO:0009749;GO:0010038;GO:0010165;GO:0016241;GO:0016485;GO:0021766;GO:0030163;GO:0030182;GO:0030216;GO:0030218;GO:0030220;GO:0031647;GO:0032025;GO:0032355;GO:0032496;GO:0032880;GO:0034349;GO:0034612;GO:0035094;GO:0035556;GO:0036269;GO:0042542;GO:0043065;GO:0043200;GO:0043523;GO:0043525;GO:0045471;GO:0048011;GO:0051146;GO:0051384;GO:0051604;GO:0070269;GO:0071887;GO:0072347;GO:0072734;GO:0097190;GO:0097193;GO:0097194;GO:0098693;GO:0098883;GO:0140639;GO:1902004;GO:1990418</t>
+          <t>GO:0000139;GO:0005515;GO:0005783;GO:0005789;GO:0005794;GO:0006357;GO:0008203;GO:0012507;GO:0016020;GO:0032933;GO:0032934;GO:0032936;GO:0032991;GO:0033552;GO:0044877;GO:0045540;GO:0045541;GO:0045542;GO:0090110</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>apoptotic process;apoptotic signaling pathway;axonal fasciculation;cellular response to staurosporine;erythrocyte differentiation;execution phase of apoptosis;glial cell apoptotic process;hippocampus development;intracellular signal transduction;intrinsic apoptotic signaling pathway;intrinsic apoptotic signaling pathway in response to osmotic stress;keratinocyte differentiation;learning or memory;leukocyte apoptotic process;luteolysis;negative regulation of cytokine production;neuron differentiation;neurotrophin TRK receptor signaling pathway;platelet formation;positive regulation of amyloid-beta formation;positive regulation of apoptotic process;positive regulation of neuron apoptotic process;positive regulation of pyroptotic inflammatory response;protein catabolic process;protein maturation;protein processing;proteolysis;pyroptotic inflammatory response;regulation of macroautophagy;regulation of neuron apoptotic process;regulation of protein localization;regulation of protein stability;regulation of synaptic vesicle cycle;response to X-ray;response to amino acid;response to anesthetic;response to cobalt ion;response to estradiol;response to ethanol;response to glucocorticoid;response to glucose;response to hydrogen peroxide;response to hypoxia;response to insulin-like growth factor stimulus;response to lipopolysaccharide;response to metal ion;response to nicotine;response to tumor necrosis factor;response to xenobiotic stimulus;striated muscle cell differentiation;swimming behavior;synapse pruning</t>
+          <t>COPII-coated vesicle cargo loading;ER to Golgi transport vesicle membrane;Golgi apparatus;Golgi membrane;SREBP signaling pathway;SREBP-SCAP complex;cholesterol metabolic process;endoplasmic reticulum;endoplasmic reticulum membrane;membrane;negative regulation of cholesterol biosynthetic process;positive regulation of cholesterol biosynthetic process;protein binding;protein-containing complex;protein-containing complex binding;regulation of cholesterol biosynthetic process;regulation of transcription by RNA polymerase II;response to vitamin B3;sterol binding</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>GO:0002020;GO:0004175;GO:0004190;GO:0004197;GO:0004861;GO:0005123;GO:0005515;GO:0008047;GO:0008233;GO:0008234;GO:0016005;GO:0044877</t>
+          <t>GO:0006357;GO:0008203;GO:0032933;GO:0033552;GO:0045540;GO:0045541;GO:0045542;GO:0090110</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>aspartic-type endopeptidase activity;cyclin-dependent protein serine/threonine kinase inhibitor activity;cysteine-type endopeptidase activity;cysteine-type peptidase activity;death receptor binding;endopeptidase activity;enzyme activator activity;peptidase activity;phospholipase A2 activator activity;protease binding;protein binding;protein-containing complex binding</t>
+          <t>COPII-coated vesicle cargo loading;SREBP signaling pathway;cholesterol metabolic process;negative regulation of cholesterol biosynthetic process;positive regulation of cholesterol biosynthetic process;regulation of cholesterol biosynthetic process;regulation of transcription by RNA polymerase II;response to vitamin B3</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>GO:0005634;GO:0005654;GO:0005737;GO:0005829;GO:0014069;GO:0031264;GO:0043025;GO:0098978</t>
+          <t>GO:0005515;GO:0032934;GO:0044877</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>cytoplasm;cytosol;death-inducing signaling complex;glutamatergic synapse;neuronal cell body;nucleoplasm;nucleus;postsynaptic density</t>
+          <t>protein binding;protein-containing complex binding;sterol binding</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>GO:0000139;GO:0005783;GO:0005789;GO:0005794;GO:0012507;GO:0016020;GO:0032936;GO:0032991</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>ER to Golgi transport vesicle membrane;Golgi apparatus;Golgi membrane;SREBP-SCAP complex;endoplasmic reticulum;endoplasmic reticulum membrane;membrane;protein-containing complex</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P49588</t>
+          <t>Q13547</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -3067,75 +3269,81 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>bethanechol</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AARS1</t>
+          <t>HDAC1</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
+        <v>3065</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>25</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>GO:0000049;GO:0000166;GO:0002161;GO:0002196;GO:0003676;GO:0004812;GO:0004813;GO:0005524;GO:0005634;GO:0005737;GO:0005829;GO:0006400;GO:0006418;GO:0006419;GO:0008033;GO:0008270;GO:0016020;GO:0016597;GO:0035332;GO:0043039;GO:0070062;GO:0106074;GO:0140018;GO:0141207;GO:1901797</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>ATP binding;Ser-tRNA(Ala) deacylase activity;alanine-tRNA ligase activity;alanyl-tRNA aminoacylation;amino acid binding;aminoacyl-tRNA deacylase activity;aminoacyl-tRNA ligase activity;aminoacyl-tRNA metabolism involved in translational fidelity;cytoplasm;cytosol;extracellular exosome;membrane;negative regulation of signal transduction by p53 class mediator;nucleic acid binding;nucleotide binding;nucleus;peptide lactyltransferase (ATP-dependent) activity;positive regulation of hippo signaling;regulation of cytoplasmic translational fidelity;tRNA aminoacylation;tRNA aminoacylation for protein translation;tRNA binding;tRNA modification;tRNA processing;zinc ion binding</t>
-        </is>
+      <c r="M34" t="n">
+        <v>76</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>GO:0006400;GO:0006418;GO:0006419;GO:0008033;GO:0035332;GO:0043039;GO:0106074;GO:0140018;GO:1901797</t>
+          <t>GO:0000118;GO:0000122;GO:0000785;GO:0000792;GO:0000976;GO:0000978;GO:0000979;GO:0001046;GO:0001222;GO:0002039;GO:0003677;GO:0003682;GO:0003714;GO:0004407;GO:0005515;GO:0005634;GO:0005654;GO:0005667;GO:0005737;GO:0005829;GO:0006325;GO:0006338;GO:0006346;GO:0006357;GO:0007623;GO:0008284;GO:0009913;GO:0010628;GO:0010629;GO:0010832;GO:0016581;GO:0016811;GO:0017053;GO:0019899;GO:0030336;GO:0030512;GO:0031492;GO:0031507;GO:0032922;GO:0032991;GO:0033148;GO:0033558;GO:0035851;GO:0036120;GO:0042475;GO:0042659;GO:0042733;GO:0042826;GO:0043025;GO:0043066;GO:0043922;GO:0045814;GO:0045892;GO:0045893;GO:0045944;GO:0045995;GO:0048661;GO:0051059;GO:0060766;GO:0060789;GO:0061029;GO:0061198;GO:0061629;GO:0070822;GO:0070888;GO:0090090;GO:0140297;GO:0141221;GO:0160008;GO:0160009;GO:0160216;GO:1902455;GO:1902459;GO:1990841;GO:1990904;GO:2000736</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>alanyl-tRNA aminoacylation;aminoacyl-tRNA metabolism involved in translational fidelity;negative regulation of signal transduction by p53 class mediator;positive regulation of hippo signaling;regulation of cytoplasmic translational fidelity;tRNA aminoacylation;tRNA aminoacylation for protein translation;tRNA modification;tRNA processing</t>
+          <t>DNA binding;DNA methylation-dependent constitutive heterochromatin formation;DNA-binding transcription factor binding;E-box binding;Krueppel-associated box domain binding;NF-kappaB binding;NuRD complex;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II core promoter sequence-specific DNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;Sin3-type complex;cellular response to platelet-derived growth factor stimulus;chromatin;chromatin binding;chromatin organization;chromatin remodeling;circadian regulation of gene expression;circadian rhythm;core promoter sequence-specific DNA binding;cytoplasm;cytosol;embryonic digit morphogenesis;enzyme binding;epidermal cell differentiation;eyelid development in camera-type eye;fungiform papilla formation;hair follicle placode formation;heterochromatin;heterochromatin formation;histone deacetylase activity;histone deacetylase activity, hydrolytic mechanism;histone deacetylase binding;histone deacetylase complex;histone decrotonylase activity;host-mediated suppression of viral transcription;hydrolase activity, acting on carbon-nitrogen (but not peptide) bonds, in linear amides;negative regulation of DNA-templated transcription;negative regulation of androgen receptor signaling pathway;negative regulation of apoptotic process;negative regulation of canonical Wnt signaling pathway;negative regulation of cell migration;negative regulation of gene expression;negative regulation of gene expression, epigenetic;negative regulation of myotube differentiation;negative regulation of stem cell population maintenance;negative regulation of transcription by RNA polymerase II;negative regulation of transforming growth factor beta receptor signaling pathway;neuronal cell body;nucleoplasm;nucleosomal DNA binding;nucleus;odontogenesis of dentin-containing tooth;p53 binding;positive regulation of DNA-templated transcription;positive regulation of cell population proliferation;positive regulation of gene expression;positive regulation of intracellular estrogen receptor signaling pathway;positive regulation of smooth muscle cell proliferation;positive regulation of stem cell population maintenance;positive regulation of transcription by RNA polymerase II;promoter-specific chromatin binding;protein binding;protein decrotonylase activity;protein lysine deacetylase activity;protein lysine delactylase activity;protein-containing complex;regulation of cell fate specification;regulation of embryonic development;regulation of stem cell differentiation;regulation of transcription by RNA polymerase II;ribonucleoprotein complex;transcription cis-regulatory region binding;transcription corepressor activity;transcription corepressor binding;transcription regulator complex;transcription repressor complex</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>GO:0000049;GO:0000166;GO:0002161;GO:0002196;GO:0003676;GO:0004812;GO:0004813;GO:0005524;GO:0008270;GO:0016597;GO:0141207</t>
+          <t>GO:0000122;GO:0006325;GO:0006338;GO:0006346;GO:0006357;GO:0007623;GO:0008284;GO:0009913;GO:0010628;GO:0010629;GO:0010832;GO:0030336;GO:0030512;GO:0031507;GO:0032922;GO:0033148;GO:0036120;GO:0042475;GO:0042659;GO:0042733;GO:0043066;GO:0043922;GO:0045814;GO:0045892;GO:0045893;GO:0045944;GO:0045995;GO:0048661;GO:0060766;GO:0060789;GO:0061029;GO:0061198;GO:0090090;GO:1902455;GO:1902459;GO:2000736</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>ATP binding;Ser-tRNA(Ala) deacylase activity;alanine-tRNA ligase activity;amino acid binding;aminoacyl-tRNA deacylase activity;aminoacyl-tRNA ligase activity;nucleic acid binding;nucleotide binding;peptide lactyltransferase (ATP-dependent) activity;tRNA binding;zinc ion binding</t>
+          <t>DNA methylation-dependent constitutive heterochromatin formation;cellular response to platelet-derived growth factor stimulus;chromatin organization;chromatin remodeling;circadian regulation of gene expression;circadian rhythm;embryonic digit morphogenesis;epidermal cell differentiation;eyelid development in camera-type eye;fungiform papilla formation;hair follicle placode formation;heterochromatin formation;host-mediated suppression of viral transcription;negative regulation of DNA-templated transcription;negative regulation of androgen receptor signaling pathway;negative regulation of apoptotic process;negative regulation of canonical Wnt signaling pathway;negative regulation of cell migration;negative regulation of gene expression;negative regulation of gene expression, epigenetic;negative regulation of myotube differentiation;negative regulation of stem cell population maintenance;negative regulation of transcription by RNA polymerase II;negative regulation of transforming growth factor beta receptor signaling pathway;odontogenesis of dentin-containing tooth;positive regulation of DNA-templated transcription;positive regulation of cell population proliferation;positive regulation of gene expression;positive regulation of intracellular estrogen receptor signaling pathway;positive regulation of smooth muscle cell proliferation;positive regulation of stem cell population maintenance;positive regulation of transcription by RNA polymerase II;regulation of cell fate specification;regulation of embryonic development;regulation of stem cell differentiation;regulation of transcription by RNA polymerase II</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>GO:0005634;GO:0005737;GO:0005829;GO:0016020;GO:0070062</t>
+          <t>GO:0000976;GO:0000978;GO:0000979;GO:0001046;GO:0001222;GO:0002039;GO:0003677;GO:0003682;GO:0003714;GO:0004407;GO:0005515;GO:0016811;GO:0019899;GO:0031492;GO:0033558;GO:0035851;GO:0042826;GO:0051059;GO:0061629;GO:0070888;GO:0140297;GO:0141221;GO:0160008;GO:0160009;GO:0160216;GO:1990841</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>cytoplasm;cytosol;extracellular exosome;membrane;nucleus</t>
+          <t>DNA binding;DNA-binding transcription factor binding;E-box binding;Krueppel-associated box domain binding;NF-kappaB binding;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II core promoter sequence-specific DNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;chromatin binding;core promoter sequence-specific DNA binding;enzyme binding;histone deacetylase activity;histone deacetylase activity, hydrolytic mechanism;histone deacetylase binding;histone decrotonylase activity;hydrolase activity, acting on carbon-nitrogen (but not peptide) bonds, in linear amides;nucleosomal DNA binding;p53 binding;promoter-specific chromatin binding;protein binding;protein decrotonylase activity;protein lysine deacetylase activity;protein lysine delactylase activity;transcription cis-regulatory region binding;transcription corepressor activity;transcription corepressor binding</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>GO:0000118;GO:0000785;GO:0000792;GO:0005634;GO:0005654;GO:0005667;GO:0005737;GO:0005829;GO:0016581;GO:0017053;GO:0032991;GO:0043025;GO:0070822;GO:1990904</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>NuRD complex;Sin3-type complex;chromatin;cytoplasm;cytosol;heterochromatin;histone deacetylase complex;neuronal cell body;nucleoplasm;nucleus;protein-containing complex;ribonucleoprotein complex;transcription regulator complex;transcription repressor complex</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P51798</t>
+          <t>Q13698</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -3146,75 +3354,81 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CLCN7</t>
+          <t>CACNA1S</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1186</v>
+        <v>779</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K35" t="n">
-        <v>14</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>GO:0005254;GO:0005515;GO:0005765;GO:0005770;GO:0006821;GO:0009268;GO:0015108;GO:0016020;GO:0030321;GO:0034707;GO:0055085;GO:0062158;GO:1902476;GO:1902600</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>chloride channel activity;chloride channel complex;chloride transmembrane transport;chloride transmembrane transporter activity;chloride transport;chloride:proton antiporter activity;late endosome;lysosomal membrane;membrane;protein binding;proton transmembrane transport;response to pH;transepithelial chloride transport;transmembrane transport</t>
-        </is>
+      <c r="M35" t="n">
+        <v>22</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>GO:0006821;GO:0009268;GO:0030321;GO:0055085;GO:1902476;GO:1902600</t>
+          <t>GO:0005216;GO:0005245;GO:0005515;GO:0005737;GO:0005886;GO:0005891;GO:0006811;GO:0006816;GO:0006936;GO:0008331;GO:0016020;GO:0030315;GO:0031674;GO:0036094;GO:0045933;GO:0051209;GO:0055085;GO:0070588;GO:0071313;GO:0098703;GO:0140677;GO:1990454</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>chloride transmembrane transport;chloride transport;proton transmembrane transport;response to pH;transepithelial chloride transport;transmembrane transport</t>
+          <t>I band;L-type voltage-gated calcium channel complex;T-tubule;calcium ion import across plasma membrane;calcium ion transmembrane transport;calcium ion transport;cellular response to caffeine;cytoplasm;high voltage-gated calcium channel activity;membrane;molecular function activator activity;monoatomic ion channel activity;monoatomic ion transport;muscle contraction;plasma membrane;positive regulation of muscle contraction;protein binding;release of sequestered calcium ion into cytosol;small molecule binding;transmembrane transport;voltage-gated calcium channel activity;voltage-gated calcium channel complex</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>GO:0005254;GO:0005515;GO:0015108;GO:0062158</t>
+          <t>GO:0006811;GO:0006816;GO:0006936;GO:0045933;GO:0051209;GO:0055085;GO:0070588;GO:0071313;GO:0098703</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>chloride channel activity;chloride transmembrane transporter activity;chloride:proton antiporter activity;protein binding</t>
+          <t>calcium ion import across plasma membrane;calcium ion transmembrane transport;calcium ion transport;cellular response to caffeine;monoatomic ion transport;muscle contraction;positive regulation of muscle contraction;release of sequestered calcium ion into cytosol;transmembrane transport</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>GO:0005765;GO:0005770;GO:0016020;GO:0034707</t>
+          <t>GO:0005216;GO:0005245;GO:0005515;GO:0008331;GO:0036094;GO:0140677</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>chloride channel complex;late endosome;lysosomal membrane;membrane</t>
+          <t>high voltage-gated calcium channel activity;molecular function activator activity;monoatomic ion channel activity;protein binding;small molecule binding;voltage-gated calcium channel activity</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005886;GO:0005891;GO:0016020;GO:0030315;GO:0031674;GO:1990454</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>I band;L-type voltage-gated calcium channel complex;T-tubule;cytoplasm;membrane;plasma membrane;voltage-gated calcium channel complex</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P57764</t>
+          <t>Q14973</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -3225,75 +3439,81 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GSDMD</t>
+          <t>SLC10A1</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>79792</v>
+        <v>6554</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K36" t="n">
-        <v>31</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>GO:0001786;GO:0005515;GO:0005546;GO:0005576;GO:0005615;GO:0005634;GO:0005654;GO:0005829;GO:0005886;GO:0009306;GO:0016020;GO:0022829;GO:0031966;GO:0032731;GO:0035580;GO:0042742;GO:0046931;GO:0050729;GO:0050829;GO:0050830;GO:0051260;GO:0055085;GO:0061702;GO:0070269;GO:0070273;GO:0070300;GO:0072559;GO:0141201;GO:1901612;GO:1904724;GO:1904813</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>NLRP3 inflammasome complex;canonical inflammasome complex;cardiolipin binding;cytosol;defense response to Gram-negative bacterium;defense response to Gram-positive bacterium;defense response to bacterium;extracellular region;ficolin-1-rich granule lumen;membrane;mitochondrial membrane;nucleoplasm;nucleus;obsolete extracellular space;phosphatidic acid binding;phosphatidylinositol-4,5-bisphosphate binding;phosphatidylinositol-4-phosphate binding;phosphatidylserine binding;plasma membrane;pore complex assembly;positive regulation of inflammatory response;positive regulation of interleukin-1 beta production;protein binding;protein homooligomerization;protein secretion;pyroptotic cell death;pyroptotic inflammatory response;specific granule lumen;tertiary granule lumen;transmembrane transport;wide pore channel activity</t>
-        </is>
+      <c r="M36" t="n">
+        <v>11</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>GO:0009306;GO:0032731;GO:0042742;GO:0046931;GO:0050729;GO:0050829;GO:0050830;GO:0051260;GO:0055085;GO:0070269;GO:0141201</t>
+          <t>GO:0005515;GO:0005886;GO:0008508;GO:0015125;GO:0015721;GO:0016020;GO:0016323;GO:0031667;GO:0043627;GO:0045471;GO:0071466</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>defense response to Gram-negative bacterium;defense response to Gram-positive bacterium;defense response to bacterium;pore complex assembly;positive regulation of inflammatory response;positive regulation of interleukin-1 beta production;protein homooligomerization;protein secretion;pyroptotic cell death;pyroptotic inflammatory response;transmembrane transport</t>
+          <t>basolateral plasma membrane;bile acid and bile salt transport;bile acid transmembrane transporter activity;bile acid:sodium symporter activity;cellular response to xenobiotic stimulus;membrane;plasma membrane;protein binding;response to estrogen;response to ethanol;response to nutrient levels</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>GO:0001786;GO:0005515;GO:0005546;GO:0022829;GO:0070273;GO:0070300;GO:1901612</t>
+          <t>GO:0015721;GO:0031667;GO:0043627;GO:0045471;GO:0071466</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>cardiolipin binding;phosphatidic acid binding;phosphatidylinositol-4,5-bisphosphate binding;phosphatidylinositol-4-phosphate binding;phosphatidylserine binding;protein binding;wide pore channel activity</t>
+          <t>bile acid and bile salt transport;cellular response to xenobiotic stimulus;response to estrogen;response to ethanol;response to nutrient levels</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>GO:0005576;GO:0005615;GO:0005634;GO:0005654;GO:0005829;GO:0005886;GO:0016020;GO:0031966;GO:0035580;GO:0061702;GO:0072559;GO:1904724;GO:1904813</t>
+          <t>GO:0005515;GO:0008508;GO:0015125</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>NLRP3 inflammasome complex;canonical inflammasome complex;cytosol;extracellular region;ficolin-1-rich granule lumen;membrane;mitochondrial membrane;nucleoplasm;nucleus;obsolete extracellular space;plasma membrane;specific granule lumen;tertiary granule lumen</t>
+          <t>bile acid transmembrane transporter activity;bile acid:sodium symporter activity;protein binding</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0016020;GO:0016323</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>basolateral plasma membrane;membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Q00168</t>
+          <t>Q14994</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -3304,75 +3524,81 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CAMKII</t>
+          <t>NR1I3</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>43828</v>
+        <v>9970</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K37" t="n">
-        <v>34</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>GO:0001818;GO:0004672;GO:0004674;GO:0004683;GO:0005515;GO:0005516;GO:0005524;GO:0005737;GO:0007154;GO:0007268;GO:0007528;GO:0007611;GO:0007613;GO:0007616;GO:0007619;GO:0008049;GO:0008582;GO:0009267;GO:0010468;GO:0010888;GO:0014069;GO:0023052;GO:0030424;GO:0030425;GO:0032226;GO:0043005;GO:0045211;GO:0048168;GO:0048786;GO:0051489;GO:0060278;GO:0106310;GO:1903076;GO:2001234</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>ATP binding;axon;calcium/calmodulin-dependent protein kinase activity;calmodulin binding;cell communication;cellular response to starvation;chemical synaptic transmission;courtship behavior;cytoplasm;dendrite;learning or memory;long-term memory;male courtship behavior;memory;negative regulation of apoptotic signaling pathway;negative regulation of cytokine production;negative regulation of lipid storage;neuromuscular junction development;neuron projection;positive regulation of synaptic transmission, dopaminergic;postsynaptic density;postsynaptic membrane;presynaptic active zone;protein binding;protein kinase activity;protein serine kinase activity;protein serine/threonine kinase activity;regulation of filopodium assembly;regulation of gene expression;regulation of neuronal synaptic plasticity;regulation of ovulation;regulation of protein localization to plasma membrane;regulation of synaptic assembly at neuromuscular junction;signaling</t>
-        </is>
+      <c r="M37" t="n">
+        <v>23</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>GO:0001818;GO:0007154;GO:0007268;GO:0007528;GO:0007611;GO:0007613;GO:0007616;GO:0007619;GO:0008049;GO:0008582;GO:0009267;GO:0010468;GO:0010888;GO:0023052;GO:0032226;GO:0048168;GO:0051489;GO:0060278;GO:1903076;GO:2001234</t>
+          <t>GO:0000122;GO:0000785;GO:0000977;GO:0000978;GO:0000981;GO:0001228;GO:0001649;GO:0003677;GO:0003700;GO:0004879;GO:0005515;GO:0005634;GO:0005654;GO:0005737;GO:0005856;GO:0006355;GO:0007165;GO:0008270;GO:0030154;GO:0030522;GO:0043565;GO:0045944;GO:1990837</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>cell communication;cellular response to starvation;chemical synaptic transmission;courtship behavior;learning or memory;long-term memory;male courtship behavior;memory;negative regulation of apoptotic signaling pathway;negative regulation of cytokine production;negative regulation of lipid storage;neuromuscular junction development;positive regulation of synaptic transmission, dopaminergic;regulation of filopodium assembly;regulation of gene expression;regulation of neuronal synaptic plasticity;regulation of ovulation;regulation of protein localization to plasma membrane;regulation of synaptic assembly at neuromuscular junction;signaling</t>
+          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II transcription regulatory region sequence-specific DNA binding;cell differentiation;chromatin;cytoplasm;cytoskeleton;intracellular receptor signaling pathway;negative regulation of transcription by RNA polymerase II;nuclear receptor activity;nucleoplasm;nucleus;osteoblast differentiation;positive regulation of transcription by RNA polymerase II;protein binding;regulation of DNA-templated transcription;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;signal transduction;zinc ion binding</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>GO:0004672;GO:0004674;GO:0004683;GO:0005515;GO:0005516;GO:0005524;GO:0106310</t>
+          <t>GO:0000122;GO:0001649;GO:0006355;GO:0007165;GO:0030154;GO:0030522;GO:0045944</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>ATP binding;calcium/calmodulin-dependent protein kinase activity;calmodulin binding;protein binding;protein kinase activity;protein serine kinase activity;protein serine/threonine kinase activity</t>
+          <t>cell differentiation;intracellular receptor signaling pathway;negative regulation of transcription by RNA polymerase II;osteoblast differentiation;positive regulation of transcription by RNA polymerase II;regulation of DNA-templated transcription;signal transduction</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>GO:0005737;GO:0014069;GO:0030424;GO:0030425;GO:0043005;GO:0045211;GO:0048786</t>
+          <t>GO:0000977;GO:0000978;GO:0000981;GO:0001228;GO:0003677;GO:0003700;GO:0004879;GO:0005515;GO:0008270;GO:0043565;GO:1990837</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>axon;cytoplasm;dendrite;neuron projection;postsynaptic density;postsynaptic membrane;presynaptic active zone</t>
+          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II transcription regulatory region sequence-specific DNA binding;nuclear receptor activity;protein binding;sequence-specific DNA binding;sequence-specific double-stranded DNA binding;zinc ion binding</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>GO:0000785;GO:0005634;GO:0005654;GO:0005737;GO:0005856</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>chromatin;cytoplasm;cytoskeleton;nucleoplasm;nucleus</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Q04206</t>
+          <t>Q1W675</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -3383,75 +3609,81 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RELA</t>
+          <t>HMGCR</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5970</v>
+        <v>100144446</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K38" t="n">
-        <v>100</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>GO:0000122;GO:0000785;GO:0000976;GO:0000977;GO:0000978;GO:0000979;GO:0000981;GO:0001223;GO:0001227;GO:0001228;GO:0001818;GO:0001889;GO:0002357;GO:0003677;GO:0003682;GO:0003700;GO:0003713;GO:0005515;GO:0005634;GO:0005654;GO:0005667;GO:0005730;GO:0005737;GO:0005829;GO:0006325;GO:0006351;GO:0006355;GO:0006357;GO:0006954;GO:0006968;GO:0007218;GO:0007249;GO:0008284;GO:0010224;GO:0010575;GO:0010628;GO:0016525;GO:0019221;GO:0019899;GO:0019901;GO:0031490;GO:0031625;GO:0032731;GO:0032755;GO:0032757;GO:0033209;GO:0033234;GO:0034097;GO:0034142;GO:0035525;GO:0035556;GO:0038061;GO:0038084;GO:0038124;GO:0038161;GO:0042277;GO:0042301;GO:0042802;GO:0042803;GO:0042805;GO:0042826;GO:0043066;GO:0043123;GO:0043565;GO:0045087;GO:0045892;GO:0045893;GO:0045944;GO:0050727;GO:0051059;GO:0051607;GO:0070301;GO:0070431;GO:0070498;GO:0070555;GO:0071159;GO:0071222;GO:0071223;GO:0071224;GO:0071316;GO:0071347;GO:0071354;GO:0071356;GO:0071532;GO:0098978;GO:0099527;GO:0140296;GO:0140297;GO:0140374;GO:0140896;GO:1900016;GO:1900017;GO:1901223;GO:1902004;GO:1902894;GO:1902895;GO:1904385;GO:1904996;GO:2000630;GO:2001237</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;DNA-binding transcription factor binding;DNA-binding transcription repressor activity, RNA polymerase II-specific;DNA-templated transcription;NF-kappaB binding;NF-kappaB complex;NF-kappaB p50/p65 complex;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II core promoter sequence-specific DNA binding;RNA polymerase II transcription regulatory region sequence-specific DNA binding;actinin binding;ankyrin repeat binding;antiviral innate immune response;cGAS/STING signaling pathway;canonical NF-kappaB signal transduction;cellular defense response;cellular response to angiotensin;cellular response to hydrogen peroxide;cellular response to interleukin-1;cellular response to interleukin-6;cellular response to lipopolysaccharide;cellular response to lipoteichoic acid;cellular response to nicotine;cellular response to peptidoglycan;cellular response to tumor necrosis factor;chromatin;chromatin DNA binding;chromatin binding;chromatin organization;cytokine-mediated signaling pathway;cytoplasm;cytosol;defense response to tumor cell;defense response to virus;enzyme binding;general transcription initiation factor binding;glutamatergic synapse;histone deacetylase binding;identical protein binding;inflammatory response;innate immune response;interleukin-1-mediated signaling pathway;intracellular signal transduction;liver development;negative regulation of DNA-templated transcription;negative regulation of angiogenesis;negative regulation of apoptotic process;negative regulation of cytokine production;negative regulation of cytokine production involved in inflammatory response;negative regulation of extrinsic apoptotic signaling pathway;negative regulation of miRNA transcription;negative regulation of non-canonical NF-kappaB signal transduction;negative regulation of protein sumoylation;negative regulation of transcription by RNA polymerase II;neuropeptide signaling pathway;non-canonical NF-kappaB signal transduction;nucleolus;nucleoplasm;nucleotide-binding oligomerization domain containing 2 signaling pathway;nucleus;peptide binding;phosphate ion binding;positive regulation of DNA-templated transcription;positive regulation of amyloid-beta formation;positive regulation of canonical NF-kappaB signal transduction;positive regulation of cell population proliferation;positive regulation of cytokine production involved in inflammatory response;positive regulation of gene expression;positive regulation of interleukin-1 beta production;positive regulation of interleukin-6 production;positive regulation of interleukin-8 production;positive regulation of leukocyte adhesion to vascular endothelial cell;positive regulation of miRNA metabolic process;positive regulation of miRNA transcription;positive regulation of transcription by RNA polymerase II;positive regulation of vascular endothelial growth factor production;postsynapse to nucleus signaling pathway;prolactin signaling pathway;protein binding;protein homodimerization activity;protein kinase binding;regulation of DNA-templated transcription;regulation of inflammatory response;regulation of transcription by RNA polymerase II;response to UV-B;response to cytokine;response to interleukin-1;sequence-specific DNA binding;toll-like receptor 4 signaling pathway;toll-like receptor TLR6:TLR2 signaling pathway;transcription cis-regulatory region binding;transcription coactivator activity;transcription coactivator binding;transcription regulator complex;tumor necrosis factor-mediated signaling pathway;ubiquitin protein ligase binding;vascular endothelial growth factor signaling pathway</t>
-        </is>
+      <c r="M38" t="n">
+        <v>9</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>GO:0000122;GO:0001818;GO:0001889;GO:0002357;GO:0006325;GO:0006351;GO:0006355;GO:0006357;GO:0006954;GO:0006968;GO:0007218;GO:0007249;GO:0008284;GO:0010224;GO:0010575;GO:0010628;GO:0016525;GO:0019221;GO:0032731;GO:0032755;GO:0032757;GO:0033209;GO:0033234;GO:0034097;GO:0034142;GO:0035556;GO:0038061;GO:0038084;GO:0038124;GO:0038161;GO:0043066;GO:0043123;GO:0045087;GO:0045892;GO:0045893;GO:0045944;GO:0050727;GO:0051607;GO:0070301;GO:0070431;GO:0070498;GO:0070555;GO:0071222;GO:0071223;GO:0071224;GO:0071316;GO:0071347;GO:0071354;GO:0071356;GO:0099527;GO:0140374;GO:0140896;GO:1900016;GO:1900017;GO:1901223;GO:1902004;GO:1902894;GO:1902895;GO:1904385;GO:1904996;GO:2000630;GO:2001237</t>
+          <t>GO:0004420;GO:0005778;GO:0005783;GO:0005789;GO:0008299;GO:0015936;GO:0016126;GO:0016616;GO:0050661</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>DNA-templated transcription;antiviral innate immune response;cGAS/STING signaling pathway;canonical NF-kappaB signal transduction;cellular defense response;cellular response to angiotensin;cellular response to hydrogen peroxide;cellular response to interleukin-1;cellular response to interleukin-6;cellular response to lipopolysaccharide;cellular response to lipoteichoic acid;cellular response to nicotine;cellular response to peptidoglycan;cellular response to tumor necrosis factor;chromatin organization;cytokine-mediated signaling pathway;defense response to tumor cell;defense response to virus;inflammatory response;innate immune response;interleukin-1-mediated signaling pathway;intracellular signal transduction;liver development;negative regulation of DNA-templated transcription;negative regulation of angiogenesis;negative regulation of apoptotic process;negative regulation of cytokine production;negative regulation of cytokine production involved in inflammatory response;negative regulation of extrinsic apoptotic signaling pathway;negative regulation of miRNA transcription;negative regulation of non-canonical NF-kappaB signal transduction;negative regulation of protein sumoylation;negative regulation of transcription by RNA polymerase II;neuropeptide signaling pathway;non-canonical NF-kappaB signal transduction;nucleotide-binding oligomerization domain containing 2 signaling pathway;positive regulation of DNA-templated transcription;positive regulation of amyloid-beta formation;positive regulation of canonical NF-kappaB signal transduction;positive regulation of cell population proliferation;positive regulation of cytokine production involved in inflammatory response;positive regulation of gene expression;positive regulation of interleukin-1 beta production;positive regulation of interleukin-6 production;positive regulation of interleukin-8 production;positive regulation of leukocyte adhesion to vascular endothelial cell;positive regulation of miRNA metabolic process;positive regulation of miRNA transcription;positive regulation of transcription by RNA polymerase II;positive regulation of vascular endothelial growth factor production;postsynapse to nucleus signaling pathway;prolactin signaling pathway;regulation of DNA-templated transcription;regulation of inflammatory response;regulation of transcription by RNA polymerase II;response to UV-B;response to cytokine;response to interleukin-1;toll-like receptor 4 signaling pathway;toll-like receptor TLR6:TLR2 signaling pathway;tumor necrosis factor-mediated signaling pathway;vascular endothelial growth factor signaling pathway</t>
+          <t>NADP binding;coenzyme A metabolic process;endoplasmic reticulum;endoplasmic reticulum membrane;hydroxymethylglutaryl-CoA reductase (NADPH) activity;isoprenoid biosynthetic process;oxidoreductase activity, acting on the CH-OH group of donors, NAD or NADP as acceptor;peroxisomal membrane;sterol biosynthetic process</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>GO:0000976;GO:0000977;GO:0000978;GO:0000979;GO:0000981;GO:0001223;GO:0001227;GO:0001228;GO:0003677;GO:0003682;GO:0003700;GO:0003713;GO:0005515;GO:0019899;GO:0019901;GO:0031490;GO:0031625;GO:0042277;GO:0042301;GO:0042802;GO:0042803;GO:0042805;GO:0042826;GO:0043565;GO:0051059;GO:0071532;GO:0140296;GO:0140297</t>
+          <t>GO:0008299;GO:0015936;GO:0016126</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;DNA-binding transcription factor binding;DNA-binding transcription repressor activity, RNA polymerase II-specific;NF-kappaB binding;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II core promoter sequence-specific DNA binding;RNA polymerase II transcription regulatory region sequence-specific DNA binding;actinin binding;ankyrin repeat binding;chromatin DNA binding;chromatin binding;enzyme binding;general transcription initiation factor binding;histone deacetylase binding;identical protein binding;peptide binding;phosphate ion binding;protein binding;protein homodimerization activity;protein kinase binding;sequence-specific DNA binding;transcription cis-regulatory region binding;transcription coactivator activity;transcription coactivator binding;ubiquitin protein ligase binding</t>
+          <t>coenzyme A metabolic process;isoprenoid biosynthetic process;sterol biosynthetic process</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>GO:0000785;GO:0005634;GO:0005654;GO:0005667;GO:0005730;GO:0005737;GO:0005829;GO:0035525;GO:0071159;GO:0098978</t>
+          <t>GO:0004420;GO:0016616;GO:0050661</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>NF-kappaB complex;NF-kappaB p50/p65 complex;chromatin;cytoplasm;cytosol;glutamatergic synapse;nucleolus;nucleoplasm;nucleus;transcription regulator complex</t>
+          <t>NADP binding;hydroxymethylglutaryl-CoA reductase (NADPH) activity;oxidoreductase activity, acting on the CH-OH group of donors, NAD or NADP as acceptor</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>GO:0005778;GO:0005783;GO:0005789</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum;endoplasmic reticulum membrane;peroxisomal membrane</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Q12809</t>
+          <t>Q6Q788</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -3462,75 +3694,81 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KCNH2</t>
+          <t>APOA5</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3757</v>
+        <v>116519</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K39" t="n">
-        <v>42</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>GO:0000976;GO:0003064;GO:0005216;GO:0005242;GO:0005249;GO:0005251;GO:0005515;GO:0005886;GO:0006811;GO:0006813;GO:0008076;GO:0009986;GO:0016020;GO:0031625;GO:0042391;GO:0042802;GO:0042803;GO:0045893;GO:0048471;GO:0055075;GO:0055085;GO:0060048;GO:0060306;GO:0060307;GO:0071466;GO:0071805;GO:0086005;GO:0086009;GO:0086010;GO:0086011;GO:0086013;GO:0086091;GO:0097110;GO:0097623;GO:0098915;GO:1901379;GO:1901380;GO:1901381;GO:1902282;GO:1902937;GO:1903765;GO:1990573</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>cardiac muscle contraction;cell surface;cellular response to xenobiotic stimulus;delayed rectifier potassium channel activity;identical protein binding;inward rectifier potassium channel activity;inward rectifier potassium channel complex;membrane;membrane depolarization during action potential;membrane repolarization;membrane repolarization during action potential;membrane repolarization during cardiac muscle cell action potential;membrane repolarization during ventricular cardiac muscle cell action potential;monoatomic ion channel activity;monoatomic ion transport;negative regulation of potassium ion export across plasma membrane;negative regulation of potassium ion transmembrane transport;perinuclear region of cytoplasm;plasma membrane;positive regulation of DNA-templated transcription;positive regulation of potassium ion transmembrane transport;potassium ion export across plasma membrane;potassium ion homeostasis;potassium ion import across plasma membrane;potassium ion transmembrane transport;potassium ion transport;protein binding;protein homodimerization activity;regulation of heart rate by cardiac conduction;regulation of heart rate by hormone;regulation of membrane potential;regulation of membrane repolarization;regulation of potassium ion transmembrane transport;regulation of ventricular cardiac muscle cell membrane repolarization;scaffold protein binding;transcription cis-regulatory region binding;transmembrane transport;ubiquitin protein ligase binding;ventricular cardiac muscle cell action potential;voltage-gated potassium channel activity;voltage-gated potassium channel activity involved in ventricular cardiac muscle cell action potential repolarization;voltage-gated potassium channel complex</t>
-        </is>
+      <c r="M39" t="n">
+        <v>40</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GO:0003064;GO:0006811;GO:0006813;GO:0042391;GO:0045893;GO:0055075;GO:0055085;GO:0060048;GO:0060306;GO:0060307;GO:0071466;GO:0071805;GO:0086005;GO:0086009;GO:0086010;GO:0086011;GO:0086013;GO:0086091;GO:0097623;GO:0098915;GO:1901379;GO:1901380;GO:1901381;GO:1903765;GO:1990573</t>
+          <t>GO:0005515;GO:0005543;GO:0005576;GO:0005769;GO:0005770;GO:0005788;GO:0005794;GO:0006641;GO:0006869;GO:0008201;GO:0008203;GO:0008289;GO:0010898;GO:0010902;GO:0019433;GO:0019899;GO:0031210;GO:0033344;GO:0033700;GO:0034361;GO:0034362;GO:0034364;GO:0034447;GO:0035473;GO:0042157;GO:0042246;GO:0042627;GO:0042632;GO:0045723;GO:0048260;GO:0050750;GO:0050996;GO:0055090;GO:0060228;GO:0060229;GO:0060230;GO:0070325;GO:0070328;GO:0120020;GO:1903561</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>cardiac muscle contraction;cellular response to xenobiotic stimulus;membrane depolarization during action potential;membrane repolarization;membrane repolarization during action potential;membrane repolarization during cardiac muscle cell action potential;membrane repolarization during ventricular cardiac muscle cell action potential;monoatomic ion transport;negative regulation of potassium ion export across plasma membrane;negative regulation of potassium ion transmembrane transport;positive regulation of DNA-templated transcription;positive regulation of potassium ion transmembrane transport;potassium ion export across plasma membrane;potassium ion homeostasis;potassium ion import across plasma membrane;potassium ion transmembrane transport;potassium ion transport;regulation of heart rate by cardiac conduction;regulation of heart rate by hormone;regulation of membrane potential;regulation of membrane repolarization;regulation of potassium ion transmembrane transport;regulation of ventricular cardiac muscle cell membrane repolarization;transmembrane transport;ventricular cardiac muscle cell action potential</t>
+          <t>Golgi apparatus;acylglycerol homeostasis;cholesterol efflux;cholesterol homeostasis;cholesterol metabolic process;cholesterol transfer activity;chylomicron;early endosome;endoplasmic reticulum lumen;enzyme binding;extracellular region;extracellular vesicle;heparin binding;high-density lipoprotein particle;late endosome;lipase activator activity;lipase binding;lipid binding;lipid transport;lipoprotein lipase activator activity;lipoprotein metabolic process;lipoprotein particle receptor binding;low-density lipoprotein particle;low-density lipoprotein particle receptor binding;phosphatidylcholine binding;phosphatidylcholine-sterol O-acyltransferase activator activity;phospholipid binding;phospholipid efflux;positive regulation of fatty acid biosynthetic process;positive regulation of lipid catabolic process;positive regulation of receptor-mediated endocytosis;positive regulation of triglyceride catabolic process;positive regulation of very-low-density lipoprotein particle remodeling;protein binding;tissue regeneration;triglyceride catabolic process;triglyceride homeostasis;triglyceride metabolic process;very-low-density lipoprotein particle;very-low-density lipoprotein particle clearance</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>GO:0000976;GO:0005216;GO:0005242;GO:0005249;GO:0005251;GO:0005515;GO:0031625;GO:0042802;GO:0042803;GO:0097110;GO:1902282</t>
+          <t>GO:0006641;GO:0006869;GO:0008203;GO:0010898;GO:0010902;GO:0019433;GO:0033344;GO:0033700;GO:0034447;GO:0042157;GO:0042246;GO:0042632;GO:0045723;GO:0048260;GO:0050996;GO:0055090;GO:0070328</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>delayed rectifier potassium channel activity;identical protein binding;inward rectifier potassium channel activity;monoatomic ion channel activity;protein binding;protein homodimerization activity;scaffold protein binding;transcription cis-regulatory region binding;ubiquitin protein ligase binding;voltage-gated potassium channel activity;voltage-gated potassium channel activity involved in ventricular cardiac muscle cell action potential repolarization</t>
+          <t>acylglycerol homeostasis;cholesterol efflux;cholesterol homeostasis;cholesterol metabolic process;lipid transport;lipoprotein metabolic process;phospholipid efflux;positive regulation of fatty acid biosynthetic process;positive regulation of lipid catabolic process;positive regulation of receptor-mediated endocytosis;positive regulation of triglyceride catabolic process;positive regulation of very-low-density lipoprotein particle remodeling;tissue regeneration;triglyceride catabolic process;triglyceride homeostasis;triglyceride metabolic process;very-low-density lipoprotein particle clearance</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>GO:0005886;GO:0008076;GO:0009986;GO:0016020;GO:0048471;GO:1902937</t>
+          <t>GO:0005515;GO:0005543;GO:0008201;GO:0008289;GO:0019899;GO:0031210;GO:0035473;GO:0050750;GO:0060228;GO:0060229;GO:0060230;GO:0070325;GO:0120020</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>cell surface;inward rectifier potassium channel complex;membrane;perinuclear region of cytoplasm;plasma membrane;voltage-gated potassium channel complex</t>
+          <t>cholesterol transfer activity;enzyme binding;heparin binding;lipase activator activity;lipase binding;lipid binding;lipoprotein lipase activator activity;lipoprotein particle receptor binding;low-density lipoprotein particle receptor binding;phosphatidylcholine binding;phosphatidylcholine-sterol O-acyltransferase activator activity;phospholipid binding;protein binding</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>GO:0005576;GO:0005769;GO:0005770;GO:0005788;GO:0005794;GO:0034361;GO:0034362;GO:0034364;GO:0042627;GO:1903561</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Golgi apparatus;chylomicron;early endosome;endoplasmic reticulum lumen;extracellular region;extracellular vesicle;high-density lipoprotein particle;late endosome;low-density lipoprotein particle;very-low-density lipoprotein particle</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Q13501</t>
+          <t>Q6ZMV9</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -3541,75 +3779,81 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SQSTM1</t>
+          <t>KIF6</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8878</v>
+        <v>221458</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>77</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>GO:0000407;GO:0000422;GO:0000423;GO:0000425;GO:0000932;GO:0001659;GO:0002931;GO:0005080;GO:0005515;GO:0005634;GO:0005654;GO:0005737;GO:0005739;GO:0005764;GO:0005770;GO:0005776;GO:0005783;GO:0005829;GO:0006511;GO:0006606;GO:0006914;GO:0007032;GO:0008104;GO:0008270;GO:0010508;GO:0010821;GO:0016197;GO:0016234;GO:0016235;GO:0016236;GO:0016605;GO:0019899;GO:0019901;GO:0030017;GO:0030163;GO:0030674;GO:0030971;GO:0031397;GO:0031625;GO:0033554;GO:0034144;GO:0035255;GO:0035556;GO:0035591;GO:0035973;GO:0038023;GO:0042169;GO:0042802;GO:0043065;GO:0043122;GO:0043130;GO:0043232;GO:0044753;GO:0044754;GO:0044877;GO:0045202;GO:0045944;GO:0046578;GO:0061635;GO:0070062;GO:0070342;GO:0070530;GO:0071211;GO:0097009;GO:0097225;GO:0097413;GO:0098780;GO:0098978;GO:0110076;GO:0140036;GO:0140311;GO:0140313;GO:0140693;GO:0140694;GO:1900273;GO:1903078;GO:1905719</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>K63-linked polyubiquitin modification-dependent protein binding;Lewy body;P-body;PML body;SH2 domain binding;aggrephagy;aggresome;amphisome;autolysosome;autophagosome;autophagy;autophagy of mitochondrion;brown fat cell proliferation;cellular response to stress;cytoplasm;cytosol;endoplasmic reticulum;endosomal transport;endosome organization;energy homeostasis;enzyme binding;extracellular exosome;glutamatergic synapse;identical protein binding;inclusion body;intracellular membraneless organelle;intracellular protein localization;intracellular signal transduction;ionotropic glutamate receptor binding;late endosome;lysosome;macroautophagy;membraneless organelle assembly;mitochondrion;mitophagy;molecular condensate scaffold activity;molecular sequestering activity;negative regulation of ferroptosis;negative regulation of protein ubiquitination;negative regulation of toll-like receptor 4 signaling pathway;nucleoplasm;nucleus;pexophagy;phagophore assembly site;positive regulation of apoptotic process;positive regulation of autophagy;positive regulation of long-term synaptic potentiation;positive regulation of protein localization to plasma membrane;positive regulation of transcription by RNA polymerase II;protein binding;protein catabolic process;protein import into nucleus;protein kinase C binding;protein kinase binding;protein localization to perinuclear region of cytoplasm;protein sequestering activity;protein targeting to vacuole involved in autophagy;protein-containing complex binding;protein-macromolecule adaptor activity;receptor tyrosine kinase binding;regulation of Ras protein signal transduction;regulation of canonical NF-kappaB signal transduction;regulation of mitochondrion organization;regulation of protein complex stability;response to ischemia;response to mitochondrial depolarisation;sarcomere;signaling adaptor activity;signaling receptor activity;sperm midpiece;synapse;temperature homeostasis;ubiquitin binding;ubiquitin protein ligase binding;ubiquitin-dependent protein catabolic process;ubiquitin-modified protein reader activity;zinc ion binding</t>
-        </is>
+      <c r="M40" t="n">
+        <v>10</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>GO:0000422;GO:0000423;GO:0000425;GO:0001659;GO:0002931;GO:0006511;GO:0006606;GO:0006914;GO:0007032;GO:0008104;GO:0010508;GO:0010821;GO:0016197;GO:0016236;GO:0030163;GO:0031397;GO:0033554;GO:0034144;GO:0035556;GO:0035973;GO:0043065;GO:0043122;GO:0045944;GO:0046578;GO:0061635;GO:0070342;GO:0071211;GO:0097009;GO:0098780;GO:0110076;GO:0140694;GO:1900273;GO:1903078;GO:1905719</t>
+          <t>GO:0003777;GO:0005515;GO:0005524;GO:0005737;GO:0005856;GO:0005871;GO:0005874;GO:0007018;GO:0008017;GO:0016887</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>aggrephagy;autophagy;autophagy of mitochondrion;brown fat cell proliferation;cellular response to stress;endosomal transport;endosome organization;energy homeostasis;intracellular protein localization;intracellular signal transduction;macroautophagy;membraneless organelle assembly;mitophagy;negative regulation of ferroptosis;negative regulation of protein ubiquitination;negative regulation of toll-like receptor 4 signaling pathway;pexophagy;positive regulation of apoptotic process;positive regulation of autophagy;positive regulation of long-term synaptic potentiation;positive regulation of protein localization to plasma membrane;positive regulation of transcription by RNA polymerase II;protein catabolic process;protein import into nucleus;protein localization to perinuclear region of cytoplasm;protein targeting to vacuole involved in autophagy;regulation of Ras protein signal transduction;regulation of canonical NF-kappaB signal transduction;regulation of mitochondrion organization;regulation of protein complex stability;response to ischemia;response to mitochondrial depolarisation;temperature homeostasis;ubiquitin-dependent protein catabolic process</t>
+          <t>ATP binding;ATP hydrolysis activity;cytoplasm;cytoskeleton;kinesin complex;microtubule;microtubule binding;microtubule motor activity;microtubule-based movement;protein binding</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>GO:0005080;GO:0005515;GO:0008270;GO:0019899;GO:0019901;GO:0030674;GO:0030971;GO:0031625;GO:0035255;GO:0035591;GO:0038023;GO:0042169;GO:0042802;GO:0043130;GO:0044877;GO:0070530;GO:0140036;GO:0140311;GO:0140313;GO:0140693</t>
+          <t>GO:0007018</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>K63-linked polyubiquitin modification-dependent protein binding;SH2 domain binding;enzyme binding;identical protein binding;ionotropic glutamate receptor binding;molecular condensate scaffold activity;molecular sequestering activity;protein binding;protein kinase C binding;protein kinase binding;protein sequestering activity;protein-containing complex binding;protein-macromolecule adaptor activity;receptor tyrosine kinase binding;signaling adaptor activity;signaling receptor activity;ubiquitin binding;ubiquitin protein ligase binding;ubiquitin-modified protein reader activity;zinc ion binding</t>
+          <t>microtubule-based movement</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>GO:0000407;GO:0000932;GO:0005634;GO:0005654;GO:0005737;GO:0005739;GO:0005764;GO:0005770;GO:0005776;GO:0005783;GO:0005829;GO:0016234;GO:0016235;GO:0016605;GO:0030017;GO:0043232;GO:0044753;GO:0044754;GO:0045202;GO:0070062;GO:0097225;GO:0097413;GO:0098978</t>
+          <t>GO:0003777;GO:0005515;GO:0005524;GO:0008017;GO:0016887</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Lewy body;P-body;PML body;aggresome;amphisome;autolysosome;autophagosome;cytoplasm;cytosol;endoplasmic reticulum;extracellular exosome;glutamatergic synapse;inclusion body;intracellular membraneless organelle;late endosome;lysosome;mitochondrion;nucleoplasm;nucleus;phagophore assembly site;sarcomere;sperm midpiece;synapse</t>
+          <t>ATP binding;ATP hydrolysis activity;microtubule binding;microtubule motor activity;protein binding</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005856;GO:0005871;GO:0005874</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>cytoplasm;cytoskeleton;kinesin complex;microtubule</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Q13685</t>
+          <t>Q8TCC7</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -3620,75 +3864,81 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>bethanechol</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AAMP</t>
+          <t>SLC22A8</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>9376</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K41" t="n">
-        <v>9</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>GO:0001525;GO:0005515;GO:0005737;GO:0005829;GO:0005886;GO:0008201;GO:0009986;GO:0010595;GO:0014909</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>angiogenesis;cell surface;cytoplasm;cytosol;heparin binding;plasma membrane;positive regulation of endothelial cell migration;protein binding;smooth muscle cell migration</t>
-        </is>
+      <c r="M41" t="n">
+        <v>15</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>GO:0001525;GO:0010595;GO:0014909</t>
+          <t>GO:0005452;GO:0005886;GO:0009925;GO:0015132;GO:0015297;GO:0015732;GO:0016020;GO:0016323;GO:0016324;GO:0022857;GO:0042908;GO:0042910;GO:0055085;GO:0070062;GO:0150104</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>angiogenesis;positive regulation of endothelial cell migration;smooth muscle cell migration</t>
+          <t>antiporter activity;apical plasma membrane;basal plasma membrane;basolateral plasma membrane;extracellular exosome;membrane;plasma membrane;prostaglandin transmembrane transporter activity;prostaglandin transport;solute:inorganic anion antiporter activity;transmembrane transport;transmembrane transporter activity;transport across blood-brain barrier;xenobiotic transmembrane transporter activity;xenobiotic transport</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>GO:0005515;GO:0008201</t>
+          <t>GO:0015732;GO:0042908;GO:0055085;GO:0150104</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>heparin binding;protein binding</t>
+          <t>prostaglandin transport;transmembrane transport;transport across blood-brain barrier;xenobiotic transport</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>GO:0005737;GO:0005829;GO:0005886;GO:0009986</t>
+          <t>GO:0005452;GO:0015132;GO:0015297;GO:0022857;GO:0042910</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>cell surface;cytoplasm;cytosol;plasma membrane</t>
+          <t>antiporter activity;prostaglandin transmembrane transporter activity;solute:inorganic anion antiporter activity;transmembrane transporter activity;xenobiotic transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0009925;GO:0016020;GO:0016323;GO:0016324;GO:0070062</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>apical plasma membrane;basal plasma membrane;basolateral plasma membrane;extracellular exosome;membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Q13950</t>
+          <t>Q92769</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -3699,75 +3949,81 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RUNX2</t>
+          <t>HDAC2</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>860</v>
+        <v>3066</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K42" t="n">
-        <v>28</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>GO:0000785;GO:0000978;GO:0000981;GO:0001216;GO:0001503;GO:0001649;GO:0002062;GO:0003677;GO:0003700;GO:0005515;GO:0005524;GO:0005634;GO:0005654;GO:0005737;GO:0005829;GO:0006355;GO:0006357;GO:0007178;GO:0030097;GO:0030182;GO:0030509;GO:0045595;GO:0045669;GO:0045892;GO:0045893;GO:0045944;GO:0060395;GO:1990837</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>ATP binding;BMP signaling pathway;DNA binding;DNA-binding transcription activator activity;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;SMAD protein signal transduction;cell surface receptor protein serine/threonine kinase signaling pathway;chondrocyte differentiation;chromatin;cytoplasm;cytosol;hemopoiesis;negative regulation of DNA-templated transcription;neuron differentiation;nucleoplasm;nucleus;ossification;osteoblast differentiation;positive regulation of DNA-templated transcription;positive regulation of osteoblast differentiation;positive regulation of transcription by RNA polymerase II;protein binding;regulation of DNA-templated transcription;regulation of cell differentiation;regulation of transcription by RNA polymerase II;sequence-specific double-stranded DNA binding</t>
-        </is>
+      <c r="M42" t="n">
+        <v>55</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>GO:0001503;GO:0001649;GO:0002062;GO:0006355;GO:0006357;GO:0007178;GO:0030097;GO:0030182;GO:0030509;GO:0045595;GO:0045669;GO:0045892;GO:0045893;GO:0045944;GO:0060395</t>
+          <t>GO:0000118;GO:0000122;GO:0000781;GO:0000785;GO:0001221;GO:0003682;GO:0003723;GO:0004407;GO:0005515;GO:0005634;GO:0005654;GO:0005737;GO:0006338;GO:0008284;GO:0009913;GO:0010977;GO:0016358;GO:0016581;GO:0016811;GO:0019899;GO:0030336;GO:0030512;GO:0031492;GO:0031507;GO:0032922;GO:0032991;GO:0033148;GO:0033558;GO:0035098;GO:0042393;GO:0042475;GO:0042659;GO:0042733;GO:0042826;GO:0043066;GO:0045862;GO:0045892;GO:0045893;GO:0045944;GO:0045995;GO:0050847;GO:0051059;GO:0060789;GO:0061029;GO:0061198;GO:0061629;GO:0070822;GO:0141221;GO:0160008;GO:0160009;GO:0160010;GO:0160216;GO:1902455;GO:1902459;GO:2000736</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>BMP signaling pathway;SMAD protein signal transduction;cell surface receptor protein serine/threonine kinase signaling pathway;chondrocyte differentiation;hemopoiesis;negative regulation of DNA-templated transcription;neuron differentiation;ossification;osteoblast differentiation;positive regulation of DNA-templated transcription;positive regulation of osteoblast differentiation;positive regulation of transcription by RNA polymerase II;regulation of DNA-templated transcription;regulation of cell differentiation;regulation of transcription by RNA polymerase II</t>
+          <t>ESC/E(Z) complex;NF-kappaB binding;NuRD complex;RNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;Sin3-type complex;chromatin;chromatin binding;chromatin remodeling;chromosome, telomeric region;circadian regulation of gene expression;cytoplasm;dendrite development;embryonic digit morphogenesis;enzyme binding;epidermal cell differentiation;eyelid development in camera-type eye;fungiform papilla formation;hair follicle placode formation;heterochromatin formation;histone binding;histone deacetylase activity;histone deacetylase activity, hydrolytic mechanism;histone deacetylase binding;histone deacetylase complex;histone decrotonylase activity;hydrolase activity, acting on carbon-nitrogen (but not peptide) bonds, in linear amides;negative regulation of DNA-templated transcription;negative regulation of apoptotic process;negative regulation of cell migration;negative regulation of neuron projection development;negative regulation of stem cell population maintenance;negative regulation of transcription by RNA polymerase II;negative regulation of transforming growth factor beta receptor signaling pathway;nucleoplasm;nucleosomal DNA binding;nucleus;odontogenesis of dentin-containing tooth;positive regulation of DNA-templated transcription;positive regulation of cell population proliferation;positive regulation of intracellular estrogen receptor signaling pathway;positive regulation of proteolysis;positive regulation of stem cell population maintenance;positive regulation of transcription by RNA polymerase II;progesterone receptor signaling pathway;protein binding;protein de-2-hydroxyisobutyrylase activity;protein decrotonylase activity;protein lysine deacetylase activity;protein lysine delactylase activity;protein-containing complex;regulation of cell fate specification;regulation of embryonic development;regulation of stem cell differentiation;transcription coregulator binding</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>GO:0000978;GO:0000981;GO:0001216;GO:0003677;GO:0003700;GO:0005515;GO:0005524;GO:1990837</t>
+          <t>GO:0000122;GO:0006338;GO:0008284;GO:0009913;GO:0010977;GO:0016358;GO:0030336;GO:0030512;GO:0031507;GO:0032922;GO:0033148;GO:0042475;GO:0042659;GO:0042733;GO:0043066;GO:0045862;GO:0045892;GO:0045893;GO:0045944;GO:0045995;GO:0050847;GO:0060789;GO:0061029;GO:0061198;GO:1902455;GO:1902459;GO:2000736</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ATP binding;DNA binding;DNA-binding transcription activator activity;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;protein binding;sequence-specific double-stranded DNA binding</t>
+          <t>chromatin remodeling;circadian regulation of gene expression;dendrite development;embryonic digit morphogenesis;epidermal cell differentiation;eyelid development in camera-type eye;fungiform papilla formation;hair follicle placode formation;heterochromatin formation;negative regulation of DNA-templated transcription;negative regulation of apoptotic process;negative regulation of cell migration;negative regulation of neuron projection development;negative regulation of stem cell population maintenance;negative regulation of transcription by RNA polymerase II;negative regulation of transforming growth factor beta receptor signaling pathway;odontogenesis of dentin-containing tooth;positive regulation of DNA-templated transcription;positive regulation of cell population proliferation;positive regulation of intracellular estrogen receptor signaling pathway;positive regulation of proteolysis;positive regulation of stem cell population maintenance;positive regulation of transcription by RNA polymerase II;progesterone receptor signaling pathway;regulation of cell fate specification;regulation of embryonic development;regulation of stem cell differentiation</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>GO:0000785;GO:0005634;GO:0005654;GO:0005737;GO:0005829</t>
+          <t>GO:0001221;GO:0003682;GO:0003723;GO:0004407;GO:0005515;GO:0016811;GO:0019899;GO:0031492;GO:0033558;GO:0042393;GO:0042826;GO:0051059;GO:0061629;GO:0141221;GO:0160008;GO:0160009;GO:0160010;GO:0160216</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>chromatin;cytoplasm;cytosol;nucleoplasm;nucleus</t>
+          <t>NF-kappaB binding;RNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;chromatin binding;enzyme binding;histone binding;histone deacetylase activity;histone deacetylase activity, hydrolytic mechanism;histone deacetylase binding;histone decrotonylase activity;hydrolase activity, acting on carbon-nitrogen (but not peptide) bonds, in linear amides;nucleosomal DNA binding;protein binding;protein de-2-hydroxyisobutyrylase activity;protein decrotonylase activity;protein lysine deacetylase activity;protein lysine delactylase activity;transcription coregulator binding</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>GO:0000118;GO:0000781;GO:0000785;GO:0005634;GO:0005654;GO:0005737;GO:0016581;GO:0032991;GO:0035098;GO:0070822</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>ESC/E(Z) complex;NuRD complex;Sin3-type complex;chromatin;chromosome, telomeric region;cytoplasm;histone deacetylase complex;nucleoplasm;nucleus;protein-containing complex</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Q14116</t>
+          <t>Q9UBN7</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -3778,75 +4034,81 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IL18</t>
+          <t>HDAC6</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3606</v>
+        <v>10013</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K43" t="n">
-        <v>45</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>GO:0001525;GO:0002826;GO:0005125;GO:0005515;GO:0005576;GO:0005615;GO:0005829;GO:0006954;GO:0006955;GO:0007166;GO:0007267;GO:0010744;GO:0019221;GO:0030155;GO:0030431;GO:0032722;GO:0032725;GO:0032729;GO:0032736;GO:0032740;GO:0032819;GO:0034105;GO:0035655;GO:0042088;GO:0042092;GO:0042104;GO:0042531;GO:0042632;GO:0045063;GO:0045515;GO:0045630;GO:0045944;GO:0048018;GO:0048661;GO:0050729;GO:0050830;GO:0051142;GO:0051897;GO:0061436;GO:0070328;GO:0071222;GO:0120162;GO:0150078;GO:1901224;GO:2000556</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>T-helper 1 cell differentiation;T-helper 1 type immune response;angiogenesis;cell surface receptor signaling pathway;cell-cell signaling;cellular response to lipopolysaccharide;cholesterol homeostasis;cytokine activity;cytokine-mediated signaling pathway;cytosol;defense response to Gram-positive bacterium;establishment of skin barrier;extracellular region;immune response;inflammatory response;interleukin-18 receptor binding;interleukin-18-mediated signaling pathway;negative regulation of T-helper 1 type immune response;obsolete extracellular space;positive regulation of NK T cell proliferation;positive regulation of T-helper 1 cell cytokine production;positive regulation of T-helper 2 cell differentiation;positive regulation of activated T cell proliferation;positive regulation of chemokine production;positive regulation of cold-induced thermogenesis;positive regulation of granulocyte macrophage colony-stimulating factor production;positive regulation of inflammatory response;positive regulation of interleukin-13 production;positive regulation of interleukin-17 production;positive regulation of macrophage derived foam cell differentiation;positive regulation of natural killer cell proliferation;positive regulation of neuroinflammatory response;positive regulation of non-canonical NF-kappaB signal transduction;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of smooth muscle cell proliferation;positive regulation of tissue remodeling;positive regulation of transcription by RNA polymerase II;positive regulation of type II interferon production;positive regulation of tyrosine phosphorylation of STAT protein;protein binding;receptor ligand activity;regulation of cell adhesion;sleep;triglyceride homeostasis;type 2 immune response</t>
-        </is>
+      <c r="M43" t="n">
+        <v>95</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GO:0001525;GO:0002826;GO:0006954;GO:0006955;GO:0007166;GO:0007267;GO:0010744;GO:0019221;GO:0030155;GO:0030431;GO:0032722;GO:0032725;GO:0032729;GO:0032736;GO:0032740;GO:0032819;GO:0034105;GO:0035655;GO:0042088;GO:0042092;GO:0042104;GO:0042531;GO:0042632;GO:0045063;GO:0045630;GO:0045944;GO:0048661;GO:0050729;GO:0050830;GO:0051142;GO:0051897;GO:0061436;GO:0070328;GO:0071222;GO:0120162;GO:0150078;GO:1901224;GO:2000556</t>
+          <t>GO:0000118;GO:0000153;GO:0000978;GO:0001222;GO:0004407;GO:0005515;GO:0005634;GO:0005737;GO:0005771;GO:0005813;GO:0005829;GO:0005856;GO:0005874;GO:0005875;GO:0005901;GO:0005929;GO:0006476;GO:0006515;GO:0006886;GO:0006950;GO:0007173;GO:0008013;GO:0008017;GO:0008270;GO:0010506;GO:0010634;GO:0010727;GO:0015630;GO:0016234;GO:0016235;GO:0016236;GO:0016241;GO:0016567;GO:0019213;GO:0019896;GO:0019899;GO:0030424;GO:0030425;GO:0031252;GO:0031333;GO:0031593;GO:0031625;GO:0031647;GO:0031648;GO:0032418;GO:0032461;GO:0032886;GO:0032991;GO:0033148;GO:0033558;GO:0034605;GO:0035967;GO:0036064;GO:0036479;GO:0042030;GO:0042826;GO:0042903;GO:0043005;GO:0043014;GO:0043130;GO:0043204;GO:0043242;GO:0044297;GO:0045814;GO:0045861;GO:0045892;GO:0047611;GO:0048156;GO:0048471;GO:0048487;GO:0051129;GO:0051130;GO:0051646;GO:0051787;GO:0051788;GO:0051879;GO:0060271;GO:0060632;GO:0060765;GO:0061523;GO:0061630;GO:0061734;GO:0070301;GO:0070840;GO:0070842;GO:0070845;GO:0090042;GO:0098732;GO:0106047;GO:0106048;GO:0120025;GO:1903146;GO:1904115;GO:1905091;GO:1905336</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>T-helper 1 cell differentiation;T-helper 1 type immune response;angiogenesis;cell surface receptor signaling pathway;cell-cell signaling;cellular response to lipopolysaccharide;cholesterol homeostasis;cytokine-mediated signaling pathway;defense response to Gram-positive bacterium;establishment of skin barrier;immune response;inflammatory response;interleukin-18-mediated signaling pathway;negative regulation of T-helper 1 type immune response;positive regulation of NK T cell proliferation;positive regulation of T-helper 1 cell cytokine production;positive regulation of T-helper 2 cell differentiation;positive regulation of activated T cell proliferation;positive regulation of chemokine production;positive regulation of cold-induced thermogenesis;positive regulation of granulocyte macrophage colony-stimulating factor production;positive regulation of inflammatory response;positive regulation of interleukin-13 production;positive regulation of interleukin-17 production;positive regulation of macrophage derived foam cell differentiation;positive regulation of natural killer cell proliferation;positive regulation of neuroinflammatory response;positive regulation of non-canonical NF-kappaB signal transduction;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of smooth muscle cell proliferation;positive regulation of tissue remodeling;positive regulation of transcription by RNA polymerase II;positive regulation of type II interferon production;positive regulation of tyrosine phosphorylation of STAT protein;regulation of cell adhesion;sleep;triglyceride homeostasis;type 2 immune response</t>
+          <t>ATPase inhibitor activity;Hsp90 protein binding;RNA polymerase II cis-regulatory region sequence-specific DNA binding;acetylspermidine deacetylase activity;aggresome;aggresome assembly;alpha-tubulin binding;axon;axon cytoplasm;axonal transport of mitochondrion;beta-catenin binding;beta-tubulin binding;caveola;cell body;cell leading edge;cellular response to heat;cellular response to hydrogen peroxide;cellular response to topologically incorrect protein;centrosome;ciliary basal body;cilium;cilium assembly;cilium disassembly;cytoplasm;cytoplasmic ubiquitin ligase complex;cytoskeleton;cytosol;deacetylase activity;dendrite;dynein complex binding;enzyme binding;epidermal growth factor receptor signaling pathway;histone deacetylase activity;histone deacetylase binding;histone deacetylase complex;inclusion body;intracellular protein transport;lysosome localization;macroautophagy;macromolecule deacylation;microtubule;microtubule associated complex;microtubule binding;microtubule cytoskeleton;misfolded protein binding;mitochondrion localization;multivesicular body;negative regulation of DNA-templated transcription;negative regulation of aggrephagy;negative regulation of cellular component organization;negative regulation of gene expression, epigenetic;negative regulation of hydrogen peroxide metabolic process;negative regulation of protein-containing complex assembly;negative regulation of protein-containing complex disassembly;negative regulation of proteolysis;neuron projection;nucleus;obsolete polyamine deacetylation;obsolete spermidine deacetylation;perikaryon;perinuclear region of cytoplasm;peroxidase inhibitor activity;plasma membrane bounded cell projection;polyubiquitin modification-dependent protein binding;polyubiquitinated misfolded protein transport;positive regulation of cellular component organization;positive regulation of epithelial cell migration;positive regulation of intracellular estrogen receptor signaling pathway;positive regulation of protein oligomerization;positive regulation of type 2 mitophagy;protein binding;protein deacetylation;protein destabilization;protein lysine deacetylase activity;protein quality control for misfolded or incompletely synthesized proteins;protein ubiquitination;protein-containing complex;regulation of androgen receptor signaling pathway;regulation of autophagy;regulation of autophagy of mitochondrion;regulation of macroautophagy;regulation of microtubule-based movement;regulation of microtubule-based process;regulation of protein stability;response to misfolded protein;response to stress;tau protein binding;transcription corepressor binding;tubulin deacetylase activity;tubulin deacetylation;type 2 mitophagy;ubiquitin binding;ubiquitin protein ligase activity;ubiquitin protein ligase binding;zinc ion binding</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>GO:0005125;GO:0005515;GO:0045515;GO:0048018</t>
+          <t>GO:0006476;GO:0006515;GO:0006886;GO:0006950;GO:0007173;GO:0010506;GO:0010634;GO:0010727;GO:0016236;GO:0016241;GO:0016567;GO:0019896;GO:0031333;GO:0031647;GO:0031648;GO:0032418;GO:0032461;GO:0032886;GO:0033148;GO:0034605;GO:0035967;GO:0043242;GO:0045814;GO:0045861;GO:0045892;GO:0051129;GO:0051130;GO:0051646;GO:0051788;GO:0060271;GO:0060632;GO:0060765;GO:0061523;GO:0061734;GO:0070301;GO:0070842;GO:0070845;GO:0090042;GO:0098732;GO:0106047;GO:0106048;GO:1903146;GO:1905091;GO:1905336</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>cytokine activity;interleukin-18 receptor binding;protein binding;receptor ligand activity</t>
+          <t>aggresome assembly;axonal transport of mitochondrion;cellular response to heat;cellular response to hydrogen peroxide;cellular response to topologically incorrect protein;cilium assembly;cilium disassembly;epidermal growth factor receptor signaling pathway;intracellular protein transport;lysosome localization;macroautophagy;macromolecule deacylation;mitochondrion localization;negative regulation of DNA-templated transcription;negative regulation of aggrephagy;negative regulation of cellular component organization;negative regulation of gene expression, epigenetic;negative regulation of hydrogen peroxide metabolic process;negative regulation of protein-containing complex assembly;negative regulation of protein-containing complex disassembly;negative regulation of proteolysis;obsolete polyamine deacetylation;obsolete spermidine deacetylation;polyubiquitinated misfolded protein transport;positive regulation of cellular component organization;positive regulation of epithelial cell migration;positive regulation of intracellular estrogen receptor signaling pathway;positive regulation of protein oligomerization;positive regulation of type 2 mitophagy;protein deacetylation;protein destabilization;protein quality control for misfolded or incompletely synthesized proteins;protein ubiquitination;regulation of androgen receptor signaling pathway;regulation of autophagy;regulation of autophagy of mitochondrion;regulation of macroautophagy;regulation of microtubule-based movement;regulation of microtubule-based process;regulation of protein stability;response to misfolded protein;response to stress;tubulin deacetylation;type 2 mitophagy</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>GO:0005576;GO:0005615;GO:0005829</t>
+          <t>GO:0000978;GO:0001222;GO:0004407;GO:0005515;GO:0008013;GO:0008017;GO:0008270;GO:0019213;GO:0019899;GO:0031593;GO:0031625;GO:0033558;GO:0036479;GO:0042030;GO:0042826;GO:0042903;GO:0043014;GO:0043130;GO:0047611;GO:0048156;GO:0048487;GO:0051787;GO:0051879;GO:0061630;GO:0070840</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>cytosol;extracellular region;obsolete extracellular space</t>
+          <t>ATPase inhibitor activity;Hsp90 protein binding;RNA polymerase II cis-regulatory region sequence-specific DNA binding;acetylspermidine deacetylase activity;alpha-tubulin binding;beta-catenin binding;beta-tubulin binding;deacetylase activity;dynein complex binding;enzyme binding;histone deacetylase activity;histone deacetylase binding;microtubule binding;misfolded protein binding;peroxidase inhibitor activity;polyubiquitin modification-dependent protein binding;protein binding;protein lysine deacetylase activity;tau protein binding;transcription corepressor binding;tubulin deacetylase activity;ubiquitin binding;ubiquitin protein ligase activity;ubiquitin protein ligase binding;zinc ion binding</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>GO:0000118;GO:0000153;GO:0005634;GO:0005737;GO:0005771;GO:0005813;GO:0005829;GO:0005856;GO:0005874;GO:0005875;GO:0005901;GO:0005929;GO:0015630;GO:0016234;GO:0016235;GO:0030424;GO:0030425;GO:0031252;GO:0032991;GO:0036064;GO:0043005;GO:0043204;GO:0044297;GO:0048471;GO:0120025;GO:1904115</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>aggresome;axon;axon cytoplasm;caveola;cell body;cell leading edge;centrosome;ciliary basal body;cilium;cytoplasm;cytoplasmic ubiquitin ligase complex;cytoskeleton;cytosol;dendrite;histone deacetylase complex;inclusion body;microtubule;microtubule associated complex;microtubule cytoskeleton;multivesicular body;neuron projection;nucleus;perikaryon;perinuclear region of cytoplasm;plasma membrane bounded cell projection;protein-containing complex</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Q16236</t>
+          <t>Q9UPU5</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -3857,75 +4119,81 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NFE2L2</t>
+          <t>USP24</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4780</v>
+        <v>23358</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K44" t="n">
-        <v>66</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>GO:0000785;GO:0000976;GO:0000978;GO:0000981;GO:0001221;GO:0001228;GO:0002931;GO:0003677;GO:0003700;GO:0005515;GO:0005634;GO:0005654;GO:0005737;GO:0005829;GO:0006355;GO:0006357;GO:0006979;GO:0009410;GO:0010499;GO:0010628;GO:0010667;GO:0010976;GO:0016567;GO:0016592;GO:0019904;GO:0030194;GO:0030217;GO:0030968;GO:0031625;GO:0032993;GO:0034599;GO:0034976;GO:0036499;GO:0042149;GO:0043161;GO:0043536;GO:0043565;GO:0045088;GO:0045454;GO:0045766;GO:0045893;GO:0045944;GO:0046223;GO:0046326;GO:0061431;GO:0061629;GO:0070301;GO:0071356;GO:0071456;GO:0071498;GO:0071499;GO:0110076;GO:0140467;GO:0140693;GO:1900038;GO:1900407;GO:1902037;GO:1902176;GO:1903788;GO:1904294;GO:1904385;GO:1904753;GO:2000060;GO:2000121;GO:2000352;GO:2000379</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;PERK-mediated unfolded protein response;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;T cell differentiation;aflatoxin catabolic process;cell redox homeostasis;cellular response to angiotensin;cellular response to fluid shear stress;cellular response to glucose starvation;cellular response to hydrogen peroxide;cellular response to hypoxia;cellular response to laminar fluid shear stress;cellular response to methionine;cellular response to oxidative stress;cellular response to tumor necrosis factor;chromatin;cytoplasm;cytosol;endoplasmic reticulum unfolded protein response;integrated stress response signaling;mediator complex;molecular condensate scaffold activity;negative regulation of cardiac muscle cell apoptotic process;negative regulation of cellular response to hypoxia;negative regulation of endothelial cell apoptotic process;negative regulation of ferroptosis;negative regulation of hematopoietic stem cell differentiation;negative regulation of oxidative stress-induced intrinsic apoptotic signaling pathway;negative regulation of vascular associated smooth muscle cell migration;nucleoplasm;nucleus;positive regulation of D-glucose import across plasma membrane;positive regulation of DNA-templated transcription;positive regulation of ERAD pathway;positive regulation of angiogenesis;positive regulation of blood coagulation;positive regulation of blood vessel endothelial cell migration;positive regulation of gene expression;positive regulation of glutathione biosynthetic process;positive regulation of neuron projection development;positive regulation of reactive oxygen species metabolic process;positive regulation of transcription by RNA polymerase II;positive regulation of ubiquitin-dependent protein catabolic process;proteasomal ubiquitin-independent protein catabolic process;proteasome-mediated ubiquitin-dependent protein catabolic process;protein binding;protein domain specific binding;protein ubiquitination;protein-DNA complex;regulation of DNA-templated transcription;regulation of cellular response to oxidative stress;regulation of innate immune response;regulation of removal of superoxide radicals;regulation of transcription by RNA polymerase II;response to endoplasmic reticulum stress;response to ischemia;response to oxidative stress;response to xenobiotic stimulus;sequence-specific DNA binding;transcription cis-regulatory region binding;transcription coregulator binding;ubiquitin protein ligase binding</t>
-        </is>
+      <c r="M44" t="n">
+        <v>7</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GO:0002931;GO:0006355;GO:0006357;GO:0006979;GO:0009410;GO:0010499;GO:0010628;GO:0010667;GO:0010976;GO:0016567;GO:0030194;GO:0030217;GO:0030968;GO:0034599;GO:0034976;GO:0036499;GO:0042149;GO:0043161;GO:0043536;GO:0045088;GO:0045454;GO:0045766;GO:0045893;GO:0045944;GO:0046223;GO:0046326;GO:0061431;GO:0070301;GO:0071356;GO:0071456;GO:0071498;GO:0071499;GO:0110076;GO:0140467;GO:1900038;GO:1900407;GO:1902037;GO:1902176;GO:1903788;GO:1904294;GO:1904385;GO:1904753;GO:2000060;GO:2000121;GO:2000352;GO:2000379</t>
+          <t>GO:0004843;GO:0005515;GO:0005634;GO:0005654;GO:0005829;GO:0016579;GO:0031647</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>PERK-mediated unfolded protein response;T cell differentiation;aflatoxin catabolic process;cell redox homeostasis;cellular response to angiotensin;cellular response to fluid shear stress;cellular response to glucose starvation;cellular response to hydrogen peroxide;cellular response to hypoxia;cellular response to laminar fluid shear stress;cellular response to methionine;cellular response to oxidative stress;cellular response to tumor necrosis factor;endoplasmic reticulum unfolded protein response;integrated stress response signaling;negative regulation of cardiac muscle cell apoptotic process;negative regulation of cellular response to hypoxia;negative regulation of endothelial cell apoptotic process;negative regulation of ferroptosis;negative regulation of hematopoietic stem cell differentiation;negative regulation of oxidative stress-induced intrinsic apoptotic signaling pathway;negative regulation of vascular associated smooth muscle cell migration;positive regulation of D-glucose import across plasma membrane;positive regulation of DNA-templated transcription;positive regulation of ERAD pathway;positive regulation of angiogenesis;positive regulation of blood coagulation;positive regulation of blood vessel endothelial cell migration;positive regulation of gene expression;positive regulation of glutathione biosynthetic process;positive regulation of neuron projection development;positive regulation of reactive oxygen species metabolic process;positive regulation of transcription by RNA polymerase II;positive regulation of ubiquitin-dependent protein catabolic process;proteasomal ubiquitin-independent protein catabolic process;proteasome-mediated ubiquitin-dependent protein catabolic process;protein ubiquitination;regulation of DNA-templated transcription;regulation of cellular response to oxidative stress;regulation of innate immune response;regulation of removal of superoxide radicals;regulation of transcription by RNA polymerase II;response to endoplasmic reticulum stress;response to ischemia;response to oxidative stress;response to xenobiotic stimulus</t>
+          <t>cysteine-type deubiquitinase activity;cytosol;nucleoplasm;nucleus;protein binding;protein deubiquitination;regulation of protein stability</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>GO:0000976;GO:0000978;GO:0000981;GO:0001221;GO:0001228;GO:0003677;GO:0003700;GO:0005515;GO:0019904;GO:0031625;GO:0043565;GO:0061629;GO:0140693</t>
+          <t>GO:0016579;GO:0031647</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>DNA binding;DNA-binding transcription activator activity, RNA polymerase II-specific;DNA-binding transcription factor activity;DNA-binding transcription factor activity, RNA polymerase II-specific;RNA polymerase II cis-regulatory region sequence-specific DNA binding;RNA polymerase II-specific DNA-binding transcription factor binding;molecular condensate scaffold activity;protein binding;protein domain specific binding;sequence-specific DNA binding;transcription cis-regulatory region binding;transcription coregulator binding;ubiquitin protein ligase binding</t>
+          <t>protein deubiquitination;regulation of protein stability</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>GO:0000785;GO:0005634;GO:0005654;GO:0005737;GO:0005829;GO:0016592;GO:0032993</t>
+          <t>GO:0004843;GO:0005515</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>chromatin;cytoplasm;cytosol;mediator complex;nucleoplasm;nucleus;protein-DNA complex</t>
+          <t>cysteine-type deubiquitinase activity;protein binding</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>GO:0005634;GO:0005654;GO:0005829</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>cytosol;nucleoplasm;nucleus</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Q16613</t>
+          <t>Q9UPY5</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -3936,470 +4204,546 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>bethanechol</t>
+          <t>Rosuvastatin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AANAT</t>
+          <t>SLC7A11</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>23657</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>interaction_predominant</t>
         </is>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>26</v>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>GO:0004059;GO:0004060;GO:0005515;GO:0005737;GO:0005829;GO:0006474;GO:0007623;GO:0008080;GO:0009416;GO:0009648;GO:0010043;GO:0016747;GO:0030187;GO:0032868;GO:0034097;GO:0034695;GO:0035651;GO:0046219;GO:0046688;GO:0048471;GO:0051412;GO:0051591;GO:0051592;GO:0071320;GO:0071889;GO:1901652</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>14-3-3 protein binding;AP-3 adaptor complex binding;N-acetyltransferase activity;N-terminal protein amino acid acetylation;acyltransferase activity, transferring groups other than amino-acyl groups;aralkylamine N-acetyltransferase activity;arylamine N-acetyltransferase activity;cellular response to cAMP;circadian rhythm;cytoplasm;cytosol;indolalkylamine biosynthetic process;melatonin biosynthetic process;perinuclear region of cytoplasm;photoperiodism;protein binding;response to cAMP;response to calcium ion;response to copper ion;response to corticosterone;response to cytokine;response to insulin;response to light stimulus;response to peptide;response to prostaglandin E;response to zinc ion</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>GO:0006474;GO:0007623;GO:0009416;GO:0009648;GO:0010043;GO:0030187;GO:0032868;GO:0034097;GO:0034695;GO:0046219;GO:0046688;GO:0051412;GO:0051591;GO:0051592;GO:0071320;GO:1901652</t>
+          <t>GO:0003333;GO:0005515;GO:0005765;GO:0005886;GO:0006865;GO:0009636;GO:0009986;GO:0015252;GO:0015327;GO:0015811;GO:0015813;GO:0016020;GO:0022840;GO:0022857;GO:0031526;GO:0031528;GO:0035752;GO:0043067;GO:0045177;GO:0055085;GO:0089718;GO:0097449;GO:0110076;GO:0140924;GO:0140926;GO:1902600</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>N-terminal protein amino acid acetylation;cellular response to cAMP;circadian rhythm;indolalkylamine biosynthetic process;melatonin biosynthetic process;photoperiodism;response to cAMP;response to calcium ion;response to copper ion;response to corticosterone;response to cytokine;response to insulin;response to light stimulus;response to peptide;response to prostaglandin E;response to zinc ion</t>
+          <t>L-cystine transport;L-glutamate transmembrane transport;L-kynurenine transmembrane transport;L-kynurenine transmembrane transporter activity;amino acid import across plasma membrane;amino acid transmembrane transport;amino acid transport;apical part of cell;astrocyte projection;brush border membrane;cell surface;cystine:glutamate antiporter activity;leak channel activity;lysosomal lumen pH elevation;lysosomal membrane;membrane;microvillus membrane;negative regulation of ferroptosis;plasma membrane;protein binding;proton channel activity;proton transmembrane transport;regulation of programmed cell death;response to toxic substance;transmembrane transport;transmembrane transporter activity</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>GO:0004059;GO:0004060;GO:0005515;GO:0008080;GO:0016747;GO:0035651;GO:0071889</t>
+          <t>GO:0003333;GO:0006865;GO:0009636;GO:0015811;GO:0015813;GO:0035752;GO:0043067;GO:0055085;GO:0089718;GO:0110076;GO:0140924;GO:1902600</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>14-3-3 protein binding;AP-3 adaptor complex binding;N-acetyltransferase activity;acyltransferase activity, transferring groups other than amino-acyl groups;aralkylamine N-acetyltransferase activity;arylamine N-acetyltransferase activity;protein binding</t>
+          <t>L-cystine transport;L-glutamate transmembrane transport;L-kynurenine transmembrane transport;amino acid import across plasma membrane;amino acid transmembrane transport;amino acid transport;lysosomal lumen pH elevation;negative regulation of ferroptosis;proton transmembrane transport;regulation of programmed cell death;response to toxic substance;transmembrane transport</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>GO:0005737;GO:0005829;GO:0048471</t>
+          <t>GO:0005515;GO:0015252;GO:0015327;GO:0022840;GO:0022857;GO:0140926</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>cytoplasm;cytosol;perinuclear region of cytoplasm</t>
+          <t>L-kynurenine transmembrane transporter activity;cystine:glutamate antiporter activity;leak channel activity;protein binding;proton channel activity;transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>GO:0005765;GO:0005886;GO:0009986;GO:0016020;GO:0031526;GO:0031528;GO:0045177;GO:0097449</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>apical part of cell;astrocyte projection;brush border membrane;cell surface;lysosomal membrane;membrane;microvillus membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Q7KTX7</t>
+          <t>P04035</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PARK</t>
+          <t>HMGCR</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>40336</v>
+        <v>3156</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>interaction_predominant</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>GO:0000151;GO:0000209;GO:0000266;GO:0000423;GO:0004842;GO:0005515;GO:0005737;GO:0005739;GO:0005783;GO:0005794;GO:0005829;GO:0006511;GO:0006513;GO:0006950;GO:0006979;GO:0007005;GO:0007283;GO:0008270;GO:0008344;GO:0008345;GO:0009896;GO:0010637;GO:0010821;GO:0016567;GO:0022603;GO:0030382;GO:0031624;GO:0046329;GO:0048078;GO:0048477;GO:0050804;GO:0051865;GO:0061630;GO:0061734;GO:0070050;GO:0090141;GO:1900407;GO:1901526;GO:1902532;GO:1903599;GO:1904061;GO:1904457</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Golgi apparatus;adult locomotory behavior;cytoplasm;cytosol;endoplasmic reticulum;larval locomotory behavior;mitochondrial fission;mitochondrion;mitochondrion organization;mitophagy;modulation of chemical synaptic transmission;negative regulation of JNK cascade;negative regulation of intracellular signal transduction;negative regulation of mitochondrial fusion;neuron cellular homeostasis;oogenesis;positive regulation of autophagy of mitochondrion;positive regulation of catabolic process;positive regulation of compound eye pigmentation;positive regulation of locomotor rhythm;positive regulation of mitochondrial fission;positive regulation of mitophagy;positive regulation of neuronal action potential;protein autoubiquitination;protein binding;protein monoubiquitination;protein polyubiquitination;protein ubiquitination;regulation of anatomical structure morphogenesis;regulation of cellular response to oxidative stress;regulation of mitochondrion organization;response to oxidative stress;response to stress;sperm mitochondrion organization;spermatogenesis;type 2 mitophagy;ubiquitin conjugating enzyme binding;ubiquitin ligase complex;ubiquitin protein ligase activity;ubiquitin-dependent protein catabolic process;ubiquitin-protein transferase activity;zinc ion binding</t>
-        </is>
+          <t>interaction_and_pathway</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>24</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>GO:0000209;GO:0000266;GO:0000423;GO:0006511;GO:0006513;GO:0006950;GO:0006979;GO:0007005;GO:0007283;GO:0008344;GO:0008345;GO:0009896;GO:0010637;GO:0010821;GO:0016567;GO:0022603;GO:0030382;GO:0046329;GO:0048078;GO:0048477;GO:0050804;GO:0051865;GO:0061734;GO:0070050;GO:0090141;GO:1900407;GO:1901526;GO:1902532;GO:1903599;GO:1904061;GO:1904457</t>
+          <t>GO:0004420;GO:0005515;GO:0005778;GO:0005783;GO:0005789;GO:0006695;GO:0008299;GO:0010142;GO:0015936;GO:0016126;GO:0016616;GO:0019287;GO:0030695;GO:0033386;GO:0033489;GO:0033490;GO:0036197;GO:0042177;GO:0050661;GO:0050709;GO:0070402;GO:0098554;GO:0120225;GO:1900222</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>adult locomotory behavior;larval locomotory behavior;mitochondrial fission;mitochondrion organization;mitophagy;modulation of chemical synaptic transmission;negative regulation of JNK cascade;negative regulation of intracellular signal transduction;negative regulation of mitochondrial fusion;neuron cellular homeostasis;oogenesis;positive regulation of autophagy of mitochondrion;positive regulation of catabolic process;positive regulation of compound eye pigmentation;positive regulation of locomotor rhythm;positive regulation of mitochondrial fission;positive regulation of mitophagy;positive regulation of neuronal action potential;protein autoubiquitination;protein monoubiquitination;protein polyubiquitination;protein ubiquitination;regulation of anatomical structure morphogenesis;regulation of cellular response to oxidative stress;regulation of mitochondrion organization;response to oxidative stress;response to stress;sperm mitochondrion organization;spermatogenesis;type 2 mitophagy;ubiquitin-dependent protein catabolic process</t>
+          <t>GTPase regulator activity;NADP binding;NADPH binding;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;coenzyme A binding;coenzyme A metabolic process;cytoplasmic side of endoplasmic reticulum membrane;endoplasmic reticulum;endoplasmic reticulum membrane;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranylgeranyl diphosphate biosynthetic process;hydroxymethylglutaryl-CoA reductase (NADPH) activity;isopentenyl diphosphate biosynthetic process, mevalonate pathway;isoprenoid biosynthetic process;negative regulation of amyloid-beta clearance;negative regulation of protein catabolic process;negative regulation of protein secretion;oxidoreductase activity, acting on the CH-OH group of donors, NAD or NADP as acceptor;peroxisomal membrane;protein binding;sterol biosynthetic process;zymosterol biosynthetic process</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>GO:0004842;GO:0005515;GO:0008270;GO:0031624;GO:0061630</t>
+          <t>GO:0006695;GO:0008299;GO:0010142;GO:0015936;GO:0016126;GO:0019287;GO:0033386;GO:0033489;GO:0033490;GO:0036197;GO:0042177;GO:0050709;GO:1900222</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>protein binding;ubiquitin conjugating enzyme binding;ubiquitin protein ligase activity;ubiquitin-protein transferase activity;zinc ion binding</t>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;coenzyme A metabolic process;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranylgeranyl diphosphate biosynthetic process;isopentenyl diphosphate biosynthetic process, mevalonate pathway;isoprenoid biosynthetic process;negative regulation of amyloid-beta clearance;negative regulation of protein catabolic process;negative regulation of protein secretion;sterol biosynthetic process;zymosterol biosynthetic process</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>GO:0000151;GO:0005737;GO:0005739;GO:0005783;GO:0005794;GO:0005829</t>
+          <t>GO:0004420;GO:0005515;GO:0016616;GO:0030695;GO:0050661;GO:0070402;GO:0120225</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Golgi apparatus;cytoplasm;cytosol;endoplasmic reticulum;mitochondrion;ubiquitin ligase complex</t>
+          <t>GTPase regulator activity;NADP binding;NADPH binding;coenzyme A binding;hydroxymethylglutaryl-CoA reductase (NADPH) activity;oxidoreductase activity, acting on the CH-OH group of donors, NAD or NADP as acceptor;protein binding</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>GO:0005778;GO:0005783;GO:0005789;GO:0098554</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>cytoplasmic side of endoplasmic reticulum membrane;endoplasmic reticulum;endoplasmic reticulum membrane;peroxisomal membrane</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Q96P20</t>
+          <t>P08684</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NLRP3</t>
+          <t>CYP3A4</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>114548</v>
+        <v>1576</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>PharmGKB:PA145011109</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>interaction_predominant</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>GO:0000139;GO:0002221;GO:0002674;GO:0002830;GO:0005515;GO:0005524;GO:0005576;GO:0005634;GO:0005737;GO:0005739;GO:0005783;GO:0005815;GO:0005829;GO:0006915;GO:0006952;GO:0006954;GO:0007165;GO:0007231;GO:0009595;GO:0009615;GO:0016020;GO:0016887;GO:0030674;GO:0031021;GO:0032588;GO:0032691;GO:0032731;GO:0032753;GO:0035591;GO:0042802;GO:0042834;GO:0043531;GO:0043565;GO:0044546;GO:0045630;GO:0045944;GO:0050727;GO:0050728;GO:0050729;GO:0051260;GO:0051604;GO:0060090;GO:0061702;GO:0070269;GO:0070273;GO:0071222;GO:0072559;GO:0098586;GO:0140297;GO:0140299;GO:0140608;GO:0140693;GO:1901223;GO:1901224;GO:1901981;GO:2000553</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>ADP binding;ATP binding;ATP hydrolysis activity;DNA-binding transcription factor binding;Golgi membrane;NLRP3 inflammasome complex;NLRP3 inflammasome complex assembly;apoptotic process;canonical inflammasome complex;cellular response to lipopolysaccharide;cellular response to virus;cysteine-type endopeptidase activator activity;cytoplasm;cytosol;defense response;detection of biotic stimulus;endoplasmic reticulum;extracellular region;identical protein binding;inflammatory response;interphase microtubule organizing center;membrane;microtubule organizing center;mitochondrion;molecular adaptor activity;molecular condensate scaffold activity;molecular sensor activity;negative regulation of acute inflammatory response;negative regulation of inflammatory response;negative regulation of interleukin-1 beta production;negative regulation of non-canonical NF-kappaB signal transduction;nucleus;osmosensory signaling pathway;pattern recognition receptor signaling pathway;peptidoglycan binding;phosphatidylinositol phosphate binding;phosphatidylinositol-4-phosphate binding;positive regulation of T-helper 2 cell cytokine production;positive regulation of T-helper 2 cell differentiation;positive regulation of inflammatory response;positive regulation of interleukin-1 beta production;positive regulation of interleukin-4 production;positive regulation of non-canonical NF-kappaB signal transduction;positive regulation of transcription by RNA polymerase II;positive regulation of type 2 immune response;protein binding;protein homooligomerization;protein maturation;protein-macromolecule adaptor activity;pyroptotic inflammatory response;regulation of inflammatory response;response to virus;sequence-specific DNA binding;signal transduction;signaling adaptor activity;trans-Golgi network membrane</t>
-        </is>
+          <t>interaction_and_pathway</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>48</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GO:0002221;GO:0002674;GO:0002830;GO:0006915;GO:0006952;GO:0006954;GO:0007165;GO:0007231;GO:0009595;GO:0009615;GO:0032691;GO:0032731;GO:0032753;GO:0044546;GO:0045630;GO:0045944;GO:0050727;GO:0050728;GO:0050729;GO:0051260;GO:0051604;GO:0070269;GO:0071222;GO:0098586;GO:1901223;GO:1901224;GO:2000553</t>
+          <t>GO:0002933;GO:0004497;GO:0005496;GO:0005506;GO:0005515;GO:0005737;GO:0005789;GO:0006629;GO:0006631;GO:0006706;GO:0006805;GO:0008202;GO:0008203;GO:0008209;GO:0008210;GO:0008395;GO:0008401;GO:0008404;GO:0009822;GO:0016098;GO:0016491;GO:0016705;GO:0016712;GO:0019825;GO:0019899;GO:0020037;GO:0030343;GO:0034875;GO:0036378;GO:0042178;GO:0042359;GO:0042369;GO:0042572;GO:0042573;GO:0042759;GO:0043231;GO:0046222;GO:0050591;GO:0050649;GO:0062181;GO:0062187;GO:0062188;GO:0062189;GO:0070576;GO:0070989;GO:0101020;GO:0101021;GO:0102320</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>NLRP3 inflammasome complex assembly;apoptotic process;cellular response to lipopolysaccharide;cellular response to virus;defense response;detection of biotic stimulus;inflammatory response;negative regulation of acute inflammatory response;negative regulation of inflammatory response;negative regulation of interleukin-1 beta production;negative regulation of non-canonical NF-kappaB signal transduction;osmosensory signaling pathway;pattern recognition receptor signaling pathway;positive regulation of T-helper 2 cell cytokine production;positive regulation of T-helper 2 cell differentiation;positive regulation of inflammatory response;positive regulation of interleukin-1 beta production;positive regulation of interleukin-4 production;positive regulation of non-canonical NF-kappaB signal transduction;positive regulation of transcription by RNA polymerase II;positive regulation of type 2 immune response;protein homooligomerization;protein maturation;pyroptotic inflammatory response;regulation of inflammatory response;response to virus;signal transduction</t>
+          <t>1,8-cineole 2-exo-monooxygenase activity;1-alpha,25-dihydroxyvitamin D3 23-hydroxylase activity;aflatoxin metabolic process;alkaloid catabolic process;anandamide 11,12 epoxidase activity;anandamide 14,15 epoxidase activity;anandamide 8,9 epoxidase activity;androgen metabolic process;arachidonate 14,15-epoxygenase activity;caffeine oxidase activity;calcitriol biosynthetic process from calciol;cholesterol metabolic process;cytoplasm;endoplasmic reticulum membrane;enzyme binding;estrogen 16-alpha-hydroxylase activity;estrogen 2-hydroxylase activity;estrogen metabolic process;fatty acid metabolic process;heme binding;intracellular membrane-bounded organelle;iron ion binding;lipid hydroxylation;lipid metabolic process;long-chain fatty acid biosynthetic process;monooxygenase activity;monoterpenoid metabolic process;oxidative demethylation;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;oxygen binding;protein binding;quinine 3-monooxygenase activity;retinoic acid 4-hydroxylase activity;retinoic acid metabolic process;retinol metabolic process;steroid binding;steroid catabolic process;steroid hydroxylase activity;steroid metabolic process;testosterone 6-beta-hydroxylase activity;vitamin D 24-hydroxylase activity;vitamin D catabolic process;vitamin D metabolic process;vitamin D3 25-hydroxylase activity;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>GO:0005515;GO:0005524;GO:0016887;GO:0030674;GO:0035591;GO:0042802;GO:0042834;GO:0043531;GO:0043565;GO:0060090;GO:0070273;GO:0140297;GO:0140299;GO:0140608;GO:0140693;GO:1901981</t>
+          <t>GO:0002933;GO:0006629;GO:0006631;GO:0006706;GO:0006805;GO:0008202;GO:0008203;GO:0008209;GO:0008210;GO:0009822;GO:0016098;GO:0036378;GO:0042178;GO:0042359;GO:0042369;GO:0042572;GO:0042573;GO:0042759;GO:0046222;GO:0070989</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>ADP binding;ATP binding;ATP hydrolysis activity;DNA-binding transcription factor binding;cysteine-type endopeptidase activator activity;identical protein binding;molecular adaptor activity;molecular condensate scaffold activity;molecular sensor activity;peptidoglycan binding;phosphatidylinositol phosphate binding;phosphatidylinositol-4-phosphate binding;protein binding;protein-macromolecule adaptor activity;sequence-specific DNA binding;signaling adaptor activity</t>
+          <t>aflatoxin metabolic process;alkaloid catabolic process;androgen metabolic process;calcitriol biosynthetic process from calciol;cholesterol metabolic process;estrogen metabolic process;fatty acid metabolic process;lipid hydroxylation;lipid metabolic process;long-chain fatty acid biosynthetic process;monoterpenoid metabolic process;oxidative demethylation;retinoic acid metabolic process;retinol metabolic process;steroid catabolic process;steroid metabolic process;vitamin D catabolic process;vitamin D metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>GO:0000139;GO:0005576;GO:0005634;GO:0005737;GO:0005739;GO:0005783;GO:0005815;GO:0005829;GO:0016020;GO:0031021;GO:0032588;GO:0061702;GO:0072559</t>
+          <t>GO:0004497;GO:0005496;GO:0005506;GO:0005515;GO:0008395;GO:0008401;GO:0008404;GO:0016491;GO:0016705;GO:0016712;GO:0019825;GO:0019899;GO:0020037;GO:0030343;GO:0034875;GO:0050591;GO:0050649;GO:0062181;GO:0062187;GO:0062188;GO:0062189;GO:0070576;GO:0101020;GO:0101021;GO:0102320</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Golgi membrane;NLRP3 inflammasome complex;canonical inflammasome complex;cytoplasm;cytosol;endoplasmic reticulum;extracellular region;interphase microtubule organizing center;membrane;microtubule organizing center;mitochondrion;nucleus;trans-Golgi network membrane</t>
+          <t>1,8-cineole 2-exo-monooxygenase activity;1-alpha,25-dihydroxyvitamin D3 23-hydroxylase activity;anandamide 11,12 epoxidase activity;anandamide 14,15 epoxidase activity;anandamide 8,9 epoxidase activity;arachidonate 14,15-epoxygenase activity;caffeine oxidase activity;enzyme binding;estrogen 16-alpha-hydroxylase activity;estrogen 2-hydroxylase activity;heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;oxygen binding;protein binding;quinine 3-monooxygenase activity;retinoic acid 4-hydroxylase activity;steroid binding;steroid hydroxylase activity;testosterone 6-beta-hydroxylase activity;vitamin D 24-hydroxylase activity;vitamin D3 25-hydroxylase activity</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005789;GO:0043231</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>cytoplasm;endoplasmic reticulum membrane;intracellular membrane-bounded organelle</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Q99571</t>
+          <t>P11712</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P2RX4</t>
+          <t>CYP2C9</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5025</v>
+        <v>1559</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>PharmGKB:PA145011109</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>interaction_predominant</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>GO:0001614;GO:0001894;GO:0002028;GO:0002931;GO:0004931;GO:0005102;GO:0005216;GO:0005507;GO:0005515;GO:0005524;GO:0005765;GO:0005886;GO:0006811;GO:0006950;GO:0007165;GO:0008217;GO:0008270;GO:0010524;GO:0010614;GO:0010959;GO:0016020;GO:0019233;GO:0019722;GO:0030054;GO:0030335;GO:0032308;GO:0033198;GO:0034220;GO:0034405;GO:0035590;GO:0042118;GO:0042802;GO:0043536;GO:0044297;GO:0045296;GO:0045429;GO:0048266;GO:0048471;GO:0048678;GO:0050850;GO:0050920;GO:0050975;GO:0051897;GO:0051899;GO:0051928;GO:0055117;GO:0055119;GO:0060079;GO:0070062;GO:0070588;GO:0071294;GO:0071318;GO:0097190;GO:0098655;GO:0098794;GO:0099604;GO:1900027;GO:1902533;GO:1904141;GO:2001028</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>ATP binding;apoptotic signaling pathway;behavioral response to pain;cadherin binding;calcium ion transmembrane transport;calcium-mediated signaling;cell body;cell junction;cellular response to ATP;cellular response to zinc ion;copper ion binding;endothelial cell activation;excitatory postsynaptic potential;extracellular exosome;extracellularly ATP-gated monoatomic cation channel activity;identical protein binding;ligand-gated calcium channel activity;lysosomal membrane;membrane;membrane depolarization;monoatomic cation transmembrane transport;monoatomic ion channel activity;monoatomic ion transmembrane transport;monoatomic ion transport;negative regulation of cardiac muscle hypertrophy;perinuclear region of cytoplasm;plasma membrane;positive regulation of blood vessel endothelial cell migration;positive regulation of calcium ion transport;positive regulation of calcium ion transport into cytosol;positive regulation of calcium-mediated signaling;positive regulation of cell migration;positive regulation of endothelial cell chemotaxis;positive regulation of intracellular signal transduction;positive regulation of microglial cell migration;positive regulation of nitric oxide biosynthetic process;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of prostaglandin secretion;postsynapse;protein binding;purinergic nucleotide receptor activity;purinergic nucleotide receptor signaling pathway;regulation of blood pressure;regulation of cardiac muscle contraction;regulation of chemotaxis;regulation of metal ion transport;regulation of ruffle assembly;regulation of sodium ion transport;relaxation of cardiac muscle;response to ATP;response to axon injury;response to fluid shear stress;response to ischemia;response to stress;sensory perception of pain;sensory perception of touch;signal transduction;signaling receptor binding;tissue homeostasis;zinc ion binding</t>
-        </is>
+          <t>interaction_and_pathway</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>36</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>GO:0001894;GO:0002028;GO:0002931;GO:0006811;GO:0006950;GO:0007165;GO:0008217;GO:0010524;GO:0010614;GO:0010959;GO:0019233;GO:0019722;GO:0030335;GO:0032308;GO:0033198;GO:0034220;GO:0034405;GO:0035590;GO:0042118;GO:0043536;GO:0045429;GO:0048266;GO:0048678;GO:0050850;GO:0050920;GO:0050975;GO:0051897;GO:0051899;GO:0051928;GO:0055117;GO:0055119;GO:0060079;GO:0070588;GO:0071294;GO:0071318;GO:0097190;GO:0098655;GO:1900027;GO:1902533;GO:1904141;GO:2001028</t>
+          <t>GO:0004497;GO:0005506;GO:0005737;GO:0005789;GO:0006721;GO:0006805;GO:0008202;GO:0008203;GO:0008210;GO:0008392;GO:0008395;GO:0008404;GO:0008405;GO:0016098;GO:0016491;GO:0016705;GO:0016712;GO:0018675;GO:0018676;GO:0019369;GO:0019373;GO:0019627;GO:0020037;GO:0032787;GO:0034875;GO:0042178;GO:0042759;GO:0043231;GO:0046456;GO:0052741;GO:0070989;GO:0090346;GO:0097267;GO:0101021;GO:0106302;GO:0120502</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>apoptotic signaling pathway;behavioral response to pain;calcium ion transmembrane transport;calcium-mediated signaling;cellular response to ATP;cellular response to zinc ion;endothelial cell activation;excitatory postsynaptic potential;membrane depolarization;monoatomic cation transmembrane transport;monoatomic ion transmembrane transport;monoatomic ion transport;negative regulation of cardiac muscle hypertrophy;positive regulation of blood vessel endothelial cell migration;positive regulation of calcium ion transport;positive regulation of calcium ion transport into cytosol;positive regulation of calcium-mediated signaling;positive regulation of cell migration;positive regulation of endothelial cell chemotaxis;positive regulation of intracellular signal transduction;positive regulation of microglial cell migration;positive regulation of nitric oxide biosynthetic process;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of prostaglandin secretion;purinergic nucleotide receptor signaling pathway;regulation of blood pressure;regulation of cardiac muscle contraction;regulation of chemotaxis;regulation of metal ion transport;regulation of ruffle assembly;regulation of sodium ion transport;relaxation of cardiac muscle;response to ATP;response to axon injury;response to fluid shear stress;response to ischemia;response to stress;sensory perception of pain;sensory perception of touch;signal transduction;tissue homeostasis</t>
+          <t>(R)-limonene 6-monooxygenase activity;(S)-limonene 6-monooxygenase activity;(S)-limonene 7-monooxygenase activity;arachidonate 11,12-epoxygenase activity;arachidonate 14,15-epoxygenase activity;arachidonate 8,9-epoxygenase activity;arachidonate epoxygenase activity;arachidonate metabolic process;caffeine oxidase activity;cholesterol metabolic process;cytoplasm;endoplasmic reticulum membrane;epoxygenase P450 pathway;estrogen 2-hydroxylase activity;estrogen metabolic process;fatty acid omega-1 hydroxylase activity;heme binding;icosanoid biosynthetic process;intracellular membrane-bounded organelle;iron ion binding;long-chain fatty acid biosynthetic process;monocarboxylic acid metabolic process;monooxygenase activity;monoterpenoid metabolic process;omega-hydroxylase P450 pathway;organofluorine metabolic process;oxidative demethylation;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;steroid hydroxylase activity;steroid metabolic process;terpenoid metabolic process;urea metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>GO:0001614;GO:0004931;GO:0005102;GO:0005216;GO:0005507;GO:0005515;GO:0005524;GO:0008270;GO:0042802;GO:0045296;GO:0099604</t>
+          <t>GO:0006721;GO:0006805;GO:0008202;GO:0008203;GO:0008210;GO:0016098;GO:0019369;GO:0019373;GO:0019627;GO:0032787;GO:0042178;GO:0042759;GO:0046456;GO:0070989;GO:0090346;GO:0097267</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>ATP binding;cadherin binding;copper ion binding;extracellularly ATP-gated monoatomic cation channel activity;identical protein binding;ligand-gated calcium channel activity;monoatomic ion channel activity;protein binding;purinergic nucleotide receptor activity;signaling receptor binding;zinc ion binding</t>
+          <t>arachidonate metabolic process;cholesterol metabolic process;epoxygenase P450 pathway;estrogen metabolic process;icosanoid biosynthetic process;long-chain fatty acid biosynthetic process;monocarboxylic acid metabolic process;monoterpenoid metabolic process;omega-hydroxylase P450 pathway;organofluorine metabolic process;oxidative demethylation;steroid metabolic process;terpenoid metabolic process;urea metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>GO:0005765;GO:0005886;GO:0016020;GO:0030054;GO:0044297;GO:0048471;GO:0070062;GO:0098794</t>
+          <t>GO:0004497;GO:0005506;GO:0008392;GO:0008395;GO:0008404;GO:0008405;GO:0016491;GO:0016705;GO:0016712;GO:0018675;GO:0018676;GO:0020037;GO:0034875;GO:0052741;GO:0101021;GO:0106302;GO:0120502</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>cell body;cell junction;extracellular exosome;lysosomal membrane;membrane;perinuclear region of cytoplasm;plasma membrane;postsynapse</t>
+          <t>(R)-limonene 6-monooxygenase activity;(S)-limonene 6-monooxygenase activity;(S)-limonene 7-monooxygenase activity;arachidonate 11,12-epoxygenase activity;arachidonate 14,15-epoxygenase activity;arachidonate 8,9-epoxygenase activity;arachidonate epoxygenase activity;caffeine oxidase activity;estrogen 2-hydroxylase activity;fatty acid omega-1 hydroxylase activity;heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;steroid hydroxylase activity</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005789;GO:0043231</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>cytoplasm;endoplasmic reticulum membrane;intracellular membrane-bounded organelle</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Q9BXM7</t>
+          <t>Q92887</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PINK1</t>
+          <t>ABCC2</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>65018</v>
+        <v>1244</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>PharmGKB:PA145011109</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>interaction_predominant</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>GO:0000287;GO:0000422;GO:0000423;GO:0000785;GO:0002020;GO:0002082;GO:0002931;GO:0004672;GO:0004674;GO:0005515;GO:0005524;GO:0005634;GO:0005737;GO:0005739;GO:0005741;GO:0005743;GO:0005758;GO:0005783;GO:0005829;GO:0005856;GO:0006468;GO:0006511;GO:0006950;GO:0006979;GO:0007005;GO:0010310;GO:0010629;GO:0010821;GO:0016020;GO:0016236;GO:0016239;GO:0016242;GO:0016301;GO:0016504;GO:0016567;GO:0019900;GO:0022904;GO:0030097;GO:0030335;GO:0030424;GO:0030426;GO:0031396;GO:0031398;GO:0031625;GO:0034599;GO:0035556;GO:0038203;GO:0042981;GO:0043066;GO:0043123;GO:0043254;GO:0043422;GO:0043523;GO:0043524;GO:0044297;GO:0044877;GO:0045727;GO:0045944;GO:0046329;GO:0048471;GO:0050821;GO:0051881;GO:0051897;GO:0055131;GO:0061136;GO:0070585;GO:0071456;GO:0072656;GO:0090141;GO:0090200;GO:0090258;GO:0097237;GO:0097413;GO:0097449;GO:0099074;GO:0106310;GO:1900407;GO:1901525;GO:1902803;GO:1902902;GO:1902958;GO:1903146;GO:1903298;GO:1903377;GO:1903384;GO:1903747;GO:1903749;GO:1903751;GO:1903852;GO:1904544;GO:1904881;GO:1905091;GO:2000377;GO:2000378;GO:2001171;GO:2001243</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>ATP binding;C3HC4-type RING finger domain binding;Lewy body;TORC2 signaling;astrocyte projection;autophagy of mitochondrion;axon;cell body;cellular response to hydrogen sulfide;cellular response to hypoxia;cellular response to oxidative stress;cellular response to toxic substance;chromatin;cytoplasm;cytoskeleton;cytosol;endoplasmic reticulum;growth cone;hemopoiesis;intracellular signal transduction;kinase activity;kinase binding;macroautophagy;magnesium ion binding;maintenance of protein location in mitochondrion;membrane;mitochondrial inner membrane;mitochondrial intermembrane space;mitochondrial outer membrane;mitochondrion;mitochondrion organization;mitochondrion to lysosome vesicle-mediated transport;mitophagy;negative regulation of JNK cascade;negative regulation of apoptotic process;negative regulation of autophagosome assembly;negative regulation of gene expression;negative regulation of hydrogen peroxide-induced neuron intrinsic apoptotic signaling pathway;negative regulation of hypoxia-induced intrinsic apoptotic signaling pathway;negative regulation of intrinsic apoptotic signaling pathway;negative regulation of intrinsic apoptotic signaling pathway in response to hydrogen peroxide;negative regulation of macroautophagy;negative regulation of mitochondrial fission;negative regulation of mitophagy;negative regulation of neuron apoptotic process;negative regulation of oxidative stress-induced neuron intrinsic apoptotic signaling pathway;negative regulation of reactive oxygen species metabolic process;nucleus;peptidase activator activity;perinuclear region of cytoplasm;positive regulation of ATP biosynthetic process;positive regulation of canonical NF-kappaB signal transduction;positive regulation of cell migration;positive regulation of cristae formation;positive regulation of free ubiquitin chain polymerization;positive regulation of macroautophagy;positive regulation of mitochondrial electron transport, NADH to ubiquinone;positive regulation of mitochondrial fission;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of protein localization to mitochondrion;positive regulation of protein ubiquitination;positive regulation of release of cytochrome c from mitochondria;positive regulation of transcription by RNA polymerase II;positive regulation of translation;positive regulation of type 2 mitophagy;protease binding;protein binding;protein kinase B binding;protein kinase activity;protein localization to mitochondrion;protein phosphorylation;protein serine kinase activity;protein serine/threonine kinase activity;protein stabilization;protein ubiquitination;protein-containing complex binding;regulation of apoptotic process;regulation of autophagy of mitochondrion;regulation of cellular response to oxidative stress;regulation of hydrogen peroxide metabolic process;regulation of mitochondrial membrane potential;regulation of mitochondrion organization;regulation of neuron apoptotic process;regulation of oxidative phosphorylation;regulation of proteasomal protein catabolic process;regulation of protein localization to mitochondrion;regulation of protein ubiquitination;regulation of protein-containing complex assembly;regulation of reactive oxygen species metabolic process;regulation of synaptic vesicle transport;respiratory electron transport chain;response to ischemia;response to oxidative stress;response to stress;ubiquitin protein ligase binding;ubiquitin-dependent protein catabolic process</t>
-        </is>
+          <t>interaction_and_pathway</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>31</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>GO:0000422;GO:0000423;GO:0002082;GO:0002931;GO:0006468;GO:0006511;GO:0006950;GO:0006979;GO:0007005;GO:0010310;GO:0010629;GO:0010821;GO:0016236;GO:0016239;GO:0016242;GO:0016567;GO:0022904;GO:0030097;GO:0030335;GO:0031396;GO:0031398;GO:0034599;GO:0035556;GO:0038203;GO:0042981;GO:0043066;GO:0043123;GO:0043254;GO:0043523;GO:0043524;GO:0045727;GO:0045944;GO:0046329;GO:0050821;GO:0051881;GO:0051897;GO:0061136;GO:0070585;GO:0071456;GO:0072656;GO:0090141;GO:0090200;GO:0090258;GO:0097237;GO:0099074;GO:1900407;GO:1901525;GO:1902803;GO:1902902;GO:1902958;GO:1903146;GO:1903298;GO:1903377;GO:1903384;GO:1903747;GO:1903749;GO:1903751;GO:1903852;GO:1904544;GO:1904881;GO:1905091;GO:2000377;GO:2000378;GO:2001171;GO:2001243</t>
+          <t>GO:0005515;GO:0005524;GO:0005886;GO:0006805;GO:0006855;GO:0006869;GO:0008559;GO:0009986;GO:0010629;GO:0015127;GO:0015431;GO:0015721;GO:0015723;GO:0016020;GO:0016324;GO:0016887;GO:0019534;GO:0022857;GO:0031982;GO:0042167;GO:0042626;GO:0042910;GO:0046581;GO:0046618;GO:0046942;GO:0055085;GO:0070633;GO:0071716;GO:0140359;GO:0150104;GO:1990962</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>TORC2 signaling;autophagy of mitochondrion;cellular response to hydrogen sulfide;cellular response to hypoxia;cellular response to oxidative stress;cellular response to toxic substance;hemopoiesis;intracellular signal transduction;macroautophagy;maintenance of protein location in mitochondrion;mitochondrion organization;mitochondrion to lysosome vesicle-mediated transport;mitophagy;negative regulation of JNK cascade;negative regulation of apoptotic process;negative regulation of autophagosome assembly;negative regulation of gene expression;negative regulation of hydrogen peroxide-induced neuron intrinsic apoptotic signaling pathway;negative regulation of hypoxia-induced intrinsic apoptotic signaling pathway;negative regulation of intrinsic apoptotic signaling pathway;negative regulation of intrinsic apoptotic signaling pathway in response to hydrogen peroxide;negative regulation of macroautophagy;negative regulation of mitochondrial fission;negative regulation of mitophagy;negative regulation of neuron apoptotic process;negative regulation of oxidative stress-induced neuron intrinsic apoptotic signaling pathway;negative regulation of reactive oxygen species metabolic process;positive regulation of ATP biosynthetic process;positive regulation of canonical NF-kappaB signal transduction;positive regulation of cell migration;positive regulation of cristae formation;positive regulation of free ubiquitin chain polymerization;positive regulation of macroautophagy;positive regulation of mitochondrial electron transport, NADH to ubiquinone;positive regulation of mitochondrial fission;positive regulation of phosphatidylinositol 3-kinase/protein kinase B signal transduction;positive regulation of protein localization to mitochondrion;positive regulation of protein ubiquitination;positive regulation of release of cytochrome c from mitochondria;positive regulation of transcription by RNA polymerase II;positive regulation of translation;positive regulation of type 2 mitophagy;protein localization to mitochondrion;protein phosphorylation;protein stabilization;protein ubiquitination;regulation of apoptotic process;regulation of autophagy of mitochondrion;regulation of cellular response to oxidative stress;regulation of hydrogen peroxide metabolic process;regulation of mitochondrial membrane potential;regulation of mitochondrion organization;regulation of neuron apoptotic process;regulation of oxidative phosphorylation;regulation of proteasomal protein catabolic process;regulation of protein localization to mitochondrion;regulation of protein ubiquitination;regulation of protein-containing complex assembly;regulation of reactive oxygen species metabolic process;regulation of synaptic vesicle transport;respiratory electron transport chain;response to ischemia;response to oxidative stress;response to stress;ubiquitin-dependent protein catabolic process</t>
+          <t>ABC-type glutathione S-conjugate transporter activity;ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled transmembrane transporter activity;apical plasma membrane;bile acid and bile salt transport;bilirubin transmembrane transporter activity;bilirubin transport;carboxylic acid transport;cell surface;heme catabolic process;intercellular canaliculus;leukotriene transport;lipid transport;membrane;negative regulation of gene expression;plasma membrane;protein binding;toxin transmembrane transporter activity;transepithelial transport;transmembrane transport;transmembrane transporter activity;transport across blood-brain barrier;vesicle;xenobiotic export from cell;xenobiotic metabolic process;xenobiotic transmembrane transport;xenobiotic transmembrane transporter activity;xenobiotic transport across blood-brain barrier</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>GO:0000287;GO:0002020;GO:0004672;GO:0004674;GO:0005515;GO:0005524;GO:0016301;GO:0016504;GO:0019900;GO:0031625;GO:0043422;GO:0044877;GO:0055131;GO:0106310</t>
+          <t>GO:0006805;GO:0006855;GO:0006869;GO:0010629;GO:0015721;GO:0015723;GO:0042167;GO:0046618;GO:0046942;GO:0055085;GO:0070633;GO:0071716;GO:0150104;GO:1990962</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>ATP binding;C3HC4-type RING finger domain binding;kinase activity;kinase binding;magnesium ion binding;peptidase activator activity;protease binding;protein binding;protein kinase B binding;protein kinase activity;protein serine kinase activity;protein serine/threonine kinase activity;protein-containing complex binding;ubiquitin protein ligase binding</t>
+          <t>bile acid and bile salt transport;bilirubin transport;carboxylic acid transport;heme catabolic process;leukotriene transport;lipid transport;negative regulation of gene expression;transepithelial transport;transmembrane transport;transport across blood-brain barrier;xenobiotic export from cell;xenobiotic metabolic process;xenobiotic transmembrane transport;xenobiotic transport across blood-brain barrier</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>GO:0000785;GO:0005634;GO:0005737;GO:0005739;GO:0005741;GO:0005743;GO:0005758;GO:0005783;GO:0005829;GO:0005856;GO:0016020;GO:0030424;GO:0030426;GO:0044297;GO:0048471;GO:0097413;GO:0097449</t>
+          <t>GO:0005515;GO:0005524;GO:0008559;GO:0015127;GO:0015431;GO:0016887;GO:0019534;GO:0022857;GO:0042626;GO:0042910;GO:0140359</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Lewy body;astrocyte projection;axon;cell body;chromatin;cytoplasm;cytoskeleton;cytosol;endoplasmic reticulum;growth cone;membrane;mitochondrial inner membrane;mitochondrial intermembrane space;mitochondrial outer membrane;mitochondrion;nucleus;perinuclear region of cytoplasm</t>
+          <t>ABC-type glutathione S-conjugate transporter activity;ABC-type transporter activity;ABC-type xenobiotic transporter activity;ATP binding;ATP hydrolysis activity;ATPase-coupled transmembrane transporter activity;bilirubin transmembrane transporter activity;protein binding;toxin transmembrane transporter activity;transmembrane transporter activity;xenobiotic transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0009986;GO:0016020;GO:0016324;GO:0031982;GO:0046581</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>apical plasma membrane;cell surface;intercellular canaliculus;membrane;plasma membrane;vesicle</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Q9GZQ8</t>
+          <t>Q9NPD5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MAP1LC3B</t>
+          <t>SLCO1B3</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>81631</v>
+        <v>28234</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>PharmGKB:PA145011109</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>interaction_predominant</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>GO:0000045;GO:0000421;GO:0000422;GO:0000423;GO:0005515;GO:0005543;GO:0005739;GO:0005776;GO:0005829;GO:0005856;GO:0005930;GO:0006914;GO:0006995;GO:0008017;GO:0008429;GO:0009267;GO:0012505;GO:0016020;GO:0016236;GO:0031090;GO:0031410;GO:0031625;GO:0031966;GO:0070062;GO:0097001;GO:0097352</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>autophagosome;autophagosome assembly;autophagosome maturation;autophagosome membrane;autophagy;autophagy of mitochondrion;axoneme;cellular response to nitrogen starvation;cellular response to starvation;ceramide binding;cytoplasmic vesicle;cytoskeleton;cytosol;endomembrane system;extracellular exosome;macroautophagy;membrane;microtubule binding;mitochondrial membrane;mitochondrion;mitophagy;organelle membrane;phosphatidylethanolamine binding;phospholipid binding;protein binding;ubiquitin protein ligase binding</t>
-        </is>
+          <t>interaction_and_pathway</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>12</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>GO:0000045;GO:0000422;GO:0000423;GO:0006914;GO:0006995;GO:0009267;GO:0016236;GO:0097352</t>
+          <t>GO:0005886;GO:0006805;GO:0009925;GO:0015125;GO:0015291;GO:0015721;GO:0016020;GO:0016323;GO:0022857;GO:0042167;GO:0043252;GO:0055085</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>autophagosome assembly;autophagosome maturation;autophagy;autophagy of mitochondrion;cellular response to nitrogen starvation;cellular response to starvation;macroautophagy;mitophagy</t>
+          <t>basal plasma membrane;basolateral plasma membrane;bile acid and bile salt transport;bile acid transmembrane transporter activity;heme catabolic process;membrane;plasma membrane;secondary active transmembrane transporter activity;sodium-independent organic anion transport;transmembrane transport;transmembrane transporter activity;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>GO:0005515;GO:0005543;GO:0008017;GO:0008429;GO:0031625;GO:0097001</t>
+          <t>GO:0006805;GO:0015721;GO:0042167;GO:0043252;GO:0055085</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>ceramide binding;microtubule binding;phosphatidylethanolamine binding;phospholipid binding;protein binding;ubiquitin protein ligase binding</t>
+          <t>bile acid and bile salt transport;heme catabolic process;sodium-independent organic anion transport;transmembrane transport;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>GO:0000421;GO:0005739;GO:0005776;GO:0005829;GO:0005856;GO:0005930;GO:0012505;GO:0016020;GO:0031090;GO:0031410;GO:0031966;GO:0070062</t>
+          <t>GO:0015125;GO:0015291;GO:0022857</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>autophagosome;autophagosome membrane;axoneme;cytoplasmic vesicle;cytoskeleton;cytosol;endomembrane system;extracellular exosome;membrane;mitochondrial membrane;mitochondrion;organelle membrane</t>
+          <t>bile acid transmembrane transporter activity;secondary active transmembrane transporter activity;transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0009925;GO:0016020;GO:0016323</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>basal plasma membrane;basolateral plasma membrane;membrane;plasma membrane</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Q9NPD5</t>
+          <t>P10632</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -4410,878 +4754,2685 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SLCO1B3</t>
+          <t>CYP2C8</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>28234</v>
+        <v>1558</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>PharmGKB:PA145011109</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>interaction_predominant</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>GO:0005886;GO:0006805;GO:0009925;GO:0015125;GO:0015291;GO:0015711;GO:0015721;GO:0016020;GO:0016323;GO:0022857;GO:0042167;GO:0043252;GO:0055085</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>basal plasma membrane;basolateral plasma membrane;bile acid and bile salt transport;bile acid transmembrane transporter activity;heme catabolic process;membrane;obsolete organic anion transport;plasma membrane;secondary active transmembrane transporter activity;sodium-independent organic anion transport;transmembrane transport;transmembrane transporter activity;xenobiotic metabolic process</t>
-        </is>
+          <t>interaction_and_pathway</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>30</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>GO:0006805;GO:0015711;GO:0015721;GO:0042167;GO:0043252;GO:0055085</t>
+          <t>GO:0002933;GO:0004497;GO:0005506;GO:0005515;GO:0005737;GO:0005789;GO:0006082;GO:0006721;GO:0006805;GO:0008202;GO:0008210;GO:0008392;GO:0008401;GO:0008404;GO:0008405;GO:0016705;GO:0016712;GO:0019369;GO:0019373;GO:0020037;GO:0032787;GO:0034875;GO:0042178;GO:0042572;GO:0042573;GO:0042759;GO:0046456;GO:0070989;GO:0097267;GO:0101020</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>bile acid and bile salt transport;heme catabolic process;obsolete organic anion transport;sodium-independent organic anion transport;transmembrane transport;xenobiotic metabolic process</t>
+          <t>arachidonate 11,12-epoxygenase activity;arachidonate 14,15-epoxygenase activity;arachidonate epoxygenase activity;arachidonate metabolic process;caffeine oxidase activity;cytoplasm;endoplasmic reticulum membrane;epoxygenase P450 pathway;estrogen 16-alpha-hydroxylase activity;estrogen metabolic process;heme binding;icosanoid biosynthetic process;iron ion binding;lipid hydroxylation;long-chain fatty acid biosynthetic process;monocarboxylic acid metabolic process;monooxygenase activity;obsolete organic acid metabolic process;omega-hydroxylase P450 pathway;oxidative demethylation;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;protein binding;retinoic acid 4-hydroxylase activity;retinoic acid metabolic process;retinol metabolic process;steroid metabolic process;terpenoid metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>GO:0015125;GO:0015291;GO:0022857</t>
+          <t>GO:0002933;GO:0006082;GO:0006721;GO:0006805;GO:0008202;GO:0008210;GO:0019369;GO:0019373;GO:0032787;GO:0042178;GO:0042572;GO:0042573;GO:0042759;GO:0046456;GO:0070989;GO:0097267</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>bile acid transmembrane transporter activity;secondary active transmembrane transporter activity;transmembrane transporter activity</t>
+          <t>arachidonate metabolic process;epoxygenase P450 pathway;estrogen metabolic process;icosanoid biosynthetic process;lipid hydroxylation;long-chain fatty acid biosynthetic process;monocarboxylic acid metabolic process;obsolete organic acid metabolic process;omega-hydroxylase P450 pathway;oxidative demethylation;retinoic acid metabolic process;retinol metabolic process;steroid metabolic process;terpenoid metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>GO:0005886;GO:0009925;GO:0016020;GO:0016323</t>
+          <t>GO:0004497;GO:0005506;GO:0005515;GO:0008392;GO:0008401;GO:0008404;GO:0008405;GO:0016705;GO:0016712;GO:0020037;GO:0034875;GO:0101020</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>basal plasma membrane;basolateral plasma membrane;membrane;plasma membrane</t>
+          <t>arachidonate 11,12-epoxygenase activity;arachidonate 14,15-epoxygenase activity;arachidonate epoxygenase activity;caffeine oxidase activity;estrogen 16-alpha-hydroxylase activity;heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;protein binding;retinoic acid 4-hydroxylase activity</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005789</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>cytoplasm;endoplasmic reticulum membrane</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A0A0A6ZFR4</t>
+          <t>P20815</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UGT74AE2</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>CYP3A5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1577</v>
+      </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>BioCyc_META_PWY-5672</t>
-        </is>
+      <c r="H52" t="n">
+        <v>1</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>PharmGKB:PA145011109</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>pathway_predominant</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>GO:0002238;GO:0008194;GO:0016114;GO:0016135;GO:0046246;GO:0080043;GO:0080044</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>UDP-glycosyltransferase activity;quercetin 3-O-glucosyltransferase activity;quercetin 7-O-glucosyltransferase activity;response to molecule of fungal origin;saponin biosynthetic process;terpene biosynthetic process;terpenoid biosynthetic process</t>
-        </is>
+          <t>interaction_and_pathway</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>24</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>GO:0002238;GO:0016114;GO:0016135;GO:0046246</t>
+          <t>GO:0002933;GO:0004497;GO:0005506;GO:0005515;GO:0005789;GO:0006805;GO:0008202;GO:0008210;GO:0008401;GO:0009822;GO:0016491;GO:0016705;GO:0016712;GO:0019825;GO:0020037;GO:0042178;GO:0042572;GO:0042573;GO:0043231;GO:0046222;GO:0050649;GO:0070989;GO:0101020;GO:0101021</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>response to molecule of fungal origin;saponin biosynthetic process;terpene biosynthetic process;terpenoid biosynthetic process</t>
+          <t>aflatoxin metabolic process;alkaloid catabolic process;endoplasmic reticulum membrane;estrogen 16-alpha-hydroxylase activity;estrogen 2-hydroxylase activity;estrogen metabolic process;heme binding;intracellular membrane-bounded organelle;iron ion binding;lipid hydroxylation;monooxygenase activity;oxidative demethylation;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;oxygen binding;protein binding;retinoic acid 4-hydroxylase activity;retinoic acid metabolic process;retinol metabolic process;steroid metabolic process;testosterone 6-beta-hydroxylase activity;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>GO:0008194;GO:0080043;GO:0080044</t>
+          <t>GO:0002933;GO:0006805;GO:0008202;GO:0008210;GO:0009822;GO:0042178;GO:0042572;GO:0042573;GO:0046222;GO:0070989</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>UDP-glycosyltransferase activity;quercetin 3-O-glucosyltransferase activity;quercetin 7-O-glucosyltransferase activity</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+          <t>aflatoxin metabolic process;alkaloid catabolic process;estrogen metabolic process;lipid hydroxylation;oxidative demethylation;retinoic acid metabolic process;retinol metabolic process;steroid metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>GO:0004497;GO:0005506;GO:0005515;GO:0008401;GO:0016491;GO:0016705;GO:0016712;GO:0019825;GO:0020037;GO:0050649;GO:0101020;GO:0101021</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>estrogen 16-alpha-hydroxylase activity;estrogen 2-hydroxylase activity;heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;oxygen binding;protein binding;retinoic acid 4-hydroxylase activity;testosterone 6-beta-hydroxylase activity</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>GO:0005789;GO:0043231</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum membrane;intracellular membrane-bounded organelle</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A0A0A6ZFY4</t>
+          <t>P22309</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UGT29</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>UGT1A1</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>54658</v>
+      </c>
       <c r="G53" t="n">
         <v>1</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>BioCyc_META_PWY-5672</t>
-        </is>
+      <c r="H53" t="n">
+        <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>PharmGKB:PA145011109</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>pathway_predominant</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>GO:0002238;GO:0008194;GO:0016114;GO:0016135;GO:0016138;GO:0046246</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>UDP-glycosyltransferase activity;glycoside biosynthetic process;response to molecule of fungal origin;saponin biosynthetic process;terpene biosynthetic process;terpenoid biosynthetic process</t>
-        </is>
+          <t>interaction_and_pathway</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>29</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>GO:0002238;GO:0016114;GO:0016135;GO:0016138;GO:0046246</t>
+          <t>GO:0001889;GO:0001972;GO:0004857;GO:0005496;GO:0005515;GO:0005783;GO:0005788;GO:0005789;GO:0005886;GO:0006789;GO:0006805;GO:0008194;GO:0008202;GO:0008210;GO:0009812;GO:0015020;GO:0016125;GO:0019585;GO:0019899;GO:0032787;GO:0034663;GO:0042167;GO:0042573;GO:0042803;GO:0045939;GO:0046982;GO:0048471;GO:0051552;GO:0071385</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>glycoside biosynthetic process;response to molecule of fungal origin;saponin biosynthetic process;terpene biosynthetic process;terpenoid biosynthetic process</t>
+          <t>UDP-glycosyltransferase activity;bilirubin conjugation;cellular response to glucocorticoid stimulus;endoplasmic reticulum;endoplasmic reticulum chaperone complex;endoplasmic reticulum lumen;endoplasmic reticulum membrane;enzyme binding;enzyme inhibitor activity;estrogen metabolic process;flavone metabolic process;flavonoid metabolic process;glucuronate metabolic process;glucuronosyltransferase activity;heme catabolic process;liver development;monocarboxylic acid metabolic process;negative regulation of steroid metabolic process;perinuclear region of cytoplasm;plasma membrane;protein binding;protein heterodimerization activity;protein homodimerization activity;retinoic acid binding;retinoic acid metabolic process;steroid binding;steroid metabolic process;sterol metabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>GO:0008194</t>
+          <t>GO:0001889;GO:0006789;GO:0006805;GO:0008202;GO:0008210;GO:0009812;GO:0016125;GO:0019585;GO:0032787;GO:0042167;GO:0042573;GO:0045939;GO:0051552;GO:0071385</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>UDP-glycosyltransferase activity</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+          <t>bilirubin conjugation;cellular response to glucocorticoid stimulus;estrogen metabolic process;flavone metabolic process;flavonoid metabolic process;glucuronate metabolic process;heme catabolic process;liver development;monocarboxylic acid metabolic process;negative regulation of steroid metabolic process;retinoic acid metabolic process;steroid metabolic process;sterol metabolic process;xenobiotic metabolic process</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>GO:0001972;GO:0004857;GO:0005496;GO:0005515;GO:0008194;GO:0015020;GO:0019899;GO:0042803;GO:0046982</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>UDP-glycosyltransferase activity;enzyme binding;enzyme inhibitor activity;glucuronosyltransferase activity;protein binding;protein heterodimerization activity;protein homodimerization activity;retinoic acid binding;steroid binding</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>GO:0005783;GO:0005788;GO:0005789;GO:0005886;GO:0034663;GO:0048471</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum;endoplasmic reticulum chaperone complex;endoplasmic reticulum lumen;endoplasmic reticulum membrane;perinuclear region of cytoplasm;plasma membrane</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A0A0A7HB61</t>
+          <t>P33261</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>UGT71A27</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>CYP2C19</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1557</v>
+      </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>BioCyc_META_PWY-5672</t>
-        </is>
+      <c r="H54" t="n">
+        <v>1</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>PharmGKB:PA145011109</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>pathway_predominant</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>GO:0008194;GO:0016114;GO:0035251</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>UDP-glucosyltransferase activity;UDP-glycosyltransferase activity;terpenoid biosynthetic process</t>
-        </is>
+          <t>interaction_and_pathway</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>30</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>GO:0016114</t>
+          <t>GO:0001676;GO:0004497;GO:0005506;GO:0005737;GO:0005789;GO:0006631;GO:0006721;GO:0006805;GO:0008202;GO:0008395;GO:0008404;GO:0008405;GO:0016098;GO:0016491;GO:0016705;GO:0016712;GO:0018675;GO:0018676;GO:0019373;GO:0019825;GO:0019899;GO:0020037;GO:0032787;GO:0042178;GO:0043231;GO:0052741;GO:0097267;GO:0106302;GO:0120319;GO:0120502</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>terpenoid biosynthetic process</t>
+          <t>(R)-limonene 6-monooxygenase activity;(S)-limonene 6-monooxygenase activity;(S)-limonene 7-monooxygenase activity;arachidonate 11,12-epoxygenase activity;arachidonate 14,15-epoxygenase activity;arachidonate 8,9-epoxygenase activity;cytoplasm;endoplasmic reticulum membrane;enzyme binding;epoxygenase P450 pathway;fatty acid metabolic process;fatty acid omega-1 hydroxylase activity;heme binding;intracellular membrane-bounded organelle;iron ion binding;long-chain fatty acid metabolic process;long-chain fatty acid omega-1 hydroxylase activity;monocarboxylic acid metabolic process;monooxygenase activity;monoterpenoid metabolic process;omega-hydroxylase P450 pathway;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;oxygen binding;steroid hydroxylase activity;steroid metabolic process;terpenoid metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>GO:0008194;GO:0035251</t>
+          <t>GO:0001676;GO:0006631;GO:0006721;GO:0006805;GO:0008202;GO:0016098;GO:0019373;GO:0032787;GO:0042178;GO:0097267</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>UDP-glucosyltransferase activity;UDP-glycosyltransferase activity</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+          <t>epoxygenase P450 pathway;fatty acid metabolic process;long-chain fatty acid metabolic process;monocarboxylic acid metabolic process;monoterpenoid metabolic process;omega-hydroxylase P450 pathway;steroid metabolic process;terpenoid metabolic process;xenobiotic catabolic process;xenobiotic metabolic process</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>GO:0004497;GO:0005506;GO:0008395;GO:0008404;GO:0008405;GO:0016491;GO:0016705;GO:0016712;GO:0018675;GO:0018676;GO:0019825;GO:0019899;GO:0020037;GO:0052741;GO:0106302;GO:0120319;GO:0120502</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>(R)-limonene 6-monooxygenase activity;(S)-limonene 6-monooxygenase activity;(S)-limonene 7-monooxygenase activity;arachidonate 11,12-epoxygenase activity;arachidonate 14,15-epoxygenase activity;arachidonate 8,9-epoxygenase activity;enzyme binding;fatty acid omega-1 hydroxylase activity;heme binding;iron ion binding;long-chain fatty acid omega-1 hydroxylase activity;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;oxygen binding;steroid hydroxylase activity</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005789;GO:0043231</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>cytoplasm;endoplasmic reticulum membrane;intracellular membrane-bounded organelle</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A0A0K0PVM5</t>
+          <t>P35503</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UGT101</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>UGT1A3</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>54659</v>
+      </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>BioCyc_META_PWY-5672</t>
-        </is>
+      <c r="H55" t="n">
+        <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>PharmGKB:PA145011109</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>pathway_predominant</t>
+          <t>atorvastatin</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>GO:0008194;GO:0016114;GO:0035251</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>UDP-glucosyltransferase activity;UDP-glycosyltransferase activity;terpenoid biosynthetic process</t>
-        </is>
+          <t>interaction_and_pathway</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>21</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>GO:0016114</t>
+          <t>GO:0001889;GO:0001972;GO:0004857;GO:0005783;GO:0005789;GO:0006805;GO:0008194;GO:0008202;GO:0008210;GO:0009812;GO:0015020;GO:0016125;GO:0019899;GO:0032782;GO:0032787;GO:0042573;GO:0042803;GO:0046982;GO:0051552;GO:0070640;GO:0071385</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>terpenoid biosynthetic process</t>
+          <t>UDP-glycosyltransferase activity;bile acid secretion;cellular response to glucocorticoid stimulus;endoplasmic reticulum;endoplasmic reticulum membrane;enzyme binding;enzyme inhibitor activity;estrogen metabolic process;flavone metabolic process;flavonoid metabolic process;glucuronosyltransferase activity;liver development;monocarboxylic acid metabolic process;protein heterodimerization activity;protein homodimerization activity;retinoic acid binding;retinoic acid metabolic process;steroid metabolic process;sterol metabolic process;vitamin D3 metabolic process;xenobiotic metabolic process</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>GO:0008194;GO:0035251</t>
+          <t>GO:0001889;GO:0006805;GO:0008202;GO:0008210;GO:0009812;GO:0016125;GO:0032782;GO:0032787;GO:0042573;GO:0051552;GO:0070640;GO:0071385</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>UDP-glucosyltransferase activity;UDP-glycosyltransferase activity</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>bile acid secretion;cellular response to glucocorticoid stimulus;estrogen metabolic process;flavone metabolic process;flavonoid metabolic process;liver development;monocarboxylic acid metabolic process;retinoic acid metabolic process;steroid metabolic process;sterol metabolic process;vitamin D3 metabolic process;xenobiotic metabolic process</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>GO:0001972;GO:0004857;GO:0008194;GO:0015020;GO:0019899;GO:0042803;GO:0046982</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>UDP-glycosyltransferase activity;enzyme binding;enzyme inhibitor activity;glucuronosyltransferase activity;protein heterodimerization activity;protein homodimerization activity;retinoic acid binding</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>GO:0005783;GO:0005789</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum;endoplasmic reticulum membrane</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A0A0K0PVW1</t>
+          <t>O75845</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>UGT100</t>
+          <t>SC5D</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>BioCyc_META_PWY-5672</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t>pathway_predominant</t>
         </is>
       </c>
-      <c r="K56" t="n">
-        <v>4</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>GO:0002238;GO:0008194;GO:0016114;GO:0035251</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>UDP-glucosyltransferase activity;UDP-glycosyltransferase activity;response to molecule of fungal origin;terpenoid biosynthetic process</t>
-        </is>
+      <c r="M56" t="n">
+        <v>10</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>GO:0002238;GO:0016114</t>
+          <t>GO:0000248;GO:0005506;GO:0005789;GO:0006695;GO:0008610;GO:0033489;GO:0033490;GO:0050046;GO:0070704;GO:0110076</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>response to molecule of fungal origin;terpenoid biosynthetic process</t>
+          <t>C-5 sterol desaturase activity;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;delta7-sterol 5(6)-desaturase activity;endoplasmic reticulum membrane;iron ion binding;lipid biosynthetic process;negative regulation of ferroptosis;sterol desaturase activity</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>GO:0008194;GO:0035251</t>
+          <t>GO:0006695;GO:0008610;GO:0033489;GO:0033490;GO:0110076</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>UDP-glucosyltransferase activity;UDP-glycosyltransferase activity</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;lipid biosynthetic process;negative regulation of ferroptosis</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>GO:0000248;GO:0005506;GO:0050046;GO:0070704</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>C-5 sterol desaturase activity;delta7-sterol 5(6)-desaturase activity;iron ion binding;sterol desaturase activity</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>GO:0005789</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum membrane</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>H2DH16</t>
+          <t>O76062</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CYP716A47</t>
+          <t>TM7SF2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>BioCyc_META_PWY-5672</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t>pathway_predominant</t>
         </is>
       </c>
-      <c r="K57" t="n">
-        <v>10</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>GO:0002238;GO:0004497;GO:0005506;GO:0016020;GO:0016114;GO:0016125;GO:0016491;GO:0016705;GO:0020037;GO:0102556</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>dammarenediol 12-hydroxylase activity;heme binding;iron ion binding;membrane;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;response to molecule of fungal origin;sterol metabolic process;terpenoid biosynthetic process</t>
-        </is>
+      <c r="M57" t="n">
+        <v>13</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>GO:0002238;GO:0016114;GO:0016125</t>
+          <t>GO:0005515;GO:0005637;GO:0005783;GO:0005789;GO:0005886;GO:0006695;GO:0016020;GO:0016126;GO:0016628;GO:0033490;GO:0043235;GO:0050613;GO:0050661</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>response to molecule of fungal origin;sterol metabolic process;terpenoid biosynthetic process</t>
+          <t>Delta14-sterol reductase activity;NADP binding;cholesterol biosynthetic process;cholesterol biosynthetic process via lathosterol;endoplasmic reticulum;endoplasmic reticulum membrane;membrane;nuclear inner membrane;oxidoreductase activity, acting on the CH-CH group of donors, NAD or NADP as acceptor;plasma membrane;protein binding;signaling receptor complex;sterol biosynthetic process</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>GO:0004497;GO:0005506;GO:0016491;GO:0016705;GO:0020037;GO:0102556</t>
+          <t>GO:0006695;GO:0016126;GO:0033490</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>dammarenediol 12-hydroxylase activity;heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen</t>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via lathosterol;sterol biosynthetic process</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>GO:0016020</t>
+          <t>GO:0005515;GO:0016628;GO:0050613;GO:0050661</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>membrane</t>
+          <t>Delta14-sterol reductase activity;NADP binding;oxidoreductase activity, acting on the CH-CH group of donors, NAD or NADP as acceptor;protein binding</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>GO:0005637;GO:0005783;GO:0005789;GO:0005886;GO:0016020;GO:0043235</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum;endoplasmic reticulum membrane;membrane;nuclear inner membrane;plasma membrane;signaling receptor complex</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>I7C6E8</t>
+          <t>O95749</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CYP716A52v2</t>
+          <t>GGPS1</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>BioCyc_META_PWY-5672</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>2</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t>pathway_predominant</t>
         </is>
       </c>
-      <c r="K58" t="n">
-        <v>11</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>GO:0004497;GO:0005506;GO:0016020;GO:0016114;GO:0016125;GO:0016491;GO:0016705;GO:0016709;GO:0019742;GO:0020037;GO:0102373</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>beta-amyrin 28-monooxygenase activity;heme binding;iron ion binding;membrane;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, NAD(P)H as one donor, and incorporation of one atom of oxygen;pentacyclic triterpenoid metabolic process;sterol metabolic process;terpenoid biosynthetic process</t>
-        </is>
+      <c r="M58" t="n">
+        <v>16</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>GO:0016114;GO:0016125;GO:0019742</t>
+          <t>GO:0004161;GO:0004311;GO:0004337;GO:0004659;GO:0005515;GO:0005737;GO:0005829;GO:0006720;GO:0008299;GO:0030018;GO:0033384;GO:0033386;GO:0042802;GO:0045337;GO:0048471;GO:0120531</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>pentacyclic triterpenoid metabolic process;sterol metabolic process;terpenoid biosynthetic process</t>
+          <t>(2E,6E)-farnesyl diphosphate synthase activity;Z disc;cytoplasm;cytosol;dimethylallyltranstransferase activity;farnesyl diphosphate biosynthetic process;geranyl diphosphate biosynthetic process;geranylgeranyl diphosphate biosynthetic process;geranylgeranyl diphosphate synthase activity;identical protein binding;isoprenoid biosynthetic process;isoprenoid metabolic process;perinuclear region of cytoplasm;prenyl diphosphate synthase activity;prenyltransferase activity;protein binding</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>GO:0004497;GO:0005506;GO:0016491;GO:0016705;GO:0016709;GO:0020037;GO:0102373</t>
+          <t>GO:0006720;GO:0008299;GO:0033384;GO:0033386;GO:0045337</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>beta-amyrin 28-monooxygenase activity;heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, NAD(P)H as one donor, and incorporation of one atom of oxygen</t>
+          <t>farnesyl diphosphate biosynthetic process;geranyl diphosphate biosynthetic process;geranylgeranyl diphosphate biosynthetic process;isoprenoid biosynthetic process;isoprenoid metabolic process</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>GO:0016020</t>
+          <t>GO:0004161;GO:0004311;GO:0004337;GO:0004659;GO:0005515;GO:0042802;GO:0120531</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>membrane</t>
+          <t>(2E,6E)-farnesyl diphosphate synthase activity;dimethylallyltranstransferase activity;geranylgeranyl diphosphate synthase activity;identical protein binding;prenyl diphosphate synthase activity;prenyltransferase activity;protein binding</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005829;GO:0030018;GO:0048471</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Z disc;cytoplasm;cytosol;perinuclear region of cytoplasm</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>I7CT85</t>
+          <t>P14324</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CYP716A53v2</t>
+          <t>FDPS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>BioCyc_META_PWY-5672</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t>pathway_predominant</t>
         </is>
       </c>
-      <c r="K59" t="n">
-        <v>10</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>GO:0002238;GO:0004497;GO:0005506;GO:0016020;GO:0016114;GO:0016125;GO:0016491;GO:0016705;GO:0020037;GO:0102557</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>heme binding;iron ion binding;membrane;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;protopanaxadiol 6-hydroxylase activity;response to molecule of fungal origin;sterol metabolic process;terpenoid biosynthetic process</t>
-        </is>
+      <c r="M59" t="n">
+        <v>17</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>GO:0002238;GO:0016114;GO:0016125</t>
+          <t>GO:0003723;GO:0004161;GO:0004337;GO:0004659;GO:0005515;GO:0005737;GO:0005829;GO:0006695;GO:0008299;GO:0010142;GO:0016765;GO:0033384;GO:0033386;GO:0033489;GO:0033490;GO:0036197;GO:0045337</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>response to molecule of fungal origin;sterol metabolic process;terpenoid biosynthetic process</t>
+          <t>(2E,6E)-farnesyl diphosphate synthase activity;RNA binding;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cytoplasm;cytosol;dimethylallyltranstransferase activity;farnesyl diphosphate biosynthetic process;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranyl diphosphate biosynthetic process;geranylgeranyl diphosphate biosynthetic process;isoprenoid biosynthetic process;prenyltransferase activity;protein binding;transferase activity, transferring alkyl or aryl (other than methyl) groups;zymosterol biosynthetic process</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>GO:0004497;GO:0005506;GO:0016491;GO:0016705;GO:0020037;GO:0102557</t>
+          <t>GO:0006695;GO:0008299;GO:0010142;GO:0033384;GO:0033386;GO:0033489;GO:0033490;GO:0036197;GO:0045337</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;protopanaxadiol 6-hydroxylase activity</t>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;farnesyl diphosphate biosynthetic process;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranyl diphosphate biosynthetic process;geranylgeranyl diphosphate biosynthetic process;isoprenoid biosynthetic process;zymosterol biosynthetic process</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>GO:0016020</t>
+          <t>GO:0003723;GO:0004161;GO:0004337;GO:0004659;GO:0005515;GO:0016765</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>membrane</t>
+          <t>(2E,6E)-farnesyl diphosphate synthase activity;RNA binding;dimethylallyltranstransferase activity;prenyltransferase activity;protein binding;transferase activity, transferring alkyl or aryl (other than methyl) groups</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005829</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>cytoplasm;cytosol</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>O82140</t>
+          <t>P35610</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OSCPNY1</t>
+          <t>SOAT1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
         <v>2</v>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>BioCyc_META_PWY-5672;PlantCyc_PLANT_PWY-5672</t>
-        </is>
+      <c r="H60" t="n">
+        <v>2</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>2</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t>pathway_predominant</t>
         </is>
       </c>
-      <c r="K60" t="n">
-        <v>12</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>GO:0002238;GO:0005789;GO:0005811;GO:0009723;GO:0009753;GO:0010038;GO:0016104;GO:0016114;GO:0016866;GO:0042300;GO:0042542;GO:0071731</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>beta-amyrin synthase activity;endoplasmic reticulum membrane;intramolecular transferase activity;lipid droplet;response to ethylene;response to hydrogen peroxide;response to jasmonic acid;response to metal ion;response to molecule of fungal origin;response to nitric oxide;terpenoid biosynthetic process;triterpenoid biosynthetic process</t>
-        </is>
+      <c r="M60" t="n">
+        <v>17</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>GO:0002238;GO:0009723;GO:0009753;GO:0010038;GO:0016104;GO:0016114;GO:0042542;GO:0071731</t>
+          <t>GO:0000062;GO:0004772;GO:0005515;GO:0005783;GO:0005789;GO:0008203;GO:0008374;GO:0010742;GO:0010878;GO:0015485;GO:0016020;GO:0033344;GO:0034379;GO:0034383;GO:0034736;GO:0042632;GO:0042986</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>response to ethylene;response to hydrogen peroxide;response to jasmonic acid;response to metal ion;response to molecule of fungal origin;response to nitric oxide;terpenoid biosynthetic process;triterpenoid biosynthetic process</t>
+          <t>cholesterol O-acyltransferase activity;cholesterol binding;cholesterol efflux;cholesterol homeostasis;cholesterol metabolic process;cholesterol storage;endoplasmic reticulum;endoplasmic reticulum membrane;fatty-acyl-CoA binding;low-density lipoprotein particle clearance;macrophage derived foam cell differentiation;membrane;obsolete O-acyltransferase activity;positive regulation of amyloid precursor protein biosynthetic process;protein binding;sterol O-acyltransferase activity;very-low-density lipoprotein particle assembly</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>GO:0016866;GO:0042300</t>
+          <t>GO:0008203;GO:0010742;GO:0010878;GO:0033344;GO:0034379;GO:0034383;GO:0042632;GO:0042986</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>beta-amyrin synthase activity;intramolecular transferase activity</t>
+          <t>cholesterol efflux;cholesterol homeostasis;cholesterol metabolic process;cholesterol storage;low-density lipoprotein particle clearance;macrophage derived foam cell differentiation;positive regulation of amyloid precursor protein biosynthetic process;very-low-density lipoprotein particle assembly</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>GO:0005789;GO:0005811</t>
+          <t>GO:0000062;GO:0004772;GO:0005515;GO:0008374;GO:0015485;GO:0034736</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>endoplasmic reticulum membrane;lipid droplet</t>
+          <t>cholesterol O-acyltransferase activity;cholesterol binding;fatty-acyl-CoA binding;obsolete O-acyltransferase activity;protein binding;sterol O-acyltransferase activity</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>GO:0005783;GO:0005789;GO:0016020</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum;endoplasmic reticulum membrane;membrane</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Q08IT1</t>
+          <t>P37268</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>Rosuvastatin;atorvastatin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>FDFT1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>2</v>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>BioCyc_META_PWY-5672;PlantCyc_PLANT_PWY-5672</t>
-        </is>
+      <c r="H61" t="n">
+        <v>2</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Ginsenoside rb1</t>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>2</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t>pathway_predominant</t>
         </is>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
+        <v>14</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GO:0005515;GO:0005783;GO:0005789;GO:0006694;GO:0006695;GO:0008610;GO:0016020;GO:0016765;GO:0033489;GO:0033490;GO:0036197;GO:0045338;GO:0051996;GO:0098554</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cytoplasmic side of endoplasmic reticulum membrane;endoplasmic reticulum;endoplasmic reticulum membrane;farnesyl diphosphate metabolic process;lipid biosynthetic process;membrane;protein binding;squalene synthase [NAD(P)H] activity;steroid biosynthetic process;transferase activity, transferring alkyl or aryl (other than methyl) groups;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>GO:0006694;GO:0006695;GO:0008610;GO:0033489;GO:0033490;GO:0036197;GO:0045338</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;farnesyl diphosphate metabolic process;lipid biosynthetic process;steroid biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>GO:0005515;GO:0016765;GO:0051996</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>protein binding;squalene synthase [NAD(P)H] activity;transferase activity, transferring alkyl or aryl (other than methyl) groups</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>GO:0005783;GO:0005789;GO:0016020;GO:0098554</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>cytoplasmic side of endoplasmic reticulum membrane;endoplasmic reticulum;endoplasmic reticulum membrane;membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P38571</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LIPA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
         <v>10</v>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>GO:0002238;GO:0005789;GO:0005811;GO:0010038;GO:0016104;GO:0016114;GO:0016135;GO:0016866;GO:0042300;GO:1902438</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>beta-amyrin synthase activity;endoplasmic reticulum membrane;intramolecular transferase activity;lipid droplet;response to metal ion;response to molecule of fungal origin;response to vanadate(3-);saponin biosynthetic process;terpenoid biosynthetic process;triterpenoid biosynthetic process</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>GO:0002238;GO:0010038;GO:0016104;GO:0016114;GO:0016135;GO:1902438</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>response to metal ion;response to molecule of fungal origin;response to vanadate(3-);saponin biosynthetic process;terpenoid biosynthetic process;triterpenoid biosynthetic process</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>GO:0016866;GO:0042300</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>beta-amyrin synthase activity;intramolecular transferase activity</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>GO:0005789;GO:0005811</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>endoplasmic reticulum membrane;lipid droplet</t>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>GO:0004771;GO:0004806;GO:0005764;GO:0016125;GO:0016298;GO:0016788;GO:0034383;GO:0043202;GO:0052689;GO:0120516</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>carboxylic ester hydrolase activity;diacylglycerol lipase activity;hydrolase activity, acting on ester bonds;lipase activity;low-density lipoprotein particle clearance;lysosomal lumen;lysosome;sterol ester esterase activity;sterol metabolic process;triacylglycerol lipase activity</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>GO:0016125;GO:0034383</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>low-density lipoprotein particle clearance;sterol metabolic process</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>GO:0004771;GO:0004806;GO:0016298;GO:0016788;GO:0052689;GO:0120516</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>carboxylic ester hydrolase activity;diacylglycerol lipase activity;hydrolase activity, acting on ester bonds;lipase activity;sterol ester esterase activity;triacylglycerol lipase activity</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>GO:0005764;GO:0043202</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>lysosomal lumen;lysosome</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P48449</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LSS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>14</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>GO:0000250;GO:0005515;GO:0005789;GO:0005811;GO:0006694;GO:0006695;GO:0016020;GO:0016104;GO:0016866;GO:0031647;GO:0033489;GO:0033490;GO:0036197;GO:0098554</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cytoplasmic side of endoplasmic reticulum membrane;endoplasmic reticulum membrane;intramolecular transferase activity;lanosterol synthase activity;lipid droplet;membrane;protein binding;regulation of protein stability;steroid biosynthetic process;triterpenoid biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>GO:0006694;GO:0006695;GO:0016104;GO:0031647;GO:0033489;GO:0033490;GO:0036197</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;regulation of protein stability;steroid biosynthetic process;triterpenoid biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>GO:0000250;GO:0005515;GO:0016866</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>intramolecular transferase activity;lanosterol synthase activity;protein binding</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>GO:0005789;GO:0005811;GO:0016020;GO:0098554</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>cytoplasmic side of endoplasmic reticulum membrane;endoplasmic reticulum membrane;lipid droplet;membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P53602</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>MVD</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>16</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>GO:0004163;GO:0005737;GO:0005777;GO:0005829;GO:0006695;GO:0008284;GO:0008299;GO:0010142;GO:0016831;GO:0019287;GO:0030544;GO:0033386;GO:0033489;GO:0033490;GO:0036197;GO:0042803</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Hsp70 protein binding;carboxy-lyase activity;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cytoplasm;cytosol;diphosphomevalonate decarboxylase activity;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranylgeranyl diphosphate biosynthetic process;isopentenyl diphosphate biosynthetic process, mevalonate pathway;isoprenoid biosynthetic process;peroxisome;positive regulation of cell population proliferation;protein homodimerization activity;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>GO:0006695;GO:0008284;GO:0008299;GO:0010142;GO:0019287;GO:0033386;GO:0033489;GO:0033490;GO:0036197</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranylgeranyl diphosphate biosynthetic process;isopentenyl diphosphate biosynthetic process, mevalonate pathway;isoprenoid biosynthetic process;positive regulation of cell population proliferation;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>GO:0004163;GO:0016831;GO:0030544;GO:0042803</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Hsp70 protein binding;carboxy-lyase activity;diphosphomevalonate decarboxylase activity;protein homodimerization activity</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005777;GO:0005829</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>cytoplasm;cytosol;peroxisome</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P56937</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>HSD17B7</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>2</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>15</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>GO:0000253;GO:0004303;GO:0005739;GO:0005783;GO:0005789;GO:0006694;GO:0006695;GO:0006703;GO:0007420;GO:0008209;GO:0033489;GO:0033490;GO:0036197;GO:0047024;GO:0048568</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>3-beta-hydroxysteroid 3-dehydrogenase (NADP+) activity;5-alpha-androstane-3-beta,17-beta-diol dehydrogenase (NADP+) activity;androgen metabolic process;brain development;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;embryonic organ development;endoplasmic reticulum;endoplasmic reticulum membrane;estradiol 17-beta-dehydrogenase [NAD(P)+] activity;estrogen biosynthetic process;mitochondrion;steroid biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>GO:0006694;GO:0006695;GO:0006703;GO:0007420;GO:0008209;GO:0033489;GO:0033490;GO:0036197;GO:0048568</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>androgen metabolic process;brain development;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;embryonic organ development;estrogen biosynthetic process;steroid biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>GO:0000253;GO:0004303;GO:0047024</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>3-beta-hydroxysteroid 3-dehydrogenase (NADP+) activity;5-alpha-androstane-3-beta,17-beta-diol dehydrogenase (NADP+) activity;estradiol 17-beta-dehydrogenase [NAD(P)+] activity</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>GO:0005739;GO:0005783;GO:0005789</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum;endoplasmic reticulum membrane;mitochondrion</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Q03426</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>MVK</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>18</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>GO:0000287;GO:0004496;GO:0005515;GO:0005524;GO:0005737;GO:0005777;GO:0005829;GO:0006695;GO:0008299;GO:0010142;GO:0016125;GO:0019287;GO:0033386;GO:0033489;GO:0033490;GO:0036197;GO:0042802;GO:0050728</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>ATP binding;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cytoplasm;cytosol;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranylgeranyl diphosphate biosynthetic process;identical protein binding;isopentenyl diphosphate biosynthetic process, mevalonate pathway;isoprenoid biosynthetic process;magnesium ion binding;mevalonate kinase activity;negative regulation of inflammatory response;peroxisome;protein binding;sterol metabolic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>GO:0006695;GO:0008299;GO:0010142;GO:0016125;GO:0019287;GO:0033386;GO:0033489;GO:0033490;GO:0036197;GO:0050728</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranylgeranyl diphosphate biosynthetic process;isopentenyl diphosphate biosynthetic process, mevalonate pathway;isoprenoid biosynthetic process;negative regulation of inflammatory response;sterol metabolic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>GO:0000287;GO:0004496;GO:0005515;GO:0005524;GO:0042802</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>ATP binding;identical protein binding;magnesium ion binding;mevalonate kinase activity;protein binding</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005777;GO:0005829</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>cytoplasm;cytosol;peroxisome</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Q13907</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>IDI1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>2</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>14</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GO:0004452;GO:0005777;GO:0005829;GO:0006695;GO:0008299;GO:0009240;GO:0010142;GO:0016860;GO:0033386;GO:0033489;GO:0033490;GO:0035634;GO:0036197;GO:0050992</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cytosol;dimethylallyl diphosphate biosynthetic process;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranylgeranyl diphosphate biosynthetic process;intramolecular oxidoreductase activity;isopentenyl diphosphate biosynthetic process;isopentenyl-diphosphate delta-isomerase activity;isoprenoid biosynthetic process;peroxisome;response to stilbenoid;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>GO:0006695;GO:0008299;GO:0009240;GO:0010142;GO:0033386;GO:0033489;GO:0033490;GO:0035634;GO:0036197;GO:0050992</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;dimethylallyl diphosphate biosynthetic process;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranylgeranyl diphosphate biosynthetic process;isopentenyl diphosphate biosynthetic process;isoprenoid biosynthetic process;response to stilbenoid;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>GO:0004452;GO:0016860</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>intramolecular oxidoreductase activity;isopentenyl-diphosphate delta-isomerase activity</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>GO:0005777;GO:0005829</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>cytosol;peroxisome</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Q14534</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SQLE</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>2</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>18</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GO:0004506;GO:0005515;GO:0005783;GO:0005789;GO:0006695;GO:0008203;GO:0016020;GO:0016126;GO:0033489;GO:0033490;GO:0036197;GO:0042127;GO:0043231;GO:0050660;GO:0071949;GO:0098554;GO:0140042;GO:1904614</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>FAD binding;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cholesterol metabolic process;cytoplasmic side of endoplasmic reticulum membrane;endoplasmic reticulum;endoplasmic reticulum membrane;flavin adenine dinucleotide binding;intracellular membrane-bounded organelle;lipid droplet formation;membrane;protein binding;regulation of cell population proliferation;response to biphenyl;squalene monooxygenase activity;sterol biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>GO:0006695;GO:0008203;GO:0016126;GO:0033489;GO:0033490;GO:0036197;GO:0042127;GO:0140042;GO:1904614</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cholesterol metabolic process;lipid droplet formation;regulation of cell population proliferation;response to biphenyl;sterol biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>GO:0004506;GO:0005515;GO:0050660;GO:0071949</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>FAD binding;flavin adenine dinucleotide binding;protein binding;squalene monooxygenase activity</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>GO:0005783;GO:0005789;GO:0016020;GO:0043231;GO:0098554</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>cytoplasmic side of endoplasmic reticulum membrane;endoplasmic reticulum;endoplasmic reticulum membrane;intracellular membrane-bounded organelle;membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Q15125</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>EBP</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>19</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GO:0000247;GO:0004769;GO:0005515;GO:0005635;GO:0005783;GO:0005789;GO:0006695;GO:0008203;GO:0016020;GO:0016125;GO:0016863;GO:0031410;GO:0031965;GO:0033489;GO:0033490;GO:0033963;GO:0042802;GO:0043931;GO:0047750</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>C-8 sterol isomerase activity;cholestenol delta-isomerase activity;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cholesterol metabolic process;cholesterol-5,6-oxide hydrolase activity;cytoplasmic vesicle;endoplasmic reticulum;endoplasmic reticulum membrane;identical protein binding;intramolecular oxidoreductase activity, transposing C=C bonds;membrane;nuclear envelope;nuclear membrane;ossification involved in bone maturation;protein binding;steroid Delta-isomerase activity;sterol metabolic process</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>GO:0006695;GO:0008203;GO:0016125;GO:0033489;GO:0033490;GO:0043931</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cholesterol metabolic process;ossification involved in bone maturation;sterol metabolic process</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>GO:0000247;GO:0004769;GO:0005515;GO:0016863;GO:0033963;GO:0042802;GO:0047750</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>C-8 sterol isomerase activity;cholestenol delta-isomerase activity;cholesterol-5,6-oxide hydrolase activity;identical protein binding;intramolecular oxidoreductase activity, transposing C=C bonds;protein binding;steroid Delta-isomerase activity</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>GO:0005635;GO:0005783;GO:0005789;GO:0016020;GO:0031410;GO:0031965</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>cytoplasmic vesicle;endoplasmic reticulum;endoplasmic reticulum membrane;membrane;nuclear envelope;nuclear membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Q15126</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PMVK</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>17</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>GO:0004631;GO:0005515;GO:0005524;GO:0005737;GO:0005777;GO:0005829;GO:0006695;GO:0010142;GO:0016020;GO:0016126;GO:0019287;GO:0033386;GO:0033489;GO:0033490;GO:0036197;GO:0070062;GO:0070723</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>ATP binding;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cytoplasm;cytosol;extracellular exosome;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranylgeranyl diphosphate biosynthetic process;isopentenyl diphosphate biosynthetic process, mevalonate pathway;membrane;peroxisome;phosphomevalonate kinase activity;protein binding;response to cholesterol;sterol biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>GO:0006695;GO:0010142;GO:0016126;GO:0019287;GO:0033386;GO:0033489;GO:0033490;GO:0036197;GO:0070723</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;farnesyl diphosphate biosynthetic process, mevalonate pathway;geranylgeranyl diphosphate biosynthetic process;isopentenyl diphosphate biosynthetic process, mevalonate pathway;response to cholesterol;sterol biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>GO:0004631;GO:0005515;GO:0005524</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>ATP binding;phosphomevalonate kinase activity;protein binding</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005777;GO:0005829;GO:0016020;GO:0070062</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>cytoplasm;cytosol;extracellular exosome;membrane;peroxisome</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Q15392</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DHCR24</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>22</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GO:0000139;GO:0000246;GO:0005515;GO:0005634;GO:0005783;GO:0005789;GO:0006695;GO:0007265;GO:0008202;GO:0008285;GO:0009725;GO:0009888;GO:0016020;GO:0016628;GO:0019899;GO:0033489;GO:0033490;GO:0042605;GO:0043588;GO:0050614;GO:0050660;GO:0071949</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Delta24(24-1) sterol reductase activity;Delta24-sterol reductase activity;FAD binding;Golgi membrane;Ras protein signal transduction;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;endoplasmic reticulum;endoplasmic reticulum membrane;enzyme binding;flavin adenine dinucleotide binding;membrane;negative regulation of cell population proliferation;nucleus;oxidoreductase activity, acting on the CH-CH group of donors, NAD or NADP as acceptor;peptide antigen binding;protein binding;response to hormone;skin development;steroid metabolic process;tissue development</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>GO:0006695;GO:0007265;GO:0008202;GO:0008285;GO:0009725;GO:0009888;GO:0033489;GO:0033490;GO:0043588</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Ras protein signal transduction;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;negative regulation of cell population proliferation;response to hormone;skin development;steroid metabolic process;tissue development</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>GO:0000246;GO:0005515;GO:0016628;GO:0019899;GO:0042605;GO:0050614;GO:0050660;GO:0071949</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Delta24(24-1) sterol reductase activity;Delta24-sterol reductase activity;FAD binding;enzyme binding;flavin adenine dinucleotide binding;oxidoreductase activity, acting on the CH-CH group of donors, NAD or NADP as acceptor;peptide antigen binding;protein binding</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>GO:0000139;GO:0005634;GO:0005783;GO:0005789;GO:0016020</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Golgi membrane;endoplasmic reticulum;endoplasmic reticulum membrane;membrane;nucleus</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Q15738</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>NSDHL</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>14</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>GO:0000252;GO:0003854;GO:0005515;GO:0005783;GO:0005789;GO:0005811;GO:0006694;GO:0006695;GO:0008203;GO:0016616;GO:0033489;GO:0033490;GO:0036197;GO:0102175</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>3-beta-hydroxy-Delta5-steroid dehydrogenase (NAD+) activity;3-beta-hydroxysteroid dehydrogenase (NAD+)/C4-decarboxylase activity;3-beta-hydroxysteroid dehydrogenase [NAD(P)+]/C4-decarboxylase activity;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cholesterol metabolic process;endoplasmic reticulum;endoplasmic reticulum membrane;lipid droplet;oxidoreductase activity, acting on the CH-OH group of donors, NAD or NADP as acceptor;protein binding;steroid biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>GO:0006694;GO:0006695;GO:0008203;GO:0033489;GO:0033490;GO:0036197</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;cholesterol metabolic process;steroid biosynthetic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>GO:0000252;GO:0003854;GO:0005515;GO:0016616;GO:0102175</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>3-beta-hydroxy-Delta5-steroid dehydrogenase (NAD+) activity;3-beta-hydroxysteroid dehydrogenase (NAD+)/C4-decarboxylase activity;3-beta-hydroxysteroid dehydrogenase [NAD(P)+]/C4-decarboxylase activity;oxidoreductase activity, acting on the CH-OH group of donors, NAD or NADP as acceptor;protein binding</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>GO:0005783;GO:0005789;GO:0005811</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum;endoplasmic reticulum membrane;lipid droplet</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Q15800</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>MSMO1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>2</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>13</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GO:0000254;GO:0005506;GO:0005515;GO:0005783;GO:0005789;GO:0005886;GO:0006631;GO:0006695;GO:0008202;GO:0008610;GO:0016020;GO:0033489;GO:0036197</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>C-4 methylsterol oxidase activity;cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;endoplasmic reticulum;endoplasmic reticulum membrane;fatty acid metabolic process;iron ion binding;lipid biosynthetic process;membrane;plasma membrane;protein binding;steroid metabolic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>GO:0006631;GO:0006695;GO:0008202;GO:0008610;GO:0033489;GO:0036197</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via desmosterol;fatty acid metabolic process;lipid biosynthetic process;steroid metabolic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>GO:0000254;GO:0005506;GO:0005515</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>C-4 methylsterol oxidase activity;iron ion binding;protein binding</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>GO:0005783;GO:0005789;GO:0005886;GO:0016020</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum;endoplasmic reticulum membrane;membrane;plasma membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Q16850</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>CYP51A1</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>2</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>19</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GO:0004497;GO:0005506;GO:0005789;GO:0006694;GO:0006695;GO:0008398;GO:0016020;GO:0016125;GO:0016491;GO:0016705;GO:0016712;GO:0020037;GO:0033488;GO:0033489;GO:0033490;GO:0036197;GO:0042177;GO:0050709;GO:1900222</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via 24,25-dihydrolanosterol;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;endoplasmic reticulum membrane;heme binding;iron ion binding;membrane;monooxygenase activity;negative regulation of amyloid-beta clearance;negative regulation of protein catabolic process;negative regulation of protein secretion;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;steroid biosynthetic process;sterol 14-demethylase activity;sterol metabolic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>GO:0006694;GO:0006695;GO:0016125;GO:0033488;GO:0033489;GO:0033490;GO:0036197;GO:0042177;GO:0050709;GO:1900222</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>cholesterol biosynthetic process;cholesterol biosynthetic process via 24,25-dihydrolanosterol;cholesterol biosynthetic process via desmosterol;cholesterol biosynthetic process via lathosterol;negative regulation of amyloid-beta clearance;negative regulation of protein catabolic process;negative regulation of protein secretion;steroid biosynthetic process;sterol metabolic process;zymosterol biosynthetic process</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>GO:0004497;GO:0005506;GO:0008398;GO:0016491;GO:0016705;GO:0016712;GO:0020037</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen;sterol 14-demethylase activity</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>GO:0005789;GO:0016020</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum membrane;membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Q9BWD1</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ACAT2</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>PathBank:SMP0000092;PathBank:SMP0000131</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Rosuvastatin;atorvastatin</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>10</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GO:0003985;GO:0005515;GO:0005737;GO:0005829;GO:0006629;GO:0006631;GO:0010142;GO:0016746;GO:0016747;GO:0070062</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>acetyl-CoA C-acetyltransferase activity;acyltransferase activity;acyltransferase activity, transferring groups other than amino-acyl groups;cytoplasm;cytosol;extracellular exosome;farnesyl diphosphate biosynthetic process, mevalonate pathway;fatty acid metabolic process;lipid metabolic process;protein binding</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>GO:0006629;GO:0006631;GO:0010142</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>farnesyl diphosphate biosynthetic process, mevalonate pathway;fatty acid metabolic process;lipid metabolic process</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>GO:0003985;GO:0005515;GO:0016746;GO:0016747</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>acetyl-CoA C-acetyltransferase activity;acyltransferase activity;acyltransferase activity, transferring groups other than amino-acyl groups;protein binding</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>GO:0005737;GO:0005829;GO:0070062</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>cytoplasm;cytosol;extracellular exosome</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A4D1D2</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ABCB1</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>PharmGKB:PA145011109</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>8</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>GO:0005524;GO:0005886;GO:0016020;GO:0016887;GO:0045332;GO:0055085;GO:0090554;GO:0140359</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>ABC-type transporter activity;ATP binding;ATP hydrolysis activity;membrane;phosphatidylcholine floppase activity;phospholipid translocation;plasma membrane;transmembrane transport</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>GO:0045332;GO:0055085</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>phospholipid translocation;transmembrane transport</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>GO:0005524;GO:0016887;GO:0090554;GO:0140359</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>ABC-type transporter activity;ATP binding;ATP hydrolysis activity;phosphatidylcholine floppase activity</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0016020</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>membrane;plasma membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>B4DGA9</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>PharmGKB:PA145011109</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>P16662</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>UGT2B7</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>PharmGKB:PA145011109</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>9</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>GO:0001972;GO:0005789;GO:0006629;GO:0006805;GO:0008194;GO:0008209;GO:0008210;GO:0015020;GO:0016020</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>UDP-glycosyltransferase activity;androgen metabolic process;endoplasmic reticulum membrane;estrogen metabolic process;glucuronosyltransferase activity;lipid metabolic process;membrane;retinoic acid binding;xenobiotic metabolic process</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>GO:0006629;GO:0006805;GO:0008209;GO:0008210</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>androgen metabolic process;estrogen metabolic process;lipid metabolic process;xenobiotic metabolic process</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>GO:0001972;GO:0008194;GO:0015020</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>UDP-glycosyltransferase activity;glucuronosyltransferase activity;retinoic acid binding</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>GO:0005789;GO:0016020</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum membrane;membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Q05CV5</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SLCO1B1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>PharmGKB:PA145011109</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>4</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0016020;GO:0022857;GO:0055085</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>membrane;plasma membrane;transmembrane transport;transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>GO:0055085</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>transmembrane transport</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>GO:0022857</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>GO:0005886;GO:0016020</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>membrane;plasma membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Q6NWU0</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>CYP2D6</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>PharmGKB:PA145011109</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>atorvastatin</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>pathway_predominant</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>7</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>GO:0004497;GO:0005506;GO:0005789;GO:0016020;GO:0016705;GO:0016712;GO:0020037</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum membrane;heme binding;iron ion binding;membrane;monooxygenase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>GO:0004497;GO:0005506;GO:0016705;GO:0016712;GO:0020037</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>heme binding;iron ion binding;monooxygenase activity;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen;oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>GO:0005789;GO:0016020</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum membrane;membrane</t>
         </is>
       </c>
     </row>
